--- a/Översikt RÄTTVIK.xlsx
+++ b/Översikt RÄTTVIK.xlsx
@@ -569,7 +569,7 @@
         <v>43542</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         <v>43663</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -781,7 +781,7 @@
         <v>43619</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
         <v>44909</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>43740</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>44909</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>44874</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>45147</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
         <v>44237</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1461,7 +1461,7 @@
         <v>44624</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         <v>43634</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         <v>43663</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1736,7 +1736,7 @@
         <v>44148</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         <v>44435</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1910,7 +1910,7 @@
         <v>44799</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         <v>44909</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         <v>44909</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
         <v>45111</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>43700</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>44496</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2450,7 +2450,7 @@
         <v>45033</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
         <v>43440</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         <v>43493</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
         <v>43623</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2791,7 +2791,7 @@
         <v>43705</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
         <v>44088</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2961,7 +2961,7 @@
         <v>44361</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3046,7 +3046,7 @@
         <v>44391</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         <v>44414</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3226,7 +3226,7 @@
         <v>44470</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3316,7 +3316,7 @@
         <v>44496</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
         <v>44511</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3491,7 +3491,7 @@
         <v>44568</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
         <v>44728</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3679,7 +3679,7 @@
         <v>44855</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3769,7 +3769,7 @@
         <v>44894</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3859,7 +3859,7 @@
         <v>44918</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3949,7 +3949,7 @@
         <v>44986</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4034,7 +4034,7 @@
         <v>45077</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4119,7 +4119,7 @@
         <v>45194</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4204,7 +4204,7 @@
         <v>45194</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4289,7 +4289,7 @@
         <v>45231</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4374,7 +4374,7 @@
         <v>43333</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4431,7 +4431,7 @@
         <v>43348</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4488,7 +4488,7 @@
         <v>43356</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4545,7 +4545,7 @@
         <v>43361</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4602,7 +4602,7 @@
         <v>43362</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4659,7 +4659,7 @@
         <v>43362</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4716,7 +4716,7 @@
         <v>43362</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4773,7 +4773,7 @@
         <v>43362</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4830,7 +4830,7 @@
         <v>43367</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4887,7 +4887,7 @@
         <v>43369</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4944,7 +4944,7 @@
         <v>43373</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5001,7 +5001,7 @@
         <v>43378</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5058,7 +5058,7 @@
         <v>43381</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5115,7 +5115,7 @@
         <v>43381</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5172,7 +5172,7 @@
         <v>43388</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5229,7 +5229,7 @@
         <v>43388</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5291,7 +5291,7 @@
         <v>43388</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5348,7 +5348,7 @@
         <v>43391</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5405,7 +5405,7 @@
         <v>43398</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
         <v>43399</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5519,7 +5519,7 @@
         <v>43401</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5576,7 +5576,7 @@
         <v>43405</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5633,7 +5633,7 @@
         <v>43405</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5690,7 +5690,7 @@
         <v>43410</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5747,7 +5747,7 @@
         <v>43410</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5804,7 +5804,7 @@
         <v>43411</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5861,7 +5861,7 @@
         <v>43412</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5918,7 +5918,7 @@
         <v>43416</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5975,7 +5975,7 @@
         <v>43416</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6032,7 +6032,7 @@
         <v>43416</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6089,7 +6089,7 @@
         <v>43419</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6146,7 +6146,7 @@
         <v>43419</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6203,7 +6203,7 @@
         <v>43423</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6265,7 +6265,7 @@
         <v>43423</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         <v>43423</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6389,7 +6389,7 @@
         <v>43424</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6451,7 +6451,7 @@
         <v>43425</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6508,7 +6508,7 @@
         <v>43427</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6570,7 +6570,7 @@
         <v>43428</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6627,7 +6627,7 @@
         <v>43428</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6684,7 +6684,7 @@
         <v>43430</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6741,7 +6741,7 @@
         <v>43430</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6798,7 +6798,7 @@
         <v>43430</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6855,7 +6855,7 @@
         <v>43430</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6912,7 +6912,7 @@
         <v>43431</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6974,7 +6974,7 @@
         <v>43432</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7031,7 +7031,7 @@
         <v>43432</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7088,7 +7088,7 @@
         <v>43434</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7145,7 +7145,7 @@
         <v>43434</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7202,7 +7202,7 @@
         <v>43438</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7259,7 +7259,7 @@
         <v>43441</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7316,7 +7316,7 @@
         <v>43447</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7373,7 +7373,7 @@
         <v>43448</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7430,7 +7430,7 @@
         <v>43451</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7487,7 +7487,7 @@
         <v>43451</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7544,7 +7544,7 @@
         <v>43451</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7601,7 +7601,7 @@
         <v>43452</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7658,7 +7658,7 @@
         <v>43454</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7720,7 +7720,7 @@
         <v>43454</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7782,7 +7782,7 @@
         <v>43454</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7844,7 +7844,7 @@
         <v>43455</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7901,7 +7901,7 @@
         <v>43461</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7958,7 +7958,7 @@
         <v>43471</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8015,7 +8015,7 @@
         <v>43472</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8072,7 +8072,7 @@
         <v>43472</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8134,7 +8134,7 @@
         <v>43473</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8191,7 +8191,7 @@
         <v>43475</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8248,7 +8248,7 @@
         <v>43481</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8305,7 +8305,7 @@
         <v>43490</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8362,7 +8362,7 @@
         <v>43495</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8419,7 +8419,7 @@
         <v>43499</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8476,7 +8476,7 @@
         <v>43500</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8538,7 +8538,7 @@
         <v>43511</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8595,7 +8595,7 @@
         <v>43511</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8652,7 +8652,7 @@
         <v>43514</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8709,7 +8709,7 @@
         <v>43517</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8766,7 +8766,7 @@
         <v>43524</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8823,7 +8823,7 @@
         <v>43546</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8880,7 +8880,7 @@
         <v>43553</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8942,7 +8942,7 @@
         <v>43553</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8999,7 +8999,7 @@
         <v>43554</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9056,7 +9056,7 @@
         <v>43556</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9113,7 +9113,7 @@
         <v>43559</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9175,7 +9175,7 @@
         <v>43564</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9232,7 +9232,7 @@
         <v>43566</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9289,7 +9289,7 @@
         <v>43570</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9351,7 +9351,7 @@
         <v>43570</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9413,7 +9413,7 @@
         <v>43570</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9470,7 +9470,7 @@
         <v>43580</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9527,7 +9527,7 @@
         <v>43584</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9584,7 +9584,7 @@
         <v>43585</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9641,7 +9641,7 @@
         <v>43587</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9698,7 +9698,7 @@
         <v>43592</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9755,7 +9755,7 @@
         <v>43592</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9812,7 +9812,7 @@
         <v>43592</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9869,7 +9869,7 @@
         <v>43599</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9926,7 +9926,7 @@
         <v>43609</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9983,7 +9983,7 @@
         <v>43612</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10040,7 +10040,7 @@
         <v>43612</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10097,7 +10097,7 @@
         <v>43612</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10154,7 +10154,7 @@
         <v>43612</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10211,7 +10211,7 @@
         <v>43616</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10268,7 +10268,7 @@
         <v>43619</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10330,7 +10330,7 @@
         <v>43621</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10387,7 +10387,7 @@
         <v>43623</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10444,7 +10444,7 @@
         <v>43628</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10506,7 +10506,7 @@
         <v>43628</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10568,7 +10568,7 @@
         <v>43629</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10625,7 +10625,7 @@
         <v>43630</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10682,7 +10682,7 @@
         <v>43633</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10739,7 +10739,7 @@
         <v>43633</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10796,7 +10796,7 @@
         <v>43641</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10853,7 +10853,7 @@
         <v>43643</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10915,7 +10915,7 @@
         <v>43643</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10977,7 +10977,7 @@
         <v>43647</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11039,7 +11039,7 @@
         <v>43651</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11096,7 +11096,7 @@
         <v>43651</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11153,7 +11153,7 @@
         <v>43656</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11210,7 +11210,7 @@
         <v>43657</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11267,7 +11267,7 @@
         <v>43662</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11324,7 +11324,7 @@
         <v>43662</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11381,7 +11381,7 @@
         <v>43663</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11463,7 +11463,7 @@
         <v>43663</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11525,7 +11525,7 @@
         <v>43663</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11587,7 +11587,7 @@
         <v>43663</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11649,7 +11649,7 @@
         <v>43682</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11706,7 +11706,7 @@
         <v>43686</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11768,7 +11768,7 @@
         <v>43686</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11825,7 +11825,7 @@
         <v>43689</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11887,7 +11887,7 @@
         <v>43690</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11944,7 +11944,7 @@
         <v>43697</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12001,7 +12001,7 @@
         <v>43700</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12058,7 +12058,7 @@
         <v>43705</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12115,7 +12115,7 @@
         <v>43711</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12177,7 +12177,7 @@
         <v>43712</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12234,7 +12234,7 @@
         <v>43713</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12291,7 +12291,7 @@
         <v>43714</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12348,7 +12348,7 @@
         <v>43714</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12405,7 +12405,7 @@
         <v>43717</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12462,7 +12462,7 @@
         <v>43718</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12519,7 +12519,7 @@
         <v>43720</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12576,7 +12576,7 @@
         <v>43724</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12633,7 +12633,7 @@
         <v>43726</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12690,7 +12690,7 @@
         <v>43727</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12747,7 +12747,7 @@
         <v>43727</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12804,7 +12804,7 @@
         <v>43727</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12861,7 +12861,7 @@
         <v>43732</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12918,7 +12918,7 @@
         <v>43734</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12980,7 +12980,7 @@
         <v>43734</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13037,7 +13037,7 @@
         <v>43734</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13094,7 +13094,7 @@
         <v>43735</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13156,7 +13156,7 @@
         <v>43735</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13213,7 +13213,7 @@
         <v>43740</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13275,7 +13275,7 @@
         <v>43740</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13332,7 +13332,7 @@
         <v>43740</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13389,7 +13389,7 @@
         <v>43740</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13446,7 +13446,7 @@
         <v>43742</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13508,7 +13508,7 @@
         <v>43742</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13565,7 +13565,7 @@
         <v>43747</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13622,7 +13622,7 @@
         <v>43758</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13679,7 +13679,7 @@
         <v>43761</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13736,7 +13736,7 @@
         <v>43766</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13793,7 +13793,7 @@
         <v>43767</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13855,7 +13855,7 @@
         <v>43769</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13917,7 +13917,7 @@
         <v>43770</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13974,7 +13974,7 @@
         <v>43770</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14031,7 +14031,7 @@
         <v>43773</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14088,7 +14088,7 @@
         <v>43775</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14145,7 +14145,7 @@
         <v>43776</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14202,7 +14202,7 @@
         <v>43776</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14259,7 +14259,7 @@
         <v>43776</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14316,7 +14316,7 @@
         <v>43776</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14373,7 +14373,7 @@
         <v>43780</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14435,7 +14435,7 @@
         <v>43780</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14492,7 +14492,7 @@
         <v>43780</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14549,7 +14549,7 @@
         <v>43780</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14606,7 +14606,7 @@
         <v>43783</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14668,7 +14668,7 @@
         <v>43784</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14725,7 +14725,7 @@
         <v>43786</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14782,7 +14782,7 @@
         <v>43797</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14839,7 +14839,7 @@
         <v>43804</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14901,7 +14901,7 @@
         <v>43805</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14958,7 +14958,7 @@
         <v>43805</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15015,7 +15015,7 @@
         <v>43812</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15072,7 +15072,7 @@
         <v>43812</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15129,7 +15129,7 @@
         <v>43815</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15186,7 +15186,7 @@
         <v>43815</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15243,7 +15243,7 @@
         <v>43829</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15300,7 +15300,7 @@
         <v>43833</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15357,7 +15357,7 @@
         <v>43837</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15414,7 +15414,7 @@
         <v>43839</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15471,7 +15471,7 @@
         <v>43840</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15528,7 +15528,7 @@
         <v>43843</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15585,7 +15585,7 @@
         <v>43845</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15647,7 +15647,7 @@
         <v>43850</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15704,7 +15704,7 @@
         <v>43854</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15766,7 +15766,7 @@
         <v>43857</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15823,7 +15823,7 @@
         <v>43857</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15885,7 +15885,7 @@
         <v>43857</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15942,7 +15942,7 @@
         <v>43864</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15999,7 +15999,7 @@
         <v>43864</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16061,7 +16061,7 @@
         <v>43864</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16123,7 +16123,7 @@
         <v>43867</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16185,7 +16185,7 @@
         <v>43871</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16242,7 +16242,7 @@
         <v>43872</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16304,7 +16304,7 @@
         <v>43873</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16361,7 +16361,7 @@
         <v>43873</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16418,7 +16418,7 @@
         <v>43873</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16475,7 +16475,7 @@
         <v>43874</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16532,7 +16532,7 @@
         <v>43878</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16589,7 +16589,7 @@
         <v>43879</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16651,7 +16651,7 @@
         <v>43880</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16708,7 +16708,7 @@
         <v>43894</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16765,7 +16765,7 @@
         <v>43894</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16822,7 +16822,7 @@
         <v>43902</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16879,7 +16879,7 @@
         <v>43917</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16936,7 +16936,7 @@
         <v>43917</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16998,7 +16998,7 @@
         <v>43920</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17060,7 +17060,7 @@
         <v>43920</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17122,7 +17122,7 @@
         <v>43921</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17184,7 +17184,7 @@
         <v>43922</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17246,7 +17246,7 @@
         <v>43922</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17308,7 +17308,7 @@
         <v>43924</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17365,7 +17365,7 @@
         <v>43924</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17422,7 +17422,7 @@
         <v>43927</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17479,7 +17479,7 @@
         <v>43927</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17536,7 +17536,7 @@
         <v>43928</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17593,7 +17593,7 @@
         <v>43928</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17650,7 +17650,7 @@
         <v>43930</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17712,7 +17712,7 @@
         <v>43933</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17774,7 +17774,7 @@
         <v>43933</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17836,7 +17836,7 @@
         <v>43935</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17893,7 +17893,7 @@
         <v>43937</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17955,7 +17955,7 @@
         <v>43941</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18012,7 +18012,7 @@
         <v>43941</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18069,7 +18069,7 @@
         <v>43948</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18126,7 +18126,7 @@
         <v>43949</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18188,7 +18188,7 @@
         <v>43949</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18250,7 +18250,7 @@
         <v>43949</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18312,7 +18312,7 @@
         <v>43949</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18374,7 +18374,7 @@
         <v>43950</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18431,7 +18431,7 @@
         <v>43951</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18493,7 +18493,7 @@
         <v>43959</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18555,7 +18555,7 @@
         <v>43959</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18617,7 +18617,7 @@
         <v>43959</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18679,7 +18679,7 @@
         <v>43959</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18736,7 +18736,7 @@
         <v>43969</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18798,7 +18798,7 @@
         <v>43970</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18855,7 +18855,7 @@
         <v>43973</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18912,7 +18912,7 @@
         <v>43985</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18969,7 +18969,7 @@
         <v>43990</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19026,7 +19026,7 @@
         <v>43991</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19088,7 +19088,7 @@
         <v>43991</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19150,7 +19150,7 @@
         <v>43991</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19212,7 +19212,7 @@
         <v>43991</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19274,7 +19274,7 @@
         <v>43991</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19336,7 +19336,7 @@
         <v>44005</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19398,7 +19398,7 @@
         <v>44033</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19455,7 +19455,7 @@
         <v>44039</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19512,7 +19512,7 @@
         <v>44048</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19569,7 +19569,7 @@
         <v>44049</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19626,7 +19626,7 @@
         <v>44053</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19683,7 +19683,7 @@
         <v>44053</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19740,7 +19740,7 @@
         <v>44053</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19797,7 +19797,7 @@
         <v>44054</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19859,7 +19859,7 @@
         <v>44054</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19916,7 +19916,7 @@
         <v>44054</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19973,7 +19973,7 @@
         <v>44055</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20035,7 +20035,7 @@
         <v>44055</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20097,7 +20097,7 @@
         <v>44074</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20154,7 +20154,7 @@
         <v>44074</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20211,7 +20211,7 @@
         <v>44077</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20268,7 +20268,7 @@
         <v>44078</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20330,7 +20330,7 @@
         <v>44078</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20392,7 +20392,7 @@
         <v>44082</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20449,7 +20449,7 @@
         <v>44084</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20511,7 +20511,7 @@
         <v>44089</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20568,7 +20568,7 @@
         <v>44091</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20625,7 +20625,7 @@
         <v>44095</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20682,7 +20682,7 @@
         <v>44097</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20739,7 +20739,7 @@
         <v>44102</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20796,7 +20796,7 @@
         <v>44104</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20853,7 +20853,7 @@
         <v>44105</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20910,7 +20910,7 @@
         <v>44109</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20967,7 +20967,7 @@
         <v>44109</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21029,7 +21029,7 @@
         <v>44110</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21086,7 +21086,7 @@
         <v>44117</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21148,7 +21148,7 @@
         <v>44126</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21210,7 +21210,7 @@
         <v>44126</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21272,7 +21272,7 @@
         <v>44126</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21334,7 +21334,7 @@
         <v>44126</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21396,7 +21396,7 @@
         <v>44126</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21458,7 +21458,7 @@
         <v>44130</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21515,7 +21515,7 @@
         <v>44130</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21572,7 +21572,7 @@
         <v>44130</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21629,7 +21629,7 @@
         <v>44130</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21686,7 +21686,7 @@
         <v>44131</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21743,7 +21743,7 @@
         <v>44133</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21805,7 +21805,7 @@
         <v>44137</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21862,7 +21862,7 @@
         <v>44139</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21919,7 +21919,7 @@
         <v>44139</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21976,7 +21976,7 @@
         <v>44141</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22033,7 +22033,7 @@
         <v>44145</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22090,7 +22090,7 @@
         <v>44145</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22147,7 +22147,7 @@
         <v>44151</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22204,7 +22204,7 @@
         <v>44151</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22261,7 +22261,7 @@
         <v>44153</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22318,7 +22318,7 @@
         <v>44159</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22375,7 +22375,7 @@
         <v>44159</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22432,7 +22432,7 @@
         <v>44159</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22489,7 +22489,7 @@
         <v>44159</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22546,7 +22546,7 @@
         <v>44160</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22603,7 +22603,7 @@
         <v>44160</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22660,7 +22660,7 @@
         <v>44160</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22717,7 +22717,7 @@
         <v>44161</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22774,7 +22774,7 @@
         <v>44162</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22831,7 +22831,7 @@
         <v>44173</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22888,7 +22888,7 @@
         <v>44175</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22945,7 +22945,7 @@
         <v>44175</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23002,7 +23002,7 @@
         <v>44179</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23059,7 +23059,7 @@
         <v>44179</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23116,7 +23116,7 @@
         <v>44180</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23173,7 +23173,7 @@
         <v>44185</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23230,7 +23230,7 @@
         <v>44186</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23287,7 +23287,7 @@
         <v>44186</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23344,7 +23344,7 @@
         <v>44194</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23401,7 +23401,7 @@
         <v>44195</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23458,7 +23458,7 @@
         <v>44214</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23515,7 +23515,7 @@
         <v>44214</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23572,7 +23572,7 @@
         <v>44217</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23629,7 +23629,7 @@
         <v>44217</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23686,7 +23686,7 @@
         <v>44228</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23743,7 +23743,7 @@
         <v>44228</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23800,7 +23800,7 @@
         <v>44238</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23857,7 +23857,7 @@
         <v>44242</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23914,7 +23914,7 @@
         <v>44242</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23971,7 +23971,7 @@
         <v>44271</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24028,7 +24028,7 @@
         <v>44273</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24085,7 +24085,7 @@
         <v>44280</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24142,7 +24142,7 @@
         <v>44281</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24199,7 +24199,7 @@
         <v>44284</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24256,7 +24256,7 @@
         <v>44284</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24313,7 +24313,7 @@
         <v>44300</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24370,7 +24370,7 @@
         <v>44300</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24427,7 +24427,7 @@
         <v>44300</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24484,7 +24484,7 @@
         <v>44305</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24541,7 +24541,7 @@
         <v>44306</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24598,7 +24598,7 @@
         <v>44307</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24655,7 +24655,7 @@
         <v>44322</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24717,7 +24717,7 @@
         <v>44326</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24774,7 +24774,7 @@
         <v>44326</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24831,7 +24831,7 @@
         <v>44326</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24888,7 +24888,7 @@
         <v>44326</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24945,7 +24945,7 @@
         <v>44330</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25002,7 +25002,7 @@
         <v>44335</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25059,7 +25059,7 @@
         <v>44336</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25121,7 +25121,7 @@
         <v>44340</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25178,7 +25178,7 @@
         <v>44342</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25240,7 +25240,7 @@
         <v>44347</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25297,7 +25297,7 @@
         <v>44347</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25354,7 +25354,7 @@
         <v>44348</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25411,7 +25411,7 @@
         <v>44348</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25468,7 +25468,7 @@
         <v>44349</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25525,7 +25525,7 @@
         <v>44349</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25582,7 +25582,7 @@
         <v>44350</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25639,7 +25639,7 @@
         <v>44351</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25696,7 +25696,7 @@
         <v>44351</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25753,7 +25753,7 @@
         <v>44363</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25810,7 +25810,7 @@
         <v>44377</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25872,7 +25872,7 @@
         <v>44377</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25929,7 +25929,7 @@
         <v>44377</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25986,7 +25986,7 @@
         <v>44377</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26043,7 +26043,7 @@
         <v>44377</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26105,7 +26105,7 @@
         <v>44386</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26167,7 +26167,7 @@
         <v>44386</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26229,7 +26229,7 @@
         <v>44391</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26291,7 +26291,7 @@
         <v>44391</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26353,7 +26353,7 @@
         <v>44399</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26410,7 +26410,7 @@
         <v>44400</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26467,7 +26467,7 @@
         <v>44403</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26524,7 +26524,7 @@
         <v>44408</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26586,7 +26586,7 @@
         <v>44409</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26648,7 +26648,7 @@
         <v>44414</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26710,7 +26710,7 @@
         <v>44414</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26772,7 +26772,7 @@
         <v>44414</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26834,7 +26834,7 @@
         <v>44418</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26891,7 +26891,7 @@
         <v>44420</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26948,7 +26948,7 @@
         <v>44421</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27005,7 +27005,7 @@
         <v>44421</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27067,7 +27067,7 @@
         <v>44424</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27129,7 +27129,7 @@
         <v>44424</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27186,7 +27186,7 @@
         <v>44432</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27248,7 +27248,7 @@
         <v>44435</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27305,7 +27305,7 @@
         <v>44441</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27362,7 +27362,7 @@
         <v>44441</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27424,7 +27424,7 @@
         <v>44449</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27486,7 +27486,7 @@
         <v>44451</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27548,7 +27548,7 @@
         <v>44451</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27610,7 +27610,7 @@
         <v>44454</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27667,7 +27667,7 @@
         <v>44459</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27729,7 +27729,7 @@
         <v>44459</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27791,7 +27791,7 @@
         <v>44459</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27853,7 +27853,7 @@
         <v>44459</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27915,7 +27915,7 @@
         <v>44459</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27977,7 +27977,7 @@
         <v>44459</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28039,7 +28039,7 @@
         <v>44460</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28096,7 +28096,7 @@
         <v>44460</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28153,7 +28153,7 @@
         <v>44461</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28210,7 +28210,7 @@
         <v>44463</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28272,7 +28272,7 @@
         <v>44467</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28334,7 +28334,7 @@
         <v>44469</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28396,7 +28396,7 @@
         <v>44469</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28458,7 +28458,7 @@
         <v>44469</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28520,7 +28520,7 @@
         <v>44469</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28582,7 +28582,7 @@
         <v>44470</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28644,7 +28644,7 @@
         <v>44470</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28701,7 +28701,7 @@
         <v>44470</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28763,7 +28763,7 @@
         <v>44473</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28820,7 +28820,7 @@
         <v>44474</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28877,7 +28877,7 @@
         <v>44475</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28934,7 +28934,7 @@
         <v>44475</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28991,7 +28991,7 @@
         <v>44477</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29048,7 +29048,7 @@
         <v>44477</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29105,7 +29105,7 @@
         <v>44477</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29162,7 +29162,7 @@
         <v>44479</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29224,7 +29224,7 @@
         <v>44484</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29286,7 +29286,7 @@
         <v>44484</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29348,7 +29348,7 @@
         <v>44488</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29405,7 +29405,7 @@
         <v>44489</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29467,7 +29467,7 @@
         <v>44495</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29529,7 +29529,7 @@
         <v>44495</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29591,7 +29591,7 @@
         <v>44495</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29653,7 +29653,7 @@
         <v>44495</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29715,7 +29715,7 @@
         <v>44495</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29777,7 +29777,7 @@
         <v>44495</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29839,7 +29839,7 @@
         <v>44495</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29901,7 +29901,7 @@
         <v>44496</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29958,7 +29958,7 @@
         <v>44498</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30015,7 +30015,7 @@
         <v>44509</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30077,7 +30077,7 @@
         <v>44511</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30134,7 +30134,7 @@
         <v>44512</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30191,7 +30191,7 @@
         <v>44515</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30248,7 +30248,7 @@
         <v>44517</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30305,7 +30305,7 @@
         <v>44519</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30362,7 +30362,7 @@
         <v>44519</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30419,7 +30419,7 @@
         <v>44523</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30481,7 +30481,7 @@
         <v>44524</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30538,7 +30538,7 @@
         <v>44529</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30600,7 +30600,7 @@
         <v>44529</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30657,7 +30657,7 @@
         <v>44529</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30714,7 +30714,7 @@
         <v>44529</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30771,7 +30771,7 @@
         <v>44529</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30828,7 +30828,7 @@
         <v>44533</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30885,7 +30885,7 @@
         <v>44536</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30942,7 +30942,7 @@
         <v>44537</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30999,7 +30999,7 @@
         <v>44537</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31056,7 +31056,7 @@
         <v>44537</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31113,7 +31113,7 @@
         <v>44541</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31170,7 +31170,7 @@
         <v>44544</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31227,7 +31227,7 @@
         <v>44544</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31284,7 +31284,7 @@
         <v>44545</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31341,7 +31341,7 @@
         <v>44551</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31398,7 +31398,7 @@
         <v>44551</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31455,7 +31455,7 @@
         <v>44552</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31512,7 +31512,7 @@
         <v>44556</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31569,7 +31569,7 @@
         <v>44559</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31626,7 +31626,7 @@
         <v>44562</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31683,7 +31683,7 @@
         <v>44565</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31745,7 +31745,7 @@
         <v>44565</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31807,7 +31807,7 @@
         <v>44565</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31869,7 +31869,7 @@
         <v>44571</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31926,7 +31926,7 @@
         <v>44571</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31983,7 +31983,7 @@
         <v>44572</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32040,7 +32040,7 @@
         <v>44573</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32097,7 +32097,7 @@
         <v>44578</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32154,7 +32154,7 @@
         <v>44579</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32211,7 +32211,7 @@
         <v>44600</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32268,7 +32268,7 @@
         <v>44602</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32325,7 +32325,7 @@
         <v>44610</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32387,7 +32387,7 @@
         <v>44620</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32444,7 +32444,7 @@
         <v>44621</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32501,7 +32501,7 @@
         <v>44627</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32558,7 +32558,7 @@
         <v>44637</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32615,7 +32615,7 @@
         <v>44638</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32672,7 +32672,7 @@
         <v>44638</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32729,7 +32729,7 @@
         <v>44638</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32786,7 +32786,7 @@
         <v>44641</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32843,7 +32843,7 @@
         <v>44644</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32900,7 +32900,7 @@
         <v>44651</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32957,7 +32957,7 @@
         <v>44651</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33014,7 +33014,7 @@
         <v>44655</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33071,7 +33071,7 @@
         <v>44679</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33128,7 +33128,7 @@
         <v>44679</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33185,7 +33185,7 @@
         <v>44679</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33242,7 +33242,7 @@
         <v>44680</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33299,7 +33299,7 @@
         <v>44683</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33356,7 +33356,7 @@
         <v>44684</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33413,7 +33413,7 @@
         <v>44686</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33470,7 +33470,7 @@
         <v>44692</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33527,7 +33527,7 @@
         <v>44700</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33584,7 +33584,7 @@
         <v>44701</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33641,7 +33641,7 @@
         <v>44715</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33698,7 +33698,7 @@
         <v>44719</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33755,7 +33755,7 @@
         <v>44722</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33812,7 +33812,7 @@
         <v>44727</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33869,7 +33869,7 @@
         <v>44727</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33926,7 +33926,7 @@
         <v>44728</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33988,7 +33988,7 @@
         <v>44728</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34050,7 +34050,7 @@
         <v>44729</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34112,7 +34112,7 @@
         <v>44732</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34169,7 +34169,7 @@
         <v>44733</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34226,7 +34226,7 @@
         <v>44736</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34283,7 +34283,7 @@
         <v>44740</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34340,7 +34340,7 @@
         <v>44742</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34397,7 +34397,7 @@
         <v>44743</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34459,7 +34459,7 @@
         <v>44746</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34516,7 +34516,7 @@
         <v>44746</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34573,7 +34573,7 @@
         <v>44747</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34635,7 +34635,7 @@
         <v>44747</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34692,7 +34692,7 @@
         <v>44747</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34754,7 +34754,7 @@
         <v>44747</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34811,7 +34811,7 @@
         <v>44748</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34868,7 +34868,7 @@
         <v>44749</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34930,7 +34930,7 @@
         <v>44749</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34992,7 +34992,7 @@
         <v>44749</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35049,7 +35049,7 @@
         <v>44762</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35106,7 +35106,7 @@
         <v>44762</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35163,7 +35163,7 @@
         <v>44762</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35220,7 +35220,7 @@
         <v>44763</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35277,7 +35277,7 @@
         <v>44763</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35339,7 +35339,7 @@
         <v>44774</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35401,7 +35401,7 @@
         <v>44775</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35458,7 +35458,7 @@
         <v>44775</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35515,7 +35515,7 @@
         <v>44775</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35572,7 +35572,7 @@
         <v>44783</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35629,7 +35629,7 @@
         <v>44785</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35691,7 +35691,7 @@
         <v>44789</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35748,7 +35748,7 @@
         <v>44789</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35810,7 +35810,7 @@
         <v>44790</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35867,7 +35867,7 @@
         <v>44790</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35924,7 +35924,7 @@
         <v>44791</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35981,7 +35981,7 @@
         <v>44791</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36038,7 +36038,7 @@
         <v>44792</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36100,7 +36100,7 @@
         <v>44792</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36162,7 +36162,7 @@
         <v>44792</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36224,7 +36224,7 @@
         <v>44792</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36286,7 +36286,7 @@
         <v>44792</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36348,7 +36348,7 @@
         <v>44795</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36405,7 +36405,7 @@
         <v>44795</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36462,7 +36462,7 @@
         <v>44795</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36519,7 +36519,7 @@
         <v>44796</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36576,7 +36576,7 @@
         <v>44797</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36633,7 +36633,7 @@
         <v>44798</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36690,7 +36690,7 @@
         <v>44798</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36747,7 +36747,7 @@
         <v>44799</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36809,7 +36809,7 @@
         <v>44799</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36871,7 +36871,7 @@
         <v>44799</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36933,7 +36933,7 @@
         <v>44799</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36995,7 +36995,7 @@
         <v>44803</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37052,7 +37052,7 @@
         <v>44803</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37109,7 +37109,7 @@
         <v>44804</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37166,7 +37166,7 @@
         <v>44804</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37223,7 +37223,7 @@
         <v>44806</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37305,7 +37305,7 @@
         <v>44806</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37362,7 +37362,7 @@
         <v>44806</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37419,7 +37419,7 @@
         <v>44806</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37476,7 +37476,7 @@
         <v>44806</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37533,7 +37533,7 @@
         <v>44806</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37590,7 +37590,7 @@
         <v>44807</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37647,7 +37647,7 @@
         <v>44813</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37709,7 +37709,7 @@
         <v>44817</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37771,7 +37771,7 @@
         <v>44817</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37833,7 +37833,7 @@
         <v>44818</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37890,7 +37890,7 @@
         <v>44818</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37947,7 +37947,7 @@
         <v>44818</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38004,7 +38004,7 @@
         <v>44818</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38061,7 +38061,7 @@
         <v>44818</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38118,7 +38118,7 @@
         <v>44819</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38175,7 +38175,7 @@
         <v>44819</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38237,7 +38237,7 @@
         <v>44819</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38294,7 +38294,7 @@
         <v>44820</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38356,7 +38356,7 @@
         <v>44823</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38413,7 +38413,7 @@
         <v>44824</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38470,7 +38470,7 @@
         <v>44826</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38527,7 +38527,7 @@
         <v>44827</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38589,7 +38589,7 @@
         <v>44833</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38646,7 +38646,7 @@
         <v>44834</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38703,7 +38703,7 @@
         <v>44834</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38760,7 +38760,7 @@
         <v>44837</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38817,7 +38817,7 @@
         <v>44838</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38879,7 +38879,7 @@
         <v>44839</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38941,7 +38941,7 @@
         <v>44839</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38998,7 +38998,7 @@
         <v>44839</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39060,7 +39060,7 @@
         <v>44840</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39117,7 +39117,7 @@
         <v>44841</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39174,7 +39174,7 @@
         <v>44841</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39236,7 +39236,7 @@
         <v>44841</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39293,7 +39293,7 @@
         <v>44841</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39350,7 +39350,7 @@
         <v>44845</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39412,7 +39412,7 @@
         <v>44845</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39474,7 +39474,7 @@
         <v>44847</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39531,7 +39531,7 @@
         <v>44851</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39593,7 +39593,7 @@
         <v>44851</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39655,7 +39655,7 @@
         <v>44851</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39717,7 +39717,7 @@
         <v>44851</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39779,7 +39779,7 @@
         <v>44855</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39841,7 +39841,7 @@
         <v>44860</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39903,7 +39903,7 @@
         <v>44862</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39965,7 +39965,7 @@
         <v>44862</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40027,7 +40027,7 @@
         <v>44866</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40089,7 +40089,7 @@
         <v>44866</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40151,7 +40151,7 @@
         <v>44866</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40213,7 +40213,7 @@
         <v>44866</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40270,7 +40270,7 @@
         <v>44868</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40327,7 +40327,7 @@
         <v>44872</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40384,7 +40384,7 @@
         <v>44873</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40441,7 +40441,7 @@
         <v>44873</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40498,7 +40498,7 @@
         <v>44873</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40555,7 +40555,7 @@
         <v>44874</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40612,7 +40612,7 @@
         <v>44874</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40669,7 +40669,7 @@
         <v>44875</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40726,7 +40726,7 @@
         <v>44875</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40783,7 +40783,7 @@
         <v>44879</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40845,7 +40845,7 @@
         <v>44882</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40902,7 +40902,7 @@
         <v>44883</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40964,7 +40964,7 @@
         <v>44883</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41026,7 +41026,7 @@
         <v>44887</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41083,7 +41083,7 @@
         <v>44889</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41140,7 +41140,7 @@
         <v>44890</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41197,7 +41197,7 @@
         <v>44891</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41254,7 +41254,7 @@
         <v>44893</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41311,7 +41311,7 @@
         <v>44897</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41368,7 +41368,7 @@
         <v>44903</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41425,7 +41425,7 @@
         <v>44907</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41487,7 +41487,7 @@
         <v>44907</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41544,7 +41544,7 @@
         <v>44909</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41606,7 +41606,7 @@
         <v>44909</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41688,7 +41688,7 @@
         <v>44909</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41745,7 +41745,7 @@
         <v>44909</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41802,7 +41802,7 @@
         <v>44910</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41859,7 +41859,7 @@
         <v>44911</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41916,7 +41916,7 @@
         <v>44911</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41973,7 +41973,7 @@
         <v>44911</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42030,7 +42030,7 @@
         <v>44911</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42087,7 +42087,7 @@
         <v>44914</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42144,7 +42144,7 @@
         <v>44914</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42201,7 +42201,7 @@
         <v>44914</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42258,7 +42258,7 @@
         <v>44916</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42315,7 +42315,7 @@
         <v>44916</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42372,7 +42372,7 @@
         <v>44922</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42429,7 +42429,7 @@
         <v>44928</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42486,7 +42486,7 @@
         <v>44929</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42543,7 +42543,7 @@
         <v>44929</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42600,7 +42600,7 @@
         <v>44930</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42657,7 +42657,7 @@
         <v>44930</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42714,7 +42714,7 @@
         <v>44930</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42771,7 +42771,7 @@
         <v>44930</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42828,7 +42828,7 @@
         <v>44931</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42890,7 +42890,7 @@
         <v>44939</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42947,7 +42947,7 @@
         <v>44939</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43004,7 +43004,7 @@
         <v>44944</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43061,7 +43061,7 @@
         <v>44944</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43118,7 +43118,7 @@
         <v>44945</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43175,7 +43175,7 @@
         <v>44949</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43232,7 +43232,7 @@
         <v>44950</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43289,7 +43289,7 @@
         <v>44950</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43346,7 +43346,7 @@
         <v>44953</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43403,7 +43403,7 @@
         <v>44956</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43460,7 +43460,7 @@
         <v>44960</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43517,7 +43517,7 @@
         <v>44964</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43574,7 +43574,7 @@
         <v>44964</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43631,7 +43631,7 @@
         <v>44964</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43688,7 +43688,7 @@
         <v>44964</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43745,7 +43745,7 @@
         <v>44964</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43802,7 +43802,7 @@
         <v>44964</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43859,7 +43859,7 @@
         <v>44964</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43916,7 +43916,7 @@
         <v>44966</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43973,7 +43973,7 @@
         <v>44967</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44030,7 +44030,7 @@
         <v>44967</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44087,7 +44087,7 @@
         <v>44967</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44144,7 +44144,7 @@
         <v>44967</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44201,7 +44201,7 @@
         <v>44967</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44258,7 +44258,7 @@
         <v>44970</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44315,7 +44315,7 @@
         <v>44970</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44372,7 +44372,7 @@
         <v>44973</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44429,7 +44429,7 @@
         <v>44977</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44486,7 +44486,7 @@
         <v>44977</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44543,7 +44543,7 @@
         <v>44982</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44600,7 +44600,7 @@
         <v>44991</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -44657,7 +44657,7 @@
         <v>44997</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44714,7 +44714,7 @@
         <v>45002</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44771,7 +44771,7 @@
         <v>45002</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44828,7 +44828,7 @@
         <v>45002</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44885,7 +44885,7 @@
         <v>45019</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44942,7 +44942,7 @@
         <v>45019</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44999,7 +44999,7 @@
         <v>45019</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45056,7 +45056,7 @@
         <v>45021</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45113,7 +45113,7 @@
         <v>45027</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45170,7 +45170,7 @@
         <v>45033</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45227,7 +45227,7 @@
         <v>45040</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45289,7 +45289,7 @@
         <v>45042</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45346,7 +45346,7 @@
         <v>45058</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45403,7 +45403,7 @@
         <v>45062</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45465,7 +45465,7 @@
         <v>45063</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45522,7 +45522,7 @@
         <v>45070</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45579,7 +45579,7 @@
         <v>45071</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45636,7 +45636,7 @@
         <v>45071</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45693,7 +45693,7 @@
         <v>45071</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45750,7 +45750,7 @@
         <v>45071</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45807,7 +45807,7 @@
         <v>45071</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45864,7 +45864,7 @@
         <v>45071</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45921,7 +45921,7 @@
         <v>45072</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -45978,7 +45978,7 @@
         <v>45072</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46035,7 +46035,7 @@
         <v>45072</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46097,7 +46097,7 @@
         <v>45075</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46154,7 +46154,7 @@
         <v>45075</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46211,7 +46211,7 @@
         <v>45077</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46268,7 +46268,7 @@
         <v>45079</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46325,7 +46325,7 @@
         <v>45084</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46382,7 +46382,7 @@
         <v>45085</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46439,7 +46439,7 @@
         <v>45085</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46496,7 +46496,7 @@
         <v>45090</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46553,7 +46553,7 @@
         <v>45090</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46610,7 +46610,7 @@
         <v>45090</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46667,7 +46667,7 @@
         <v>45092</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46729,7 +46729,7 @@
         <v>45092</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46786,7 +46786,7 @@
         <v>45093</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46848,7 +46848,7 @@
         <v>45093</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46910,7 +46910,7 @@
         <v>45096</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46967,7 +46967,7 @@
         <v>45096</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47029,7 +47029,7 @@
         <v>45096</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47091,7 +47091,7 @@
         <v>45097</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47148,7 +47148,7 @@
         <v>45097</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47210,7 +47210,7 @@
         <v>45097</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47272,7 +47272,7 @@
         <v>45098</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47329,7 +47329,7 @@
         <v>45098</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47386,7 +47386,7 @@
         <v>45099</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47448,7 +47448,7 @@
         <v>45103</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -47505,7 +47505,7 @@
         <v>45103</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47562,7 +47562,7 @@
         <v>45104</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -47619,7 +47619,7 @@
         <v>45105</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -47676,7 +47676,7 @@
         <v>45105</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -47733,7 +47733,7 @@
         <v>45106</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47790,7 +47790,7 @@
         <v>45107</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -47847,7 +47847,7 @@
         <v>45107</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -47904,7 +47904,7 @@
         <v>45107</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -47961,7 +47961,7 @@
         <v>45111</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -48023,7 +48023,7 @@
         <v>45111</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48080,7 +48080,7 @@
         <v>45112</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -48137,7 +48137,7 @@
         <v>45112</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -48199,7 +48199,7 @@
         <v>45112</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48261,7 +48261,7 @@
         <v>45112</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48318,7 +48318,7 @@
         <v>45114</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48375,7 +48375,7 @@
         <v>45114</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48432,7 +48432,7 @@
         <v>45119</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -48489,7 +48489,7 @@
         <v>45120</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -48551,7 +48551,7 @@
         <v>45124</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -48613,7 +48613,7 @@
         <v>45124</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -48670,7 +48670,7 @@
         <v>45131</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -48732,7 +48732,7 @@
         <v>45131</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48794,7 +48794,7 @@
         <v>45132</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -48851,7 +48851,7 @@
         <v>45132</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -48908,7 +48908,7 @@
         <v>45138</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -48970,7 +48970,7 @@
         <v>45138</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -49032,7 +49032,7 @@
         <v>45139</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -49089,7 +49089,7 @@
         <v>45139</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -49146,7 +49146,7 @@
         <v>45140</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -49203,7 +49203,7 @@
         <v>45145</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49265,7 +49265,7 @@
         <v>45148</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -49322,7 +49322,7 @@
         <v>45152</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49379,7 +49379,7 @@
         <v>45152</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49441,7 +49441,7 @@
         <v>45152</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -49503,7 +49503,7 @@
         <v>45154</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -49560,7 +49560,7 @@
         <v>45155</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -49617,7 +49617,7 @@
         <v>45159</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -49679,7 +49679,7 @@
         <v>45159</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -49736,7 +49736,7 @@
         <v>45160</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -49798,7 +49798,7 @@
         <v>45160</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -49860,7 +49860,7 @@
         <v>45161</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -49917,7 +49917,7 @@
         <v>45161</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -49979,7 +49979,7 @@
         <v>45166</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -50036,7 +50036,7 @@
         <v>45167</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -50093,7 +50093,7 @@
         <v>45168</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -50150,7 +50150,7 @@
         <v>45168</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -50207,7 +50207,7 @@
         <v>45168</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -50264,7 +50264,7 @@
         <v>45173</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -50321,7 +50321,7 @@
         <v>45173</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -50378,7 +50378,7 @@
         <v>45173</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -50435,7 +50435,7 @@
         <v>45174</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -50492,7 +50492,7 @@
         <v>45175</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -50554,7 +50554,7 @@
         <v>45175</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -50616,7 +50616,7 @@
         <v>45176</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -50678,7 +50678,7 @@
         <v>45176</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -50740,7 +50740,7 @@
         <v>45176</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -50802,7 +50802,7 @@
         <v>45176</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -50864,7 +50864,7 @@
         <v>45176</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -50921,7 +50921,7 @@
         <v>45176</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -50978,7 +50978,7 @@
         <v>45176</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -51035,7 +51035,7 @@
         <v>45180</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -51097,7 +51097,7 @@
         <v>45180</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -51159,7 +51159,7 @@
         <v>45181</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -51216,7 +51216,7 @@
         <v>45181</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -51273,7 +51273,7 @@
         <v>45181</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -51330,7 +51330,7 @@
         <v>45181</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -51387,7 +51387,7 @@
         <v>45182</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -51444,7 +51444,7 @@
         <v>45182</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -51501,7 +51501,7 @@
         <v>45182</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -51558,7 +51558,7 @@
         <v>45183</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -51615,7 +51615,7 @@
         <v>45183</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -51672,7 +51672,7 @@
         <v>45183</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -51729,7 +51729,7 @@
         <v>45187</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -51786,7 +51786,7 @@
         <v>45187</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -51848,7 +51848,7 @@
         <v>45188</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -51905,7 +51905,7 @@
         <v>45188</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -51962,7 +51962,7 @@
         <v>45188</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -52019,7 +52019,7 @@
         <v>45188</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -52076,7 +52076,7 @@
         <v>45190</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -52133,7 +52133,7 @@
         <v>45190</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -52190,7 +52190,7 @@
         <v>45194</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -52247,7 +52247,7 @@
         <v>45194</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -52304,7 +52304,7 @@
         <v>45194</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -52361,7 +52361,7 @@
         <v>45194</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -52418,7 +52418,7 @@
         <v>45194</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -52475,7 +52475,7 @@
         <v>45194</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -52537,7 +52537,7 @@
         <v>45194</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -52594,7 +52594,7 @@
         <v>45194</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -52651,7 +52651,7 @@
         <v>45194</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -52713,7 +52713,7 @@
         <v>45194</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -52775,7 +52775,7 @@
         <v>45195</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -52832,7 +52832,7 @@
         <v>45198</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -52889,7 +52889,7 @@
         <v>45198</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -52946,7 +52946,7 @@
         <v>45201</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -53003,7 +53003,7 @@
         <v>45201</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -53060,7 +53060,7 @@
         <v>45201</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -53117,7 +53117,7 @@
         <v>45201</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -53174,7 +53174,7 @@
         <v>45202</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -53231,7 +53231,7 @@
         <v>45203</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -53288,7 +53288,7 @@
         <v>45203</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -53345,7 +53345,7 @@
         <v>45204</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -53402,7 +53402,7 @@
         <v>45204</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -53459,7 +53459,7 @@
         <v>45204</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -53516,7 +53516,7 @@
         <v>45204</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -53578,7 +53578,7 @@
         <v>45204</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -53635,7 +53635,7 @@
         <v>45205</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -53697,7 +53697,7 @@
         <v>45208</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -53754,7 +53754,7 @@
         <v>45209</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -53816,7 +53816,7 @@
         <v>45209</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -53878,7 +53878,7 @@
         <v>45210</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -53935,7 +53935,7 @@
         <v>45210</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -53992,7 +53992,7 @@
         <v>45210</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -54049,7 +54049,7 @@
         <v>45211</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -54106,7 +54106,7 @@
         <v>45211</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -54168,7 +54168,7 @@
         <v>45215</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -54225,7 +54225,7 @@
         <v>45215</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -54282,7 +54282,7 @@
         <v>45216</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -54339,7 +54339,7 @@
         <v>45217</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -54396,7 +54396,7 @@
         <v>45217</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -54453,7 +54453,7 @@
         <v>45217</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -54510,7 +54510,7 @@
         <v>45217</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -54567,7 +54567,7 @@
         <v>45222</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -54629,7 +54629,7 @@
         <v>45222</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -54686,7 +54686,7 @@
         <v>45222</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -54743,7 +54743,7 @@
         <v>45223</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -54805,7 +54805,7 @@
         <v>45223</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -54862,7 +54862,7 @@
         <v>45225</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -54924,7 +54924,7 @@
         <v>45225</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -54981,7 +54981,7 @@
         <v>45225</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -55043,7 +55043,7 @@
         <v>45225</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -55100,7 +55100,7 @@
         <v>45225</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -55157,7 +55157,7 @@
         <v>45225</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -55214,7 +55214,7 @@
         <v>45225</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -55271,7 +55271,7 @@
         <v>45225</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -55328,7 +55328,7 @@
         <v>45225</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -55385,7 +55385,7 @@
         <v>45226</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -55442,7 +55442,7 @@
         <v>45229</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -55499,7 +55499,7 @@
         <v>45229</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -55556,7 +55556,7 @@
         <v>45229</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -55613,7 +55613,7 @@
         <v>45229</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -55670,7 +55670,7 @@
         <v>45229</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -55727,7 +55727,7 @@
         <v>45230</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -55784,7 +55784,7 @@
         <v>45230</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -55841,7 +55841,7 @@
         <v>45230</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -55898,7 +55898,7 @@
         <v>45230</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -55955,7 +55955,7 @@
         <v>45230</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -56012,7 +56012,7 @@
         <v>45231</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -56069,7 +56069,7 @@
         <v>45231</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -56126,7 +56126,7 @@
         <v>45231</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -56183,7 +56183,7 @@
         <v>45231</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -56240,7 +56240,7 @@
         <v>45231</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -56297,7 +56297,7 @@
         <v>45231</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -56354,7 +56354,7 @@
         <v>45231</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -56411,7 +56411,7 @@
         <v>45232</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -56473,7 +56473,7 @@
         <v>45232</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -56530,7 +56530,7 @@
         <v>45232</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -56587,7 +56587,7 @@
         <v>45232</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -56644,7 +56644,7 @@
         <v>45233</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -56706,7 +56706,7 @@
         <v>45236</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -56763,7 +56763,7 @@
         <v>45236</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -56820,7 +56820,7 @@
         <v>45236</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -56877,7 +56877,7 @@
         <v>45237</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -56934,7 +56934,7 @@
         <v>45237</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -56996,7 +56996,7 @@
         <v>45239</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -57053,7 +57053,7 @@
         <v>45239</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -57110,7 +57110,7 @@
         <v>45240</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -57172,7 +57172,7 @@
         <v>45243</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -57229,7 +57229,7 @@
         <v>45243</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -57286,7 +57286,7 @@
         <v>45243</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -57343,7 +57343,7 @@
         <v>45243</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -57400,7 +57400,7 @@
         <v>45243</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -57457,7 +57457,7 @@
         <v>45243</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -57514,7 +57514,7 @@
         <v>45244</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -57571,7 +57571,7 @@
         <v>45244</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -57633,7 +57633,7 @@
         <v>45244</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -57695,7 +57695,7 @@
         <v>45244</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -57752,7 +57752,7 @@
         <v>45244</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -57809,7 +57809,7 @@
         <v>45244</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -57871,7 +57871,7 @@
         <v>45244</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -57928,7 +57928,7 @@
         <v>45245</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -57985,7 +57985,7 @@
         <v>45245</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -58042,7 +58042,7 @@
         <v>45245</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -58099,7 +58099,7 @@
         <v>45245</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -58156,7 +58156,7 @@
         <v>45245</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -58218,7 +58218,7 @@
         <v>45245</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -58275,7 +58275,7 @@
         <v>45245</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -58332,7 +58332,7 @@
         <v>45247</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -58389,7 +58389,7 @@
         <v>45247</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -58446,7 +58446,7 @@
         <v>45248</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -58503,7 +58503,7 @@
         <v>45250</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -58560,7 +58560,7 @@
         <v>45250</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -58617,7 +58617,7 @@
         <v>45251</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -58674,7 +58674,7 @@
         <v>45251</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -58731,7 +58731,7 @@
         <v>45251</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -58788,7 +58788,7 @@
         <v>45252</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -58845,7 +58845,7 @@
         <v>45253</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -58907,7 +58907,7 @@
         <v>45253</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -58964,7 +58964,7 @@
         <v>45253</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -59026,7 +59026,7 @@
         <v>45253</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -59083,7 +59083,7 @@
         <v>45253</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -59145,7 +59145,7 @@
         <v>45253</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -59207,7 +59207,7 @@
         <v>45253</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -59264,7 +59264,7 @@
         <v>45257</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -59321,7 +59321,7 @@
         <v>45258</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -59378,7 +59378,7 @@
         <v>45259</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -59435,7 +59435,7 @@
         <v>45260</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -59492,7 +59492,7 @@
         <v>45261</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -59549,7 +59549,7 @@
         <v>45261</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -59606,7 +59606,7 @@
         <v>45264</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -59663,7 +59663,7 @@
         <v>45264</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -59720,7 +59720,7 @@
         <v>45264</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -59777,7 +59777,7 @@
         <v>45264</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -59834,7 +59834,7 @@
         <v>45264</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -59891,7 +59891,7 @@
         <v>45264</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -59948,7 +59948,7 @@
         <v>45265</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -60005,7 +60005,7 @@
         <v>45265</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -60062,7 +60062,7 @@
         <v>45265</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -60119,7 +60119,7 @@
         <v>45266</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -60176,7 +60176,7 @@
         <v>45266</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -60233,7 +60233,7 @@
         <v>45266</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -60290,7 +60290,7 @@
         <v>45266</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -60352,7 +60352,7 @@
         <v>45267</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -60409,7 +60409,7 @@
         <v>45267</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -60466,7 +60466,7 @@
         <v>45267</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -60523,7 +60523,7 @@
         <v>45267</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -60580,7 +60580,7 @@
         <v>45267</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -60637,7 +60637,7 @@
         <v>45268</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -60694,7 +60694,7 @@
         <v>45271</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -60751,7 +60751,7 @@
         <v>45273</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -60808,7 +60808,7 @@
         <v>45273</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -60865,7 +60865,7 @@
         <v>45275</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -60922,7 +60922,7 @@
         <v>45279</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -60979,7 +60979,7 @@
         <v>45279</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -61036,7 +61036,7 @@
         <v>45279</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -61093,7 +61093,7 @@
         <v>45281</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -61150,7 +61150,7 @@
         <v>45281</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -61212,7 +61212,7 @@
         <v>45282</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -61269,7 +61269,7 @@
         <v>45287</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -61331,7 +61331,7 @@
         <v>45297</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -61393,7 +61393,7 @@
         <v>45299</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -61450,7 +61450,7 @@
         <v>45300</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -61507,7 +61507,7 @@
         <v>45300</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -61564,7 +61564,7 @@
         <v>45302</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -61621,7 +61621,7 @@
         <v>45302</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -61678,7 +61678,7 @@
         <v>45303</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -61735,7 +61735,7 @@
         <v>45306</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -61792,7 +61792,7 @@
         <v>45306</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -61849,7 +61849,7 @@
         <v>45307</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -61906,7 +61906,7 @@
         <v>45307</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -61963,7 +61963,7 @@
         <v>45307</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -62020,7 +62020,7 @@
         <v>45307</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -62077,7 +62077,7 @@
         <v>45307</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -62127,14 +62127,14 @@
     <row r="1034" ht="15" customHeight="1">
       <c r="A1034" t="inlineStr">
         <is>
-          <t>A 2252-2024</t>
+          <t>A 2259-2024</t>
         </is>
       </c>
       <c r="B1034" s="1" t="n">
         <v>45310</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -62147,7 +62147,7 @@
         </is>
       </c>
       <c r="G1034" t="n">
-        <v>5.4</v>
+        <v>2</v>
       </c>
       <c r="H1034" t="n">
         <v>0</v>
@@ -62184,14 +62184,14 @@
     <row r="1035" ht="15" customHeight="1">
       <c r="A1035" t="inlineStr">
         <is>
-          <t>A 2260-2024</t>
+          <t>A 2258-2024</t>
         </is>
       </c>
       <c r="B1035" s="1" t="n">
         <v>45310</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -62204,7 +62204,7 @@
         </is>
       </c>
       <c r="G1035" t="n">
-        <v>4.8</v>
+        <v>1.6</v>
       </c>
       <c r="H1035" t="n">
         <v>0</v>
@@ -62241,14 +62241,14 @@
     <row r="1036" ht="15" customHeight="1">
       <c r="A1036" t="inlineStr">
         <is>
-          <t>A 2264-2024</t>
+          <t>A 2262-2024</t>
         </is>
       </c>
       <c r="B1036" s="1" t="n">
         <v>45310</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -62261,7 +62261,7 @@
         </is>
       </c>
       <c r="G1036" t="n">
-        <v>3.4</v>
+        <v>0.2</v>
       </c>
       <c r="H1036" t="n">
         <v>0</v>
@@ -62298,14 +62298,14 @@
     <row r="1037" ht="15" customHeight="1">
       <c r="A1037" t="inlineStr">
         <is>
-          <t>A 2268-2024</t>
+          <t>A 2270-2024</t>
         </is>
       </c>
       <c r="B1037" s="1" t="n">
         <v>45310</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -62318,7 +62318,7 @@
         </is>
       </c>
       <c r="G1037" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="H1037" t="n">
         <v>0</v>
@@ -62355,14 +62355,14 @@
     <row r="1038" ht="15" customHeight="1">
       <c r="A1038" t="inlineStr">
         <is>
-          <t>A 2272-2024</t>
+          <t>A 2252-2024</t>
         </is>
       </c>
       <c r="B1038" s="1" t="n">
         <v>45310</v>
       </c>
       <c r="C1038" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
@@ -62375,7 +62375,7 @@
         </is>
       </c>
       <c r="G1038" t="n">
-        <v>2.4</v>
+        <v>5.4</v>
       </c>
       <c r="H1038" t="n">
         <v>0</v>
@@ -62412,14 +62412,14 @@
     <row r="1039" ht="15" customHeight="1">
       <c r="A1039" t="inlineStr">
         <is>
-          <t>A 2258-2024</t>
+          <t>A 2260-2024</t>
         </is>
       </c>
       <c r="B1039" s="1" t="n">
         <v>45310</v>
       </c>
       <c r="C1039" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
@@ -62432,7 +62432,7 @@
         </is>
       </c>
       <c r="G1039" t="n">
-        <v>1.6</v>
+        <v>4.8</v>
       </c>
       <c r="H1039" t="n">
         <v>0</v>
@@ -62469,14 +62469,14 @@
     <row r="1040" ht="15" customHeight="1">
       <c r="A1040" t="inlineStr">
         <is>
-          <t>A 2262-2024</t>
+          <t>A 2264-2024</t>
         </is>
       </c>
       <c r="B1040" s="1" t="n">
         <v>45310</v>
       </c>
       <c r="C1040" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
@@ -62489,7 +62489,7 @@
         </is>
       </c>
       <c r="G1040" t="n">
-        <v>0.2</v>
+        <v>3.4</v>
       </c>
       <c r="H1040" t="n">
         <v>0</v>
@@ -62526,14 +62526,14 @@
     <row r="1041" ht="15" customHeight="1">
       <c r="A1041" t="inlineStr">
         <is>
-          <t>A 2270-2024</t>
+          <t>A 2268-2024</t>
         </is>
       </c>
       <c r="B1041" s="1" t="n">
         <v>45310</v>
       </c>
       <c r="C1041" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
@@ -62546,7 +62546,7 @@
         </is>
       </c>
       <c r="G1041" t="n">
-        <v>0.3</v>
+        <v>1.5</v>
       </c>
       <c r="H1041" t="n">
         <v>0</v>
@@ -62583,14 +62583,14 @@
     <row r="1042" ht="15" customHeight="1">
       <c r="A1042" t="inlineStr">
         <is>
-          <t>A 2259-2024</t>
+          <t>A 2272-2024</t>
         </is>
       </c>
       <c r="B1042" s="1" t="n">
         <v>45310</v>
       </c>
       <c r="C1042" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
@@ -62603,7 +62603,7 @@
         </is>
       </c>
       <c r="G1042" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="H1042" t="n">
         <v>0</v>
@@ -62647,7 +62647,7 @@
         <v>45313</v>
       </c>
       <c r="C1043" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1043" t="inlineStr">
         <is>
@@ -62704,7 +62704,7 @@
         <v>45314</v>
       </c>
       <c r="C1044" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1044" t="inlineStr">
         <is>
@@ -62761,7 +62761,7 @@
         <v>45314</v>
       </c>
       <c r="C1045" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1045" t="inlineStr">
         <is>
@@ -62818,7 +62818,7 @@
         <v>45314</v>
       </c>
       <c r="C1046" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1046" t="inlineStr">
         <is>
@@ -62875,7 +62875,7 @@
         <v>45316</v>
       </c>
       <c r="C1047" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1047" t="inlineStr">
         <is>
@@ -62932,7 +62932,7 @@
         <v>45317</v>
       </c>
       <c r="C1048" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1048" t="inlineStr">
         <is>
@@ -62989,7 +62989,7 @@
         <v>45321</v>
       </c>
       <c r="C1049" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1049" t="inlineStr">
         <is>
@@ -63046,7 +63046,7 @@
         <v>45321</v>
       </c>
       <c r="C1050" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1050" t="inlineStr">
         <is>
@@ -63103,7 +63103,7 @@
         <v>45321</v>
       </c>
       <c r="C1051" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1051" t="inlineStr">
         <is>
@@ -63160,7 +63160,7 @@
         <v>45321</v>
       </c>
       <c r="C1052" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1052" t="inlineStr">
         <is>
@@ -63217,7 +63217,7 @@
         <v>45321</v>
       </c>
       <c r="C1053" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1053" t="inlineStr">
         <is>
@@ -63274,7 +63274,7 @@
         <v>45321</v>
       </c>
       <c r="C1054" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1054" t="inlineStr">
         <is>
@@ -63331,7 +63331,7 @@
         <v>45321</v>
       </c>
       <c r="C1055" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1055" t="inlineStr">
         <is>
@@ -63381,14 +63381,14 @@
     <row r="1056" ht="15" customHeight="1">
       <c r="A1056" t="inlineStr">
         <is>
-          <t>A 3643-2024</t>
+          <t>A 3738-2024</t>
         </is>
       </c>
       <c r="B1056" s="1" t="n">
         <v>45321</v>
       </c>
       <c r="C1056" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1056" t="inlineStr">
         <is>
@@ -63401,7 +63401,7 @@
         </is>
       </c>
       <c r="G1056" t="n">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="H1056" t="n">
         <v>0</v>
@@ -63438,14 +63438,14 @@
     <row r="1057" ht="15" customHeight="1">
       <c r="A1057" t="inlineStr">
         <is>
-          <t>A 3738-2024</t>
+          <t>A 3742-2024</t>
         </is>
       </c>
       <c r="B1057" s="1" t="n">
         <v>45321</v>
       </c>
       <c r="C1057" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1057" t="inlineStr">
         <is>
@@ -63458,7 +63458,7 @@
         </is>
       </c>
       <c r="G1057" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="H1057" t="n">
         <v>0</v>
@@ -63495,14 +63495,14 @@
     <row r="1058" ht="15" customHeight="1">
       <c r="A1058" t="inlineStr">
         <is>
-          <t>A 3742-2024</t>
+          <t>A 3643-2024</t>
         </is>
       </c>
       <c r="B1058" s="1" t="n">
         <v>45321</v>
       </c>
       <c r="C1058" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1058" t="inlineStr">
         <is>
@@ -63515,7 +63515,7 @@
         </is>
       </c>
       <c r="G1058" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="H1058" t="n">
         <v>0</v>
@@ -63559,7 +63559,7 @@
         <v>45321</v>
       </c>
       <c r="C1059" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1059" t="inlineStr">
         <is>
@@ -63616,7 +63616,7 @@
         <v>45321</v>
       </c>
       <c r="C1060" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1060" t="inlineStr">
         <is>
@@ -63673,7 +63673,7 @@
         <v>45322</v>
       </c>
       <c r="C1061" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1061" t="inlineStr">
         <is>
@@ -63730,7 +63730,7 @@
         <v>45324</v>
       </c>
       <c r="C1062" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1062" t="inlineStr">
         <is>
@@ -63787,7 +63787,7 @@
         <v>45329</v>
       </c>
       <c r="C1063" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1063" t="inlineStr">
         <is>
@@ -63844,7 +63844,7 @@
         <v>45329</v>
       </c>
       <c r="C1064" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1064" t="inlineStr">
         <is>
@@ -63901,7 +63901,7 @@
         <v>45330</v>
       </c>
       <c r="C1065" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1065" t="inlineStr">
         <is>
@@ -63951,14 +63951,14 @@
     <row r="1066" ht="15" customHeight="1">
       <c r="A1066" t="inlineStr">
         <is>
-          <t>A 5174-2024</t>
+          <t>A 5156-2024</t>
         </is>
       </c>
       <c r="B1066" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C1066" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1066" t="inlineStr">
         <is>
@@ -63971,7 +63971,7 @@
         </is>
       </c>
       <c r="G1066" t="n">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
       <c r="H1066" t="n">
         <v>0</v>
@@ -64008,14 +64008,14 @@
     <row r="1067" ht="15" customHeight="1">
       <c r="A1067" t="inlineStr">
         <is>
-          <t>A 5156-2024</t>
+          <t>A 5189-2024</t>
         </is>
       </c>
       <c r="B1067" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C1067" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1067" t="inlineStr">
         <is>
@@ -64028,7 +64028,7 @@
         </is>
       </c>
       <c r="G1067" t="n">
-        <v>0.4</v>
+        <v>1.3</v>
       </c>
       <c r="H1067" t="n">
         <v>0</v>
@@ -64065,14 +64065,14 @@
     <row r="1068" ht="15" customHeight="1">
       <c r="A1068" t="inlineStr">
         <is>
-          <t>A 5189-2024</t>
+          <t>A 5174-2024</t>
         </is>
       </c>
       <c r="B1068" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C1068" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1068" t="inlineStr">
         <is>
@@ -64085,7 +64085,7 @@
         </is>
       </c>
       <c r="G1068" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="H1068" t="n">
         <v>0</v>
@@ -64129,7 +64129,7 @@
         <v>45330</v>
       </c>
       <c r="C1069" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1069" t="inlineStr">
         <is>
@@ -64186,7 +64186,7 @@
         <v>45330</v>
       </c>
       <c r="C1070" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1070" t="inlineStr">
         <is>
@@ -64243,7 +64243,7 @@
         <v>45331</v>
       </c>
       <c r="C1071" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1071" t="inlineStr">
         <is>
@@ -64300,7 +64300,7 @@
         <v>45331</v>
       </c>
       <c r="C1072" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1072" t="inlineStr">
         <is>
@@ -64357,7 +64357,7 @@
         <v>45334</v>
       </c>
       <c r="C1073" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1073" t="inlineStr">
         <is>
@@ -64414,7 +64414,7 @@
         <v>45334</v>
       </c>
       <c r="C1074" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1074" t="inlineStr">
         <is>
@@ -64471,7 +64471,7 @@
         <v>45337</v>
       </c>
       <c r="C1075" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1075" t="inlineStr">
         <is>
@@ -64521,14 +64521,14 @@
     <row r="1076" ht="15" customHeight="1">
       <c r="A1076" t="inlineStr">
         <is>
-          <t>A 6213-2024</t>
+          <t>A 6187-2024</t>
         </is>
       </c>
       <c r="B1076" s="1" t="n">
         <v>45337</v>
       </c>
       <c r="C1076" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1076" t="inlineStr">
         <is>
@@ -64541,7 +64541,7 @@
         </is>
       </c>
       <c r="G1076" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="H1076" t="n">
         <v>0</v>
@@ -64578,14 +64578,14 @@
     <row r="1077">
       <c r="A1077" t="inlineStr">
         <is>
-          <t>A 6187-2024</t>
+          <t>A 6213-2024</t>
         </is>
       </c>
       <c r="B1077" s="1" t="n">
         <v>45337</v>
       </c>
       <c r="C1077" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1077" t="inlineStr">
         <is>
@@ -64598,7 +64598,7 @@
         </is>
       </c>
       <c r="G1077" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="H1077" t="n">
         <v>0</v>

--- a/Översikt RÄTTVIK.xlsx
+++ b/Översikt RÄTTVIK.xlsx
@@ -569,7 +569,7 @@
         <v>43542</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         <v>43663</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -781,7 +781,7 @@
         <v>43619</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
         <v>44909</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>43740</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>44909</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>44874</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>45147</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
         <v>44237</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1461,7 +1461,7 @@
         <v>44624</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         <v>43634</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         <v>43663</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1736,7 +1736,7 @@
         <v>44148</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         <v>44435</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1910,7 +1910,7 @@
         <v>44799</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         <v>44909</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         <v>44909</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
         <v>45111</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>43700</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>44496</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2450,7 +2450,7 @@
         <v>45033</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
         <v>43440</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         <v>43493</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
         <v>43623</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2791,7 +2791,7 @@
         <v>43705</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
         <v>44088</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2961,7 +2961,7 @@
         <v>44361</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3046,7 +3046,7 @@
         <v>44391</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         <v>44414</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3226,7 +3226,7 @@
         <v>44470</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3316,7 +3316,7 @@
         <v>44496</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
         <v>44511</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3491,7 +3491,7 @@
         <v>44568</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
         <v>44728</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3679,7 +3679,7 @@
         <v>44855</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3769,7 +3769,7 @@
         <v>44894</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3859,7 +3859,7 @@
         <v>44918</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3949,7 +3949,7 @@
         <v>44986</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4034,7 +4034,7 @@
         <v>45077</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4119,7 +4119,7 @@
         <v>45194</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4204,7 +4204,7 @@
         <v>45194</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4289,7 +4289,7 @@
         <v>45231</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4374,7 +4374,7 @@
         <v>43333</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4431,7 +4431,7 @@
         <v>43348</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4488,7 +4488,7 @@
         <v>43356</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4545,7 +4545,7 @@
         <v>43361</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4602,7 +4602,7 @@
         <v>43362</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4659,7 +4659,7 @@
         <v>43362</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4716,7 +4716,7 @@
         <v>43362</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4773,7 +4773,7 @@
         <v>43362</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4830,7 +4830,7 @@
         <v>43367</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4887,7 +4887,7 @@
         <v>43369</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4944,7 +4944,7 @@
         <v>43373</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5001,7 +5001,7 @@
         <v>43378</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5058,7 +5058,7 @@
         <v>43381</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5115,7 +5115,7 @@
         <v>43381</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5172,7 +5172,7 @@
         <v>43388</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5229,7 +5229,7 @@
         <v>43388</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5291,7 +5291,7 @@
         <v>43388</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5348,7 +5348,7 @@
         <v>43391</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5405,7 +5405,7 @@
         <v>43398</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
         <v>43399</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5519,7 +5519,7 @@
         <v>43401</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5576,7 +5576,7 @@
         <v>43405</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5633,7 +5633,7 @@
         <v>43405</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5690,7 +5690,7 @@
         <v>43410</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5747,7 +5747,7 @@
         <v>43410</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5804,7 +5804,7 @@
         <v>43411</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5861,7 +5861,7 @@
         <v>43412</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5918,7 +5918,7 @@
         <v>43416</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5975,7 +5975,7 @@
         <v>43416</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6032,7 +6032,7 @@
         <v>43416</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6089,7 +6089,7 @@
         <v>43419</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6146,7 +6146,7 @@
         <v>43419</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6203,7 +6203,7 @@
         <v>43423</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6265,7 +6265,7 @@
         <v>43423</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         <v>43423</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6389,7 +6389,7 @@
         <v>43424</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6451,7 +6451,7 @@
         <v>43425</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6508,7 +6508,7 @@
         <v>43427</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6570,7 +6570,7 @@
         <v>43428</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6627,7 +6627,7 @@
         <v>43428</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6684,7 +6684,7 @@
         <v>43430</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6741,7 +6741,7 @@
         <v>43430</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6798,7 +6798,7 @@
         <v>43430</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6855,7 +6855,7 @@
         <v>43430</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6912,7 +6912,7 @@
         <v>43431</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6974,7 +6974,7 @@
         <v>43432</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7031,7 +7031,7 @@
         <v>43432</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7088,7 +7088,7 @@
         <v>43434</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7145,7 +7145,7 @@
         <v>43434</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7202,7 +7202,7 @@
         <v>43438</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7259,7 +7259,7 @@
         <v>43441</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7316,7 +7316,7 @@
         <v>43447</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7373,7 +7373,7 @@
         <v>43448</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7430,7 +7430,7 @@
         <v>43451</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7487,7 +7487,7 @@
         <v>43451</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7544,7 +7544,7 @@
         <v>43451</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7601,7 +7601,7 @@
         <v>43452</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7658,7 +7658,7 @@
         <v>43454</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7720,7 +7720,7 @@
         <v>43454</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7782,7 +7782,7 @@
         <v>43454</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7844,7 +7844,7 @@
         <v>43455</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7901,7 +7901,7 @@
         <v>43461</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7958,7 +7958,7 @@
         <v>43471</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8015,7 +8015,7 @@
         <v>43472</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8072,7 +8072,7 @@
         <v>43472</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8134,7 +8134,7 @@
         <v>43473</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8191,7 +8191,7 @@
         <v>43475</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8248,7 +8248,7 @@
         <v>43481</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8305,7 +8305,7 @@
         <v>43490</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8362,7 +8362,7 @@
         <v>43495</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8419,7 +8419,7 @@
         <v>43499</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8476,7 +8476,7 @@
         <v>43500</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8538,7 +8538,7 @@
         <v>43511</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8595,7 +8595,7 @@
         <v>43511</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8652,7 +8652,7 @@
         <v>43514</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8709,7 +8709,7 @@
         <v>43517</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8766,7 +8766,7 @@
         <v>43524</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8823,7 +8823,7 @@
         <v>43546</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8880,7 +8880,7 @@
         <v>43553</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8942,7 +8942,7 @@
         <v>43553</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8999,7 +8999,7 @@
         <v>43554</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9056,7 +9056,7 @@
         <v>43556</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9113,7 +9113,7 @@
         <v>43559</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9175,7 +9175,7 @@
         <v>43564</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9232,7 +9232,7 @@
         <v>43566</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9289,7 +9289,7 @@
         <v>43570</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9351,7 +9351,7 @@
         <v>43570</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9413,7 +9413,7 @@
         <v>43570</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9470,7 +9470,7 @@
         <v>43580</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9527,7 +9527,7 @@
         <v>43584</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9584,7 +9584,7 @@
         <v>43585</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9641,7 +9641,7 @@
         <v>43587</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9698,7 +9698,7 @@
         <v>43592</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9755,7 +9755,7 @@
         <v>43592</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9812,7 +9812,7 @@
         <v>43592</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9869,7 +9869,7 @@
         <v>43599</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9926,7 +9926,7 @@
         <v>43609</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9983,7 +9983,7 @@
         <v>43612</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10040,7 +10040,7 @@
         <v>43612</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10097,7 +10097,7 @@
         <v>43612</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10154,7 +10154,7 @@
         <v>43612</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10211,7 +10211,7 @@
         <v>43616</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10268,7 +10268,7 @@
         <v>43619</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10330,7 +10330,7 @@
         <v>43621</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10387,7 +10387,7 @@
         <v>43623</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10444,7 +10444,7 @@
         <v>43628</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10506,7 +10506,7 @@
         <v>43628</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10568,7 +10568,7 @@
         <v>43629</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10625,7 +10625,7 @@
         <v>43630</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10682,7 +10682,7 @@
         <v>43633</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10739,7 +10739,7 @@
         <v>43633</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10796,7 +10796,7 @@
         <v>43641</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10853,7 +10853,7 @@
         <v>43643</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10915,7 +10915,7 @@
         <v>43643</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10977,7 +10977,7 @@
         <v>43647</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11039,7 +11039,7 @@
         <v>43651</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11096,7 +11096,7 @@
         <v>43651</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11153,7 +11153,7 @@
         <v>43656</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11210,7 +11210,7 @@
         <v>43657</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11267,7 +11267,7 @@
         <v>43662</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11324,7 +11324,7 @@
         <v>43662</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11381,7 +11381,7 @@
         <v>43663</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11463,7 +11463,7 @@
         <v>43663</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11525,7 +11525,7 @@
         <v>43663</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11587,7 +11587,7 @@
         <v>43663</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11649,7 +11649,7 @@
         <v>43682</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11706,7 +11706,7 @@
         <v>43686</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11768,7 +11768,7 @@
         <v>43686</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11825,7 +11825,7 @@
         <v>43689</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11887,7 +11887,7 @@
         <v>43690</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11944,7 +11944,7 @@
         <v>43697</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12001,7 +12001,7 @@
         <v>43700</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12058,7 +12058,7 @@
         <v>43705</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12115,7 +12115,7 @@
         <v>43711</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12177,7 +12177,7 @@
         <v>43712</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12234,7 +12234,7 @@
         <v>43713</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12291,7 +12291,7 @@
         <v>43714</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12348,7 +12348,7 @@
         <v>43714</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12405,7 +12405,7 @@
         <v>43717</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12462,7 +12462,7 @@
         <v>43718</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12519,7 +12519,7 @@
         <v>43720</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12576,7 +12576,7 @@
         <v>43724</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12633,7 +12633,7 @@
         <v>43726</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12690,7 +12690,7 @@
         <v>43727</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12747,7 +12747,7 @@
         <v>43727</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12804,7 +12804,7 @@
         <v>43727</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12861,7 +12861,7 @@
         <v>43732</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12918,7 +12918,7 @@
         <v>43734</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12980,7 +12980,7 @@
         <v>43734</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13037,7 +13037,7 @@
         <v>43734</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13094,7 +13094,7 @@
         <v>43735</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13156,7 +13156,7 @@
         <v>43735</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13213,7 +13213,7 @@
         <v>43740</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13275,7 +13275,7 @@
         <v>43740</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13332,7 +13332,7 @@
         <v>43740</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13389,7 +13389,7 @@
         <v>43740</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13446,7 +13446,7 @@
         <v>43742</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13508,7 +13508,7 @@
         <v>43742</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13565,7 +13565,7 @@
         <v>43747</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13622,7 +13622,7 @@
         <v>43758</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13679,7 +13679,7 @@
         <v>43761</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13736,7 +13736,7 @@
         <v>43766</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13793,7 +13793,7 @@
         <v>43767</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13855,7 +13855,7 @@
         <v>43769</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13917,7 +13917,7 @@
         <v>43770</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13974,7 +13974,7 @@
         <v>43770</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14031,7 +14031,7 @@
         <v>43773</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14088,7 +14088,7 @@
         <v>43775</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14145,7 +14145,7 @@
         <v>43776</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14202,7 +14202,7 @@
         <v>43776</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14259,7 +14259,7 @@
         <v>43776</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14316,7 +14316,7 @@
         <v>43776</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14373,7 +14373,7 @@
         <v>43780</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14435,7 +14435,7 @@
         <v>43780</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14492,7 +14492,7 @@
         <v>43780</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14549,7 +14549,7 @@
         <v>43780</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14606,7 +14606,7 @@
         <v>43783</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14668,7 +14668,7 @@
         <v>43784</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14725,7 +14725,7 @@
         <v>43786</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14782,7 +14782,7 @@
         <v>43797</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14839,7 +14839,7 @@
         <v>43804</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14901,7 +14901,7 @@
         <v>43805</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14958,7 +14958,7 @@
         <v>43805</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15015,7 +15015,7 @@
         <v>43812</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15072,7 +15072,7 @@
         <v>43812</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15129,7 +15129,7 @@
         <v>43815</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15186,7 +15186,7 @@
         <v>43815</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15243,7 +15243,7 @@
         <v>43829</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15300,7 +15300,7 @@
         <v>43833</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15357,7 +15357,7 @@
         <v>43837</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15414,7 +15414,7 @@
         <v>43839</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15471,7 +15471,7 @@
         <v>43840</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15528,7 +15528,7 @@
         <v>43843</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15585,7 +15585,7 @@
         <v>43845</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15647,7 +15647,7 @@
         <v>43850</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15704,7 +15704,7 @@
         <v>43854</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15766,7 +15766,7 @@
         <v>43857</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15823,7 +15823,7 @@
         <v>43857</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15885,7 +15885,7 @@
         <v>43857</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15942,7 +15942,7 @@
         <v>43864</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15999,7 +15999,7 @@
         <v>43864</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16061,7 +16061,7 @@
         <v>43864</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16123,7 +16123,7 @@
         <v>43867</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16185,7 +16185,7 @@
         <v>43871</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16242,7 +16242,7 @@
         <v>43872</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16304,7 +16304,7 @@
         <v>43873</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16361,7 +16361,7 @@
         <v>43873</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16418,7 +16418,7 @@
         <v>43873</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16475,7 +16475,7 @@
         <v>43874</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16532,7 +16532,7 @@
         <v>43878</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16589,7 +16589,7 @@
         <v>43879</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16651,7 +16651,7 @@
         <v>43880</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16708,7 +16708,7 @@
         <v>43894</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16765,7 +16765,7 @@
         <v>43894</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16822,7 +16822,7 @@
         <v>43902</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16879,7 +16879,7 @@
         <v>43917</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16936,7 +16936,7 @@
         <v>43917</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16998,7 +16998,7 @@
         <v>43920</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17060,7 +17060,7 @@
         <v>43920</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17122,7 +17122,7 @@
         <v>43921</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17184,7 +17184,7 @@
         <v>43922</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17246,7 +17246,7 @@
         <v>43922</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17308,7 +17308,7 @@
         <v>43924</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17365,7 +17365,7 @@
         <v>43924</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17422,7 +17422,7 @@
         <v>43927</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17479,7 +17479,7 @@
         <v>43927</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17536,7 +17536,7 @@
         <v>43928</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17593,7 +17593,7 @@
         <v>43928</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17650,7 +17650,7 @@
         <v>43930</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17712,7 +17712,7 @@
         <v>43933</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17774,7 +17774,7 @@
         <v>43933</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17836,7 +17836,7 @@
         <v>43935</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17893,7 +17893,7 @@
         <v>43937</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17955,7 +17955,7 @@
         <v>43941</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18012,7 +18012,7 @@
         <v>43941</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18069,7 +18069,7 @@
         <v>43948</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18126,7 +18126,7 @@
         <v>43949</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18188,7 +18188,7 @@
         <v>43949</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18250,7 +18250,7 @@
         <v>43949</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18312,7 +18312,7 @@
         <v>43949</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18374,7 +18374,7 @@
         <v>43950</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18431,7 +18431,7 @@
         <v>43951</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18493,7 +18493,7 @@
         <v>43959</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18555,7 +18555,7 @@
         <v>43959</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18617,7 +18617,7 @@
         <v>43959</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18679,7 +18679,7 @@
         <v>43959</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18736,7 +18736,7 @@
         <v>43969</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18798,7 +18798,7 @@
         <v>43970</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18855,7 +18855,7 @@
         <v>43973</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18912,7 +18912,7 @@
         <v>43985</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18969,7 +18969,7 @@
         <v>43990</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19026,7 +19026,7 @@
         <v>43991</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19088,7 +19088,7 @@
         <v>43991</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19150,7 +19150,7 @@
         <v>43991</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19212,7 +19212,7 @@
         <v>43991</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19274,7 +19274,7 @@
         <v>43991</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19336,7 +19336,7 @@
         <v>44005</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19398,7 +19398,7 @@
         <v>44033</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19455,7 +19455,7 @@
         <v>44039</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19512,7 +19512,7 @@
         <v>44048</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19569,7 +19569,7 @@
         <v>44049</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19626,7 +19626,7 @@
         <v>44053</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19683,7 +19683,7 @@
         <v>44053</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19740,7 +19740,7 @@
         <v>44053</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19797,7 +19797,7 @@
         <v>44054</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19859,7 +19859,7 @@
         <v>44054</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19916,7 +19916,7 @@
         <v>44054</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19973,7 +19973,7 @@
         <v>44055</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20035,7 +20035,7 @@
         <v>44055</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20097,7 +20097,7 @@
         <v>44074</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20154,7 +20154,7 @@
         <v>44074</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20211,7 +20211,7 @@
         <v>44077</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20268,7 +20268,7 @@
         <v>44078</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20330,7 +20330,7 @@
         <v>44078</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20392,7 +20392,7 @@
         <v>44082</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20449,7 +20449,7 @@
         <v>44084</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20511,7 +20511,7 @@
         <v>44089</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20568,7 +20568,7 @@
         <v>44091</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20625,7 +20625,7 @@
         <v>44095</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20682,7 +20682,7 @@
         <v>44097</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20739,7 +20739,7 @@
         <v>44102</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20796,7 +20796,7 @@
         <v>44104</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20853,7 +20853,7 @@
         <v>44105</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20910,7 +20910,7 @@
         <v>44109</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20967,7 +20967,7 @@
         <v>44109</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21029,7 +21029,7 @@
         <v>44110</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21086,7 +21086,7 @@
         <v>44117</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21148,7 +21148,7 @@
         <v>44126</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21210,7 +21210,7 @@
         <v>44126</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21272,7 +21272,7 @@
         <v>44126</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21334,7 +21334,7 @@
         <v>44126</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21396,7 +21396,7 @@
         <v>44126</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21458,7 +21458,7 @@
         <v>44130</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21515,7 +21515,7 @@
         <v>44130</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21572,7 +21572,7 @@
         <v>44130</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21629,7 +21629,7 @@
         <v>44130</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21686,7 +21686,7 @@
         <v>44131</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21743,7 +21743,7 @@
         <v>44133</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21805,7 +21805,7 @@
         <v>44137</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21862,7 +21862,7 @@
         <v>44139</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21919,7 +21919,7 @@
         <v>44139</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21976,7 +21976,7 @@
         <v>44141</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22033,7 +22033,7 @@
         <v>44145</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22090,7 +22090,7 @@
         <v>44145</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22147,7 +22147,7 @@
         <v>44151</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22204,7 +22204,7 @@
         <v>44151</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22261,7 +22261,7 @@
         <v>44153</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22318,7 +22318,7 @@
         <v>44159</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22375,7 +22375,7 @@
         <v>44159</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22432,7 +22432,7 @@
         <v>44159</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22489,7 +22489,7 @@
         <v>44159</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22546,7 +22546,7 @@
         <v>44160</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22603,7 +22603,7 @@
         <v>44160</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22660,7 +22660,7 @@
         <v>44160</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22717,7 +22717,7 @@
         <v>44161</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22774,7 +22774,7 @@
         <v>44162</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22831,7 +22831,7 @@
         <v>44173</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22888,7 +22888,7 @@
         <v>44175</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22945,7 +22945,7 @@
         <v>44175</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23002,7 +23002,7 @@
         <v>44179</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23059,7 +23059,7 @@
         <v>44179</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23116,7 +23116,7 @@
         <v>44180</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23173,7 +23173,7 @@
         <v>44185</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23230,7 +23230,7 @@
         <v>44186</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23287,7 +23287,7 @@
         <v>44186</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23344,7 +23344,7 @@
         <v>44194</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23401,7 +23401,7 @@
         <v>44195</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23458,7 +23458,7 @@
         <v>44214</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23515,7 +23515,7 @@
         <v>44214</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23572,7 +23572,7 @@
         <v>44217</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23629,7 +23629,7 @@
         <v>44217</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23686,7 +23686,7 @@
         <v>44228</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23743,7 +23743,7 @@
         <v>44228</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23800,7 +23800,7 @@
         <v>44238</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23857,7 +23857,7 @@
         <v>44242</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23914,7 +23914,7 @@
         <v>44242</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23971,7 +23971,7 @@
         <v>44271</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24028,7 +24028,7 @@
         <v>44273</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24085,7 +24085,7 @@
         <v>44280</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24142,7 +24142,7 @@
         <v>44281</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24199,7 +24199,7 @@
         <v>44284</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24256,7 +24256,7 @@
         <v>44284</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24313,7 +24313,7 @@
         <v>44300</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24370,7 +24370,7 @@
         <v>44300</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24427,7 +24427,7 @@
         <v>44300</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24484,7 +24484,7 @@
         <v>44305</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24541,7 +24541,7 @@
         <v>44306</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24598,7 +24598,7 @@
         <v>44307</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24655,7 +24655,7 @@
         <v>44322</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24717,7 +24717,7 @@
         <v>44326</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24774,7 +24774,7 @@
         <v>44326</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24831,7 +24831,7 @@
         <v>44326</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24888,7 +24888,7 @@
         <v>44326</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24945,7 +24945,7 @@
         <v>44330</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25002,7 +25002,7 @@
         <v>44335</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25059,7 +25059,7 @@
         <v>44336</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25121,7 +25121,7 @@
         <v>44340</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25178,7 +25178,7 @@
         <v>44342</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25240,7 +25240,7 @@
         <v>44347</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25297,7 +25297,7 @@
         <v>44347</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25354,7 +25354,7 @@
         <v>44348</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25411,7 +25411,7 @@
         <v>44348</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25468,7 +25468,7 @@
         <v>44349</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25525,7 +25525,7 @@
         <v>44349</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25582,7 +25582,7 @@
         <v>44350</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25639,7 +25639,7 @@
         <v>44351</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25696,7 +25696,7 @@
         <v>44351</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25753,7 +25753,7 @@
         <v>44363</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25810,7 +25810,7 @@
         <v>44377</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25872,7 +25872,7 @@
         <v>44377</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25929,7 +25929,7 @@
         <v>44377</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25986,7 +25986,7 @@
         <v>44377</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26043,7 +26043,7 @@
         <v>44377</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26105,7 +26105,7 @@
         <v>44386</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26167,7 +26167,7 @@
         <v>44386</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26229,7 +26229,7 @@
         <v>44391</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26291,7 +26291,7 @@
         <v>44391</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26353,7 +26353,7 @@
         <v>44399</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26410,7 +26410,7 @@
         <v>44400</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26467,7 +26467,7 @@
         <v>44403</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26524,7 +26524,7 @@
         <v>44408</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26586,7 +26586,7 @@
         <v>44409</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26648,7 +26648,7 @@
         <v>44414</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26710,7 +26710,7 @@
         <v>44414</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26772,7 +26772,7 @@
         <v>44414</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26834,7 +26834,7 @@
         <v>44418</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26891,7 +26891,7 @@
         <v>44420</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26948,7 +26948,7 @@
         <v>44421</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27005,7 +27005,7 @@
         <v>44421</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27067,7 +27067,7 @@
         <v>44424</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27129,7 +27129,7 @@
         <v>44424</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27186,7 +27186,7 @@
         <v>44432</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27248,7 +27248,7 @@
         <v>44435</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27305,7 +27305,7 @@
         <v>44441</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27362,7 +27362,7 @@
         <v>44441</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27424,7 +27424,7 @@
         <v>44449</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27486,7 +27486,7 @@
         <v>44451</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27548,7 +27548,7 @@
         <v>44451</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27610,7 +27610,7 @@
         <v>44454</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27667,7 +27667,7 @@
         <v>44459</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27729,7 +27729,7 @@
         <v>44459</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27791,7 +27791,7 @@
         <v>44459</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27853,7 +27853,7 @@
         <v>44459</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27915,7 +27915,7 @@
         <v>44459</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27977,7 +27977,7 @@
         <v>44459</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28039,7 +28039,7 @@
         <v>44460</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28096,7 +28096,7 @@
         <v>44460</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28153,7 +28153,7 @@
         <v>44461</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28210,7 +28210,7 @@
         <v>44463</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28272,7 +28272,7 @@
         <v>44467</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28334,7 +28334,7 @@
         <v>44469</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28396,7 +28396,7 @@
         <v>44469</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28458,7 +28458,7 @@
         <v>44469</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28520,7 +28520,7 @@
         <v>44469</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28582,7 +28582,7 @@
         <v>44470</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28644,7 +28644,7 @@
         <v>44470</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28701,7 +28701,7 @@
         <v>44470</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28763,7 +28763,7 @@
         <v>44473</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28820,7 +28820,7 @@
         <v>44474</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28877,7 +28877,7 @@
         <v>44475</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28934,7 +28934,7 @@
         <v>44475</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28991,7 +28991,7 @@
         <v>44477</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29048,7 +29048,7 @@
         <v>44477</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29105,7 +29105,7 @@
         <v>44477</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29162,7 +29162,7 @@
         <v>44479</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29224,7 +29224,7 @@
         <v>44484</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29286,7 +29286,7 @@
         <v>44484</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29348,7 +29348,7 @@
         <v>44488</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29405,7 +29405,7 @@
         <v>44489</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29467,7 +29467,7 @@
         <v>44495</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29529,7 +29529,7 @@
         <v>44495</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29591,7 +29591,7 @@
         <v>44495</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29653,7 +29653,7 @@
         <v>44495</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29715,7 +29715,7 @@
         <v>44495</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29777,7 +29777,7 @@
         <v>44495</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29839,7 +29839,7 @@
         <v>44495</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29901,7 +29901,7 @@
         <v>44496</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29958,7 +29958,7 @@
         <v>44498</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30015,7 +30015,7 @@
         <v>44509</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30077,7 +30077,7 @@
         <v>44511</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30134,7 +30134,7 @@
         <v>44512</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30191,7 +30191,7 @@
         <v>44515</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30248,7 +30248,7 @@
         <v>44517</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30305,7 +30305,7 @@
         <v>44519</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30362,7 +30362,7 @@
         <v>44519</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30419,7 +30419,7 @@
         <v>44523</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30481,7 +30481,7 @@
         <v>44524</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30538,7 +30538,7 @@
         <v>44529</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30600,7 +30600,7 @@
         <v>44529</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30657,7 +30657,7 @@
         <v>44529</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30714,7 +30714,7 @@
         <v>44529</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30771,7 +30771,7 @@
         <v>44529</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30828,7 +30828,7 @@
         <v>44533</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30885,7 +30885,7 @@
         <v>44536</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30942,7 +30942,7 @@
         <v>44537</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30999,7 +30999,7 @@
         <v>44537</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31056,7 +31056,7 @@
         <v>44537</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31113,7 +31113,7 @@
         <v>44541</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31170,7 +31170,7 @@
         <v>44544</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31227,7 +31227,7 @@
         <v>44544</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31284,7 +31284,7 @@
         <v>44545</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31341,7 +31341,7 @@
         <v>44551</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31398,7 +31398,7 @@
         <v>44551</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31455,7 +31455,7 @@
         <v>44552</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31512,7 +31512,7 @@
         <v>44556</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31569,7 +31569,7 @@
         <v>44559</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31626,7 +31626,7 @@
         <v>44562</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31683,7 +31683,7 @@
         <v>44565</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31745,7 +31745,7 @@
         <v>44565</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31807,7 +31807,7 @@
         <v>44565</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31869,7 +31869,7 @@
         <v>44571</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31926,7 +31926,7 @@
         <v>44571</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31983,7 +31983,7 @@
         <v>44572</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32040,7 +32040,7 @@
         <v>44573</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32097,7 +32097,7 @@
         <v>44578</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32154,7 +32154,7 @@
         <v>44579</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32211,7 +32211,7 @@
         <v>44600</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32268,7 +32268,7 @@
         <v>44602</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32325,7 +32325,7 @@
         <v>44610</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32387,7 +32387,7 @@
         <v>44620</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32444,7 +32444,7 @@
         <v>44621</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32501,7 +32501,7 @@
         <v>44627</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32558,7 +32558,7 @@
         <v>44637</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32615,7 +32615,7 @@
         <v>44638</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32672,7 +32672,7 @@
         <v>44638</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32729,7 +32729,7 @@
         <v>44638</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32786,7 +32786,7 @@
         <v>44641</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32843,7 +32843,7 @@
         <v>44644</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32900,7 +32900,7 @@
         <v>44651</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32957,7 +32957,7 @@
         <v>44651</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33014,7 +33014,7 @@
         <v>44655</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33071,7 +33071,7 @@
         <v>44679</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33128,7 +33128,7 @@
         <v>44679</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33185,7 +33185,7 @@
         <v>44679</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33242,7 +33242,7 @@
         <v>44680</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33299,7 +33299,7 @@
         <v>44683</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33356,7 +33356,7 @@
         <v>44684</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33413,7 +33413,7 @@
         <v>44686</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33470,7 +33470,7 @@
         <v>44692</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33527,7 +33527,7 @@
         <v>44700</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33584,7 +33584,7 @@
         <v>44701</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33641,7 +33641,7 @@
         <v>44715</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33698,7 +33698,7 @@
         <v>44719</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33755,7 +33755,7 @@
         <v>44722</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33812,7 +33812,7 @@
         <v>44727</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33869,7 +33869,7 @@
         <v>44727</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33926,7 +33926,7 @@
         <v>44728</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33988,7 +33988,7 @@
         <v>44728</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34050,7 +34050,7 @@
         <v>44729</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34112,7 +34112,7 @@
         <v>44732</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34169,7 +34169,7 @@
         <v>44733</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34226,7 +34226,7 @@
         <v>44736</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34283,7 +34283,7 @@
         <v>44740</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34340,7 +34340,7 @@
         <v>44742</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34397,7 +34397,7 @@
         <v>44743</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34459,7 +34459,7 @@
         <v>44746</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34516,7 +34516,7 @@
         <v>44746</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34573,7 +34573,7 @@
         <v>44747</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34635,7 +34635,7 @@
         <v>44747</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34692,7 +34692,7 @@
         <v>44747</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34754,7 +34754,7 @@
         <v>44747</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34811,7 +34811,7 @@
         <v>44748</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34868,7 +34868,7 @@
         <v>44749</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34930,7 +34930,7 @@
         <v>44749</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34992,7 +34992,7 @@
         <v>44749</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35049,7 +35049,7 @@
         <v>44762</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35106,7 +35106,7 @@
         <v>44762</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35163,7 +35163,7 @@
         <v>44762</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35220,7 +35220,7 @@
         <v>44763</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35277,7 +35277,7 @@
         <v>44763</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35339,7 +35339,7 @@
         <v>44774</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35401,7 +35401,7 @@
         <v>44775</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35458,7 +35458,7 @@
         <v>44775</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35515,7 +35515,7 @@
         <v>44775</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35572,7 +35572,7 @@
         <v>44783</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35629,7 +35629,7 @@
         <v>44785</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35691,7 +35691,7 @@
         <v>44789</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35748,7 +35748,7 @@
         <v>44789</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35810,7 +35810,7 @@
         <v>44790</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35867,7 +35867,7 @@
         <v>44790</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35924,7 +35924,7 @@
         <v>44791</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35981,7 +35981,7 @@
         <v>44791</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36038,7 +36038,7 @@
         <v>44792</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36100,7 +36100,7 @@
         <v>44792</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36162,7 +36162,7 @@
         <v>44792</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36224,7 +36224,7 @@
         <v>44792</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36286,7 +36286,7 @@
         <v>44792</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36348,7 +36348,7 @@
         <v>44795</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36405,7 +36405,7 @@
         <v>44795</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36462,7 +36462,7 @@
         <v>44795</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36519,7 +36519,7 @@
         <v>44796</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36576,7 +36576,7 @@
         <v>44797</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36633,7 +36633,7 @@
         <v>44798</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36690,7 +36690,7 @@
         <v>44798</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36747,7 +36747,7 @@
         <v>44799</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36809,7 +36809,7 @@
         <v>44799</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36871,7 +36871,7 @@
         <v>44799</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36933,7 +36933,7 @@
         <v>44799</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36995,7 +36995,7 @@
         <v>44803</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37052,7 +37052,7 @@
         <v>44803</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37109,7 +37109,7 @@
         <v>44804</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37166,7 +37166,7 @@
         <v>44804</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37223,7 +37223,7 @@
         <v>44806</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37305,7 +37305,7 @@
         <v>44806</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37362,7 +37362,7 @@
         <v>44806</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37419,7 +37419,7 @@
         <v>44806</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37476,7 +37476,7 @@
         <v>44806</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37533,7 +37533,7 @@
         <v>44806</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37590,7 +37590,7 @@
         <v>44807</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37647,7 +37647,7 @@
         <v>44813</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37709,7 +37709,7 @@
         <v>44817</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37771,7 +37771,7 @@
         <v>44817</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37833,7 +37833,7 @@
         <v>44818</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37890,7 +37890,7 @@
         <v>44818</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37947,7 +37947,7 @@
         <v>44818</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38004,7 +38004,7 @@
         <v>44818</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38061,7 +38061,7 @@
         <v>44818</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38118,7 +38118,7 @@
         <v>44819</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38175,7 +38175,7 @@
         <v>44819</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38237,7 +38237,7 @@
         <v>44819</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38294,7 +38294,7 @@
         <v>44820</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38356,7 +38356,7 @@
         <v>44823</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38413,7 +38413,7 @@
         <v>44824</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38470,7 +38470,7 @@
         <v>44826</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38527,7 +38527,7 @@
         <v>44827</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38589,7 +38589,7 @@
         <v>44833</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38646,7 +38646,7 @@
         <v>44834</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38703,7 +38703,7 @@
         <v>44834</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38760,7 +38760,7 @@
         <v>44837</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38817,7 +38817,7 @@
         <v>44838</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38879,7 +38879,7 @@
         <v>44839</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38941,7 +38941,7 @@
         <v>44839</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38998,7 +38998,7 @@
         <v>44839</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39060,7 +39060,7 @@
         <v>44840</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39117,7 +39117,7 @@
         <v>44841</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39174,7 +39174,7 @@
         <v>44841</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39236,7 +39236,7 @@
         <v>44841</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39293,7 +39293,7 @@
         <v>44841</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39350,7 +39350,7 @@
         <v>44845</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39412,7 +39412,7 @@
         <v>44845</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39474,7 +39474,7 @@
         <v>44847</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39531,7 +39531,7 @@
         <v>44851</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39593,7 +39593,7 @@
         <v>44851</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39655,7 +39655,7 @@
         <v>44851</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39717,7 +39717,7 @@
         <v>44851</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39779,7 +39779,7 @@
         <v>44855</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39841,7 +39841,7 @@
         <v>44860</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39903,7 +39903,7 @@
         <v>44862</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39965,7 +39965,7 @@
         <v>44862</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40027,7 +40027,7 @@
         <v>44866</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40089,7 +40089,7 @@
         <v>44866</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40151,7 +40151,7 @@
         <v>44866</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40213,7 +40213,7 @@
         <v>44866</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40270,7 +40270,7 @@
         <v>44868</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40327,7 +40327,7 @@
         <v>44872</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40384,7 +40384,7 @@
         <v>44873</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40441,7 +40441,7 @@
         <v>44873</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40498,7 +40498,7 @@
         <v>44873</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40555,7 +40555,7 @@
         <v>44874</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40612,7 +40612,7 @@
         <v>44874</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40669,7 +40669,7 @@
         <v>44875</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40726,7 +40726,7 @@
         <v>44875</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40783,7 +40783,7 @@
         <v>44879</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40845,7 +40845,7 @@
         <v>44882</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40902,7 +40902,7 @@
         <v>44883</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40964,7 +40964,7 @@
         <v>44883</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41026,7 +41026,7 @@
         <v>44887</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41083,7 +41083,7 @@
         <v>44889</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41140,7 +41140,7 @@
         <v>44890</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41197,7 +41197,7 @@
         <v>44891</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41254,7 +41254,7 @@
         <v>44893</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41311,7 +41311,7 @@
         <v>44897</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41368,7 +41368,7 @@
         <v>44903</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41425,7 +41425,7 @@
         <v>44907</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41487,7 +41487,7 @@
         <v>44907</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41544,7 +41544,7 @@
         <v>44909</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41606,7 +41606,7 @@
         <v>44909</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41688,7 +41688,7 @@
         <v>44909</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41745,7 +41745,7 @@
         <v>44909</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41802,7 +41802,7 @@
         <v>44910</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41859,7 +41859,7 @@
         <v>44911</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41916,7 +41916,7 @@
         <v>44911</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41973,7 +41973,7 @@
         <v>44911</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42030,7 +42030,7 @@
         <v>44911</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42087,7 +42087,7 @@
         <v>44914</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42144,7 +42144,7 @@
         <v>44914</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42201,7 +42201,7 @@
         <v>44914</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42258,7 +42258,7 @@
         <v>44916</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42315,7 +42315,7 @@
         <v>44916</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42372,7 +42372,7 @@
         <v>44922</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42429,7 +42429,7 @@
         <v>44928</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42486,7 +42486,7 @@
         <v>44929</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42543,7 +42543,7 @@
         <v>44929</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42600,7 +42600,7 @@
         <v>44930</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42657,7 +42657,7 @@
         <v>44930</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42714,7 +42714,7 @@
         <v>44930</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42771,7 +42771,7 @@
         <v>44930</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42828,7 +42828,7 @@
         <v>44931</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42890,7 +42890,7 @@
         <v>44939</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42947,7 +42947,7 @@
         <v>44939</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43004,7 +43004,7 @@
         <v>44944</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43061,7 +43061,7 @@
         <v>44944</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43118,7 +43118,7 @@
         <v>44945</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43175,7 +43175,7 @@
         <v>44949</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43232,7 +43232,7 @@
         <v>44950</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43289,7 +43289,7 @@
         <v>44950</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43346,7 +43346,7 @@
         <v>44953</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43403,7 +43403,7 @@
         <v>44956</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43460,7 +43460,7 @@
         <v>44960</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43517,7 +43517,7 @@
         <v>44964</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43574,7 +43574,7 @@
         <v>44964</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43631,7 +43631,7 @@
         <v>44964</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43688,7 +43688,7 @@
         <v>44964</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43745,7 +43745,7 @@
         <v>44964</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43802,7 +43802,7 @@
         <v>44964</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43859,7 +43859,7 @@
         <v>44964</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43916,7 +43916,7 @@
         <v>44966</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43973,7 +43973,7 @@
         <v>44967</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44030,7 +44030,7 @@
         <v>44967</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44087,7 +44087,7 @@
         <v>44967</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44144,7 +44144,7 @@
         <v>44967</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44201,7 +44201,7 @@
         <v>44967</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44258,7 +44258,7 @@
         <v>44970</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44315,7 +44315,7 @@
         <v>44970</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44372,7 +44372,7 @@
         <v>44973</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44429,7 +44429,7 @@
         <v>44977</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44486,7 +44486,7 @@
         <v>44977</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44543,7 +44543,7 @@
         <v>44982</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44600,7 +44600,7 @@
         <v>44991</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -44657,7 +44657,7 @@
         <v>44997</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44714,7 +44714,7 @@
         <v>45002</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44771,7 +44771,7 @@
         <v>45002</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44828,7 +44828,7 @@
         <v>45002</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44885,7 +44885,7 @@
         <v>45019</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44942,7 +44942,7 @@
         <v>45019</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44999,7 +44999,7 @@
         <v>45019</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45056,7 +45056,7 @@
         <v>45021</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45113,7 +45113,7 @@
         <v>45027</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45170,7 +45170,7 @@
         <v>45033</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45227,7 +45227,7 @@
         <v>45040</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45289,7 +45289,7 @@
         <v>45042</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45346,7 +45346,7 @@
         <v>45058</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45403,7 +45403,7 @@
         <v>45062</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45465,7 +45465,7 @@
         <v>45063</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45522,7 +45522,7 @@
         <v>45070</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45579,7 +45579,7 @@
         <v>45071</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45636,7 +45636,7 @@
         <v>45071</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45693,7 +45693,7 @@
         <v>45071</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45750,7 +45750,7 @@
         <v>45071</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45807,7 +45807,7 @@
         <v>45071</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45864,7 +45864,7 @@
         <v>45071</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45921,7 +45921,7 @@
         <v>45072</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -45978,7 +45978,7 @@
         <v>45072</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46035,7 +46035,7 @@
         <v>45072</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46097,7 +46097,7 @@
         <v>45075</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46154,7 +46154,7 @@
         <v>45075</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46211,7 +46211,7 @@
         <v>45077</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46268,7 +46268,7 @@
         <v>45079</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46325,7 +46325,7 @@
         <v>45084</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46382,7 +46382,7 @@
         <v>45085</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46439,7 +46439,7 @@
         <v>45085</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46496,7 +46496,7 @@
         <v>45090</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46553,7 +46553,7 @@
         <v>45090</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46610,7 +46610,7 @@
         <v>45090</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46667,7 +46667,7 @@
         <v>45092</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46729,7 +46729,7 @@
         <v>45092</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46786,7 +46786,7 @@
         <v>45093</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46848,7 +46848,7 @@
         <v>45093</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46910,7 +46910,7 @@
         <v>45096</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46967,7 +46967,7 @@
         <v>45096</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47029,7 +47029,7 @@
         <v>45096</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47091,7 +47091,7 @@
         <v>45097</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47148,7 +47148,7 @@
         <v>45097</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47210,7 +47210,7 @@
         <v>45097</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47272,7 +47272,7 @@
         <v>45098</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47329,7 +47329,7 @@
         <v>45098</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47386,7 +47386,7 @@
         <v>45099</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47448,7 +47448,7 @@
         <v>45103</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -47505,7 +47505,7 @@
         <v>45103</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47562,7 +47562,7 @@
         <v>45104</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -47619,7 +47619,7 @@
         <v>45105</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -47676,7 +47676,7 @@
         <v>45105</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -47733,7 +47733,7 @@
         <v>45106</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47790,7 +47790,7 @@
         <v>45107</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -47847,7 +47847,7 @@
         <v>45107</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -47904,7 +47904,7 @@
         <v>45107</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -47961,7 +47961,7 @@
         <v>45111</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -48023,7 +48023,7 @@
         <v>45111</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48080,7 +48080,7 @@
         <v>45112</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -48137,7 +48137,7 @@
         <v>45112</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -48199,7 +48199,7 @@
         <v>45112</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48261,7 +48261,7 @@
         <v>45112</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48318,7 +48318,7 @@
         <v>45114</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48375,7 +48375,7 @@
         <v>45114</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48432,7 +48432,7 @@
         <v>45119</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -48489,7 +48489,7 @@
         <v>45120</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -48551,7 +48551,7 @@
         <v>45124</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -48613,7 +48613,7 @@
         <v>45124</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -48670,7 +48670,7 @@
         <v>45131</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -48732,7 +48732,7 @@
         <v>45131</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48794,7 +48794,7 @@
         <v>45132</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -48851,7 +48851,7 @@
         <v>45132</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -48908,7 +48908,7 @@
         <v>45138</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -48970,7 +48970,7 @@
         <v>45138</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -49032,7 +49032,7 @@
         <v>45139</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -49089,7 +49089,7 @@
         <v>45139</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -49146,7 +49146,7 @@
         <v>45140</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -49203,7 +49203,7 @@
         <v>45145</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49265,7 +49265,7 @@
         <v>45148</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -49322,7 +49322,7 @@
         <v>45152</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49379,7 +49379,7 @@
         <v>45152</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49441,7 +49441,7 @@
         <v>45152</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -49503,7 +49503,7 @@
         <v>45154</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -49560,7 +49560,7 @@
         <v>45155</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -49617,7 +49617,7 @@
         <v>45159</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -49679,7 +49679,7 @@
         <v>45159</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -49736,7 +49736,7 @@
         <v>45160</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -49798,7 +49798,7 @@
         <v>45160</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -49860,7 +49860,7 @@
         <v>45161</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -49917,7 +49917,7 @@
         <v>45161</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -49979,7 +49979,7 @@
         <v>45166</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -50036,7 +50036,7 @@
         <v>45167</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -50093,7 +50093,7 @@
         <v>45168</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -50150,7 +50150,7 @@
         <v>45168</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -50207,7 +50207,7 @@
         <v>45168</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -50264,7 +50264,7 @@
         <v>45173</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -50321,7 +50321,7 @@
         <v>45173</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -50378,7 +50378,7 @@
         <v>45173</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -50435,7 +50435,7 @@
         <v>45174</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -50492,7 +50492,7 @@
         <v>45175</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -50554,7 +50554,7 @@
         <v>45175</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -50616,7 +50616,7 @@
         <v>45176</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -50678,7 +50678,7 @@
         <v>45176</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -50740,7 +50740,7 @@
         <v>45176</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -50802,7 +50802,7 @@
         <v>45176</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -50864,7 +50864,7 @@
         <v>45176</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -50921,7 +50921,7 @@
         <v>45176</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -50978,7 +50978,7 @@
         <v>45176</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -51035,7 +51035,7 @@
         <v>45180</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -51097,7 +51097,7 @@
         <v>45180</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -51159,7 +51159,7 @@
         <v>45181</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -51216,7 +51216,7 @@
         <v>45181</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -51273,7 +51273,7 @@
         <v>45181</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -51330,7 +51330,7 @@
         <v>45181</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -51387,7 +51387,7 @@
         <v>45182</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -51444,7 +51444,7 @@
         <v>45182</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -51501,7 +51501,7 @@
         <v>45182</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -51558,7 +51558,7 @@
         <v>45183</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -51615,7 +51615,7 @@
         <v>45183</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -51672,7 +51672,7 @@
         <v>45183</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -51729,7 +51729,7 @@
         <v>45187</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -51786,7 +51786,7 @@
         <v>45187</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -51848,7 +51848,7 @@
         <v>45188</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -51905,7 +51905,7 @@
         <v>45188</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -51962,7 +51962,7 @@
         <v>45188</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -52019,7 +52019,7 @@
         <v>45188</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -52076,7 +52076,7 @@
         <v>45190</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -52133,7 +52133,7 @@
         <v>45190</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -52190,7 +52190,7 @@
         <v>45194</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -52247,7 +52247,7 @@
         <v>45194</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -52304,7 +52304,7 @@
         <v>45194</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -52361,7 +52361,7 @@
         <v>45194</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -52418,7 +52418,7 @@
         <v>45194</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -52475,7 +52475,7 @@
         <v>45194</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -52537,7 +52537,7 @@
         <v>45194</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -52594,7 +52594,7 @@
         <v>45194</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -52651,7 +52651,7 @@
         <v>45194</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -52713,7 +52713,7 @@
         <v>45194</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -52775,7 +52775,7 @@
         <v>45195</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -52832,7 +52832,7 @@
         <v>45198</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -52889,7 +52889,7 @@
         <v>45198</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -52946,7 +52946,7 @@
         <v>45201</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -53003,7 +53003,7 @@
         <v>45201</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -53060,7 +53060,7 @@
         <v>45201</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -53117,7 +53117,7 @@
         <v>45201</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -53174,7 +53174,7 @@
         <v>45202</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -53231,7 +53231,7 @@
         <v>45203</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -53288,7 +53288,7 @@
         <v>45203</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -53345,7 +53345,7 @@
         <v>45204</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -53402,7 +53402,7 @@
         <v>45204</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -53459,7 +53459,7 @@
         <v>45204</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -53516,7 +53516,7 @@
         <v>45204</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -53578,7 +53578,7 @@
         <v>45204</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -53635,7 +53635,7 @@
         <v>45205</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -53697,7 +53697,7 @@
         <v>45208</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -53754,7 +53754,7 @@
         <v>45209</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -53816,7 +53816,7 @@
         <v>45209</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -53878,7 +53878,7 @@
         <v>45210</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -53935,7 +53935,7 @@
         <v>45210</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -53992,7 +53992,7 @@
         <v>45210</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -54049,7 +54049,7 @@
         <v>45211</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -54106,7 +54106,7 @@
         <v>45211</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -54168,7 +54168,7 @@
         <v>45215</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -54225,7 +54225,7 @@
         <v>45215</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -54282,7 +54282,7 @@
         <v>45216</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -54339,7 +54339,7 @@
         <v>45217</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -54396,7 +54396,7 @@
         <v>45217</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -54453,7 +54453,7 @@
         <v>45217</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -54510,7 +54510,7 @@
         <v>45217</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -54567,7 +54567,7 @@
         <v>45222</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -54629,7 +54629,7 @@
         <v>45222</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -54686,7 +54686,7 @@
         <v>45222</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -54743,7 +54743,7 @@
         <v>45223</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -54805,7 +54805,7 @@
         <v>45223</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -54862,7 +54862,7 @@
         <v>45225</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -54924,7 +54924,7 @@
         <v>45225</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -54981,7 +54981,7 @@
         <v>45225</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -55043,7 +55043,7 @@
         <v>45225</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -55100,7 +55100,7 @@
         <v>45225</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -55157,7 +55157,7 @@
         <v>45225</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -55214,7 +55214,7 @@
         <v>45225</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -55271,7 +55271,7 @@
         <v>45225</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -55328,7 +55328,7 @@
         <v>45225</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -55385,7 +55385,7 @@
         <v>45226</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -55442,7 +55442,7 @@
         <v>45229</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -55499,7 +55499,7 @@
         <v>45229</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -55556,7 +55556,7 @@
         <v>45229</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -55613,7 +55613,7 @@
         <v>45229</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -55670,7 +55670,7 @@
         <v>45229</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -55727,7 +55727,7 @@
         <v>45230</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -55784,7 +55784,7 @@
         <v>45230</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -55841,7 +55841,7 @@
         <v>45230</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -55898,7 +55898,7 @@
         <v>45230</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -55955,7 +55955,7 @@
         <v>45230</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -56012,7 +56012,7 @@
         <v>45231</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -56069,7 +56069,7 @@
         <v>45231</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -56126,7 +56126,7 @@
         <v>45231</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -56183,7 +56183,7 @@
         <v>45231</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -56240,7 +56240,7 @@
         <v>45231</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -56297,7 +56297,7 @@
         <v>45231</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -56354,7 +56354,7 @@
         <v>45231</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -56411,7 +56411,7 @@
         <v>45232</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -56473,7 +56473,7 @@
         <v>45232</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -56530,7 +56530,7 @@
         <v>45232</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -56587,7 +56587,7 @@
         <v>45232</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -56644,7 +56644,7 @@
         <v>45233</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -56706,7 +56706,7 @@
         <v>45236</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -56763,7 +56763,7 @@
         <v>45236</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -56820,7 +56820,7 @@
         <v>45236</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -56877,7 +56877,7 @@
         <v>45237</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -56934,7 +56934,7 @@
         <v>45237</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -56996,7 +56996,7 @@
         <v>45239</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -57053,7 +57053,7 @@
         <v>45239</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -57110,7 +57110,7 @@
         <v>45240</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -57172,7 +57172,7 @@
         <v>45243</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -57229,7 +57229,7 @@
         <v>45243</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -57286,7 +57286,7 @@
         <v>45243</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -57343,7 +57343,7 @@
         <v>45243</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -57400,7 +57400,7 @@
         <v>45243</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -57457,7 +57457,7 @@
         <v>45243</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -57514,7 +57514,7 @@
         <v>45244</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -57571,7 +57571,7 @@
         <v>45244</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -57633,7 +57633,7 @@
         <v>45244</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -57695,7 +57695,7 @@
         <v>45244</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -57752,7 +57752,7 @@
         <v>45244</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -57809,7 +57809,7 @@
         <v>45244</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -57871,7 +57871,7 @@
         <v>45244</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -57928,7 +57928,7 @@
         <v>45245</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -57985,7 +57985,7 @@
         <v>45245</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -58042,7 +58042,7 @@
         <v>45245</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -58099,7 +58099,7 @@
         <v>45245</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -58156,7 +58156,7 @@
         <v>45245</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -58218,7 +58218,7 @@
         <v>45245</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -58275,7 +58275,7 @@
         <v>45245</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -58332,7 +58332,7 @@
         <v>45247</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -58389,7 +58389,7 @@
         <v>45247</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -58446,7 +58446,7 @@
         <v>45248</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -58503,7 +58503,7 @@
         <v>45250</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -58560,7 +58560,7 @@
         <v>45250</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -58617,7 +58617,7 @@
         <v>45251</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -58674,7 +58674,7 @@
         <v>45251</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -58731,7 +58731,7 @@
         <v>45251</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -58788,7 +58788,7 @@
         <v>45252</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -58845,7 +58845,7 @@
         <v>45253</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -58907,7 +58907,7 @@
         <v>45253</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -58964,7 +58964,7 @@
         <v>45253</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -59026,7 +59026,7 @@
         <v>45253</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -59083,7 +59083,7 @@
         <v>45253</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -59145,7 +59145,7 @@
         <v>45253</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -59207,7 +59207,7 @@
         <v>45253</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -59264,7 +59264,7 @@
         <v>45257</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -59321,7 +59321,7 @@
         <v>45258</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -59378,7 +59378,7 @@
         <v>45259</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -59435,7 +59435,7 @@
         <v>45260</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -59492,7 +59492,7 @@
         <v>45261</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -59549,7 +59549,7 @@
         <v>45261</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -59606,7 +59606,7 @@
         <v>45264</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -59663,7 +59663,7 @@
         <v>45264</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -59720,7 +59720,7 @@
         <v>45264</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -59777,7 +59777,7 @@
         <v>45264</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -59834,7 +59834,7 @@
         <v>45264</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -59891,7 +59891,7 @@
         <v>45264</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -59948,7 +59948,7 @@
         <v>45265</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -60005,7 +60005,7 @@
         <v>45265</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -60062,7 +60062,7 @@
         <v>45265</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -60119,7 +60119,7 @@
         <v>45266</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -60176,7 +60176,7 @@
         <v>45266</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -60233,7 +60233,7 @@
         <v>45266</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -60290,7 +60290,7 @@
         <v>45266</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -60352,7 +60352,7 @@
         <v>45267</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -60409,7 +60409,7 @@
         <v>45267</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -60466,7 +60466,7 @@
         <v>45267</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -60523,7 +60523,7 @@
         <v>45267</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -60580,7 +60580,7 @@
         <v>45267</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -60637,7 +60637,7 @@
         <v>45268</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -60694,7 +60694,7 @@
         <v>45271</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -60751,7 +60751,7 @@
         <v>45273</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -60808,7 +60808,7 @@
         <v>45273</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -60865,7 +60865,7 @@
         <v>45275</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -60922,7 +60922,7 @@
         <v>45279</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -60979,7 +60979,7 @@
         <v>45279</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -61036,7 +61036,7 @@
         <v>45279</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -61093,7 +61093,7 @@
         <v>45281</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -61150,7 +61150,7 @@
         <v>45281</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -61212,7 +61212,7 @@
         <v>45282</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -61269,7 +61269,7 @@
         <v>45287</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -61331,7 +61331,7 @@
         <v>45297</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -61393,7 +61393,7 @@
         <v>45299</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -61450,7 +61450,7 @@
         <v>45300</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -61507,7 +61507,7 @@
         <v>45300</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -61564,7 +61564,7 @@
         <v>45302</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -61621,7 +61621,7 @@
         <v>45302</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -61678,7 +61678,7 @@
         <v>45303</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -61735,7 +61735,7 @@
         <v>45306</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -61792,7 +61792,7 @@
         <v>45306</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -61849,7 +61849,7 @@
         <v>45307</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -61906,7 +61906,7 @@
         <v>45307</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -61963,7 +61963,7 @@
         <v>45307</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -62020,7 +62020,7 @@
         <v>45307</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -62077,7 +62077,7 @@
         <v>45307</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -62134,7 +62134,7 @@
         <v>45310</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -62191,7 +62191,7 @@
         <v>45310</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -62248,7 +62248,7 @@
         <v>45310</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -62305,7 +62305,7 @@
         <v>45310</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -62362,7 +62362,7 @@
         <v>45310</v>
       </c>
       <c r="C1038" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
@@ -62419,7 +62419,7 @@
         <v>45310</v>
       </c>
       <c r="C1039" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
@@ -62476,7 +62476,7 @@
         <v>45310</v>
       </c>
       <c r="C1040" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
@@ -62533,7 +62533,7 @@
         <v>45310</v>
       </c>
       <c r="C1041" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
@@ -62590,7 +62590,7 @@
         <v>45310</v>
       </c>
       <c r="C1042" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
@@ -62647,7 +62647,7 @@
         <v>45313</v>
       </c>
       <c r="C1043" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1043" t="inlineStr">
         <is>
@@ -62704,7 +62704,7 @@
         <v>45314</v>
       </c>
       <c r="C1044" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1044" t="inlineStr">
         <is>
@@ -62761,7 +62761,7 @@
         <v>45314</v>
       </c>
       <c r="C1045" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1045" t="inlineStr">
         <is>
@@ -62818,7 +62818,7 @@
         <v>45314</v>
       </c>
       <c r="C1046" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1046" t="inlineStr">
         <is>
@@ -62875,7 +62875,7 @@
         <v>45316</v>
       </c>
       <c r="C1047" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1047" t="inlineStr">
         <is>
@@ -62932,7 +62932,7 @@
         <v>45317</v>
       </c>
       <c r="C1048" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1048" t="inlineStr">
         <is>
@@ -62982,14 +62982,14 @@
     <row r="1049" ht="15" customHeight="1">
       <c r="A1049" t="inlineStr">
         <is>
-          <t>A 3640-2024</t>
+          <t>A 3638-2024</t>
         </is>
       </c>
       <c r="B1049" s="1" t="n">
         <v>45321</v>
       </c>
       <c r="C1049" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1049" t="inlineStr">
         <is>
@@ -63002,7 +63002,7 @@
         </is>
       </c>
       <c r="G1049" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="H1049" t="n">
         <v>0</v>
@@ -63039,14 +63039,14 @@
     <row r="1050" ht="15" customHeight="1">
       <c r="A1050" t="inlineStr">
         <is>
-          <t>A 3644-2024</t>
+          <t>A 3651-2024</t>
         </is>
       </c>
       <c r="B1050" s="1" t="n">
         <v>45321</v>
       </c>
       <c r="C1050" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1050" t="inlineStr">
         <is>
@@ -63059,7 +63059,7 @@
         </is>
       </c>
       <c r="G1050" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="H1050" t="n">
         <v>0</v>
@@ -63096,14 +63096,14 @@
     <row r="1051" ht="15" customHeight="1">
       <c r="A1051" t="inlineStr">
         <is>
-          <t>A 3638-2024</t>
+          <t>A 3655-2024</t>
         </is>
       </c>
       <c r="B1051" s="1" t="n">
         <v>45321</v>
       </c>
       <c r="C1051" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1051" t="inlineStr">
         <is>
@@ -63116,7 +63116,7 @@
         </is>
       </c>
       <c r="G1051" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="H1051" t="n">
         <v>0</v>
@@ -63153,14 +63153,14 @@
     <row r="1052" ht="15" customHeight="1">
       <c r="A1052" t="inlineStr">
         <is>
-          <t>A 3651-2024</t>
+          <t>A 3686-2024</t>
         </is>
       </c>
       <c r="B1052" s="1" t="n">
         <v>45321</v>
       </c>
       <c r="C1052" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1052" t="inlineStr">
         <is>
@@ -63173,7 +63173,7 @@
         </is>
       </c>
       <c r="G1052" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="H1052" t="n">
         <v>0</v>
@@ -63210,14 +63210,14 @@
     <row r="1053" ht="15" customHeight="1">
       <c r="A1053" t="inlineStr">
         <is>
-          <t>A 3655-2024</t>
+          <t>A 3640-2024</t>
         </is>
       </c>
       <c r="B1053" s="1" t="n">
         <v>45321</v>
       </c>
       <c r="C1053" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1053" t="inlineStr">
         <is>
@@ -63230,7 +63230,7 @@
         </is>
       </c>
       <c r="G1053" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="H1053" t="n">
         <v>0</v>
@@ -63267,14 +63267,14 @@
     <row r="1054" ht="15" customHeight="1">
       <c r="A1054" t="inlineStr">
         <is>
-          <t>A 3686-2024</t>
+          <t>A 3644-2024</t>
         </is>
       </c>
       <c r="B1054" s="1" t="n">
         <v>45321</v>
       </c>
       <c r="C1054" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1054" t="inlineStr">
         <is>
@@ -63287,7 +63287,7 @@
         </is>
       </c>
       <c r="G1054" t="n">
-        <v>0.2</v>
+        <v>1.5</v>
       </c>
       <c r="H1054" t="n">
         <v>0</v>
@@ -63324,14 +63324,14 @@
     <row r="1055" ht="15" customHeight="1">
       <c r="A1055" t="inlineStr">
         <is>
-          <t>A 3722-2024</t>
+          <t>A 3725-2024</t>
         </is>
       </c>
       <c r="B1055" s="1" t="n">
         <v>45321</v>
       </c>
       <c r="C1055" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1055" t="inlineStr">
         <is>
@@ -63344,7 +63344,7 @@
         </is>
       </c>
       <c r="G1055" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="H1055" t="n">
         <v>0</v>
@@ -63381,14 +63381,14 @@
     <row r="1056" ht="15" customHeight="1">
       <c r="A1056" t="inlineStr">
         <is>
-          <t>A 3738-2024</t>
+          <t>A 3741-2024</t>
         </is>
       </c>
       <c r="B1056" s="1" t="n">
         <v>45321</v>
       </c>
       <c r="C1056" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1056" t="inlineStr">
         <is>
@@ -63401,7 +63401,7 @@
         </is>
       </c>
       <c r="G1056" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="H1056" t="n">
         <v>0</v>
@@ -63438,14 +63438,14 @@
     <row r="1057" ht="15" customHeight="1">
       <c r="A1057" t="inlineStr">
         <is>
-          <t>A 3742-2024</t>
+          <t>A 3643-2024</t>
         </is>
       </c>
       <c r="B1057" s="1" t="n">
         <v>45321</v>
       </c>
       <c r="C1057" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1057" t="inlineStr">
         <is>
@@ -63458,7 +63458,7 @@
         </is>
       </c>
       <c r="G1057" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="H1057" t="n">
         <v>0</v>
@@ -63495,14 +63495,14 @@
     <row r="1058" ht="15" customHeight="1">
       <c r="A1058" t="inlineStr">
         <is>
-          <t>A 3643-2024</t>
+          <t>A 3722-2024</t>
         </is>
       </c>
       <c r="B1058" s="1" t="n">
         <v>45321</v>
       </c>
       <c r="C1058" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1058" t="inlineStr">
         <is>
@@ -63515,7 +63515,7 @@
         </is>
       </c>
       <c r="G1058" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="H1058" t="n">
         <v>0</v>
@@ -63552,14 +63552,14 @@
     <row r="1059" ht="15" customHeight="1">
       <c r="A1059" t="inlineStr">
         <is>
-          <t>A 3725-2024</t>
+          <t>A 3738-2024</t>
         </is>
       </c>
       <c r="B1059" s="1" t="n">
         <v>45321</v>
       </c>
       <c r="C1059" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1059" t="inlineStr">
         <is>
@@ -63572,7 +63572,7 @@
         </is>
       </c>
       <c r="G1059" t="n">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="H1059" t="n">
         <v>0</v>
@@ -63609,14 +63609,14 @@
     <row r="1060" ht="15" customHeight="1">
       <c r="A1060" t="inlineStr">
         <is>
-          <t>A 3741-2024</t>
+          <t>A 3742-2024</t>
         </is>
       </c>
       <c r="B1060" s="1" t="n">
         <v>45321</v>
       </c>
       <c r="C1060" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1060" t="inlineStr">
         <is>
@@ -63629,7 +63629,7 @@
         </is>
       </c>
       <c r="G1060" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="H1060" t="n">
         <v>0</v>
@@ -63673,7 +63673,7 @@
         <v>45322</v>
       </c>
       <c r="C1061" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1061" t="inlineStr">
         <is>
@@ -63730,7 +63730,7 @@
         <v>45324</v>
       </c>
       <c r="C1062" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1062" t="inlineStr">
         <is>
@@ -63787,7 +63787,7 @@
         <v>45329</v>
       </c>
       <c r="C1063" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1063" t="inlineStr">
         <is>
@@ -63844,7 +63844,7 @@
         <v>45329</v>
       </c>
       <c r="C1064" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1064" t="inlineStr">
         <is>
@@ -63894,14 +63894,14 @@
     <row r="1065" ht="15" customHeight="1">
       <c r="A1065" t="inlineStr">
         <is>
-          <t>A 5124-2024</t>
+          <t>A 5156-2024</t>
         </is>
       </c>
       <c r="B1065" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C1065" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1065" t="inlineStr">
         <is>
@@ -63914,7 +63914,7 @@
         </is>
       </c>
       <c r="G1065" t="n">
-        <v>2.6</v>
+        <v>0.4</v>
       </c>
       <c r="H1065" t="n">
         <v>0</v>
@@ -63951,14 +63951,14 @@
     <row r="1066" ht="15" customHeight="1">
       <c r="A1066" t="inlineStr">
         <is>
-          <t>A 5156-2024</t>
+          <t>A 5189-2024</t>
         </is>
       </c>
       <c r="B1066" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C1066" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1066" t="inlineStr">
         <is>
@@ -63971,7 +63971,7 @@
         </is>
       </c>
       <c r="G1066" t="n">
-        <v>0.4</v>
+        <v>1.3</v>
       </c>
       <c r="H1066" t="n">
         <v>0</v>
@@ -64008,14 +64008,14 @@
     <row r="1067" ht="15" customHeight="1">
       <c r="A1067" t="inlineStr">
         <is>
-          <t>A 5189-2024</t>
+          <t>A 5110-2024</t>
         </is>
       </c>
       <c r="B1067" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C1067" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1067" t="inlineStr">
         <is>
@@ -64028,7 +64028,7 @@
         </is>
       </c>
       <c r="G1067" t="n">
-        <v>1.3</v>
+        <v>3.3</v>
       </c>
       <c r="H1067" t="n">
         <v>0</v>
@@ -64065,14 +64065,14 @@
     <row r="1068" ht="15" customHeight="1">
       <c r="A1068" t="inlineStr">
         <is>
-          <t>A 5174-2024</t>
+          <t>A 5122-2024</t>
         </is>
       </c>
       <c r="B1068" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C1068" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1068" t="inlineStr">
         <is>
@@ -64085,7 +64085,7 @@
         </is>
       </c>
       <c r="G1068" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="H1068" t="n">
         <v>0</v>
@@ -64122,14 +64122,14 @@
     <row r="1069" ht="15" customHeight="1">
       <c r="A1069" t="inlineStr">
         <is>
-          <t>A 5110-2024</t>
+          <t>A 5124-2024</t>
         </is>
       </c>
       <c r="B1069" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C1069" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1069" t="inlineStr">
         <is>
@@ -64142,7 +64142,7 @@
         </is>
       </c>
       <c r="G1069" t="n">
-        <v>3.3</v>
+        <v>2.6</v>
       </c>
       <c r="H1069" t="n">
         <v>0</v>
@@ -64179,14 +64179,14 @@
     <row r="1070" ht="15" customHeight="1">
       <c r="A1070" t="inlineStr">
         <is>
-          <t>A 5122-2024</t>
+          <t>A 5174-2024</t>
         </is>
       </c>
       <c r="B1070" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C1070" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1070" t="inlineStr">
         <is>
@@ -64199,7 +64199,7 @@
         </is>
       </c>
       <c r="G1070" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="H1070" t="n">
         <v>0</v>
@@ -64243,7 +64243,7 @@
         <v>45331</v>
       </c>
       <c r="C1071" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1071" t="inlineStr">
         <is>
@@ -64300,7 +64300,7 @@
         <v>45331</v>
       </c>
       <c r="C1072" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1072" t="inlineStr">
         <is>
@@ -64357,7 +64357,7 @@
         <v>45334</v>
       </c>
       <c r="C1073" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1073" t="inlineStr">
         <is>
@@ -64414,7 +64414,7 @@
         <v>45334</v>
       </c>
       <c r="C1074" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1074" t="inlineStr">
         <is>
@@ -64471,7 +64471,7 @@
         <v>45337</v>
       </c>
       <c r="C1075" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1075" t="inlineStr">
         <is>
@@ -64528,7 +64528,7 @@
         <v>45337</v>
       </c>
       <c r="C1076" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1076" t="inlineStr">
         <is>
@@ -64585,7 +64585,7 @@
         <v>45337</v>
       </c>
       <c r="C1077" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1077" t="inlineStr">
         <is>

--- a/Översikt RÄTTVIK.xlsx
+++ b/Översikt RÄTTVIK.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z1077"/>
+  <dimension ref="A1:Z1078"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="26"/>
@@ -569,7 +569,7 @@
         <v>43542</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         <v>43663</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -781,7 +781,7 @@
         <v>43619</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
         <v>44909</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>43740</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>44909</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>44874</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>45147</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
         <v>44237</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1461,7 +1461,7 @@
         <v>44624</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         <v>43634</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         <v>43663</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1736,7 +1736,7 @@
         <v>44148</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         <v>44435</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1910,7 +1910,7 @@
         <v>44799</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         <v>44909</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         <v>44909</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
         <v>45111</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>43700</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>44496</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2450,7 +2450,7 @@
         <v>45033</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
         <v>43440</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         <v>43493</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
         <v>43623</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2791,7 +2791,7 @@
         <v>43705</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
         <v>44088</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2961,7 +2961,7 @@
         <v>44361</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3046,7 +3046,7 @@
         <v>44391</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         <v>44414</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3226,7 +3226,7 @@
         <v>44470</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3316,7 +3316,7 @@
         <v>44496</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
         <v>44511</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3491,7 +3491,7 @@
         <v>44568</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
         <v>44728</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3679,7 +3679,7 @@
         <v>44855</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3769,7 +3769,7 @@
         <v>44894</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3859,7 +3859,7 @@
         <v>44918</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3949,7 +3949,7 @@
         <v>44986</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4034,7 +4034,7 @@
         <v>45077</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4119,7 +4119,7 @@
         <v>45194</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4204,7 +4204,7 @@
         <v>45194</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4289,7 +4289,7 @@
         <v>45231</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4374,7 +4374,7 @@
         <v>43333</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4431,7 +4431,7 @@
         <v>43348</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4488,7 +4488,7 @@
         <v>43356</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4545,7 +4545,7 @@
         <v>43361</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4602,7 +4602,7 @@
         <v>43362</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4659,7 +4659,7 @@
         <v>43362</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4716,7 +4716,7 @@
         <v>43362</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4773,7 +4773,7 @@
         <v>43362</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4830,7 +4830,7 @@
         <v>43367</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4887,7 +4887,7 @@
         <v>43369</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4944,7 +4944,7 @@
         <v>43373</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5001,7 +5001,7 @@
         <v>43378</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5058,7 +5058,7 @@
         <v>43381</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5115,7 +5115,7 @@
         <v>43381</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5172,7 +5172,7 @@
         <v>43388</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5229,7 +5229,7 @@
         <v>43388</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5291,7 +5291,7 @@
         <v>43388</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5348,7 +5348,7 @@
         <v>43391</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5405,7 +5405,7 @@
         <v>43398</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
         <v>43399</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5519,7 +5519,7 @@
         <v>43401</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5576,7 +5576,7 @@
         <v>43405</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5633,7 +5633,7 @@
         <v>43405</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5690,7 +5690,7 @@
         <v>43410</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5747,7 +5747,7 @@
         <v>43410</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5804,7 +5804,7 @@
         <v>43411</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5861,7 +5861,7 @@
         <v>43412</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5918,7 +5918,7 @@
         <v>43416</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5975,7 +5975,7 @@
         <v>43416</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6032,7 +6032,7 @@
         <v>43416</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6089,7 +6089,7 @@
         <v>43419</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6146,7 +6146,7 @@
         <v>43419</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6203,7 +6203,7 @@
         <v>43423</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6265,7 +6265,7 @@
         <v>43423</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         <v>43423</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6389,7 +6389,7 @@
         <v>43424</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6451,7 +6451,7 @@
         <v>43425</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6508,7 +6508,7 @@
         <v>43427</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6570,7 +6570,7 @@
         <v>43428</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6627,7 +6627,7 @@
         <v>43428</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6684,7 +6684,7 @@
         <v>43430</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6741,7 +6741,7 @@
         <v>43430</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6798,7 +6798,7 @@
         <v>43430</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6855,7 +6855,7 @@
         <v>43430</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6912,7 +6912,7 @@
         <v>43431</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6974,7 +6974,7 @@
         <v>43432</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7031,7 +7031,7 @@
         <v>43432</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7088,7 +7088,7 @@
         <v>43434</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7145,7 +7145,7 @@
         <v>43434</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7202,7 +7202,7 @@
         <v>43438</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7259,7 +7259,7 @@
         <v>43441</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7316,7 +7316,7 @@
         <v>43447</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7373,7 +7373,7 @@
         <v>43448</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7430,7 +7430,7 @@
         <v>43451</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7487,7 +7487,7 @@
         <v>43451</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7544,7 +7544,7 @@
         <v>43451</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7601,7 +7601,7 @@
         <v>43452</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7658,7 +7658,7 @@
         <v>43454</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7720,7 +7720,7 @@
         <v>43454</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7782,7 +7782,7 @@
         <v>43454</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7844,7 +7844,7 @@
         <v>43455</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7901,7 +7901,7 @@
         <v>43461</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7958,7 +7958,7 @@
         <v>43471</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8015,7 +8015,7 @@
         <v>43472</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8072,7 +8072,7 @@
         <v>43472</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8134,7 +8134,7 @@
         <v>43473</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8191,7 +8191,7 @@
         <v>43475</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8248,7 +8248,7 @@
         <v>43481</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8305,7 +8305,7 @@
         <v>43490</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8362,7 +8362,7 @@
         <v>43495</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8419,7 +8419,7 @@
         <v>43499</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8476,7 +8476,7 @@
         <v>43500</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8538,7 +8538,7 @@
         <v>43511</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8595,7 +8595,7 @@
         <v>43511</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8652,7 +8652,7 @@
         <v>43514</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8709,7 +8709,7 @@
         <v>43517</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8766,7 +8766,7 @@
         <v>43524</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8823,7 +8823,7 @@
         <v>43546</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8880,7 +8880,7 @@
         <v>43553</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8942,7 +8942,7 @@
         <v>43553</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8999,7 +8999,7 @@
         <v>43554</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9056,7 +9056,7 @@
         <v>43556</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9113,7 +9113,7 @@
         <v>43559</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9175,7 +9175,7 @@
         <v>43564</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9232,7 +9232,7 @@
         <v>43566</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9289,7 +9289,7 @@
         <v>43570</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9351,7 +9351,7 @@
         <v>43570</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9413,7 +9413,7 @@
         <v>43570</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9470,7 +9470,7 @@
         <v>43580</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9527,7 +9527,7 @@
         <v>43584</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9584,7 +9584,7 @@
         <v>43585</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9641,7 +9641,7 @@
         <v>43587</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9698,7 +9698,7 @@
         <v>43592</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9755,7 +9755,7 @@
         <v>43592</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9812,7 +9812,7 @@
         <v>43592</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9869,7 +9869,7 @@
         <v>43599</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9926,7 +9926,7 @@
         <v>43609</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9983,7 +9983,7 @@
         <v>43612</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10040,7 +10040,7 @@
         <v>43612</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10097,7 +10097,7 @@
         <v>43612</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10154,7 +10154,7 @@
         <v>43612</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10211,7 +10211,7 @@
         <v>43616</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10268,7 +10268,7 @@
         <v>43619</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10330,7 +10330,7 @@
         <v>43621</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10387,7 +10387,7 @@
         <v>43623</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10444,7 +10444,7 @@
         <v>43628</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10506,7 +10506,7 @@
         <v>43628</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10568,7 +10568,7 @@
         <v>43629</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10625,7 +10625,7 @@
         <v>43630</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10682,7 +10682,7 @@
         <v>43633</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10739,7 +10739,7 @@
         <v>43633</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10796,7 +10796,7 @@
         <v>43641</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10853,7 +10853,7 @@
         <v>43643</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10915,7 +10915,7 @@
         <v>43643</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10977,7 +10977,7 @@
         <v>43647</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11039,7 +11039,7 @@
         <v>43651</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11096,7 +11096,7 @@
         <v>43651</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11153,7 +11153,7 @@
         <v>43656</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11210,7 +11210,7 @@
         <v>43657</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11267,7 +11267,7 @@
         <v>43662</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11324,7 +11324,7 @@
         <v>43662</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11381,7 +11381,7 @@
         <v>43663</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11463,7 +11463,7 @@
         <v>43663</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11525,7 +11525,7 @@
         <v>43663</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11587,7 +11587,7 @@
         <v>43663</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11649,7 +11649,7 @@
         <v>43682</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11706,7 +11706,7 @@
         <v>43686</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11768,7 +11768,7 @@
         <v>43686</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11825,7 +11825,7 @@
         <v>43689</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11887,7 +11887,7 @@
         <v>43690</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11944,7 +11944,7 @@
         <v>43697</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12001,7 +12001,7 @@
         <v>43700</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12058,7 +12058,7 @@
         <v>43705</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12115,7 +12115,7 @@
         <v>43711</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12177,7 +12177,7 @@
         <v>43712</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12234,7 +12234,7 @@
         <v>43713</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12291,7 +12291,7 @@
         <v>43714</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12348,7 +12348,7 @@
         <v>43714</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12405,7 +12405,7 @@
         <v>43717</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12462,7 +12462,7 @@
         <v>43718</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12519,7 +12519,7 @@
         <v>43720</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12576,7 +12576,7 @@
         <v>43724</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12633,7 +12633,7 @@
         <v>43726</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12690,7 +12690,7 @@
         <v>43727</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12747,7 +12747,7 @@
         <v>43727</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12804,7 +12804,7 @@
         <v>43727</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12861,7 +12861,7 @@
         <v>43732</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12918,7 +12918,7 @@
         <v>43734</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12980,7 +12980,7 @@
         <v>43734</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13037,7 +13037,7 @@
         <v>43734</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13094,7 +13094,7 @@
         <v>43735</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13156,7 +13156,7 @@
         <v>43735</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13213,7 +13213,7 @@
         <v>43740</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13275,7 +13275,7 @@
         <v>43740</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13332,7 +13332,7 @@
         <v>43740</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13389,7 +13389,7 @@
         <v>43740</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13446,7 +13446,7 @@
         <v>43742</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13508,7 +13508,7 @@
         <v>43742</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13565,7 +13565,7 @@
         <v>43747</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13622,7 +13622,7 @@
         <v>43758</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13679,7 +13679,7 @@
         <v>43761</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13736,7 +13736,7 @@
         <v>43766</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13793,7 +13793,7 @@
         <v>43767</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13855,7 +13855,7 @@
         <v>43769</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13917,7 +13917,7 @@
         <v>43770</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13974,7 +13974,7 @@
         <v>43770</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14031,7 +14031,7 @@
         <v>43773</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14088,7 +14088,7 @@
         <v>43775</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14145,7 +14145,7 @@
         <v>43776</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14202,7 +14202,7 @@
         <v>43776</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14259,7 +14259,7 @@
         <v>43776</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14316,7 +14316,7 @@
         <v>43776</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14373,7 +14373,7 @@
         <v>43780</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14435,7 +14435,7 @@
         <v>43780</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14492,7 +14492,7 @@
         <v>43780</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14549,7 +14549,7 @@
         <v>43780</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14606,7 +14606,7 @@
         <v>43783</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14668,7 +14668,7 @@
         <v>43784</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14725,7 +14725,7 @@
         <v>43786</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14782,7 +14782,7 @@
         <v>43797</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14839,7 +14839,7 @@
         <v>43804</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14901,7 +14901,7 @@
         <v>43805</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14958,7 +14958,7 @@
         <v>43805</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15015,7 +15015,7 @@
         <v>43812</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15072,7 +15072,7 @@
         <v>43812</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15129,7 +15129,7 @@
         <v>43815</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15186,7 +15186,7 @@
         <v>43815</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15243,7 +15243,7 @@
         <v>43829</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15300,7 +15300,7 @@
         <v>43833</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15357,7 +15357,7 @@
         <v>43837</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15414,7 +15414,7 @@
         <v>43839</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15471,7 +15471,7 @@
         <v>43840</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15528,7 +15528,7 @@
         <v>43843</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15585,7 +15585,7 @@
         <v>43845</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15647,7 +15647,7 @@
         <v>43850</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15704,7 +15704,7 @@
         <v>43854</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15766,7 +15766,7 @@
         <v>43857</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15823,7 +15823,7 @@
         <v>43857</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15885,7 +15885,7 @@
         <v>43857</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15942,7 +15942,7 @@
         <v>43864</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15999,7 +15999,7 @@
         <v>43864</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16061,7 +16061,7 @@
         <v>43864</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16123,7 +16123,7 @@
         <v>43867</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16185,7 +16185,7 @@
         <v>43871</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16242,7 +16242,7 @@
         <v>43872</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16304,7 +16304,7 @@
         <v>43873</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16361,7 +16361,7 @@
         <v>43873</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16418,7 +16418,7 @@
         <v>43873</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16475,7 +16475,7 @@
         <v>43874</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16532,7 +16532,7 @@
         <v>43878</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16589,7 +16589,7 @@
         <v>43879</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16651,7 +16651,7 @@
         <v>43880</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16708,7 +16708,7 @@
         <v>43894</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16765,7 +16765,7 @@
         <v>43894</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16822,7 +16822,7 @@
         <v>43902</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16879,7 +16879,7 @@
         <v>43917</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16936,7 +16936,7 @@
         <v>43917</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16998,7 +16998,7 @@
         <v>43920</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17060,7 +17060,7 @@
         <v>43920</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17122,7 +17122,7 @@
         <v>43921</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17184,7 +17184,7 @@
         <v>43922</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17246,7 +17246,7 @@
         <v>43922</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17308,7 +17308,7 @@
         <v>43924</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17365,7 +17365,7 @@
         <v>43924</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17422,7 +17422,7 @@
         <v>43927</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17479,7 +17479,7 @@
         <v>43927</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17536,7 +17536,7 @@
         <v>43928</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17593,7 +17593,7 @@
         <v>43928</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17650,7 +17650,7 @@
         <v>43930</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17712,7 +17712,7 @@
         <v>43933</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17774,7 +17774,7 @@
         <v>43933</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17836,7 +17836,7 @@
         <v>43935</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17893,7 +17893,7 @@
         <v>43937</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17955,7 +17955,7 @@
         <v>43941</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18012,7 +18012,7 @@
         <v>43941</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18069,7 +18069,7 @@
         <v>43948</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18126,7 +18126,7 @@
         <v>43949</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18188,7 +18188,7 @@
         <v>43949</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18250,7 +18250,7 @@
         <v>43949</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18312,7 +18312,7 @@
         <v>43949</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18374,7 +18374,7 @@
         <v>43950</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18431,7 +18431,7 @@
         <v>43951</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18493,7 +18493,7 @@
         <v>43959</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18555,7 +18555,7 @@
         <v>43959</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18617,7 +18617,7 @@
         <v>43959</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18679,7 +18679,7 @@
         <v>43959</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18736,7 +18736,7 @@
         <v>43969</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18798,7 +18798,7 @@
         <v>43970</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18855,7 +18855,7 @@
         <v>43973</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18912,7 +18912,7 @@
         <v>43985</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18969,7 +18969,7 @@
         <v>43990</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19026,7 +19026,7 @@
         <v>43991</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19088,7 +19088,7 @@
         <v>43991</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19150,7 +19150,7 @@
         <v>43991</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19212,7 +19212,7 @@
         <v>43991</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19274,7 +19274,7 @@
         <v>43991</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19336,7 +19336,7 @@
         <v>44005</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19398,7 +19398,7 @@
         <v>44033</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19455,7 +19455,7 @@
         <v>44039</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19512,7 +19512,7 @@
         <v>44048</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19569,7 +19569,7 @@
         <v>44049</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19626,7 +19626,7 @@
         <v>44053</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19683,7 +19683,7 @@
         <v>44053</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19740,7 +19740,7 @@
         <v>44053</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19797,7 +19797,7 @@
         <v>44054</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19859,7 +19859,7 @@
         <v>44054</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19916,7 +19916,7 @@
         <v>44054</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19973,7 +19973,7 @@
         <v>44055</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20035,7 +20035,7 @@
         <v>44055</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20097,7 +20097,7 @@
         <v>44074</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20154,7 +20154,7 @@
         <v>44074</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20211,7 +20211,7 @@
         <v>44077</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20268,7 +20268,7 @@
         <v>44078</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20330,7 +20330,7 @@
         <v>44078</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20392,7 +20392,7 @@
         <v>44082</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20449,7 +20449,7 @@
         <v>44084</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20511,7 +20511,7 @@
         <v>44089</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20568,7 +20568,7 @@
         <v>44091</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20625,7 +20625,7 @@
         <v>44095</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20682,7 +20682,7 @@
         <v>44097</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20739,7 +20739,7 @@
         <v>44102</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20796,7 +20796,7 @@
         <v>44104</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20853,7 +20853,7 @@
         <v>44105</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20910,7 +20910,7 @@
         <v>44109</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20967,7 +20967,7 @@
         <v>44109</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21029,7 +21029,7 @@
         <v>44110</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21086,7 +21086,7 @@
         <v>44117</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21148,7 +21148,7 @@
         <v>44126</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21210,7 +21210,7 @@
         <v>44126</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21272,7 +21272,7 @@
         <v>44126</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21334,7 +21334,7 @@
         <v>44126</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21396,7 +21396,7 @@
         <v>44126</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21458,7 +21458,7 @@
         <v>44130</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21515,7 +21515,7 @@
         <v>44130</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21572,7 +21572,7 @@
         <v>44130</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21629,7 +21629,7 @@
         <v>44130</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21686,7 +21686,7 @@
         <v>44131</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21743,7 +21743,7 @@
         <v>44133</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21805,7 +21805,7 @@
         <v>44137</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21862,7 +21862,7 @@
         <v>44139</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21919,7 +21919,7 @@
         <v>44139</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21976,7 +21976,7 @@
         <v>44141</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22033,7 +22033,7 @@
         <v>44145</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22090,7 +22090,7 @@
         <v>44145</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22147,7 +22147,7 @@
         <v>44151</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22204,7 +22204,7 @@
         <v>44151</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22261,7 +22261,7 @@
         <v>44153</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22318,7 +22318,7 @@
         <v>44159</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22375,7 +22375,7 @@
         <v>44159</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22432,7 +22432,7 @@
         <v>44159</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22489,7 +22489,7 @@
         <v>44159</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22546,7 +22546,7 @@
         <v>44160</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22603,7 +22603,7 @@
         <v>44160</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22660,7 +22660,7 @@
         <v>44160</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22717,7 +22717,7 @@
         <v>44161</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22774,7 +22774,7 @@
         <v>44162</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22831,7 +22831,7 @@
         <v>44173</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22888,7 +22888,7 @@
         <v>44175</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22945,7 +22945,7 @@
         <v>44175</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23002,7 +23002,7 @@
         <v>44179</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23059,7 +23059,7 @@
         <v>44179</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23116,7 +23116,7 @@
         <v>44180</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23173,7 +23173,7 @@
         <v>44185</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23230,7 +23230,7 @@
         <v>44186</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23287,7 +23287,7 @@
         <v>44186</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23344,7 +23344,7 @@
         <v>44194</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23401,7 +23401,7 @@
         <v>44195</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23458,7 +23458,7 @@
         <v>44214</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23515,7 +23515,7 @@
         <v>44214</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23572,7 +23572,7 @@
         <v>44217</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23629,7 +23629,7 @@
         <v>44217</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23686,7 +23686,7 @@
         <v>44228</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23743,7 +23743,7 @@
         <v>44228</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23800,7 +23800,7 @@
         <v>44238</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23857,7 +23857,7 @@
         <v>44242</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23914,7 +23914,7 @@
         <v>44242</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23971,7 +23971,7 @@
         <v>44271</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24028,7 +24028,7 @@
         <v>44273</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24085,7 +24085,7 @@
         <v>44280</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24142,7 +24142,7 @@
         <v>44281</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24199,7 +24199,7 @@
         <v>44284</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24256,7 +24256,7 @@
         <v>44284</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24313,7 +24313,7 @@
         <v>44300</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24370,7 +24370,7 @@
         <v>44300</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24427,7 +24427,7 @@
         <v>44300</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24484,7 +24484,7 @@
         <v>44305</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24541,7 +24541,7 @@
         <v>44306</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24598,7 +24598,7 @@
         <v>44307</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24655,7 +24655,7 @@
         <v>44322</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24717,7 +24717,7 @@
         <v>44326</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24774,7 +24774,7 @@
         <v>44326</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24831,7 +24831,7 @@
         <v>44326</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24888,7 +24888,7 @@
         <v>44326</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24945,7 +24945,7 @@
         <v>44330</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25002,7 +25002,7 @@
         <v>44335</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25059,7 +25059,7 @@
         <v>44336</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25121,7 +25121,7 @@
         <v>44340</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25178,7 +25178,7 @@
         <v>44342</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25240,7 +25240,7 @@
         <v>44347</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25297,7 +25297,7 @@
         <v>44347</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25354,7 +25354,7 @@
         <v>44348</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25411,7 +25411,7 @@
         <v>44348</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25468,7 +25468,7 @@
         <v>44349</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25525,7 +25525,7 @@
         <v>44349</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25582,7 +25582,7 @@
         <v>44350</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25639,7 +25639,7 @@
         <v>44351</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25696,7 +25696,7 @@
         <v>44351</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25753,7 +25753,7 @@
         <v>44363</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25810,7 +25810,7 @@
         <v>44377</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25872,7 +25872,7 @@
         <v>44377</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25929,7 +25929,7 @@
         <v>44377</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25986,7 +25986,7 @@
         <v>44377</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26043,7 +26043,7 @@
         <v>44377</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26105,7 +26105,7 @@
         <v>44386</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26167,7 +26167,7 @@
         <v>44386</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26229,7 +26229,7 @@
         <v>44391</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26291,7 +26291,7 @@
         <v>44391</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26353,7 +26353,7 @@
         <v>44399</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26410,7 +26410,7 @@
         <v>44400</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26467,7 +26467,7 @@
         <v>44403</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26524,7 +26524,7 @@
         <v>44408</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26586,7 +26586,7 @@
         <v>44409</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26648,7 +26648,7 @@
         <v>44414</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26710,7 +26710,7 @@
         <v>44414</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26772,7 +26772,7 @@
         <v>44414</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26834,7 +26834,7 @@
         <v>44418</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26891,7 +26891,7 @@
         <v>44420</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26948,7 +26948,7 @@
         <v>44421</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27005,7 +27005,7 @@
         <v>44421</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27067,7 +27067,7 @@
         <v>44424</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27129,7 +27129,7 @@
         <v>44424</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27186,7 +27186,7 @@
         <v>44432</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27248,7 +27248,7 @@
         <v>44435</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27305,7 +27305,7 @@
         <v>44441</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27362,7 +27362,7 @@
         <v>44441</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27424,7 +27424,7 @@
         <v>44449</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27486,7 +27486,7 @@
         <v>44451</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27548,7 +27548,7 @@
         <v>44451</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27610,7 +27610,7 @@
         <v>44454</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27667,7 +27667,7 @@
         <v>44459</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27729,7 +27729,7 @@
         <v>44459</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27791,7 +27791,7 @@
         <v>44459</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27853,7 +27853,7 @@
         <v>44459</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27915,7 +27915,7 @@
         <v>44459</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27977,7 +27977,7 @@
         <v>44459</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28039,7 +28039,7 @@
         <v>44460</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28096,7 +28096,7 @@
         <v>44460</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28153,7 +28153,7 @@
         <v>44461</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28210,7 +28210,7 @@
         <v>44463</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28272,7 +28272,7 @@
         <v>44467</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28334,7 +28334,7 @@
         <v>44469</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28396,7 +28396,7 @@
         <v>44469</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28458,7 +28458,7 @@
         <v>44469</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28520,7 +28520,7 @@
         <v>44469</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28582,7 +28582,7 @@
         <v>44470</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28644,7 +28644,7 @@
         <v>44470</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28701,7 +28701,7 @@
         <v>44470</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28763,7 +28763,7 @@
         <v>44473</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28820,7 +28820,7 @@
         <v>44474</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28877,7 +28877,7 @@
         <v>44475</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28934,7 +28934,7 @@
         <v>44475</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28991,7 +28991,7 @@
         <v>44477</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29048,7 +29048,7 @@
         <v>44477</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29105,7 +29105,7 @@
         <v>44477</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29162,7 +29162,7 @@
         <v>44479</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29224,7 +29224,7 @@
         <v>44484</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29286,7 +29286,7 @@
         <v>44484</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29348,7 +29348,7 @@
         <v>44488</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29405,7 +29405,7 @@
         <v>44489</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29467,7 +29467,7 @@
         <v>44495</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29529,7 +29529,7 @@
         <v>44495</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29591,7 +29591,7 @@
         <v>44495</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29653,7 +29653,7 @@
         <v>44495</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29715,7 +29715,7 @@
         <v>44495</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29777,7 +29777,7 @@
         <v>44495</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29839,7 +29839,7 @@
         <v>44495</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29901,7 +29901,7 @@
         <v>44496</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29958,7 +29958,7 @@
         <v>44498</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30015,7 +30015,7 @@
         <v>44509</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30077,7 +30077,7 @@
         <v>44511</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30134,7 +30134,7 @@
         <v>44512</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30191,7 +30191,7 @@
         <v>44515</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30248,7 +30248,7 @@
         <v>44517</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30305,7 +30305,7 @@
         <v>44519</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30362,7 +30362,7 @@
         <v>44519</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30419,7 +30419,7 @@
         <v>44523</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30481,7 +30481,7 @@
         <v>44524</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30538,7 +30538,7 @@
         <v>44529</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30600,7 +30600,7 @@
         <v>44529</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30657,7 +30657,7 @@
         <v>44529</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30714,7 +30714,7 @@
         <v>44529</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30771,7 +30771,7 @@
         <v>44529</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30828,7 +30828,7 @@
         <v>44533</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30885,7 +30885,7 @@
         <v>44536</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30942,7 +30942,7 @@
         <v>44537</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30999,7 +30999,7 @@
         <v>44537</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31056,7 +31056,7 @@
         <v>44537</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31113,7 +31113,7 @@
         <v>44541</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31170,7 +31170,7 @@
         <v>44544</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31227,7 +31227,7 @@
         <v>44544</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31284,7 +31284,7 @@
         <v>44545</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31341,7 +31341,7 @@
         <v>44551</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31398,7 +31398,7 @@
         <v>44551</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31455,7 +31455,7 @@
         <v>44552</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31512,7 +31512,7 @@
         <v>44556</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31569,7 +31569,7 @@
         <v>44559</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31626,7 +31626,7 @@
         <v>44562</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31683,7 +31683,7 @@
         <v>44565</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31745,7 +31745,7 @@
         <v>44565</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31807,7 +31807,7 @@
         <v>44565</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31869,7 +31869,7 @@
         <v>44571</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31926,7 +31926,7 @@
         <v>44571</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31983,7 +31983,7 @@
         <v>44572</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32040,7 +32040,7 @@
         <v>44573</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32097,7 +32097,7 @@
         <v>44578</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32154,7 +32154,7 @@
         <v>44579</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32211,7 +32211,7 @@
         <v>44600</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32268,7 +32268,7 @@
         <v>44602</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32325,7 +32325,7 @@
         <v>44610</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32387,7 +32387,7 @@
         <v>44620</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32444,7 +32444,7 @@
         <v>44621</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32501,7 +32501,7 @@
         <v>44627</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32558,7 +32558,7 @@
         <v>44637</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32615,7 +32615,7 @@
         <v>44638</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32672,7 +32672,7 @@
         <v>44638</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32729,7 +32729,7 @@
         <v>44638</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32786,7 +32786,7 @@
         <v>44641</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32843,7 +32843,7 @@
         <v>44644</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32900,7 +32900,7 @@
         <v>44651</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32957,7 +32957,7 @@
         <v>44651</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33014,7 +33014,7 @@
         <v>44655</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33071,7 +33071,7 @@
         <v>44679</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33128,7 +33128,7 @@
         <v>44679</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33185,7 +33185,7 @@
         <v>44679</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33242,7 +33242,7 @@
         <v>44680</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33299,7 +33299,7 @@
         <v>44683</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33356,7 +33356,7 @@
         <v>44684</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33413,7 +33413,7 @@
         <v>44686</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33470,7 +33470,7 @@
         <v>44692</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33527,7 +33527,7 @@
         <v>44700</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33584,7 +33584,7 @@
         <v>44701</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33641,7 +33641,7 @@
         <v>44715</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33698,7 +33698,7 @@
         <v>44719</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33755,7 +33755,7 @@
         <v>44722</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33812,7 +33812,7 @@
         <v>44727</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33869,7 +33869,7 @@
         <v>44727</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33926,7 +33926,7 @@
         <v>44728</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33988,7 +33988,7 @@
         <v>44728</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34050,7 +34050,7 @@
         <v>44729</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34112,7 +34112,7 @@
         <v>44732</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34169,7 +34169,7 @@
         <v>44733</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34226,7 +34226,7 @@
         <v>44736</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34283,7 +34283,7 @@
         <v>44740</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34340,7 +34340,7 @@
         <v>44742</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34397,7 +34397,7 @@
         <v>44743</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34459,7 +34459,7 @@
         <v>44746</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34516,7 +34516,7 @@
         <v>44746</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34573,7 +34573,7 @@
         <v>44747</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34635,7 +34635,7 @@
         <v>44747</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34692,7 +34692,7 @@
         <v>44747</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34754,7 +34754,7 @@
         <v>44747</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34811,7 +34811,7 @@
         <v>44748</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34868,7 +34868,7 @@
         <v>44749</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34930,7 +34930,7 @@
         <v>44749</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34992,7 +34992,7 @@
         <v>44749</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35049,7 +35049,7 @@
         <v>44762</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35106,7 +35106,7 @@
         <v>44762</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35163,7 +35163,7 @@
         <v>44762</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35220,7 +35220,7 @@
         <v>44763</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35277,7 +35277,7 @@
         <v>44763</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35339,7 +35339,7 @@
         <v>44774</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35401,7 +35401,7 @@
         <v>44775</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35458,7 +35458,7 @@
         <v>44775</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35515,7 +35515,7 @@
         <v>44775</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35572,7 +35572,7 @@
         <v>44783</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35629,7 +35629,7 @@
         <v>44785</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35691,7 +35691,7 @@
         <v>44789</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35748,7 +35748,7 @@
         <v>44789</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35810,7 +35810,7 @@
         <v>44790</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35867,7 +35867,7 @@
         <v>44790</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35924,7 +35924,7 @@
         <v>44791</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35981,7 +35981,7 @@
         <v>44791</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36038,7 +36038,7 @@
         <v>44792</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36100,7 +36100,7 @@
         <v>44792</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36162,7 +36162,7 @@
         <v>44792</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36224,7 +36224,7 @@
         <v>44792</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36286,7 +36286,7 @@
         <v>44792</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36348,7 +36348,7 @@
         <v>44795</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36405,7 +36405,7 @@
         <v>44795</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36462,7 +36462,7 @@
         <v>44795</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36519,7 +36519,7 @@
         <v>44796</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36576,7 +36576,7 @@
         <v>44797</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36633,7 +36633,7 @@
         <v>44798</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36690,7 +36690,7 @@
         <v>44798</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36747,7 +36747,7 @@
         <v>44799</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36809,7 +36809,7 @@
         <v>44799</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36871,7 +36871,7 @@
         <v>44799</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36933,7 +36933,7 @@
         <v>44799</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36995,7 +36995,7 @@
         <v>44803</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37052,7 +37052,7 @@
         <v>44803</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37109,7 +37109,7 @@
         <v>44804</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37166,7 +37166,7 @@
         <v>44804</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37223,7 +37223,7 @@
         <v>44806</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37305,7 +37305,7 @@
         <v>44806</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37362,7 +37362,7 @@
         <v>44806</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37419,7 +37419,7 @@
         <v>44806</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37476,7 +37476,7 @@
         <v>44806</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37533,7 +37533,7 @@
         <v>44806</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37590,7 +37590,7 @@
         <v>44807</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37647,7 +37647,7 @@
         <v>44813</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37709,7 +37709,7 @@
         <v>44817</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37771,7 +37771,7 @@
         <v>44817</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37833,7 +37833,7 @@
         <v>44818</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37890,7 +37890,7 @@
         <v>44818</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37947,7 +37947,7 @@
         <v>44818</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38004,7 +38004,7 @@
         <v>44818</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38061,7 +38061,7 @@
         <v>44818</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38118,7 +38118,7 @@
         <v>44819</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38175,7 +38175,7 @@
         <v>44819</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38237,7 +38237,7 @@
         <v>44819</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38294,7 +38294,7 @@
         <v>44820</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38356,7 +38356,7 @@
         <v>44823</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38413,7 +38413,7 @@
         <v>44824</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38470,7 +38470,7 @@
         <v>44826</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38527,7 +38527,7 @@
         <v>44827</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38589,7 +38589,7 @@
         <v>44833</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38646,7 +38646,7 @@
         <v>44834</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38703,7 +38703,7 @@
         <v>44834</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38760,7 +38760,7 @@
         <v>44837</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38817,7 +38817,7 @@
         <v>44838</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38879,7 +38879,7 @@
         <v>44839</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38941,7 +38941,7 @@
         <v>44839</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38998,7 +38998,7 @@
         <v>44839</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39060,7 +39060,7 @@
         <v>44840</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39117,7 +39117,7 @@
         <v>44841</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39174,7 +39174,7 @@
         <v>44841</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39236,7 +39236,7 @@
         <v>44841</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39293,7 +39293,7 @@
         <v>44841</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39350,7 +39350,7 @@
         <v>44845</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39412,7 +39412,7 @@
         <v>44845</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39474,7 +39474,7 @@
         <v>44847</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39531,7 +39531,7 @@
         <v>44851</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39593,7 +39593,7 @@
         <v>44851</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39655,7 +39655,7 @@
         <v>44851</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39717,7 +39717,7 @@
         <v>44851</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39779,7 +39779,7 @@
         <v>44855</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39841,7 +39841,7 @@
         <v>44860</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39903,7 +39903,7 @@
         <v>44862</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39965,7 +39965,7 @@
         <v>44862</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40027,7 +40027,7 @@
         <v>44866</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40089,7 +40089,7 @@
         <v>44866</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40151,7 +40151,7 @@
         <v>44866</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40213,7 +40213,7 @@
         <v>44866</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40270,7 +40270,7 @@
         <v>44868</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40327,7 +40327,7 @@
         <v>44872</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40384,7 +40384,7 @@
         <v>44873</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40441,7 +40441,7 @@
         <v>44873</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40498,7 +40498,7 @@
         <v>44873</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40555,7 +40555,7 @@
         <v>44874</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40612,7 +40612,7 @@
         <v>44874</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40669,7 +40669,7 @@
         <v>44875</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40726,7 +40726,7 @@
         <v>44875</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40783,7 +40783,7 @@
         <v>44879</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40845,7 +40845,7 @@
         <v>44882</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40902,7 +40902,7 @@
         <v>44883</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40964,7 +40964,7 @@
         <v>44883</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41026,7 +41026,7 @@
         <v>44887</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41083,7 +41083,7 @@
         <v>44889</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41140,7 +41140,7 @@
         <v>44890</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41197,7 +41197,7 @@
         <v>44891</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41254,7 +41254,7 @@
         <v>44893</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41311,7 +41311,7 @@
         <v>44897</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41368,7 +41368,7 @@
         <v>44903</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41425,7 +41425,7 @@
         <v>44907</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41487,7 +41487,7 @@
         <v>44907</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41544,7 +41544,7 @@
         <v>44909</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41606,7 +41606,7 @@
         <v>44909</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41688,7 +41688,7 @@
         <v>44909</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41745,7 +41745,7 @@
         <v>44909</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41802,7 +41802,7 @@
         <v>44910</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41859,7 +41859,7 @@
         <v>44911</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41916,7 +41916,7 @@
         <v>44911</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41973,7 +41973,7 @@
         <v>44911</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42030,7 +42030,7 @@
         <v>44911</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42087,7 +42087,7 @@
         <v>44914</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42144,7 +42144,7 @@
         <v>44914</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42201,7 +42201,7 @@
         <v>44914</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42258,7 +42258,7 @@
         <v>44916</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42315,7 +42315,7 @@
         <v>44916</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42372,7 +42372,7 @@
         <v>44922</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42429,7 +42429,7 @@
         <v>44928</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42486,7 +42486,7 @@
         <v>44929</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42543,7 +42543,7 @@
         <v>44929</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42600,7 +42600,7 @@
         <v>44930</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42657,7 +42657,7 @@
         <v>44930</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42714,7 +42714,7 @@
         <v>44930</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42771,7 +42771,7 @@
         <v>44930</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42828,7 +42828,7 @@
         <v>44931</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42890,7 +42890,7 @@
         <v>44939</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42947,7 +42947,7 @@
         <v>44939</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43004,7 +43004,7 @@
         <v>44944</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43061,7 +43061,7 @@
         <v>44944</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43118,7 +43118,7 @@
         <v>44945</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43175,7 +43175,7 @@
         <v>44949</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43232,7 +43232,7 @@
         <v>44950</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43289,7 +43289,7 @@
         <v>44950</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43346,7 +43346,7 @@
         <v>44953</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43403,7 +43403,7 @@
         <v>44956</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43460,7 +43460,7 @@
         <v>44960</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43517,7 +43517,7 @@
         <v>44964</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43574,7 +43574,7 @@
         <v>44964</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43631,7 +43631,7 @@
         <v>44964</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43688,7 +43688,7 @@
         <v>44964</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43745,7 +43745,7 @@
         <v>44964</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43802,7 +43802,7 @@
         <v>44964</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43859,7 +43859,7 @@
         <v>44964</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43916,7 +43916,7 @@
         <v>44966</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43973,7 +43973,7 @@
         <v>44967</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44030,7 +44030,7 @@
         <v>44967</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44087,7 +44087,7 @@
         <v>44967</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44144,7 +44144,7 @@
         <v>44967</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44201,7 +44201,7 @@
         <v>44967</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44258,7 +44258,7 @@
         <v>44970</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44315,7 +44315,7 @@
         <v>44970</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44372,7 +44372,7 @@
         <v>44973</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44429,7 +44429,7 @@
         <v>44977</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44486,7 +44486,7 @@
         <v>44977</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44543,7 +44543,7 @@
         <v>44982</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44600,7 +44600,7 @@
         <v>44991</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -44657,7 +44657,7 @@
         <v>44997</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44714,7 +44714,7 @@
         <v>45002</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44771,7 +44771,7 @@
         <v>45002</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44828,7 +44828,7 @@
         <v>45002</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44885,7 +44885,7 @@
         <v>45019</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44942,7 +44942,7 @@
         <v>45019</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44999,7 +44999,7 @@
         <v>45019</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45056,7 +45056,7 @@
         <v>45021</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45113,7 +45113,7 @@
         <v>45027</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45170,7 +45170,7 @@
         <v>45033</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45227,7 +45227,7 @@
         <v>45040</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45289,7 +45289,7 @@
         <v>45042</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45346,7 +45346,7 @@
         <v>45058</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45403,7 +45403,7 @@
         <v>45062</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45465,7 +45465,7 @@
         <v>45063</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45522,7 +45522,7 @@
         <v>45070</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45579,7 +45579,7 @@
         <v>45071</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45636,7 +45636,7 @@
         <v>45071</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45693,7 +45693,7 @@
         <v>45071</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45750,7 +45750,7 @@
         <v>45071</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45807,7 +45807,7 @@
         <v>45071</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45864,7 +45864,7 @@
         <v>45071</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45921,7 +45921,7 @@
         <v>45072</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -45978,7 +45978,7 @@
         <v>45072</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46035,7 +46035,7 @@
         <v>45072</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46097,7 +46097,7 @@
         <v>45075</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46154,7 +46154,7 @@
         <v>45075</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46211,7 +46211,7 @@
         <v>45077</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46268,7 +46268,7 @@
         <v>45079</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46325,7 +46325,7 @@
         <v>45084</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46382,7 +46382,7 @@
         <v>45085</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46439,7 +46439,7 @@
         <v>45085</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46496,7 +46496,7 @@
         <v>45090</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46553,7 +46553,7 @@
         <v>45090</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46610,7 +46610,7 @@
         <v>45090</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46667,7 +46667,7 @@
         <v>45092</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46729,7 +46729,7 @@
         <v>45092</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46786,7 +46786,7 @@
         <v>45093</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46848,7 +46848,7 @@
         <v>45093</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46910,7 +46910,7 @@
         <v>45096</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46967,7 +46967,7 @@
         <v>45096</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47029,7 +47029,7 @@
         <v>45096</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47091,7 +47091,7 @@
         <v>45097</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47148,7 +47148,7 @@
         <v>45097</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47210,7 +47210,7 @@
         <v>45097</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47272,7 +47272,7 @@
         <v>45098</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47329,7 +47329,7 @@
         <v>45098</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47386,7 +47386,7 @@
         <v>45099</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47448,7 +47448,7 @@
         <v>45103</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -47505,7 +47505,7 @@
         <v>45103</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47562,7 +47562,7 @@
         <v>45104</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -47619,7 +47619,7 @@
         <v>45105</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -47676,7 +47676,7 @@
         <v>45105</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -47733,7 +47733,7 @@
         <v>45106</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47790,7 +47790,7 @@
         <v>45107</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -47847,7 +47847,7 @@
         <v>45107</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -47904,7 +47904,7 @@
         <v>45107</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -47961,7 +47961,7 @@
         <v>45111</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -48023,7 +48023,7 @@
         <v>45111</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48080,7 +48080,7 @@
         <v>45112</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -48137,7 +48137,7 @@
         <v>45112</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -48199,7 +48199,7 @@
         <v>45112</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48261,7 +48261,7 @@
         <v>45112</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48318,7 +48318,7 @@
         <v>45114</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48375,7 +48375,7 @@
         <v>45114</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48432,7 +48432,7 @@
         <v>45119</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -48489,7 +48489,7 @@
         <v>45120</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -48551,7 +48551,7 @@
         <v>45124</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -48613,7 +48613,7 @@
         <v>45124</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -48670,7 +48670,7 @@
         <v>45131</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -48732,7 +48732,7 @@
         <v>45131</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48794,7 +48794,7 @@
         <v>45132</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -48851,7 +48851,7 @@
         <v>45132</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -48908,7 +48908,7 @@
         <v>45138</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -48970,7 +48970,7 @@
         <v>45138</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -49032,7 +49032,7 @@
         <v>45139</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -49089,7 +49089,7 @@
         <v>45139</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -49146,7 +49146,7 @@
         <v>45140</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -49203,7 +49203,7 @@
         <v>45145</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49265,7 +49265,7 @@
         <v>45148</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -49322,7 +49322,7 @@
         <v>45152</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49379,7 +49379,7 @@
         <v>45152</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49441,7 +49441,7 @@
         <v>45152</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -49503,7 +49503,7 @@
         <v>45154</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -49560,7 +49560,7 @@
         <v>45155</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -49617,7 +49617,7 @@
         <v>45159</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -49679,7 +49679,7 @@
         <v>45159</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -49736,7 +49736,7 @@
         <v>45160</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -49798,7 +49798,7 @@
         <v>45160</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -49860,7 +49860,7 @@
         <v>45161</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -49917,7 +49917,7 @@
         <v>45161</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -49979,7 +49979,7 @@
         <v>45166</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -50036,7 +50036,7 @@
         <v>45167</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -50093,7 +50093,7 @@
         <v>45168</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -50150,7 +50150,7 @@
         <v>45168</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -50207,7 +50207,7 @@
         <v>45168</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -50264,7 +50264,7 @@
         <v>45173</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -50321,7 +50321,7 @@
         <v>45173</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -50378,7 +50378,7 @@
         <v>45173</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -50435,7 +50435,7 @@
         <v>45174</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -50492,7 +50492,7 @@
         <v>45175</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -50554,7 +50554,7 @@
         <v>45175</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -50616,7 +50616,7 @@
         <v>45176</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -50678,7 +50678,7 @@
         <v>45176</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -50740,7 +50740,7 @@
         <v>45176</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -50802,7 +50802,7 @@
         <v>45176</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -50864,7 +50864,7 @@
         <v>45176</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -50921,7 +50921,7 @@
         <v>45176</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -50978,7 +50978,7 @@
         <v>45176</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -51035,7 +51035,7 @@
         <v>45180</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -51097,7 +51097,7 @@
         <v>45180</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -51159,7 +51159,7 @@
         <v>45181</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -51216,7 +51216,7 @@
         <v>45181</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -51273,7 +51273,7 @@
         <v>45181</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -51330,7 +51330,7 @@
         <v>45181</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -51387,7 +51387,7 @@
         <v>45182</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -51444,7 +51444,7 @@
         <v>45182</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -51501,7 +51501,7 @@
         <v>45182</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -51558,7 +51558,7 @@
         <v>45183</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -51615,7 +51615,7 @@
         <v>45183</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -51672,7 +51672,7 @@
         <v>45183</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -51729,7 +51729,7 @@
         <v>45187</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -51786,7 +51786,7 @@
         <v>45187</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -51848,7 +51848,7 @@
         <v>45188</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -51905,7 +51905,7 @@
         <v>45188</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -51962,7 +51962,7 @@
         <v>45188</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -52019,7 +52019,7 @@
         <v>45188</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -52076,7 +52076,7 @@
         <v>45190</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -52133,7 +52133,7 @@
         <v>45190</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -52190,7 +52190,7 @@
         <v>45194</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -52247,7 +52247,7 @@
         <v>45194</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -52304,7 +52304,7 @@
         <v>45194</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -52361,7 +52361,7 @@
         <v>45194</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -52418,7 +52418,7 @@
         <v>45194</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -52475,7 +52475,7 @@
         <v>45194</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -52537,7 +52537,7 @@
         <v>45194</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -52594,7 +52594,7 @@
         <v>45194</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -52651,7 +52651,7 @@
         <v>45194</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -52713,7 +52713,7 @@
         <v>45194</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -52775,7 +52775,7 @@
         <v>45195</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -52832,7 +52832,7 @@
         <v>45198</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -52889,7 +52889,7 @@
         <v>45198</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -52946,7 +52946,7 @@
         <v>45201</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -53003,7 +53003,7 @@
         <v>45201</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -53060,7 +53060,7 @@
         <v>45201</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -53117,7 +53117,7 @@
         <v>45201</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -53174,7 +53174,7 @@
         <v>45202</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -53231,7 +53231,7 @@
         <v>45203</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -53288,7 +53288,7 @@
         <v>45203</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -53345,7 +53345,7 @@
         <v>45204</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -53402,7 +53402,7 @@
         <v>45204</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -53459,7 +53459,7 @@
         <v>45204</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -53516,7 +53516,7 @@
         <v>45204</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -53578,7 +53578,7 @@
         <v>45204</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -53635,7 +53635,7 @@
         <v>45205</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -53697,7 +53697,7 @@
         <v>45208</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -53754,7 +53754,7 @@
         <v>45209</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -53816,7 +53816,7 @@
         <v>45209</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -53878,7 +53878,7 @@
         <v>45210</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -53935,7 +53935,7 @@
         <v>45210</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -53992,7 +53992,7 @@
         <v>45210</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -54049,7 +54049,7 @@
         <v>45211</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -54106,7 +54106,7 @@
         <v>45211</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -54168,7 +54168,7 @@
         <v>45215</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -54225,7 +54225,7 @@
         <v>45215</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -54282,7 +54282,7 @@
         <v>45216</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -54339,7 +54339,7 @@
         <v>45217</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -54396,7 +54396,7 @@
         <v>45217</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -54453,7 +54453,7 @@
         <v>45217</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -54510,7 +54510,7 @@
         <v>45217</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -54567,7 +54567,7 @@
         <v>45222</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -54629,7 +54629,7 @@
         <v>45222</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -54686,7 +54686,7 @@
         <v>45222</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -54743,7 +54743,7 @@
         <v>45223</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -54805,7 +54805,7 @@
         <v>45223</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -54862,7 +54862,7 @@
         <v>45225</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -54924,7 +54924,7 @@
         <v>45225</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -54981,7 +54981,7 @@
         <v>45225</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -55043,7 +55043,7 @@
         <v>45225</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -55100,7 +55100,7 @@
         <v>45225</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -55157,7 +55157,7 @@
         <v>45225</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -55214,7 +55214,7 @@
         <v>45225</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -55271,7 +55271,7 @@
         <v>45225</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -55328,7 +55328,7 @@
         <v>45225</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -55385,7 +55385,7 @@
         <v>45226</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -55442,7 +55442,7 @@
         <v>45229</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -55499,7 +55499,7 @@
         <v>45229</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -55556,7 +55556,7 @@
         <v>45229</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -55613,7 +55613,7 @@
         <v>45229</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -55670,7 +55670,7 @@
         <v>45229</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -55727,7 +55727,7 @@
         <v>45230</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -55784,7 +55784,7 @@
         <v>45230</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -55841,7 +55841,7 @@
         <v>45230</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -55898,7 +55898,7 @@
         <v>45230</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -55955,7 +55955,7 @@
         <v>45230</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -56012,7 +56012,7 @@
         <v>45231</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -56069,7 +56069,7 @@
         <v>45231</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -56126,7 +56126,7 @@
         <v>45231</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -56183,7 +56183,7 @@
         <v>45231</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -56240,7 +56240,7 @@
         <v>45231</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -56297,7 +56297,7 @@
         <v>45231</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -56354,7 +56354,7 @@
         <v>45231</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -56411,7 +56411,7 @@
         <v>45232</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -56473,7 +56473,7 @@
         <v>45232</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -56530,7 +56530,7 @@
         <v>45232</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -56587,7 +56587,7 @@
         <v>45232</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -56644,7 +56644,7 @@
         <v>45233</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -56706,7 +56706,7 @@
         <v>45236</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -56763,7 +56763,7 @@
         <v>45236</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -56820,7 +56820,7 @@
         <v>45236</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -56877,7 +56877,7 @@
         <v>45237</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -56934,7 +56934,7 @@
         <v>45237</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -56996,7 +56996,7 @@
         <v>45239</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -57053,7 +57053,7 @@
         <v>45239</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -57110,7 +57110,7 @@
         <v>45240</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -57172,7 +57172,7 @@
         <v>45243</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -57229,7 +57229,7 @@
         <v>45243</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -57286,7 +57286,7 @@
         <v>45243</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -57343,7 +57343,7 @@
         <v>45243</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -57400,7 +57400,7 @@
         <v>45243</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -57457,7 +57457,7 @@
         <v>45243</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -57514,7 +57514,7 @@
         <v>45244</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -57571,7 +57571,7 @@
         <v>45244</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -57633,7 +57633,7 @@
         <v>45244</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -57695,7 +57695,7 @@
         <v>45244</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -57752,7 +57752,7 @@
         <v>45244</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -57809,7 +57809,7 @@
         <v>45244</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -57871,7 +57871,7 @@
         <v>45244</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -57928,7 +57928,7 @@
         <v>45245</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -57985,7 +57985,7 @@
         <v>45245</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -58042,7 +58042,7 @@
         <v>45245</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -58099,7 +58099,7 @@
         <v>45245</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -58156,7 +58156,7 @@
         <v>45245</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -58218,7 +58218,7 @@
         <v>45245</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -58275,7 +58275,7 @@
         <v>45245</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -58332,7 +58332,7 @@
         <v>45247</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -58389,7 +58389,7 @@
         <v>45247</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -58446,7 +58446,7 @@
         <v>45248</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -58503,7 +58503,7 @@
         <v>45250</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -58560,7 +58560,7 @@
         <v>45250</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -58617,7 +58617,7 @@
         <v>45251</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -58674,7 +58674,7 @@
         <v>45251</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -58731,7 +58731,7 @@
         <v>45251</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -58788,7 +58788,7 @@
         <v>45252</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -58845,7 +58845,7 @@
         <v>45253</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -58907,7 +58907,7 @@
         <v>45253</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -58964,7 +58964,7 @@
         <v>45253</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -59026,7 +59026,7 @@
         <v>45253</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -59083,7 +59083,7 @@
         <v>45253</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -59145,7 +59145,7 @@
         <v>45253</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -59207,7 +59207,7 @@
         <v>45253</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -59264,7 +59264,7 @@
         <v>45257</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -59321,7 +59321,7 @@
         <v>45258</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -59378,7 +59378,7 @@
         <v>45259</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -59435,7 +59435,7 @@
         <v>45260</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -59492,7 +59492,7 @@
         <v>45261</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -59549,7 +59549,7 @@
         <v>45261</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -59606,7 +59606,7 @@
         <v>45264</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -59663,7 +59663,7 @@
         <v>45264</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -59720,7 +59720,7 @@
         <v>45264</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -59777,7 +59777,7 @@
         <v>45264</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -59834,7 +59834,7 @@
         <v>45264</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -59891,7 +59891,7 @@
         <v>45264</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -59948,7 +59948,7 @@
         <v>45265</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -60005,7 +60005,7 @@
         <v>45265</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -60062,7 +60062,7 @@
         <v>45265</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -60119,7 +60119,7 @@
         <v>45266</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -60176,7 +60176,7 @@
         <v>45266</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -60233,7 +60233,7 @@
         <v>45266</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -60290,7 +60290,7 @@
         <v>45266</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -60352,7 +60352,7 @@
         <v>45267</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -60409,7 +60409,7 @@
         <v>45267</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -60466,7 +60466,7 @@
         <v>45267</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -60523,7 +60523,7 @@
         <v>45267</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -60580,7 +60580,7 @@
         <v>45267</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -60637,7 +60637,7 @@
         <v>45268</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -60694,7 +60694,7 @@
         <v>45271</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -60751,7 +60751,7 @@
         <v>45273</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -60808,7 +60808,7 @@
         <v>45273</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -60865,7 +60865,7 @@
         <v>45275</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -60922,7 +60922,7 @@
         <v>45279</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -60979,7 +60979,7 @@
         <v>45279</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -61036,7 +61036,7 @@
         <v>45279</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -61093,7 +61093,7 @@
         <v>45281</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -61150,7 +61150,7 @@
         <v>45281</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -61212,7 +61212,7 @@
         <v>45282</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -61269,7 +61269,7 @@
         <v>45287</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -61331,7 +61331,7 @@
         <v>45297</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -61393,7 +61393,7 @@
         <v>45299</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -61450,7 +61450,7 @@
         <v>45300</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -61507,7 +61507,7 @@
         <v>45300</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -61564,7 +61564,7 @@
         <v>45302</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -61621,7 +61621,7 @@
         <v>45302</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -61678,7 +61678,7 @@
         <v>45303</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -61735,7 +61735,7 @@
         <v>45306</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -61792,7 +61792,7 @@
         <v>45306</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -61849,7 +61849,7 @@
         <v>45307</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -61906,7 +61906,7 @@
         <v>45307</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -61963,7 +61963,7 @@
         <v>45307</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -62020,7 +62020,7 @@
         <v>45307</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -62077,7 +62077,7 @@
         <v>45307</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -62134,7 +62134,7 @@
         <v>45310</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -62191,7 +62191,7 @@
         <v>45310</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -62248,7 +62248,7 @@
         <v>45310</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -62305,7 +62305,7 @@
         <v>45310</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -62362,7 +62362,7 @@
         <v>45310</v>
       </c>
       <c r="C1038" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
@@ -62419,7 +62419,7 @@
         <v>45310</v>
       </c>
       <c r="C1039" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
@@ -62476,7 +62476,7 @@
         <v>45310</v>
       </c>
       <c r="C1040" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
@@ -62533,7 +62533,7 @@
         <v>45310</v>
       </c>
       <c r="C1041" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
@@ -62590,7 +62590,7 @@
         <v>45310</v>
       </c>
       <c r="C1042" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
@@ -62647,7 +62647,7 @@
         <v>45313</v>
       </c>
       <c r="C1043" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1043" t="inlineStr">
         <is>
@@ -62704,7 +62704,7 @@
         <v>45314</v>
       </c>
       <c r="C1044" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1044" t="inlineStr">
         <is>
@@ -62761,7 +62761,7 @@
         <v>45314</v>
       </c>
       <c r="C1045" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1045" t="inlineStr">
         <is>
@@ -62818,7 +62818,7 @@
         <v>45314</v>
       </c>
       <c r="C1046" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1046" t="inlineStr">
         <is>
@@ -62875,7 +62875,7 @@
         <v>45316</v>
       </c>
       <c r="C1047" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1047" t="inlineStr">
         <is>
@@ -62932,7 +62932,7 @@
         <v>45317</v>
       </c>
       <c r="C1048" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1048" t="inlineStr">
         <is>
@@ -62982,14 +62982,14 @@
     <row r="1049" ht="15" customHeight="1">
       <c r="A1049" t="inlineStr">
         <is>
-          <t>A 3638-2024</t>
+          <t>A 3640-2024</t>
         </is>
       </c>
       <c r="B1049" s="1" t="n">
         <v>45321</v>
       </c>
       <c r="C1049" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1049" t="inlineStr">
         <is>
@@ -63002,7 +63002,7 @@
         </is>
       </c>
       <c r="G1049" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="H1049" t="n">
         <v>0</v>
@@ -63039,14 +63039,14 @@
     <row r="1050" ht="15" customHeight="1">
       <c r="A1050" t="inlineStr">
         <is>
-          <t>A 3651-2024</t>
+          <t>A 3644-2024</t>
         </is>
       </c>
       <c r="B1050" s="1" t="n">
         <v>45321</v>
       </c>
       <c r="C1050" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1050" t="inlineStr">
         <is>
@@ -63059,7 +63059,7 @@
         </is>
       </c>
       <c r="G1050" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="H1050" t="n">
         <v>0</v>
@@ -63096,14 +63096,14 @@
     <row r="1051" ht="15" customHeight="1">
       <c r="A1051" t="inlineStr">
         <is>
-          <t>A 3655-2024</t>
+          <t>A 3638-2024</t>
         </is>
       </c>
       <c r="B1051" s="1" t="n">
         <v>45321</v>
       </c>
       <c r="C1051" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1051" t="inlineStr">
         <is>
@@ -63116,7 +63116,7 @@
         </is>
       </c>
       <c r="G1051" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="H1051" t="n">
         <v>0</v>
@@ -63153,14 +63153,14 @@
     <row r="1052" ht="15" customHeight="1">
       <c r="A1052" t="inlineStr">
         <is>
-          <t>A 3686-2024</t>
+          <t>A 3651-2024</t>
         </is>
       </c>
       <c r="B1052" s="1" t="n">
         <v>45321</v>
       </c>
       <c r="C1052" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1052" t="inlineStr">
         <is>
@@ -63173,7 +63173,7 @@
         </is>
       </c>
       <c r="G1052" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="H1052" t="n">
         <v>0</v>
@@ -63210,14 +63210,14 @@
     <row r="1053" ht="15" customHeight="1">
       <c r="A1053" t="inlineStr">
         <is>
-          <t>A 3640-2024</t>
+          <t>A 3655-2024</t>
         </is>
       </c>
       <c r="B1053" s="1" t="n">
         <v>45321</v>
       </c>
       <c r="C1053" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1053" t="inlineStr">
         <is>
@@ -63230,7 +63230,7 @@
         </is>
       </c>
       <c r="G1053" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="H1053" t="n">
         <v>0</v>
@@ -63267,14 +63267,14 @@
     <row r="1054" ht="15" customHeight="1">
       <c r="A1054" t="inlineStr">
         <is>
-          <t>A 3644-2024</t>
+          <t>A 3686-2024</t>
         </is>
       </c>
       <c r="B1054" s="1" t="n">
         <v>45321</v>
       </c>
       <c r="C1054" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1054" t="inlineStr">
         <is>
@@ -63287,7 +63287,7 @@
         </is>
       </c>
       <c r="G1054" t="n">
-        <v>1.5</v>
+        <v>0.2</v>
       </c>
       <c r="H1054" t="n">
         <v>0</v>
@@ -63331,7 +63331,7 @@
         <v>45321</v>
       </c>
       <c r="C1055" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1055" t="inlineStr">
         <is>
@@ -63388,7 +63388,7 @@
         <v>45321</v>
       </c>
       <c r="C1056" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1056" t="inlineStr">
         <is>
@@ -63445,7 +63445,7 @@
         <v>45321</v>
       </c>
       <c r="C1057" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1057" t="inlineStr">
         <is>
@@ -63502,7 +63502,7 @@
         <v>45321</v>
       </c>
       <c r="C1058" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1058" t="inlineStr">
         <is>
@@ -63559,7 +63559,7 @@
         <v>45321</v>
       </c>
       <c r="C1059" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1059" t="inlineStr">
         <is>
@@ -63616,7 +63616,7 @@
         <v>45321</v>
       </c>
       <c r="C1060" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1060" t="inlineStr">
         <is>
@@ -63673,7 +63673,7 @@
         <v>45322</v>
       </c>
       <c r="C1061" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1061" t="inlineStr">
         <is>
@@ -63730,7 +63730,7 @@
         <v>45324</v>
       </c>
       <c r="C1062" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1062" t="inlineStr">
         <is>
@@ -63787,7 +63787,7 @@
         <v>45329</v>
       </c>
       <c r="C1063" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1063" t="inlineStr">
         <is>
@@ -63844,7 +63844,7 @@
         <v>45329</v>
       </c>
       <c r="C1064" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1064" t="inlineStr">
         <is>
@@ -63894,14 +63894,14 @@
     <row r="1065" ht="15" customHeight="1">
       <c r="A1065" t="inlineStr">
         <is>
-          <t>A 5156-2024</t>
+          <t>A 5110-2024</t>
         </is>
       </c>
       <c r="B1065" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C1065" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1065" t="inlineStr">
         <is>
@@ -63914,7 +63914,7 @@
         </is>
       </c>
       <c r="G1065" t="n">
-        <v>0.4</v>
+        <v>3.3</v>
       </c>
       <c r="H1065" t="n">
         <v>0</v>
@@ -63951,14 +63951,14 @@
     <row r="1066" ht="15" customHeight="1">
       <c r="A1066" t="inlineStr">
         <is>
-          <t>A 5189-2024</t>
+          <t>A 5122-2024</t>
         </is>
       </c>
       <c r="B1066" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C1066" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1066" t="inlineStr">
         <is>
@@ -63971,7 +63971,7 @@
         </is>
       </c>
       <c r="G1066" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="H1066" t="n">
         <v>0</v>
@@ -64008,14 +64008,14 @@
     <row r="1067" ht="15" customHeight="1">
       <c r="A1067" t="inlineStr">
         <is>
-          <t>A 5110-2024</t>
+          <t>A 5124-2024</t>
         </is>
       </c>
       <c r="B1067" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C1067" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1067" t="inlineStr">
         <is>
@@ -64028,7 +64028,7 @@
         </is>
       </c>
       <c r="G1067" t="n">
-        <v>3.3</v>
+        <v>2.6</v>
       </c>
       <c r="H1067" t="n">
         <v>0</v>
@@ -64065,14 +64065,14 @@
     <row r="1068" ht="15" customHeight="1">
       <c r="A1068" t="inlineStr">
         <is>
-          <t>A 5122-2024</t>
+          <t>A 5156-2024</t>
         </is>
       </c>
       <c r="B1068" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C1068" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1068" t="inlineStr">
         <is>
@@ -64085,7 +64085,7 @@
         </is>
       </c>
       <c r="G1068" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="H1068" t="n">
         <v>0</v>
@@ -64122,14 +64122,14 @@
     <row r="1069" ht="15" customHeight="1">
       <c r="A1069" t="inlineStr">
         <is>
-          <t>A 5124-2024</t>
+          <t>A 5174-2024</t>
         </is>
       </c>
       <c r="B1069" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C1069" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1069" t="inlineStr">
         <is>
@@ -64142,7 +64142,7 @@
         </is>
       </c>
       <c r="G1069" t="n">
-        <v>2.6</v>
+        <v>1.4</v>
       </c>
       <c r="H1069" t="n">
         <v>0</v>
@@ -64179,14 +64179,14 @@
     <row r="1070" ht="15" customHeight="1">
       <c r="A1070" t="inlineStr">
         <is>
-          <t>A 5174-2024</t>
+          <t>A 5189-2024</t>
         </is>
       </c>
       <c r="B1070" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C1070" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1070" t="inlineStr">
         <is>
@@ -64199,7 +64199,7 @@
         </is>
       </c>
       <c r="G1070" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="H1070" t="n">
         <v>0</v>
@@ -64243,7 +64243,7 @@
         <v>45331</v>
       </c>
       <c r="C1071" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1071" t="inlineStr">
         <is>
@@ -64300,7 +64300,7 @@
         <v>45331</v>
       </c>
       <c r="C1072" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1072" t="inlineStr">
         <is>
@@ -64357,7 +64357,7 @@
         <v>45334</v>
       </c>
       <c r="C1073" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1073" t="inlineStr">
         <is>
@@ -64414,7 +64414,7 @@
         <v>45334</v>
       </c>
       <c r="C1074" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1074" t="inlineStr">
         <is>
@@ -64471,7 +64471,7 @@
         <v>45337</v>
       </c>
       <c r="C1075" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1075" t="inlineStr">
         <is>
@@ -64528,7 +64528,7 @@
         <v>45337</v>
       </c>
       <c r="C1076" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1076" t="inlineStr">
         <is>
@@ -64575,7 +64575,7 @@
       </c>
       <c r="R1076" s="2" t="inlineStr"/>
     </row>
-    <row r="1077">
+    <row r="1077" ht="15" customHeight="1">
       <c r="A1077" t="inlineStr">
         <is>
           <t>A 6213-2024</t>
@@ -64585,7 +64585,7 @@
         <v>45337</v>
       </c>
       <c r="C1077" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1077" t="inlineStr">
         <is>
@@ -64631,6 +64631,68 @@
         <v>0</v>
       </c>
       <c r="R1077" s="2" t="inlineStr"/>
+    </row>
+    <row r="1078">
+      <c r="A1078" t="inlineStr">
+        <is>
+          <t>A 7035-2024</t>
+        </is>
+      </c>
+      <c r="B1078" s="1" t="n">
+        <v>45343</v>
+      </c>
+      <c r="C1078" s="1" t="n">
+        <v>45344</v>
+      </c>
+      <c r="D1078" t="inlineStr">
+        <is>
+          <t>DALARNAS LÄN</t>
+        </is>
+      </c>
+      <c r="E1078" t="inlineStr">
+        <is>
+          <t>RÄTTVIK</t>
+        </is>
+      </c>
+      <c r="F1078" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="G1078" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="H1078" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1078" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1078" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1078" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1078" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1078" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1078" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1078" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1078" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1078" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1078" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt RÄTTVIK.xlsx
+++ b/Översikt RÄTTVIK.xlsx
@@ -569,7 +569,7 @@
         <v>43542</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         <v>43663</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -781,7 +781,7 @@
         <v>43619</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
         <v>44909</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>43740</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>44909</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>44874</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>45147</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
         <v>44237</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1461,7 +1461,7 @@
         <v>44624</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         <v>43634</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         <v>43663</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1736,7 +1736,7 @@
         <v>44148</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         <v>44435</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1910,7 +1910,7 @@
         <v>44799</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         <v>44909</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         <v>44909</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
         <v>45111</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>43700</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>44496</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2450,7 +2450,7 @@
         <v>45033</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
         <v>43440</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         <v>43493</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
         <v>43623</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2791,7 +2791,7 @@
         <v>43705</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
         <v>44088</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2961,7 +2961,7 @@
         <v>44361</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3046,7 +3046,7 @@
         <v>44391</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         <v>44414</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3226,7 +3226,7 @@
         <v>44470</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3316,7 +3316,7 @@
         <v>44496</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
         <v>44511</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3491,7 +3491,7 @@
         <v>44568</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
         <v>44728</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3679,7 +3679,7 @@
         <v>44855</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3769,7 +3769,7 @@
         <v>44894</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3859,7 +3859,7 @@
         <v>44918</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3949,7 +3949,7 @@
         <v>44986</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4034,7 +4034,7 @@
         <v>45077</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4119,7 +4119,7 @@
         <v>45194</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4204,7 +4204,7 @@
         <v>45194</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4289,7 +4289,7 @@
         <v>45231</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4374,7 +4374,7 @@
         <v>43333</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4431,7 +4431,7 @@
         <v>43348</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4488,7 +4488,7 @@
         <v>43356</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4545,7 +4545,7 @@
         <v>43361</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4602,7 +4602,7 @@
         <v>43362</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4659,7 +4659,7 @@
         <v>43362</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4716,7 +4716,7 @@
         <v>43362</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4773,7 +4773,7 @@
         <v>43362</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4830,7 +4830,7 @@
         <v>43367</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4887,7 +4887,7 @@
         <v>43369</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4944,7 +4944,7 @@
         <v>43373</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5001,7 +5001,7 @@
         <v>43378</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5058,7 +5058,7 @@
         <v>43381</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5115,7 +5115,7 @@
         <v>43381</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5172,7 +5172,7 @@
         <v>43388</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5229,7 +5229,7 @@
         <v>43388</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5291,7 +5291,7 @@
         <v>43388</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5348,7 +5348,7 @@
         <v>43391</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5405,7 +5405,7 @@
         <v>43398</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
         <v>43399</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5519,7 +5519,7 @@
         <v>43401</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5576,7 +5576,7 @@
         <v>43405</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5633,7 +5633,7 @@
         <v>43405</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5690,7 +5690,7 @@
         <v>43410</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5747,7 +5747,7 @@
         <v>43410</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5804,7 +5804,7 @@
         <v>43411</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5861,7 +5861,7 @@
         <v>43412</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5918,7 +5918,7 @@
         <v>43416</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5975,7 +5975,7 @@
         <v>43416</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6032,7 +6032,7 @@
         <v>43416</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6089,7 +6089,7 @@
         <v>43419</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6146,7 +6146,7 @@
         <v>43419</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6203,7 +6203,7 @@
         <v>43423</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6265,7 +6265,7 @@
         <v>43423</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         <v>43423</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6389,7 +6389,7 @@
         <v>43424</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6451,7 +6451,7 @@
         <v>43425</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6508,7 +6508,7 @@
         <v>43427</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6570,7 +6570,7 @@
         <v>43428</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6627,7 +6627,7 @@
         <v>43428</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6684,7 +6684,7 @@
         <v>43430</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6741,7 +6741,7 @@
         <v>43430</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6798,7 +6798,7 @@
         <v>43430</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6855,7 +6855,7 @@
         <v>43430</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6912,7 +6912,7 @@
         <v>43431</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6974,7 +6974,7 @@
         <v>43432</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7031,7 +7031,7 @@
         <v>43432</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7088,7 +7088,7 @@
         <v>43434</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7145,7 +7145,7 @@
         <v>43434</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7202,7 +7202,7 @@
         <v>43438</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7259,7 +7259,7 @@
         <v>43441</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7316,7 +7316,7 @@
         <v>43447</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7373,7 +7373,7 @@
         <v>43448</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7430,7 +7430,7 @@
         <v>43451</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7487,7 +7487,7 @@
         <v>43451</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7544,7 +7544,7 @@
         <v>43451</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7601,7 +7601,7 @@
         <v>43452</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7658,7 +7658,7 @@
         <v>43454</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7720,7 +7720,7 @@
         <v>43454</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7782,7 +7782,7 @@
         <v>43454</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7844,7 +7844,7 @@
         <v>43455</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7901,7 +7901,7 @@
         <v>43461</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7958,7 +7958,7 @@
         <v>43471</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8015,7 +8015,7 @@
         <v>43472</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8072,7 +8072,7 @@
         <v>43472</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8134,7 +8134,7 @@
         <v>43473</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8191,7 +8191,7 @@
         <v>43475</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8248,7 +8248,7 @@
         <v>43481</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8305,7 +8305,7 @@
         <v>43490</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8362,7 +8362,7 @@
         <v>43495</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8419,7 +8419,7 @@
         <v>43499</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8476,7 +8476,7 @@
         <v>43500</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8538,7 +8538,7 @@
         <v>43511</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8595,7 +8595,7 @@
         <v>43511</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8652,7 +8652,7 @@
         <v>43514</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8709,7 +8709,7 @@
         <v>43517</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8766,7 +8766,7 @@
         <v>43524</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8823,7 +8823,7 @@
         <v>43546</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8880,7 +8880,7 @@
         <v>43553</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8942,7 +8942,7 @@
         <v>43553</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8999,7 +8999,7 @@
         <v>43554</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9056,7 +9056,7 @@
         <v>43556</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9113,7 +9113,7 @@
         <v>43559</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9175,7 +9175,7 @@
         <v>43564</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9232,7 +9232,7 @@
         <v>43566</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9289,7 +9289,7 @@
         <v>43570</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9351,7 +9351,7 @@
         <v>43570</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9413,7 +9413,7 @@
         <v>43570</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9470,7 +9470,7 @@
         <v>43580</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9527,7 +9527,7 @@
         <v>43584</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9584,7 +9584,7 @@
         <v>43585</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9641,7 +9641,7 @@
         <v>43587</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9698,7 +9698,7 @@
         <v>43592</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9755,7 +9755,7 @@
         <v>43592</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9812,7 +9812,7 @@
         <v>43592</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9869,7 +9869,7 @@
         <v>43599</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9926,7 +9926,7 @@
         <v>43609</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9983,7 +9983,7 @@
         <v>43612</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10040,7 +10040,7 @@
         <v>43612</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10097,7 +10097,7 @@
         <v>43612</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10154,7 +10154,7 @@
         <v>43612</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10211,7 +10211,7 @@
         <v>43616</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10268,7 +10268,7 @@
         <v>43619</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10330,7 +10330,7 @@
         <v>43621</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10387,7 +10387,7 @@
         <v>43623</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10444,7 +10444,7 @@
         <v>43628</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10506,7 +10506,7 @@
         <v>43628</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10568,7 +10568,7 @@
         <v>43629</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10625,7 +10625,7 @@
         <v>43630</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10682,7 +10682,7 @@
         <v>43633</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10739,7 +10739,7 @@
         <v>43633</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10796,7 +10796,7 @@
         <v>43641</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10853,7 +10853,7 @@
         <v>43643</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10915,7 +10915,7 @@
         <v>43643</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10977,7 +10977,7 @@
         <v>43647</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11039,7 +11039,7 @@
         <v>43651</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11096,7 +11096,7 @@
         <v>43651</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11153,7 +11153,7 @@
         <v>43656</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11210,7 +11210,7 @@
         <v>43657</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11267,7 +11267,7 @@
         <v>43662</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11324,7 +11324,7 @@
         <v>43662</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11381,7 +11381,7 @@
         <v>43663</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11463,7 +11463,7 @@
         <v>43663</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11525,7 +11525,7 @@
         <v>43663</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11587,7 +11587,7 @@
         <v>43663</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11649,7 +11649,7 @@
         <v>43682</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11706,7 +11706,7 @@
         <v>43686</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11768,7 +11768,7 @@
         <v>43686</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11825,7 +11825,7 @@
         <v>43689</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11887,7 +11887,7 @@
         <v>43690</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11944,7 +11944,7 @@
         <v>43697</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12001,7 +12001,7 @@
         <v>43700</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12058,7 +12058,7 @@
         <v>43705</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12115,7 +12115,7 @@
         <v>43711</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12177,7 +12177,7 @@
         <v>43712</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12234,7 +12234,7 @@
         <v>43713</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12291,7 +12291,7 @@
         <v>43714</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12348,7 +12348,7 @@
         <v>43714</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12405,7 +12405,7 @@
         <v>43717</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12462,7 +12462,7 @@
         <v>43718</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12519,7 +12519,7 @@
         <v>43720</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12576,7 +12576,7 @@
         <v>43724</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12633,7 +12633,7 @@
         <v>43726</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12690,7 +12690,7 @@
         <v>43727</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12747,7 +12747,7 @@
         <v>43727</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12804,7 +12804,7 @@
         <v>43727</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12861,7 +12861,7 @@
         <v>43732</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12918,7 +12918,7 @@
         <v>43734</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12980,7 +12980,7 @@
         <v>43734</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13037,7 +13037,7 @@
         <v>43734</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13094,7 +13094,7 @@
         <v>43735</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13156,7 +13156,7 @@
         <v>43735</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13213,7 +13213,7 @@
         <v>43740</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13275,7 +13275,7 @@
         <v>43740</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13332,7 +13332,7 @@
         <v>43740</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13389,7 +13389,7 @@
         <v>43740</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13446,7 +13446,7 @@
         <v>43742</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13508,7 +13508,7 @@
         <v>43742</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13565,7 +13565,7 @@
         <v>43747</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13622,7 +13622,7 @@
         <v>43758</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13679,7 +13679,7 @@
         <v>43761</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13736,7 +13736,7 @@
         <v>43766</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13793,7 +13793,7 @@
         <v>43767</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13855,7 +13855,7 @@
         <v>43769</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13917,7 +13917,7 @@
         <v>43770</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13974,7 +13974,7 @@
         <v>43770</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14031,7 +14031,7 @@
         <v>43773</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14088,7 +14088,7 @@
         <v>43775</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14145,7 +14145,7 @@
         <v>43776</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14202,7 +14202,7 @@
         <v>43776</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14259,7 +14259,7 @@
         <v>43776</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14316,7 +14316,7 @@
         <v>43776</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14373,7 +14373,7 @@
         <v>43780</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14435,7 +14435,7 @@
         <v>43780</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14492,7 +14492,7 @@
         <v>43780</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14549,7 +14549,7 @@
         <v>43780</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14606,7 +14606,7 @@
         <v>43783</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14668,7 +14668,7 @@
         <v>43784</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14725,7 +14725,7 @@
         <v>43786</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14782,7 +14782,7 @@
         <v>43797</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14839,7 +14839,7 @@
         <v>43804</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14901,7 +14901,7 @@
         <v>43805</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14958,7 +14958,7 @@
         <v>43805</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15015,7 +15015,7 @@
         <v>43812</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15072,7 +15072,7 @@
         <v>43812</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15129,7 +15129,7 @@
         <v>43815</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15186,7 +15186,7 @@
         <v>43815</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15243,7 +15243,7 @@
         <v>43829</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15300,7 +15300,7 @@
         <v>43833</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15357,7 +15357,7 @@
         <v>43837</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15414,7 +15414,7 @@
         <v>43839</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15471,7 +15471,7 @@
         <v>43840</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15528,7 +15528,7 @@
         <v>43843</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15585,7 +15585,7 @@
         <v>43845</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15647,7 +15647,7 @@
         <v>43850</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15704,7 +15704,7 @@
         <v>43854</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15766,7 +15766,7 @@
         <v>43857</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15823,7 +15823,7 @@
         <v>43857</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15885,7 +15885,7 @@
         <v>43857</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15942,7 +15942,7 @@
         <v>43864</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15999,7 +15999,7 @@
         <v>43864</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16061,7 +16061,7 @@
         <v>43864</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16123,7 +16123,7 @@
         <v>43867</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16185,7 +16185,7 @@
         <v>43871</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16242,7 +16242,7 @@
         <v>43872</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16304,7 +16304,7 @@
         <v>43873</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16361,7 +16361,7 @@
         <v>43873</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16418,7 +16418,7 @@
         <v>43873</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16475,7 +16475,7 @@
         <v>43874</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16532,7 +16532,7 @@
         <v>43878</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16589,7 +16589,7 @@
         <v>43879</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16651,7 +16651,7 @@
         <v>43880</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16708,7 +16708,7 @@
         <v>43894</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16765,7 +16765,7 @@
         <v>43894</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16822,7 +16822,7 @@
         <v>43902</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16879,7 +16879,7 @@
         <v>43917</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16936,7 +16936,7 @@
         <v>43917</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16998,7 +16998,7 @@
         <v>43920</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17060,7 +17060,7 @@
         <v>43920</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17122,7 +17122,7 @@
         <v>43921</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17184,7 +17184,7 @@
         <v>43922</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17246,7 +17246,7 @@
         <v>43922</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17308,7 +17308,7 @@
         <v>43924</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17365,7 +17365,7 @@
         <v>43924</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17422,7 +17422,7 @@
         <v>43927</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17479,7 +17479,7 @@
         <v>43927</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17536,7 +17536,7 @@
         <v>43928</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17593,7 +17593,7 @@
         <v>43928</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17650,7 +17650,7 @@
         <v>43930</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17712,7 +17712,7 @@
         <v>43933</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17774,7 +17774,7 @@
         <v>43933</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17836,7 +17836,7 @@
         <v>43935</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17893,7 +17893,7 @@
         <v>43937</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17955,7 +17955,7 @@
         <v>43941</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18012,7 +18012,7 @@
         <v>43941</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18069,7 +18069,7 @@
         <v>43948</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18126,7 +18126,7 @@
         <v>43949</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18188,7 +18188,7 @@
         <v>43949</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18250,7 +18250,7 @@
         <v>43949</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18312,7 +18312,7 @@
         <v>43949</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18374,7 +18374,7 @@
         <v>43950</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18431,7 +18431,7 @@
         <v>43951</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18493,7 +18493,7 @@
         <v>43959</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18555,7 +18555,7 @@
         <v>43959</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18617,7 +18617,7 @@
         <v>43959</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18679,7 +18679,7 @@
         <v>43959</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18736,7 +18736,7 @@
         <v>43969</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18798,7 +18798,7 @@
         <v>43970</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18855,7 +18855,7 @@
         <v>43973</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18912,7 +18912,7 @@
         <v>43985</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18969,7 +18969,7 @@
         <v>43990</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19026,7 +19026,7 @@
         <v>43991</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19088,7 +19088,7 @@
         <v>43991</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19150,7 +19150,7 @@
         <v>43991</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19212,7 +19212,7 @@
         <v>43991</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19274,7 +19274,7 @@
         <v>43991</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19336,7 +19336,7 @@
         <v>44005</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19398,7 +19398,7 @@
         <v>44033</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19455,7 +19455,7 @@
         <v>44039</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19512,7 +19512,7 @@
         <v>44048</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19569,7 +19569,7 @@
         <v>44049</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19626,7 +19626,7 @@
         <v>44053</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19683,7 +19683,7 @@
         <v>44053</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19740,7 +19740,7 @@
         <v>44053</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19797,7 +19797,7 @@
         <v>44054</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19859,7 +19859,7 @@
         <v>44054</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19916,7 +19916,7 @@
         <v>44054</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19973,7 +19973,7 @@
         <v>44055</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20035,7 +20035,7 @@
         <v>44055</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20097,7 +20097,7 @@
         <v>44074</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20154,7 +20154,7 @@
         <v>44074</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20211,7 +20211,7 @@
         <v>44077</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20268,7 +20268,7 @@
         <v>44078</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20330,7 +20330,7 @@
         <v>44078</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20392,7 +20392,7 @@
         <v>44082</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20449,7 +20449,7 @@
         <v>44084</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20511,7 +20511,7 @@
         <v>44089</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20568,7 +20568,7 @@
         <v>44091</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20625,7 +20625,7 @@
         <v>44095</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20682,7 +20682,7 @@
         <v>44097</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20739,7 +20739,7 @@
         <v>44102</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20796,7 +20796,7 @@
         <v>44104</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20853,7 +20853,7 @@
         <v>44105</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20910,7 +20910,7 @@
         <v>44109</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20967,7 +20967,7 @@
         <v>44109</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21029,7 +21029,7 @@
         <v>44110</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21086,7 +21086,7 @@
         <v>44117</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21148,7 +21148,7 @@
         <v>44126</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21210,7 +21210,7 @@
         <v>44126</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21272,7 +21272,7 @@
         <v>44126</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21334,7 +21334,7 @@
         <v>44126</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21396,7 +21396,7 @@
         <v>44126</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21458,7 +21458,7 @@
         <v>44130</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21515,7 +21515,7 @@
         <v>44130</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21572,7 +21572,7 @@
         <v>44130</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21629,7 +21629,7 @@
         <v>44130</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21686,7 +21686,7 @@
         <v>44131</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21743,7 +21743,7 @@
         <v>44133</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21805,7 +21805,7 @@
         <v>44137</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21862,7 +21862,7 @@
         <v>44139</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21919,7 +21919,7 @@
         <v>44139</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21976,7 +21976,7 @@
         <v>44141</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22033,7 +22033,7 @@
         <v>44145</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22090,7 +22090,7 @@
         <v>44145</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22147,7 +22147,7 @@
         <v>44151</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22204,7 +22204,7 @@
         <v>44151</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22261,7 +22261,7 @@
         <v>44153</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22318,7 +22318,7 @@
         <v>44159</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22375,7 +22375,7 @@
         <v>44159</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22432,7 +22432,7 @@
         <v>44159</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22489,7 +22489,7 @@
         <v>44159</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22546,7 +22546,7 @@
         <v>44160</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22603,7 +22603,7 @@
         <v>44160</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22660,7 +22660,7 @@
         <v>44160</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22717,7 +22717,7 @@
         <v>44161</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22774,7 +22774,7 @@
         <v>44162</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22831,7 +22831,7 @@
         <v>44173</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22888,7 +22888,7 @@
         <v>44175</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22945,7 +22945,7 @@
         <v>44175</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23002,7 +23002,7 @@
         <v>44179</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23059,7 +23059,7 @@
         <v>44179</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23116,7 +23116,7 @@
         <v>44180</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23173,7 +23173,7 @@
         <v>44185</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23230,7 +23230,7 @@
         <v>44186</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23287,7 +23287,7 @@
         <v>44186</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23344,7 +23344,7 @@
         <v>44194</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23401,7 +23401,7 @@
         <v>44195</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23458,7 +23458,7 @@
         <v>44214</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23515,7 +23515,7 @@
         <v>44214</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23572,7 +23572,7 @@
         <v>44217</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23629,7 +23629,7 @@
         <v>44217</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23686,7 +23686,7 @@
         <v>44228</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23743,7 +23743,7 @@
         <v>44228</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23800,7 +23800,7 @@
         <v>44238</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23857,7 +23857,7 @@
         <v>44242</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23914,7 +23914,7 @@
         <v>44242</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23971,7 +23971,7 @@
         <v>44271</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24028,7 +24028,7 @@
         <v>44273</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24085,7 +24085,7 @@
         <v>44280</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24142,7 +24142,7 @@
         <v>44281</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24199,7 +24199,7 @@
         <v>44284</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24256,7 +24256,7 @@
         <v>44284</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24313,7 +24313,7 @@
         <v>44300</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24370,7 +24370,7 @@
         <v>44300</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24427,7 +24427,7 @@
         <v>44300</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24484,7 +24484,7 @@
         <v>44305</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24541,7 +24541,7 @@
         <v>44306</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24598,7 +24598,7 @@
         <v>44307</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24655,7 +24655,7 @@
         <v>44322</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24717,7 +24717,7 @@
         <v>44326</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24774,7 +24774,7 @@
         <v>44326</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24831,7 +24831,7 @@
         <v>44326</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24888,7 +24888,7 @@
         <v>44326</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24945,7 +24945,7 @@
         <v>44330</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25002,7 +25002,7 @@
         <v>44335</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25059,7 +25059,7 @@
         <v>44336</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25121,7 +25121,7 @@
         <v>44340</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25178,7 +25178,7 @@
         <v>44342</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25240,7 +25240,7 @@
         <v>44347</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25297,7 +25297,7 @@
         <v>44347</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25354,7 +25354,7 @@
         <v>44348</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25411,7 +25411,7 @@
         <v>44348</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25468,7 +25468,7 @@
         <v>44349</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25525,7 +25525,7 @@
         <v>44349</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25582,7 +25582,7 @@
         <v>44350</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25639,7 +25639,7 @@
         <v>44351</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25696,7 +25696,7 @@
         <v>44351</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25753,7 +25753,7 @@
         <v>44363</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25810,7 +25810,7 @@
         <v>44377</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25872,7 +25872,7 @@
         <v>44377</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25929,7 +25929,7 @@
         <v>44377</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25986,7 +25986,7 @@
         <v>44377</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26043,7 +26043,7 @@
         <v>44377</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26105,7 +26105,7 @@
         <v>44386</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26167,7 +26167,7 @@
         <v>44386</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26229,7 +26229,7 @@
         <v>44391</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26291,7 +26291,7 @@
         <v>44391</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26353,7 +26353,7 @@
         <v>44399</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26410,7 +26410,7 @@
         <v>44400</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26467,7 +26467,7 @@
         <v>44403</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26524,7 +26524,7 @@
         <v>44408</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26586,7 +26586,7 @@
         <v>44409</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26648,7 +26648,7 @@
         <v>44414</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26710,7 +26710,7 @@
         <v>44414</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26772,7 +26772,7 @@
         <v>44414</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26834,7 +26834,7 @@
         <v>44418</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26891,7 +26891,7 @@
         <v>44420</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26948,7 +26948,7 @@
         <v>44421</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27005,7 +27005,7 @@
         <v>44421</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27067,7 +27067,7 @@
         <v>44424</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27129,7 +27129,7 @@
         <v>44424</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27186,7 +27186,7 @@
         <v>44432</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27248,7 +27248,7 @@
         <v>44435</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27305,7 +27305,7 @@
         <v>44441</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27362,7 +27362,7 @@
         <v>44441</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27424,7 +27424,7 @@
         <v>44449</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27486,7 +27486,7 @@
         <v>44451</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27548,7 +27548,7 @@
         <v>44451</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27610,7 +27610,7 @@
         <v>44454</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27667,7 +27667,7 @@
         <v>44459</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27729,7 +27729,7 @@
         <v>44459</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27791,7 +27791,7 @@
         <v>44459</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27853,7 +27853,7 @@
         <v>44459</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27915,7 +27915,7 @@
         <v>44459</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27977,7 +27977,7 @@
         <v>44459</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28039,7 +28039,7 @@
         <v>44460</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28096,7 +28096,7 @@
         <v>44460</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28153,7 +28153,7 @@
         <v>44461</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28210,7 +28210,7 @@
         <v>44463</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28272,7 +28272,7 @@
         <v>44467</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28334,7 +28334,7 @@
         <v>44469</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28396,7 +28396,7 @@
         <v>44469</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28458,7 +28458,7 @@
         <v>44469</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28520,7 +28520,7 @@
         <v>44469</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28582,7 +28582,7 @@
         <v>44470</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28644,7 +28644,7 @@
         <v>44470</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28701,7 +28701,7 @@
         <v>44470</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28763,7 +28763,7 @@
         <v>44473</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28820,7 +28820,7 @@
         <v>44474</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28877,7 +28877,7 @@
         <v>44475</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28934,7 +28934,7 @@
         <v>44475</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28991,7 +28991,7 @@
         <v>44477</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29048,7 +29048,7 @@
         <v>44477</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29105,7 +29105,7 @@
         <v>44477</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29162,7 +29162,7 @@
         <v>44479</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29224,7 +29224,7 @@
         <v>44484</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29286,7 +29286,7 @@
         <v>44484</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29348,7 +29348,7 @@
         <v>44488</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29405,7 +29405,7 @@
         <v>44489</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29467,7 +29467,7 @@
         <v>44495</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29529,7 +29529,7 @@
         <v>44495</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29591,7 +29591,7 @@
         <v>44495</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29653,7 +29653,7 @@
         <v>44495</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29715,7 +29715,7 @@
         <v>44495</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29777,7 +29777,7 @@
         <v>44495</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29839,7 +29839,7 @@
         <v>44495</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29901,7 +29901,7 @@
         <v>44496</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29958,7 +29958,7 @@
         <v>44498</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30015,7 +30015,7 @@
         <v>44509</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30077,7 +30077,7 @@
         <v>44511</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30134,7 +30134,7 @@
         <v>44512</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30191,7 +30191,7 @@
         <v>44515</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30248,7 +30248,7 @@
         <v>44517</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30305,7 +30305,7 @@
         <v>44519</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30362,7 +30362,7 @@
         <v>44519</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30419,7 +30419,7 @@
         <v>44523</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30481,7 +30481,7 @@
         <v>44524</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30538,7 +30538,7 @@
         <v>44529</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30600,7 +30600,7 @@
         <v>44529</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30657,7 +30657,7 @@
         <v>44529</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30714,7 +30714,7 @@
         <v>44529</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30771,7 +30771,7 @@
         <v>44529</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30828,7 +30828,7 @@
         <v>44533</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30885,7 +30885,7 @@
         <v>44536</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30942,7 +30942,7 @@
         <v>44537</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30999,7 +30999,7 @@
         <v>44537</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31056,7 +31056,7 @@
         <v>44537</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31113,7 +31113,7 @@
         <v>44541</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31170,7 +31170,7 @@
         <v>44544</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31227,7 +31227,7 @@
         <v>44544</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31284,7 +31284,7 @@
         <v>44545</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31341,7 +31341,7 @@
         <v>44551</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31398,7 +31398,7 @@
         <v>44551</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31455,7 +31455,7 @@
         <v>44552</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31512,7 +31512,7 @@
         <v>44556</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31569,7 +31569,7 @@
         <v>44559</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31626,7 +31626,7 @@
         <v>44562</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31683,7 +31683,7 @@
         <v>44565</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31745,7 +31745,7 @@
         <v>44565</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31807,7 +31807,7 @@
         <v>44565</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31869,7 +31869,7 @@
         <v>44571</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31926,7 +31926,7 @@
         <v>44571</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31983,7 +31983,7 @@
         <v>44572</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32040,7 +32040,7 @@
         <v>44573</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32097,7 +32097,7 @@
         <v>44578</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32154,7 +32154,7 @@
         <v>44579</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32211,7 +32211,7 @@
         <v>44600</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32268,7 +32268,7 @@
         <v>44602</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32325,7 +32325,7 @@
         <v>44610</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32387,7 +32387,7 @@
         <v>44620</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32444,7 +32444,7 @@
         <v>44621</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32501,7 +32501,7 @@
         <v>44627</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32558,7 +32558,7 @@
         <v>44637</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32615,7 +32615,7 @@
         <v>44638</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32672,7 +32672,7 @@
         <v>44638</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32729,7 +32729,7 @@
         <v>44638</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32786,7 +32786,7 @@
         <v>44641</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32843,7 +32843,7 @@
         <v>44644</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32900,7 +32900,7 @@
         <v>44651</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32957,7 +32957,7 @@
         <v>44651</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33014,7 +33014,7 @@
         <v>44655</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33071,7 +33071,7 @@
         <v>44679</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33128,7 +33128,7 @@
         <v>44679</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33185,7 +33185,7 @@
         <v>44679</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33242,7 +33242,7 @@
         <v>44680</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33299,7 +33299,7 @@
         <v>44683</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33356,7 +33356,7 @@
         <v>44684</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33413,7 +33413,7 @@
         <v>44686</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33470,7 +33470,7 @@
         <v>44692</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33527,7 +33527,7 @@
         <v>44700</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33584,7 +33584,7 @@
         <v>44701</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33641,7 +33641,7 @@
         <v>44715</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33698,7 +33698,7 @@
         <v>44719</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33755,7 +33755,7 @@
         <v>44722</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33812,7 +33812,7 @@
         <v>44727</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33869,7 +33869,7 @@
         <v>44727</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33926,7 +33926,7 @@
         <v>44728</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33988,7 +33988,7 @@
         <v>44728</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34050,7 +34050,7 @@
         <v>44729</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34112,7 +34112,7 @@
         <v>44732</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34169,7 +34169,7 @@
         <v>44733</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34226,7 +34226,7 @@
         <v>44736</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34283,7 +34283,7 @@
         <v>44740</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34340,7 +34340,7 @@
         <v>44742</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34397,7 +34397,7 @@
         <v>44743</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34459,7 +34459,7 @@
         <v>44746</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34516,7 +34516,7 @@
         <v>44746</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34573,7 +34573,7 @@
         <v>44747</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34635,7 +34635,7 @@
         <v>44747</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34692,7 +34692,7 @@
         <v>44747</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34754,7 +34754,7 @@
         <v>44747</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34811,7 +34811,7 @@
         <v>44748</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34868,7 +34868,7 @@
         <v>44749</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34930,7 +34930,7 @@
         <v>44749</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34992,7 +34992,7 @@
         <v>44749</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35049,7 +35049,7 @@
         <v>44762</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35106,7 +35106,7 @@
         <v>44762</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35163,7 +35163,7 @@
         <v>44762</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35220,7 +35220,7 @@
         <v>44763</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35277,7 +35277,7 @@
         <v>44763</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35339,7 +35339,7 @@
         <v>44774</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35401,7 +35401,7 @@
         <v>44775</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35458,7 +35458,7 @@
         <v>44775</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35515,7 +35515,7 @@
         <v>44775</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35572,7 +35572,7 @@
         <v>44783</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35629,7 +35629,7 @@
         <v>44785</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35691,7 +35691,7 @@
         <v>44789</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35748,7 +35748,7 @@
         <v>44789</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35810,7 +35810,7 @@
         <v>44790</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35867,7 +35867,7 @@
         <v>44790</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35924,7 +35924,7 @@
         <v>44791</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35981,7 +35981,7 @@
         <v>44791</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36038,7 +36038,7 @@
         <v>44792</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36100,7 +36100,7 @@
         <v>44792</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36162,7 +36162,7 @@
         <v>44792</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36224,7 +36224,7 @@
         <v>44792</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36286,7 +36286,7 @@
         <v>44792</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36348,7 +36348,7 @@
         <v>44795</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36405,7 +36405,7 @@
         <v>44795</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36462,7 +36462,7 @@
         <v>44795</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36519,7 +36519,7 @@
         <v>44796</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36576,7 +36576,7 @@
         <v>44797</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36633,7 +36633,7 @@
         <v>44798</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36690,7 +36690,7 @@
         <v>44798</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36747,7 +36747,7 @@
         <v>44799</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36809,7 +36809,7 @@
         <v>44799</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36871,7 +36871,7 @@
         <v>44799</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36933,7 +36933,7 @@
         <v>44799</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36995,7 +36995,7 @@
         <v>44803</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37052,7 +37052,7 @@
         <v>44803</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37109,7 +37109,7 @@
         <v>44804</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37166,7 +37166,7 @@
         <v>44804</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37223,7 +37223,7 @@
         <v>44806</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37305,7 +37305,7 @@
         <v>44806</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37362,7 +37362,7 @@
         <v>44806</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37419,7 +37419,7 @@
         <v>44806</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37476,7 +37476,7 @@
         <v>44806</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37533,7 +37533,7 @@
         <v>44806</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37590,7 +37590,7 @@
         <v>44807</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37647,7 +37647,7 @@
         <v>44813</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37709,7 +37709,7 @@
         <v>44817</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37771,7 +37771,7 @@
         <v>44817</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37833,7 +37833,7 @@
         <v>44818</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37890,7 +37890,7 @@
         <v>44818</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37947,7 +37947,7 @@
         <v>44818</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38004,7 +38004,7 @@
         <v>44818</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38061,7 +38061,7 @@
         <v>44818</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38118,7 +38118,7 @@
         <v>44819</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38175,7 +38175,7 @@
         <v>44819</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38237,7 +38237,7 @@
         <v>44819</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38294,7 +38294,7 @@
         <v>44820</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38356,7 +38356,7 @@
         <v>44823</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38413,7 +38413,7 @@
         <v>44824</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38470,7 +38470,7 @@
         <v>44826</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38527,7 +38527,7 @@
         <v>44827</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38589,7 +38589,7 @@
         <v>44833</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38646,7 +38646,7 @@
         <v>44834</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38703,7 +38703,7 @@
         <v>44834</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38760,7 +38760,7 @@
         <v>44837</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38817,7 +38817,7 @@
         <v>44838</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38879,7 +38879,7 @@
         <v>44839</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38941,7 +38941,7 @@
         <v>44839</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38998,7 +38998,7 @@
         <v>44839</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39060,7 +39060,7 @@
         <v>44840</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39117,7 +39117,7 @@
         <v>44841</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39174,7 +39174,7 @@
         <v>44841</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39236,7 +39236,7 @@
         <v>44841</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39293,7 +39293,7 @@
         <v>44841</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39350,7 +39350,7 @@
         <v>44845</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39412,7 +39412,7 @@
         <v>44845</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39474,7 +39474,7 @@
         <v>44847</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39531,7 +39531,7 @@
         <v>44851</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39593,7 +39593,7 @@
         <v>44851</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39655,7 +39655,7 @@
         <v>44851</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39717,7 +39717,7 @@
         <v>44851</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39779,7 +39779,7 @@
         <v>44855</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39841,7 +39841,7 @@
         <v>44860</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39903,7 +39903,7 @@
         <v>44862</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39965,7 +39965,7 @@
         <v>44862</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40027,7 +40027,7 @@
         <v>44866</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40089,7 +40089,7 @@
         <v>44866</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40151,7 +40151,7 @@
         <v>44866</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40213,7 +40213,7 @@
         <v>44866</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40270,7 +40270,7 @@
         <v>44868</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40327,7 +40327,7 @@
         <v>44872</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40384,7 +40384,7 @@
         <v>44873</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40441,7 +40441,7 @@
         <v>44873</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40498,7 +40498,7 @@
         <v>44873</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40555,7 +40555,7 @@
         <v>44874</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40612,7 +40612,7 @@
         <v>44874</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40669,7 +40669,7 @@
         <v>44875</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40726,7 +40726,7 @@
         <v>44875</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40783,7 +40783,7 @@
         <v>44879</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40845,7 +40845,7 @@
         <v>44882</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40902,7 +40902,7 @@
         <v>44883</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40964,7 +40964,7 @@
         <v>44883</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41026,7 +41026,7 @@
         <v>44887</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41083,7 +41083,7 @@
         <v>44889</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41140,7 +41140,7 @@
         <v>44890</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41197,7 +41197,7 @@
         <v>44891</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41254,7 +41254,7 @@
         <v>44893</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41311,7 +41311,7 @@
         <v>44897</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41368,7 +41368,7 @@
         <v>44903</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41425,7 +41425,7 @@
         <v>44907</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41487,7 +41487,7 @@
         <v>44907</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41544,7 +41544,7 @@
         <v>44909</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41606,7 +41606,7 @@
         <v>44909</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41688,7 +41688,7 @@
         <v>44909</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41745,7 +41745,7 @@
         <v>44909</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41802,7 +41802,7 @@
         <v>44910</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41859,7 +41859,7 @@
         <v>44911</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41916,7 +41916,7 @@
         <v>44911</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41973,7 +41973,7 @@
         <v>44911</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42030,7 +42030,7 @@
         <v>44911</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42087,7 +42087,7 @@
         <v>44914</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42144,7 +42144,7 @@
         <v>44914</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42201,7 +42201,7 @@
         <v>44914</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42258,7 +42258,7 @@
         <v>44916</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42315,7 +42315,7 @@
         <v>44916</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42372,7 +42372,7 @@
         <v>44922</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42429,7 +42429,7 @@
         <v>44928</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42486,7 +42486,7 @@
         <v>44929</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42543,7 +42543,7 @@
         <v>44929</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42600,7 +42600,7 @@
         <v>44930</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42657,7 +42657,7 @@
         <v>44930</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42714,7 +42714,7 @@
         <v>44930</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42771,7 +42771,7 @@
         <v>44930</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42828,7 +42828,7 @@
         <v>44931</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42890,7 +42890,7 @@
         <v>44939</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42947,7 +42947,7 @@
         <v>44939</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43004,7 +43004,7 @@
         <v>44944</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43061,7 +43061,7 @@
         <v>44944</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43118,7 +43118,7 @@
         <v>44945</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43175,7 +43175,7 @@
         <v>44949</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43232,7 +43232,7 @@
         <v>44950</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43289,7 +43289,7 @@
         <v>44950</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43346,7 +43346,7 @@
         <v>44953</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43403,7 +43403,7 @@
         <v>44956</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43460,7 +43460,7 @@
         <v>44960</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43517,7 +43517,7 @@
         <v>44964</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43574,7 +43574,7 @@
         <v>44964</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43631,7 +43631,7 @@
         <v>44964</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43688,7 +43688,7 @@
         <v>44964</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43745,7 +43745,7 @@
         <v>44964</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43802,7 +43802,7 @@
         <v>44964</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43859,7 +43859,7 @@
         <v>44964</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43916,7 +43916,7 @@
         <v>44966</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43973,7 +43973,7 @@
         <v>44967</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44030,7 +44030,7 @@
         <v>44967</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44087,7 +44087,7 @@
         <v>44967</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44144,7 +44144,7 @@
         <v>44967</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44201,7 +44201,7 @@
         <v>44967</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44258,7 +44258,7 @@
         <v>44970</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44315,7 +44315,7 @@
         <v>44970</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44372,7 +44372,7 @@
         <v>44973</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44429,7 +44429,7 @@
         <v>44977</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44486,7 +44486,7 @@
         <v>44977</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44543,7 +44543,7 @@
         <v>44982</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44600,7 +44600,7 @@
         <v>44991</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -44657,7 +44657,7 @@
         <v>44997</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44714,7 +44714,7 @@
         <v>45002</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44771,7 +44771,7 @@
         <v>45002</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44828,7 +44828,7 @@
         <v>45002</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44885,7 +44885,7 @@
         <v>45019</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44942,7 +44942,7 @@
         <v>45019</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44999,7 +44999,7 @@
         <v>45019</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45056,7 +45056,7 @@
         <v>45021</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45113,7 +45113,7 @@
         <v>45027</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45170,7 +45170,7 @@
         <v>45033</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45227,7 +45227,7 @@
         <v>45040</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45289,7 +45289,7 @@
         <v>45042</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45346,7 +45346,7 @@
         <v>45058</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45403,7 +45403,7 @@
         <v>45062</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45465,7 +45465,7 @@
         <v>45063</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45522,7 +45522,7 @@
         <v>45070</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45579,7 +45579,7 @@
         <v>45071</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45636,7 +45636,7 @@
         <v>45071</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45693,7 +45693,7 @@
         <v>45071</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45750,7 +45750,7 @@
         <v>45071</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45807,7 +45807,7 @@
         <v>45071</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45864,7 +45864,7 @@
         <v>45071</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45921,7 +45921,7 @@
         <v>45072</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -45978,7 +45978,7 @@
         <v>45072</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46035,7 +46035,7 @@
         <v>45072</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46097,7 +46097,7 @@
         <v>45075</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46154,7 +46154,7 @@
         <v>45075</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46211,7 +46211,7 @@
         <v>45077</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46268,7 +46268,7 @@
         <v>45079</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46325,7 +46325,7 @@
         <v>45084</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46382,7 +46382,7 @@
         <v>45085</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46439,7 +46439,7 @@
         <v>45085</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46496,7 +46496,7 @@
         <v>45090</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46553,7 +46553,7 @@
         <v>45090</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46610,7 +46610,7 @@
         <v>45090</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46667,7 +46667,7 @@
         <v>45092</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46729,7 +46729,7 @@
         <v>45092</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46786,7 +46786,7 @@
         <v>45093</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46848,7 +46848,7 @@
         <v>45093</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46910,7 +46910,7 @@
         <v>45096</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46967,7 +46967,7 @@
         <v>45096</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47029,7 +47029,7 @@
         <v>45096</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47091,7 +47091,7 @@
         <v>45097</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47148,7 +47148,7 @@
         <v>45097</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47210,7 +47210,7 @@
         <v>45097</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47272,7 +47272,7 @@
         <v>45098</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47329,7 +47329,7 @@
         <v>45098</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47386,7 +47386,7 @@
         <v>45099</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47448,7 +47448,7 @@
         <v>45103</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -47505,7 +47505,7 @@
         <v>45103</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47562,7 +47562,7 @@
         <v>45104</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -47619,7 +47619,7 @@
         <v>45105</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -47676,7 +47676,7 @@
         <v>45105</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -47733,7 +47733,7 @@
         <v>45106</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47790,7 +47790,7 @@
         <v>45107</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -47847,7 +47847,7 @@
         <v>45107</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -47904,7 +47904,7 @@
         <v>45107</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -47961,7 +47961,7 @@
         <v>45111</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -48023,7 +48023,7 @@
         <v>45111</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48080,7 +48080,7 @@
         <v>45112</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -48137,7 +48137,7 @@
         <v>45112</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -48199,7 +48199,7 @@
         <v>45112</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48261,7 +48261,7 @@
         <v>45112</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48318,7 +48318,7 @@
         <v>45114</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48375,7 +48375,7 @@
         <v>45114</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48432,7 +48432,7 @@
         <v>45119</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -48489,7 +48489,7 @@
         <v>45120</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -48551,7 +48551,7 @@
         <v>45124</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -48613,7 +48613,7 @@
         <v>45124</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -48670,7 +48670,7 @@
         <v>45131</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -48732,7 +48732,7 @@
         <v>45131</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48794,7 +48794,7 @@
         <v>45132</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -48851,7 +48851,7 @@
         <v>45132</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -48908,7 +48908,7 @@
         <v>45138</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -48970,7 +48970,7 @@
         <v>45138</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -49032,7 +49032,7 @@
         <v>45139</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -49089,7 +49089,7 @@
         <v>45139</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -49146,7 +49146,7 @@
         <v>45140</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -49203,7 +49203,7 @@
         <v>45145</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49265,7 +49265,7 @@
         <v>45148</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -49322,7 +49322,7 @@
         <v>45152</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49379,7 +49379,7 @@
         <v>45152</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49441,7 +49441,7 @@
         <v>45152</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -49503,7 +49503,7 @@
         <v>45154</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -49560,7 +49560,7 @@
         <v>45155</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -49617,7 +49617,7 @@
         <v>45159</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -49679,7 +49679,7 @@
         <v>45159</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -49736,7 +49736,7 @@
         <v>45160</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -49798,7 +49798,7 @@
         <v>45160</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -49860,7 +49860,7 @@
         <v>45161</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -49917,7 +49917,7 @@
         <v>45161</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -49979,7 +49979,7 @@
         <v>45166</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -50036,7 +50036,7 @@
         <v>45167</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -50093,7 +50093,7 @@
         <v>45168</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -50150,7 +50150,7 @@
         <v>45168</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -50207,7 +50207,7 @@
         <v>45168</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -50264,7 +50264,7 @@
         <v>45173</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -50321,7 +50321,7 @@
         <v>45173</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -50378,7 +50378,7 @@
         <v>45173</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -50435,7 +50435,7 @@
         <v>45174</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -50492,7 +50492,7 @@
         <v>45175</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -50554,7 +50554,7 @@
         <v>45175</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -50616,7 +50616,7 @@
         <v>45176</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -50678,7 +50678,7 @@
         <v>45176</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -50740,7 +50740,7 @@
         <v>45176</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -50802,7 +50802,7 @@
         <v>45176</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -50864,7 +50864,7 @@
         <v>45176</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -50921,7 +50921,7 @@
         <v>45176</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -50978,7 +50978,7 @@
         <v>45176</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -51035,7 +51035,7 @@
         <v>45180</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -51097,7 +51097,7 @@
         <v>45180</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -51159,7 +51159,7 @@
         <v>45181</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -51216,7 +51216,7 @@
         <v>45181</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -51273,7 +51273,7 @@
         <v>45181</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -51330,7 +51330,7 @@
         <v>45181</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -51387,7 +51387,7 @@
         <v>45182</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -51444,7 +51444,7 @@
         <v>45182</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -51501,7 +51501,7 @@
         <v>45182</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -51558,7 +51558,7 @@
         <v>45183</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -51615,7 +51615,7 @@
         <v>45183</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -51672,7 +51672,7 @@
         <v>45183</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -51729,7 +51729,7 @@
         <v>45187</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -51786,7 +51786,7 @@
         <v>45187</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -51848,7 +51848,7 @@
         <v>45188</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -51905,7 +51905,7 @@
         <v>45188</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -51962,7 +51962,7 @@
         <v>45188</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -52019,7 +52019,7 @@
         <v>45188</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -52076,7 +52076,7 @@
         <v>45190</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -52133,7 +52133,7 @@
         <v>45190</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -52190,7 +52190,7 @@
         <v>45194</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -52247,7 +52247,7 @@
         <v>45194</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -52304,7 +52304,7 @@
         <v>45194</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -52361,7 +52361,7 @@
         <v>45194</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -52418,7 +52418,7 @@
         <v>45194</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -52475,7 +52475,7 @@
         <v>45194</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -52537,7 +52537,7 @@
         <v>45194</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -52594,7 +52594,7 @@
         <v>45194</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -52651,7 +52651,7 @@
         <v>45194</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -52713,7 +52713,7 @@
         <v>45194</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -52775,7 +52775,7 @@
         <v>45195</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -52832,7 +52832,7 @@
         <v>45198</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -52889,7 +52889,7 @@
         <v>45198</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -52946,7 +52946,7 @@
         <v>45201</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -53003,7 +53003,7 @@
         <v>45201</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -53060,7 +53060,7 @@
         <v>45201</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -53117,7 +53117,7 @@
         <v>45201</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -53174,7 +53174,7 @@
         <v>45202</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -53231,7 +53231,7 @@
         <v>45203</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -53288,7 +53288,7 @@
         <v>45203</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -53345,7 +53345,7 @@
         <v>45204</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -53402,7 +53402,7 @@
         <v>45204</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -53459,7 +53459,7 @@
         <v>45204</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -53516,7 +53516,7 @@
         <v>45204</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -53578,7 +53578,7 @@
         <v>45204</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -53635,7 +53635,7 @@
         <v>45205</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -53697,7 +53697,7 @@
         <v>45208</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -53754,7 +53754,7 @@
         <v>45209</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -53816,7 +53816,7 @@
         <v>45209</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -53878,7 +53878,7 @@
         <v>45210</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -53935,7 +53935,7 @@
         <v>45210</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -53992,7 +53992,7 @@
         <v>45210</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -54049,7 +54049,7 @@
         <v>45211</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -54106,7 +54106,7 @@
         <v>45211</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -54168,7 +54168,7 @@
         <v>45215</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -54225,7 +54225,7 @@
         <v>45215</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -54282,7 +54282,7 @@
         <v>45216</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -54339,7 +54339,7 @@
         <v>45217</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -54396,7 +54396,7 @@
         <v>45217</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -54453,7 +54453,7 @@
         <v>45217</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -54510,7 +54510,7 @@
         <v>45217</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -54567,7 +54567,7 @@
         <v>45222</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -54629,7 +54629,7 @@
         <v>45222</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -54686,7 +54686,7 @@
         <v>45222</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -54743,7 +54743,7 @@
         <v>45223</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -54805,7 +54805,7 @@
         <v>45223</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -54862,7 +54862,7 @@
         <v>45225</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -54924,7 +54924,7 @@
         <v>45225</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -54981,7 +54981,7 @@
         <v>45225</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -55043,7 +55043,7 @@
         <v>45225</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -55100,7 +55100,7 @@
         <v>45225</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -55157,7 +55157,7 @@
         <v>45225</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -55214,7 +55214,7 @@
         <v>45225</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -55271,7 +55271,7 @@
         <v>45225</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -55328,7 +55328,7 @@
         <v>45225</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -55385,7 +55385,7 @@
         <v>45226</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -55442,7 +55442,7 @@
         <v>45229</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -55499,7 +55499,7 @@
         <v>45229</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -55556,7 +55556,7 @@
         <v>45229</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -55613,7 +55613,7 @@
         <v>45229</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -55670,7 +55670,7 @@
         <v>45229</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -55727,7 +55727,7 @@
         <v>45230</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -55784,7 +55784,7 @@
         <v>45230</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -55841,7 +55841,7 @@
         <v>45230</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -55898,7 +55898,7 @@
         <v>45230</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -55955,7 +55955,7 @@
         <v>45230</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -56012,7 +56012,7 @@
         <v>45231</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -56069,7 +56069,7 @@
         <v>45231</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -56126,7 +56126,7 @@
         <v>45231</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -56183,7 +56183,7 @@
         <v>45231</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -56240,7 +56240,7 @@
         <v>45231</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -56297,7 +56297,7 @@
         <v>45231</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -56354,7 +56354,7 @@
         <v>45231</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -56411,7 +56411,7 @@
         <v>45232</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -56473,7 +56473,7 @@
         <v>45232</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -56530,7 +56530,7 @@
         <v>45232</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -56587,7 +56587,7 @@
         <v>45232</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -56644,7 +56644,7 @@
         <v>45233</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -56706,7 +56706,7 @@
         <v>45236</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -56763,7 +56763,7 @@
         <v>45236</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -56820,7 +56820,7 @@
         <v>45236</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -56877,7 +56877,7 @@
         <v>45237</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -56934,7 +56934,7 @@
         <v>45237</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -56996,7 +56996,7 @@
         <v>45239</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -57053,7 +57053,7 @@
         <v>45239</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -57110,7 +57110,7 @@
         <v>45240</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -57172,7 +57172,7 @@
         <v>45243</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -57229,7 +57229,7 @@
         <v>45243</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -57286,7 +57286,7 @@
         <v>45243</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -57343,7 +57343,7 @@
         <v>45243</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -57400,7 +57400,7 @@
         <v>45243</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -57457,7 +57457,7 @@
         <v>45243</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -57514,7 +57514,7 @@
         <v>45244</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -57571,7 +57571,7 @@
         <v>45244</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -57633,7 +57633,7 @@
         <v>45244</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -57695,7 +57695,7 @@
         <v>45244</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -57752,7 +57752,7 @@
         <v>45244</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -57809,7 +57809,7 @@
         <v>45244</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -57871,7 +57871,7 @@
         <v>45244</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -57928,7 +57928,7 @@
         <v>45245</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -57985,7 +57985,7 @@
         <v>45245</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -58042,7 +58042,7 @@
         <v>45245</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -58099,7 +58099,7 @@
         <v>45245</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -58156,7 +58156,7 @@
         <v>45245</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -58218,7 +58218,7 @@
         <v>45245</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -58275,7 +58275,7 @@
         <v>45245</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -58332,7 +58332,7 @@
         <v>45247</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -58389,7 +58389,7 @@
         <v>45247</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -58446,7 +58446,7 @@
         <v>45248</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -58503,7 +58503,7 @@
         <v>45250</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -58560,7 +58560,7 @@
         <v>45250</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -58617,7 +58617,7 @@
         <v>45251</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -58674,7 +58674,7 @@
         <v>45251</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -58731,7 +58731,7 @@
         <v>45251</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -58788,7 +58788,7 @@
         <v>45252</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -58845,7 +58845,7 @@
         <v>45253</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -58907,7 +58907,7 @@
         <v>45253</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -58964,7 +58964,7 @@
         <v>45253</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -59026,7 +59026,7 @@
         <v>45253</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -59083,7 +59083,7 @@
         <v>45253</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -59145,7 +59145,7 @@
         <v>45253</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -59207,7 +59207,7 @@
         <v>45253</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -59264,7 +59264,7 @@
         <v>45257</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -59321,7 +59321,7 @@
         <v>45258</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -59378,7 +59378,7 @@
         <v>45259</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -59435,7 +59435,7 @@
         <v>45260</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -59492,7 +59492,7 @@
         <v>45261</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -59549,7 +59549,7 @@
         <v>45261</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -59606,7 +59606,7 @@
         <v>45264</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -59663,7 +59663,7 @@
         <v>45264</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -59720,7 +59720,7 @@
         <v>45264</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -59777,7 +59777,7 @@
         <v>45264</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -59834,7 +59834,7 @@
         <v>45264</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -59891,7 +59891,7 @@
         <v>45264</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -59948,7 +59948,7 @@
         <v>45265</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -60005,7 +60005,7 @@
         <v>45265</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -60062,7 +60062,7 @@
         <v>45265</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -60119,7 +60119,7 @@
         <v>45266</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -60176,7 +60176,7 @@
         <v>45266</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -60233,7 +60233,7 @@
         <v>45266</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -60290,7 +60290,7 @@
         <v>45266</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -60352,7 +60352,7 @@
         <v>45267</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -60409,7 +60409,7 @@
         <v>45267</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -60466,7 +60466,7 @@
         <v>45267</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -60523,7 +60523,7 @@
         <v>45267</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -60580,7 +60580,7 @@
         <v>45267</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -60637,7 +60637,7 @@
         <v>45268</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -60694,7 +60694,7 @@
         <v>45271</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -60751,7 +60751,7 @@
         <v>45273</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -60808,7 +60808,7 @@
         <v>45273</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -60865,7 +60865,7 @@
         <v>45275</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -60922,7 +60922,7 @@
         <v>45279</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -60979,7 +60979,7 @@
         <v>45279</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -61036,7 +61036,7 @@
         <v>45279</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -61093,7 +61093,7 @@
         <v>45281</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -61150,7 +61150,7 @@
         <v>45281</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -61212,7 +61212,7 @@
         <v>45282</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -61269,7 +61269,7 @@
         <v>45287</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -61331,7 +61331,7 @@
         <v>45297</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -61393,7 +61393,7 @@
         <v>45299</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -61450,7 +61450,7 @@
         <v>45300</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -61507,7 +61507,7 @@
         <v>45300</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -61564,7 +61564,7 @@
         <v>45302</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -61621,7 +61621,7 @@
         <v>45302</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -61678,7 +61678,7 @@
         <v>45303</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -61735,7 +61735,7 @@
         <v>45306</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -61792,7 +61792,7 @@
         <v>45306</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -61849,7 +61849,7 @@
         <v>45307</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -61906,7 +61906,7 @@
         <v>45307</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -61963,7 +61963,7 @@
         <v>45307</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -62020,7 +62020,7 @@
         <v>45307</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -62077,7 +62077,7 @@
         <v>45307</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -62134,7 +62134,7 @@
         <v>45310</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -62191,7 +62191,7 @@
         <v>45310</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -62248,7 +62248,7 @@
         <v>45310</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -62305,7 +62305,7 @@
         <v>45310</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -62362,7 +62362,7 @@
         <v>45310</v>
       </c>
       <c r="C1038" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
@@ -62419,7 +62419,7 @@
         <v>45310</v>
       </c>
       <c r="C1039" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
@@ -62476,7 +62476,7 @@
         <v>45310</v>
       </c>
       <c r="C1040" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
@@ -62533,7 +62533,7 @@
         <v>45310</v>
       </c>
       <c r="C1041" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
@@ -62590,7 +62590,7 @@
         <v>45310</v>
       </c>
       <c r="C1042" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
@@ -62647,7 +62647,7 @@
         <v>45313</v>
       </c>
       <c r="C1043" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1043" t="inlineStr">
         <is>
@@ -62704,7 +62704,7 @@
         <v>45314</v>
       </c>
       <c r="C1044" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1044" t="inlineStr">
         <is>
@@ -62761,7 +62761,7 @@
         <v>45314</v>
       </c>
       <c r="C1045" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1045" t="inlineStr">
         <is>
@@ -62818,7 +62818,7 @@
         <v>45314</v>
       </c>
       <c r="C1046" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1046" t="inlineStr">
         <is>
@@ -62875,7 +62875,7 @@
         <v>45316</v>
       </c>
       <c r="C1047" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1047" t="inlineStr">
         <is>
@@ -62932,7 +62932,7 @@
         <v>45317</v>
       </c>
       <c r="C1048" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1048" t="inlineStr">
         <is>
@@ -62989,7 +62989,7 @@
         <v>45321</v>
       </c>
       <c r="C1049" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1049" t="inlineStr">
         <is>
@@ -63046,7 +63046,7 @@
         <v>45321</v>
       </c>
       <c r="C1050" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1050" t="inlineStr">
         <is>
@@ -63096,14 +63096,14 @@
     <row r="1051" ht="15" customHeight="1">
       <c r="A1051" t="inlineStr">
         <is>
-          <t>A 3686-2024</t>
+          <t>A 3643-2024</t>
         </is>
       </c>
       <c r="B1051" s="1" t="n">
         <v>45321</v>
       </c>
       <c r="C1051" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1051" t="inlineStr">
         <is>
@@ -63153,14 +63153,14 @@
     <row r="1052" ht="15" customHeight="1">
       <c r="A1052" t="inlineStr">
         <is>
-          <t>A 3638-2024</t>
+          <t>A 3722-2024</t>
         </is>
       </c>
       <c r="B1052" s="1" t="n">
         <v>45321</v>
       </c>
       <c r="C1052" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1052" t="inlineStr">
         <is>
@@ -63173,7 +63173,7 @@
         </is>
       </c>
       <c r="G1052" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="H1052" t="n">
         <v>0</v>
@@ -63210,14 +63210,14 @@
     <row r="1053" ht="15" customHeight="1">
       <c r="A1053" t="inlineStr">
         <is>
-          <t>A 3651-2024</t>
+          <t>A 3738-2024</t>
         </is>
       </c>
       <c r="B1053" s="1" t="n">
         <v>45321</v>
       </c>
       <c r="C1053" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1053" t="inlineStr">
         <is>
@@ -63230,7 +63230,7 @@
         </is>
       </c>
       <c r="G1053" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="H1053" t="n">
         <v>0</v>
@@ -63267,14 +63267,14 @@
     <row r="1054" ht="15" customHeight="1">
       <c r="A1054" t="inlineStr">
         <is>
-          <t>A 3655-2024</t>
+          <t>A 3742-2024</t>
         </is>
       </c>
       <c r="B1054" s="1" t="n">
         <v>45321</v>
       </c>
       <c r="C1054" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1054" t="inlineStr">
         <is>
@@ -63287,7 +63287,7 @@
         </is>
       </c>
       <c r="G1054" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="H1054" t="n">
         <v>0</v>
@@ -63324,14 +63324,14 @@
     <row r="1055" ht="15" customHeight="1">
       <c r="A1055" t="inlineStr">
         <is>
-          <t>A 3725-2024</t>
+          <t>A 3638-2024</t>
         </is>
       </c>
       <c r="B1055" s="1" t="n">
         <v>45321</v>
       </c>
       <c r="C1055" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1055" t="inlineStr">
         <is>
@@ -63344,7 +63344,7 @@
         </is>
       </c>
       <c r="G1055" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="H1055" t="n">
         <v>0</v>
@@ -63381,14 +63381,14 @@
     <row r="1056" ht="15" customHeight="1">
       <c r="A1056" t="inlineStr">
         <is>
-          <t>A 3741-2024</t>
+          <t>A 3651-2024</t>
         </is>
       </c>
       <c r="B1056" s="1" t="n">
         <v>45321</v>
       </c>
       <c r="C1056" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1056" t="inlineStr">
         <is>
@@ -63401,7 +63401,7 @@
         </is>
       </c>
       <c r="G1056" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="H1056" t="n">
         <v>0</v>
@@ -63438,14 +63438,14 @@
     <row r="1057" ht="15" customHeight="1">
       <c r="A1057" t="inlineStr">
         <is>
-          <t>A 3643-2024</t>
+          <t>A 3655-2024</t>
         </is>
       </c>
       <c r="B1057" s="1" t="n">
         <v>45321</v>
       </c>
       <c r="C1057" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1057" t="inlineStr">
         <is>
@@ -63458,7 +63458,7 @@
         </is>
       </c>
       <c r="G1057" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="H1057" t="n">
         <v>0</v>
@@ -63495,14 +63495,14 @@
     <row r="1058" ht="15" customHeight="1">
       <c r="A1058" t="inlineStr">
         <is>
-          <t>A 3722-2024</t>
+          <t>A 3725-2024</t>
         </is>
       </c>
       <c r="B1058" s="1" t="n">
         <v>45321</v>
       </c>
       <c r="C1058" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1058" t="inlineStr">
         <is>
@@ -63515,7 +63515,7 @@
         </is>
       </c>
       <c r="G1058" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="H1058" t="n">
         <v>0</v>
@@ -63552,14 +63552,14 @@
     <row r="1059" ht="15" customHeight="1">
       <c r="A1059" t="inlineStr">
         <is>
-          <t>A 3738-2024</t>
+          <t>A 3741-2024</t>
         </is>
       </c>
       <c r="B1059" s="1" t="n">
         <v>45321</v>
       </c>
       <c r="C1059" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1059" t="inlineStr">
         <is>
@@ -63572,7 +63572,7 @@
         </is>
       </c>
       <c r="G1059" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="H1059" t="n">
         <v>0</v>
@@ -63609,14 +63609,14 @@
     <row r="1060" ht="15" customHeight="1">
       <c r="A1060" t="inlineStr">
         <is>
-          <t>A 3742-2024</t>
+          <t>A 3686-2024</t>
         </is>
       </c>
       <c r="B1060" s="1" t="n">
         <v>45321</v>
       </c>
       <c r="C1060" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1060" t="inlineStr">
         <is>
@@ -63629,7 +63629,7 @@
         </is>
       </c>
       <c r="G1060" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="H1060" t="n">
         <v>0</v>
@@ -63673,7 +63673,7 @@
         <v>45322</v>
       </c>
       <c r="C1061" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1061" t="inlineStr">
         <is>
@@ -63730,7 +63730,7 @@
         <v>45324</v>
       </c>
       <c r="C1062" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1062" t="inlineStr">
         <is>
@@ -63787,7 +63787,7 @@
         <v>45329</v>
       </c>
       <c r="C1063" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1063" t="inlineStr">
         <is>
@@ -63844,7 +63844,7 @@
         <v>45329</v>
       </c>
       <c r="C1064" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1064" t="inlineStr">
         <is>
@@ -63901,7 +63901,7 @@
         <v>45330</v>
       </c>
       <c r="C1065" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1065" t="inlineStr">
         <is>
@@ -63951,14 +63951,14 @@
     <row r="1066" ht="15" customHeight="1">
       <c r="A1066" t="inlineStr">
         <is>
-          <t>A 5110-2024</t>
+          <t>A 5174-2024</t>
         </is>
       </c>
       <c r="B1066" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C1066" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1066" t="inlineStr">
         <is>
@@ -63971,7 +63971,7 @@
         </is>
       </c>
       <c r="G1066" t="n">
-        <v>3.3</v>
+        <v>1.4</v>
       </c>
       <c r="H1066" t="n">
         <v>0</v>
@@ -64008,14 +64008,14 @@
     <row r="1067" ht="15" customHeight="1">
       <c r="A1067" t="inlineStr">
         <is>
-          <t>A 5122-2024</t>
+          <t>A 5156-2024</t>
         </is>
       </c>
       <c r="B1067" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C1067" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1067" t="inlineStr">
         <is>
@@ -64028,7 +64028,7 @@
         </is>
       </c>
       <c r="G1067" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="H1067" t="n">
         <v>0</v>
@@ -64065,14 +64065,14 @@
     <row r="1068" ht="15" customHeight="1">
       <c r="A1068" t="inlineStr">
         <is>
-          <t>A 5156-2024</t>
+          <t>A 5189-2024</t>
         </is>
       </c>
       <c r="B1068" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C1068" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1068" t="inlineStr">
         <is>
@@ -64085,7 +64085,7 @@
         </is>
       </c>
       <c r="G1068" t="n">
-        <v>0.4</v>
+        <v>1.3</v>
       </c>
       <c r="H1068" t="n">
         <v>0</v>
@@ -64122,14 +64122,14 @@
     <row r="1069" ht="15" customHeight="1">
       <c r="A1069" t="inlineStr">
         <is>
-          <t>A 5189-2024</t>
+          <t>A 5110-2024</t>
         </is>
       </c>
       <c r="B1069" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C1069" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1069" t="inlineStr">
         <is>
@@ -64142,7 +64142,7 @@
         </is>
       </c>
       <c r="G1069" t="n">
-        <v>1.3</v>
+        <v>3.3</v>
       </c>
       <c r="H1069" t="n">
         <v>0</v>
@@ -64179,14 +64179,14 @@
     <row r="1070" ht="15" customHeight="1">
       <c r="A1070" t="inlineStr">
         <is>
-          <t>A 5174-2024</t>
+          <t>A 5122-2024</t>
         </is>
       </c>
       <c r="B1070" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C1070" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1070" t="inlineStr">
         <is>
@@ -64199,7 +64199,7 @@
         </is>
       </c>
       <c r="G1070" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="H1070" t="n">
         <v>0</v>
@@ -64243,7 +64243,7 @@
         <v>45331</v>
       </c>
       <c r="C1071" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1071" t="inlineStr">
         <is>
@@ -64300,7 +64300,7 @@
         <v>45331</v>
       </c>
       <c r="C1072" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1072" t="inlineStr">
         <is>
@@ -64357,7 +64357,7 @@
         <v>45334</v>
       </c>
       <c r="C1073" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1073" t="inlineStr">
         <is>
@@ -64414,7 +64414,7 @@
         <v>45334</v>
       </c>
       <c r="C1074" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1074" t="inlineStr">
         <is>
@@ -64471,7 +64471,7 @@
         <v>45337</v>
       </c>
       <c r="C1075" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1075" t="inlineStr">
         <is>
@@ -64528,7 +64528,7 @@
         <v>45337</v>
       </c>
       <c r="C1076" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1076" t="inlineStr">
         <is>
@@ -64585,7 +64585,7 @@
         <v>45337</v>
       </c>
       <c r="C1077" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1077" t="inlineStr">
         <is>
@@ -64642,7 +64642,7 @@
         <v>45343</v>
       </c>
       <c r="C1078" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1078" t="inlineStr">
         <is>
@@ -64704,7 +64704,7 @@
         <v>45344</v>
       </c>
       <c r="C1079" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1079" t="inlineStr">
         <is>

--- a/Översikt RÄTTVIK.xlsx
+++ b/Översikt RÄTTVIK.xlsx
@@ -569,7 +569,7 @@
         <v>43542</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         <v>43663</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -781,7 +781,7 @@
         <v>43619</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
         <v>44909</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>43740</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>44909</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>44874</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>45147</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
         <v>44237</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1461,7 +1461,7 @@
         <v>44624</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         <v>43634</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         <v>43663</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1736,7 +1736,7 @@
         <v>44148</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         <v>44435</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1910,7 +1910,7 @@
         <v>44799</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         <v>44909</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         <v>44909</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
         <v>45111</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>43700</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>44496</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2450,7 +2450,7 @@
         <v>45033</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
         <v>43440</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         <v>43493</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
         <v>43623</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2791,7 +2791,7 @@
         <v>43705</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
         <v>44088</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2961,7 +2961,7 @@
         <v>44361</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3046,7 +3046,7 @@
         <v>44391</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         <v>44414</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3226,7 +3226,7 @@
         <v>44470</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3316,7 +3316,7 @@
         <v>44496</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
         <v>44511</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3491,7 +3491,7 @@
         <v>44568</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
         <v>44728</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3679,7 +3679,7 @@
         <v>44855</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3769,7 +3769,7 @@
         <v>44894</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3859,7 +3859,7 @@
         <v>44918</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3949,7 +3949,7 @@
         <v>44986</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4034,7 +4034,7 @@
         <v>45077</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4119,7 +4119,7 @@
         <v>45194</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4204,7 +4204,7 @@
         <v>45194</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4289,7 +4289,7 @@
         <v>45231</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4374,7 +4374,7 @@
         <v>43333</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4431,7 +4431,7 @@
         <v>43348</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4488,7 +4488,7 @@
         <v>43356</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4545,7 +4545,7 @@
         <v>43361</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4602,7 +4602,7 @@
         <v>43362</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4659,7 +4659,7 @@
         <v>43362</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4716,7 +4716,7 @@
         <v>43362</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4773,7 +4773,7 @@
         <v>43362</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4830,7 +4830,7 @@
         <v>43367</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4887,7 +4887,7 @@
         <v>43369</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4944,7 +4944,7 @@
         <v>43373</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5001,7 +5001,7 @@
         <v>43378</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5058,7 +5058,7 @@
         <v>43381</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5115,7 +5115,7 @@
         <v>43381</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5172,7 +5172,7 @@
         <v>43388</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5229,7 +5229,7 @@
         <v>43388</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5291,7 +5291,7 @@
         <v>43388</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5348,7 +5348,7 @@
         <v>43391</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5405,7 +5405,7 @@
         <v>43398</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
         <v>43399</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5519,7 +5519,7 @@
         <v>43401</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5576,7 +5576,7 @@
         <v>43405</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5633,7 +5633,7 @@
         <v>43405</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5690,7 +5690,7 @@
         <v>43410</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5747,7 +5747,7 @@
         <v>43410</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5804,7 +5804,7 @@
         <v>43411</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5861,7 +5861,7 @@
         <v>43412</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5918,7 +5918,7 @@
         <v>43416</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5975,7 +5975,7 @@
         <v>43416</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6032,7 +6032,7 @@
         <v>43416</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6089,7 +6089,7 @@
         <v>43419</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6146,7 +6146,7 @@
         <v>43419</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6203,7 +6203,7 @@
         <v>43423</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6265,7 +6265,7 @@
         <v>43423</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         <v>43423</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6389,7 +6389,7 @@
         <v>43424</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6451,7 +6451,7 @@
         <v>43425</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6508,7 +6508,7 @@
         <v>43427</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6570,7 +6570,7 @@
         <v>43428</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6627,7 +6627,7 @@
         <v>43428</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6684,7 +6684,7 @@
         <v>43430</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6741,7 +6741,7 @@
         <v>43430</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6798,7 +6798,7 @@
         <v>43430</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6855,7 +6855,7 @@
         <v>43430</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6912,7 +6912,7 @@
         <v>43431</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6974,7 +6974,7 @@
         <v>43432</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7031,7 +7031,7 @@
         <v>43432</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7088,7 +7088,7 @@
         <v>43434</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7145,7 +7145,7 @@
         <v>43434</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7202,7 +7202,7 @@
         <v>43438</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7259,7 +7259,7 @@
         <v>43441</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7316,7 +7316,7 @@
         <v>43447</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7373,7 +7373,7 @@
         <v>43448</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7430,7 +7430,7 @@
         <v>43451</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7487,7 +7487,7 @@
         <v>43451</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7544,7 +7544,7 @@
         <v>43451</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7601,7 +7601,7 @@
         <v>43452</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7658,7 +7658,7 @@
         <v>43454</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7720,7 +7720,7 @@
         <v>43454</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7782,7 +7782,7 @@
         <v>43454</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7844,7 +7844,7 @@
         <v>43455</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7901,7 +7901,7 @@
         <v>43461</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7958,7 +7958,7 @@
         <v>43471</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8015,7 +8015,7 @@
         <v>43472</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8072,7 +8072,7 @@
         <v>43472</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8134,7 +8134,7 @@
         <v>43473</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8191,7 +8191,7 @@
         <v>43475</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8248,7 +8248,7 @@
         <v>43481</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8305,7 +8305,7 @@
         <v>43490</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8362,7 +8362,7 @@
         <v>43495</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8419,7 +8419,7 @@
         <v>43499</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8476,7 +8476,7 @@
         <v>43500</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8538,7 +8538,7 @@
         <v>43511</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8595,7 +8595,7 @@
         <v>43511</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8652,7 +8652,7 @@
         <v>43514</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8709,7 +8709,7 @@
         <v>43517</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8766,7 +8766,7 @@
         <v>43524</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8823,7 +8823,7 @@
         <v>43546</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8880,7 +8880,7 @@
         <v>43553</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8942,7 +8942,7 @@
         <v>43553</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8999,7 +8999,7 @@
         <v>43554</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9056,7 +9056,7 @@
         <v>43556</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9113,7 +9113,7 @@
         <v>43559</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9175,7 +9175,7 @@
         <v>43564</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9232,7 +9232,7 @@
         <v>43566</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9289,7 +9289,7 @@
         <v>43570</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9351,7 +9351,7 @@
         <v>43570</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9413,7 +9413,7 @@
         <v>43570</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9470,7 +9470,7 @@
         <v>43580</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9527,7 +9527,7 @@
         <v>43584</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9584,7 +9584,7 @@
         <v>43585</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9641,7 +9641,7 @@
         <v>43587</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9698,7 +9698,7 @@
         <v>43592</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9755,7 +9755,7 @@
         <v>43592</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9812,7 +9812,7 @@
         <v>43592</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9869,7 +9869,7 @@
         <v>43599</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9926,7 +9926,7 @@
         <v>43609</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9983,7 +9983,7 @@
         <v>43612</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10040,7 +10040,7 @@
         <v>43612</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10097,7 +10097,7 @@
         <v>43612</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10154,7 +10154,7 @@
         <v>43612</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10211,7 +10211,7 @@
         <v>43616</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10268,7 +10268,7 @@
         <v>43619</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10330,7 +10330,7 @@
         <v>43621</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10387,7 +10387,7 @@
         <v>43623</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10444,7 +10444,7 @@
         <v>43628</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10506,7 +10506,7 @@
         <v>43628</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10568,7 +10568,7 @@
         <v>43629</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10625,7 +10625,7 @@
         <v>43630</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10682,7 +10682,7 @@
         <v>43633</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10739,7 +10739,7 @@
         <v>43633</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10796,7 +10796,7 @@
         <v>43641</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10853,7 +10853,7 @@
         <v>43643</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10915,7 +10915,7 @@
         <v>43643</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10977,7 +10977,7 @@
         <v>43647</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11039,7 +11039,7 @@
         <v>43651</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11096,7 +11096,7 @@
         <v>43651</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11153,7 +11153,7 @@
         <v>43656</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11210,7 +11210,7 @@
         <v>43657</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11267,7 +11267,7 @@
         <v>43662</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11324,7 +11324,7 @@
         <v>43662</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11381,7 +11381,7 @@
         <v>43663</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11463,7 +11463,7 @@
         <v>43663</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11525,7 +11525,7 @@
         <v>43663</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11587,7 +11587,7 @@
         <v>43663</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11649,7 +11649,7 @@
         <v>43682</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11706,7 +11706,7 @@
         <v>43686</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11768,7 +11768,7 @@
         <v>43686</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11825,7 +11825,7 @@
         <v>43689</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11887,7 +11887,7 @@
         <v>43690</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11944,7 +11944,7 @@
         <v>43697</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12001,7 +12001,7 @@
         <v>43700</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12058,7 +12058,7 @@
         <v>43705</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12115,7 +12115,7 @@
         <v>43711</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12177,7 +12177,7 @@
         <v>43712</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12234,7 +12234,7 @@
         <v>43713</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12291,7 +12291,7 @@
         <v>43714</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12348,7 +12348,7 @@
         <v>43714</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12405,7 +12405,7 @@
         <v>43717</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12462,7 +12462,7 @@
         <v>43718</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12519,7 +12519,7 @@
         <v>43720</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12576,7 +12576,7 @@
         <v>43724</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12633,7 +12633,7 @@
         <v>43726</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12690,7 +12690,7 @@
         <v>43727</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12747,7 +12747,7 @@
         <v>43727</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12804,7 +12804,7 @@
         <v>43727</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12861,7 +12861,7 @@
         <v>43732</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12918,7 +12918,7 @@
         <v>43734</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12980,7 +12980,7 @@
         <v>43734</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13037,7 +13037,7 @@
         <v>43734</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13094,7 +13094,7 @@
         <v>43735</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13156,7 +13156,7 @@
         <v>43735</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13213,7 +13213,7 @@
         <v>43740</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13275,7 +13275,7 @@
         <v>43740</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13332,7 +13332,7 @@
         <v>43740</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13389,7 +13389,7 @@
         <v>43740</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13446,7 +13446,7 @@
         <v>43742</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13508,7 +13508,7 @@
         <v>43742</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13565,7 +13565,7 @@
         <v>43747</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13622,7 +13622,7 @@
         <v>43758</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13679,7 +13679,7 @@
         <v>43761</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13736,7 +13736,7 @@
         <v>43766</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13793,7 +13793,7 @@
         <v>43767</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13855,7 +13855,7 @@
         <v>43769</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13917,7 +13917,7 @@
         <v>43770</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13974,7 +13974,7 @@
         <v>43770</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14031,7 +14031,7 @@
         <v>43773</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14088,7 +14088,7 @@
         <v>43775</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14145,7 +14145,7 @@
         <v>43776</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14202,7 +14202,7 @@
         <v>43776</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14259,7 +14259,7 @@
         <v>43776</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14316,7 +14316,7 @@
         <v>43776</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14373,7 +14373,7 @@
         <v>43780</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14435,7 +14435,7 @@
         <v>43780</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14492,7 +14492,7 @@
         <v>43780</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14549,7 +14549,7 @@
         <v>43780</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14606,7 +14606,7 @@
         <v>43783</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14668,7 +14668,7 @@
         <v>43784</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14725,7 +14725,7 @@
         <v>43786</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14782,7 +14782,7 @@
         <v>43797</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14839,7 +14839,7 @@
         <v>43804</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14901,7 +14901,7 @@
         <v>43805</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14958,7 +14958,7 @@
         <v>43805</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15015,7 +15015,7 @@
         <v>43812</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15072,7 +15072,7 @@
         <v>43812</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15129,7 +15129,7 @@
         <v>43815</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15186,7 +15186,7 @@
         <v>43815</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15243,7 +15243,7 @@
         <v>43829</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15300,7 +15300,7 @@
         <v>43833</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15357,7 +15357,7 @@
         <v>43837</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15414,7 +15414,7 @@
         <v>43839</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15471,7 +15471,7 @@
         <v>43840</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15528,7 +15528,7 @@
         <v>43843</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15585,7 +15585,7 @@
         <v>43845</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15647,7 +15647,7 @@
         <v>43850</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15704,7 +15704,7 @@
         <v>43854</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15766,7 +15766,7 @@
         <v>43857</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15823,7 +15823,7 @@
         <v>43857</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15885,7 +15885,7 @@
         <v>43857</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15942,7 +15942,7 @@
         <v>43864</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15999,7 +15999,7 @@
         <v>43864</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16061,7 +16061,7 @@
         <v>43864</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16123,7 +16123,7 @@
         <v>43867</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16185,7 +16185,7 @@
         <v>43871</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16242,7 +16242,7 @@
         <v>43872</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16304,7 +16304,7 @@
         <v>43873</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16361,7 +16361,7 @@
         <v>43873</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16418,7 +16418,7 @@
         <v>43873</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16475,7 +16475,7 @@
         <v>43874</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16532,7 +16532,7 @@
         <v>43878</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16589,7 +16589,7 @@
         <v>43879</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16651,7 +16651,7 @@
         <v>43880</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16708,7 +16708,7 @@
         <v>43894</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16765,7 +16765,7 @@
         <v>43894</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16822,7 +16822,7 @@
         <v>43902</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16879,7 +16879,7 @@
         <v>43917</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16936,7 +16936,7 @@
         <v>43917</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16998,7 +16998,7 @@
         <v>43920</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17060,7 +17060,7 @@
         <v>43920</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17122,7 +17122,7 @@
         <v>43921</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17184,7 +17184,7 @@
         <v>43922</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17246,7 +17246,7 @@
         <v>43922</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17308,7 +17308,7 @@
         <v>43924</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17365,7 +17365,7 @@
         <v>43924</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17422,7 +17422,7 @@
         <v>43927</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17479,7 +17479,7 @@
         <v>43927</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17536,7 +17536,7 @@
         <v>43928</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17593,7 +17593,7 @@
         <v>43928</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17650,7 +17650,7 @@
         <v>43930</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17712,7 +17712,7 @@
         <v>43933</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17774,7 +17774,7 @@
         <v>43933</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17836,7 +17836,7 @@
         <v>43935</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17893,7 +17893,7 @@
         <v>43937</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17955,7 +17955,7 @@
         <v>43941</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18012,7 +18012,7 @@
         <v>43941</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18069,7 +18069,7 @@
         <v>43948</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18126,7 +18126,7 @@
         <v>43949</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18188,7 +18188,7 @@
         <v>43949</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18250,7 +18250,7 @@
         <v>43949</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18312,7 +18312,7 @@
         <v>43949</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18374,7 +18374,7 @@
         <v>43950</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18431,7 +18431,7 @@
         <v>43951</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18493,7 +18493,7 @@
         <v>43959</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18555,7 +18555,7 @@
         <v>43959</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18617,7 +18617,7 @@
         <v>43959</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18679,7 +18679,7 @@
         <v>43959</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18736,7 +18736,7 @@
         <v>43969</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18798,7 +18798,7 @@
         <v>43970</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18855,7 +18855,7 @@
         <v>43973</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18912,7 +18912,7 @@
         <v>43985</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18969,7 +18969,7 @@
         <v>43990</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19026,7 +19026,7 @@
         <v>43991</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19088,7 +19088,7 @@
         <v>43991</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19150,7 +19150,7 @@
         <v>43991</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19212,7 +19212,7 @@
         <v>43991</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19274,7 +19274,7 @@
         <v>43991</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19336,7 +19336,7 @@
         <v>44005</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19398,7 +19398,7 @@
         <v>44033</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19455,7 +19455,7 @@
         <v>44039</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19512,7 +19512,7 @@
         <v>44048</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19569,7 +19569,7 @@
         <v>44049</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19626,7 +19626,7 @@
         <v>44053</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19683,7 +19683,7 @@
         <v>44053</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19740,7 +19740,7 @@
         <v>44053</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19797,7 +19797,7 @@
         <v>44054</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19859,7 +19859,7 @@
         <v>44054</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19916,7 +19916,7 @@
         <v>44054</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19973,7 +19973,7 @@
         <v>44055</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20035,7 +20035,7 @@
         <v>44055</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20097,7 +20097,7 @@
         <v>44074</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20154,7 +20154,7 @@
         <v>44074</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20211,7 +20211,7 @@
         <v>44077</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20268,7 +20268,7 @@
         <v>44078</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20330,7 +20330,7 @@
         <v>44078</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20392,7 +20392,7 @@
         <v>44082</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20449,7 +20449,7 @@
         <v>44084</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20511,7 +20511,7 @@
         <v>44089</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20568,7 +20568,7 @@
         <v>44091</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20625,7 +20625,7 @@
         <v>44095</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20682,7 +20682,7 @@
         <v>44097</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20739,7 +20739,7 @@
         <v>44102</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20796,7 +20796,7 @@
         <v>44104</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20853,7 +20853,7 @@
         <v>44105</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20910,7 +20910,7 @@
         <v>44109</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20967,7 +20967,7 @@
         <v>44109</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21029,7 +21029,7 @@
         <v>44110</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21086,7 +21086,7 @@
         <v>44117</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21148,7 +21148,7 @@
         <v>44126</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21210,7 +21210,7 @@
         <v>44126</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21272,7 +21272,7 @@
         <v>44126</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21334,7 +21334,7 @@
         <v>44126</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21396,7 +21396,7 @@
         <v>44126</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21458,7 +21458,7 @@
         <v>44130</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21515,7 +21515,7 @@
         <v>44130</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21572,7 +21572,7 @@
         <v>44130</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21629,7 +21629,7 @@
         <v>44130</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21686,7 +21686,7 @@
         <v>44131</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21743,7 +21743,7 @@
         <v>44133</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21805,7 +21805,7 @@
         <v>44137</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21862,7 +21862,7 @@
         <v>44139</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21919,7 +21919,7 @@
         <v>44139</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21976,7 +21976,7 @@
         <v>44141</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22033,7 +22033,7 @@
         <v>44145</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22090,7 +22090,7 @@
         <v>44145</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22147,7 +22147,7 @@
         <v>44151</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22204,7 +22204,7 @@
         <v>44151</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22261,7 +22261,7 @@
         <v>44153</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22318,7 +22318,7 @@
         <v>44159</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22375,7 +22375,7 @@
         <v>44159</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22432,7 +22432,7 @@
         <v>44159</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22489,7 +22489,7 @@
         <v>44159</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22546,7 +22546,7 @@
         <v>44160</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22603,7 +22603,7 @@
         <v>44160</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22660,7 +22660,7 @@
         <v>44160</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22717,7 +22717,7 @@
         <v>44161</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22774,7 +22774,7 @@
         <v>44162</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22831,7 +22831,7 @@
         <v>44173</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22888,7 +22888,7 @@
         <v>44175</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22945,7 +22945,7 @@
         <v>44175</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23002,7 +23002,7 @@
         <v>44179</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23059,7 +23059,7 @@
         <v>44179</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23116,7 +23116,7 @@
         <v>44180</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23173,7 +23173,7 @@
         <v>44185</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23230,7 +23230,7 @@
         <v>44186</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23287,7 +23287,7 @@
         <v>44186</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23344,7 +23344,7 @@
         <v>44194</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23401,7 +23401,7 @@
         <v>44195</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23458,7 +23458,7 @@
         <v>44214</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23515,7 +23515,7 @@
         <v>44214</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23572,7 +23572,7 @@
         <v>44217</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23629,7 +23629,7 @@
         <v>44217</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23686,7 +23686,7 @@
         <v>44228</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23743,7 +23743,7 @@
         <v>44228</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23800,7 +23800,7 @@
         <v>44238</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23857,7 +23857,7 @@
         <v>44242</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23914,7 +23914,7 @@
         <v>44242</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23971,7 +23971,7 @@
         <v>44271</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24028,7 +24028,7 @@
         <v>44273</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24085,7 +24085,7 @@
         <v>44280</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24142,7 +24142,7 @@
         <v>44281</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24199,7 +24199,7 @@
         <v>44284</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24256,7 +24256,7 @@
         <v>44284</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24313,7 +24313,7 @@
         <v>44300</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24370,7 +24370,7 @@
         <v>44300</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24427,7 +24427,7 @@
         <v>44300</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24484,7 +24484,7 @@
         <v>44305</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24541,7 +24541,7 @@
         <v>44306</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24598,7 +24598,7 @@
         <v>44307</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24655,7 +24655,7 @@
         <v>44322</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24717,7 +24717,7 @@
         <v>44326</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24774,7 +24774,7 @@
         <v>44326</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24831,7 +24831,7 @@
         <v>44326</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24888,7 +24888,7 @@
         <v>44326</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24945,7 +24945,7 @@
         <v>44330</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25002,7 +25002,7 @@
         <v>44335</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25059,7 +25059,7 @@
         <v>44336</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25121,7 +25121,7 @@
         <v>44340</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25178,7 +25178,7 @@
         <v>44342</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25240,7 +25240,7 @@
         <v>44347</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25297,7 +25297,7 @@
         <v>44347</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25354,7 +25354,7 @@
         <v>44348</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25411,7 +25411,7 @@
         <v>44348</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25468,7 +25468,7 @@
         <v>44349</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25525,7 +25525,7 @@
         <v>44349</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25582,7 +25582,7 @@
         <v>44350</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25639,7 +25639,7 @@
         <v>44351</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25696,7 +25696,7 @@
         <v>44351</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25753,7 +25753,7 @@
         <v>44363</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25810,7 +25810,7 @@
         <v>44377</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25872,7 +25872,7 @@
         <v>44377</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25929,7 +25929,7 @@
         <v>44377</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25986,7 +25986,7 @@
         <v>44377</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26043,7 +26043,7 @@
         <v>44377</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26105,7 +26105,7 @@
         <v>44386</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26167,7 +26167,7 @@
         <v>44386</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26229,7 +26229,7 @@
         <v>44391</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26291,7 +26291,7 @@
         <v>44391</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26353,7 +26353,7 @@
         <v>44399</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26410,7 +26410,7 @@
         <v>44400</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26467,7 +26467,7 @@
         <v>44403</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26524,7 +26524,7 @@
         <v>44408</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26586,7 +26586,7 @@
         <v>44409</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26648,7 +26648,7 @@
         <v>44414</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26710,7 +26710,7 @@
         <v>44414</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26772,7 +26772,7 @@
         <v>44414</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26834,7 +26834,7 @@
         <v>44418</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26891,7 +26891,7 @@
         <v>44420</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26948,7 +26948,7 @@
         <v>44421</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27005,7 +27005,7 @@
         <v>44421</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27067,7 +27067,7 @@
         <v>44424</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27129,7 +27129,7 @@
         <v>44424</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27186,7 +27186,7 @@
         <v>44432</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27248,7 +27248,7 @@
         <v>44435</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27305,7 +27305,7 @@
         <v>44441</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27362,7 +27362,7 @@
         <v>44441</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27424,7 +27424,7 @@
         <v>44449</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27486,7 +27486,7 @@
         <v>44451</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27548,7 +27548,7 @@
         <v>44451</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27610,7 +27610,7 @@
         <v>44454</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27667,7 +27667,7 @@
         <v>44459</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27729,7 +27729,7 @@
         <v>44459</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27791,7 +27791,7 @@
         <v>44459</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27853,7 +27853,7 @@
         <v>44459</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27915,7 +27915,7 @@
         <v>44459</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27977,7 +27977,7 @@
         <v>44459</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28039,7 +28039,7 @@
         <v>44460</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28096,7 +28096,7 @@
         <v>44460</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28153,7 +28153,7 @@
         <v>44461</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28210,7 +28210,7 @@
         <v>44463</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28272,7 +28272,7 @@
         <v>44467</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28334,7 +28334,7 @@
         <v>44469</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28396,7 +28396,7 @@
         <v>44469</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28458,7 +28458,7 @@
         <v>44469</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28520,7 +28520,7 @@
         <v>44469</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28582,7 +28582,7 @@
         <v>44470</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28644,7 +28644,7 @@
         <v>44470</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28701,7 +28701,7 @@
         <v>44470</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28763,7 +28763,7 @@
         <v>44473</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28820,7 +28820,7 @@
         <v>44474</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28877,7 +28877,7 @@
         <v>44475</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28934,7 +28934,7 @@
         <v>44475</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28991,7 +28991,7 @@
         <v>44477</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29048,7 +29048,7 @@
         <v>44477</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29105,7 +29105,7 @@
         <v>44477</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29162,7 +29162,7 @@
         <v>44479</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29224,7 +29224,7 @@
         <v>44484</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29286,7 +29286,7 @@
         <v>44484</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29348,7 +29348,7 @@
         <v>44488</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29405,7 +29405,7 @@
         <v>44489</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29467,7 +29467,7 @@
         <v>44495</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29529,7 +29529,7 @@
         <v>44495</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29591,7 +29591,7 @@
         <v>44495</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29653,7 +29653,7 @@
         <v>44495</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29715,7 +29715,7 @@
         <v>44495</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29777,7 +29777,7 @@
         <v>44495</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29839,7 +29839,7 @@
         <v>44495</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29901,7 +29901,7 @@
         <v>44496</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29958,7 +29958,7 @@
         <v>44498</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30015,7 +30015,7 @@
         <v>44509</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30077,7 +30077,7 @@
         <v>44511</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30134,7 +30134,7 @@
         <v>44512</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30191,7 +30191,7 @@
         <v>44515</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30248,7 +30248,7 @@
         <v>44517</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30305,7 +30305,7 @@
         <v>44519</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30362,7 +30362,7 @@
         <v>44519</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30419,7 +30419,7 @@
         <v>44523</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30481,7 +30481,7 @@
         <v>44524</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30538,7 +30538,7 @@
         <v>44529</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30600,7 +30600,7 @@
         <v>44529</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30657,7 +30657,7 @@
         <v>44529</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30714,7 +30714,7 @@
         <v>44529</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30771,7 +30771,7 @@
         <v>44529</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30828,7 +30828,7 @@
         <v>44533</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30885,7 +30885,7 @@
         <v>44536</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30942,7 +30942,7 @@
         <v>44537</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30999,7 +30999,7 @@
         <v>44537</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31056,7 +31056,7 @@
         <v>44537</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31113,7 +31113,7 @@
         <v>44541</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31170,7 +31170,7 @@
         <v>44544</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31227,7 +31227,7 @@
         <v>44544</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31284,7 +31284,7 @@
         <v>44545</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31341,7 +31341,7 @@
         <v>44551</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31398,7 +31398,7 @@
         <v>44551</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31455,7 +31455,7 @@
         <v>44552</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31512,7 +31512,7 @@
         <v>44556</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31569,7 +31569,7 @@
         <v>44559</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31626,7 +31626,7 @@
         <v>44562</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31683,7 +31683,7 @@
         <v>44565</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31745,7 +31745,7 @@
         <v>44565</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31807,7 +31807,7 @@
         <v>44565</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31869,7 +31869,7 @@
         <v>44571</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31926,7 +31926,7 @@
         <v>44571</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31983,7 +31983,7 @@
         <v>44572</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32040,7 +32040,7 @@
         <v>44573</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32097,7 +32097,7 @@
         <v>44578</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32154,7 +32154,7 @@
         <v>44579</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32211,7 +32211,7 @@
         <v>44600</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32268,7 +32268,7 @@
         <v>44602</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32325,7 +32325,7 @@
         <v>44610</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32387,7 +32387,7 @@
         <v>44620</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32444,7 +32444,7 @@
         <v>44621</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32501,7 +32501,7 @@
         <v>44627</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32558,7 +32558,7 @@
         <v>44637</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32615,7 +32615,7 @@
         <v>44638</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32672,7 +32672,7 @@
         <v>44638</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32729,7 +32729,7 @@
         <v>44638</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32786,7 +32786,7 @@
         <v>44641</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32843,7 +32843,7 @@
         <v>44644</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32900,7 +32900,7 @@
         <v>44651</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32957,7 +32957,7 @@
         <v>44651</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33014,7 +33014,7 @@
         <v>44655</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33071,7 +33071,7 @@
         <v>44679</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33128,7 +33128,7 @@
         <v>44679</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33185,7 +33185,7 @@
         <v>44679</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33242,7 +33242,7 @@
         <v>44680</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33299,7 +33299,7 @@
         <v>44683</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33356,7 +33356,7 @@
         <v>44684</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33413,7 +33413,7 @@
         <v>44686</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33470,7 +33470,7 @@
         <v>44692</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33527,7 +33527,7 @@
         <v>44700</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33584,7 +33584,7 @@
         <v>44701</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33641,7 +33641,7 @@
         <v>44715</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33698,7 +33698,7 @@
         <v>44719</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33755,7 +33755,7 @@
         <v>44722</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33812,7 +33812,7 @@
         <v>44727</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33869,7 +33869,7 @@
         <v>44727</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33926,7 +33926,7 @@
         <v>44728</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33988,7 +33988,7 @@
         <v>44728</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34050,7 +34050,7 @@
         <v>44729</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34112,7 +34112,7 @@
         <v>44732</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34169,7 +34169,7 @@
         <v>44733</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34226,7 +34226,7 @@
         <v>44736</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34283,7 +34283,7 @@
         <v>44740</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34340,7 +34340,7 @@
         <v>44742</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34397,7 +34397,7 @@
         <v>44743</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34459,7 +34459,7 @@
         <v>44746</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34516,7 +34516,7 @@
         <v>44746</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34573,7 +34573,7 @@
         <v>44747</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34635,7 +34635,7 @@
         <v>44747</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34692,7 +34692,7 @@
         <v>44747</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34754,7 +34754,7 @@
         <v>44747</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34811,7 +34811,7 @@
         <v>44748</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34868,7 +34868,7 @@
         <v>44749</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34930,7 +34930,7 @@
         <v>44749</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34992,7 +34992,7 @@
         <v>44749</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35049,7 +35049,7 @@
         <v>44762</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35106,7 +35106,7 @@
         <v>44762</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35163,7 +35163,7 @@
         <v>44762</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35220,7 +35220,7 @@
         <v>44763</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35277,7 +35277,7 @@
         <v>44763</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35339,7 +35339,7 @@
         <v>44774</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35401,7 +35401,7 @@
         <v>44775</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35458,7 +35458,7 @@
         <v>44775</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35515,7 +35515,7 @@
         <v>44775</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35572,7 +35572,7 @@
         <v>44783</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35629,7 +35629,7 @@
         <v>44785</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35691,7 +35691,7 @@
         <v>44789</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35748,7 +35748,7 @@
         <v>44789</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35810,7 +35810,7 @@
         <v>44790</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35867,7 +35867,7 @@
         <v>44790</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35924,7 +35924,7 @@
         <v>44791</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35981,7 +35981,7 @@
         <v>44791</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36038,7 +36038,7 @@
         <v>44792</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36100,7 +36100,7 @@
         <v>44792</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36162,7 +36162,7 @@
         <v>44792</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36224,7 +36224,7 @@
         <v>44792</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36286,7 +36286,7 @@
         <v>44792</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36348,7 +36348,7 @@
         <v>44795</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36405,7 +36405,7 @@
         <v>44795</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36462,7 +36462,7 @@
         <v>44795</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36519,7 +36519,7 @@
         <v>44796</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36576,7 +36576,7 @@
         <v>44797</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36633,7 +36633,7 @@
         <v>44798</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36690,7 +36690,7 @@
         <v>44798</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36747,7 +36747,7 @@
         <v>44799</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36809,7 +36809,7 @@
         <v>44799</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36871,7 +36871,7 @@
         <v>44799</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36933,7 +36933,7 @@
         <v>44799</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36995,7 +36995,7 @@
         <v>44803</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37052,7 +37052,7 @@
         <v>44803</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37109,7 +37109,7 @@
         <v>44804</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37166,7 +37166,7 @@
         <v>44804</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37223,7 +37223,7 @@
         <v>44806</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37305,7 +37305,7 @@
         <v>44806</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37362,7 +37362,7 @@
         <v>44806</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37419,7 +37419,7 @@
         <v>44806</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37476,7 +37476,7 @@
         <v>44806</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37533,7 +37533,7 @@
         <v>44806</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37590,7 +37590,7 @@
         <v>44807</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37647,7 +37647,7 @@
         <v>44813</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37709,7 +37709,7 @@
         <v>44817</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37771,7 +37771,7 @@
         <v>44817</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37833,7 +37833,7 @@
         <v>44818</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37890,7 +37890,7 @@
         <v>44818</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37947,7 +37947,7 @@
         <v>44818</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38004,7 +38004,7 @@
         <v>44818</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38061,7 +38061,7 @@
         <v>44818</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38118,7 +38118,7 @@
         <v>44819</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38175,7 +38175,7 @@
         <v>44819</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38237,7 +38237,7 @@
         <v>44819</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38294,7 +38294,7 @@
         <v>44820</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38356,7 +38356,7 @@
         <v>44823</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38413,7 +38413,7 @@
         <v>44824</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38470,7 +38470,7 @@
         <v>44826</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38527,7 +38527,7 @@
         <v>44827</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38589,7 +38589,7 @@
         <v>44833</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38646,7 +38646,7 @@
         <v>44834</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38703,7 +38703,7 @@
         <v>44834</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38760,7 +38760,7 @@
         <v>44837</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38817,7 +38817,7 @@
         <v>44838</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38879,7 +38879,7 @@
         <v>44839</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38941,7 +38941,7 @@
         <v>44839</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38998,7 +38998,7 @@
         <v>44839</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39060,7 +39060,7 @@
         <v>44840</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39117,7 +39117,7 @@
         <v>44841</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39174,7 +39174,7 @@
         <v>44841</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39236,7 +39236,7 @@
         <v>44841</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39293,7 +39293,7 @@
         <v>44841</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39350,7 +39350,7 @@
         <v>44845</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39412,7 +39412,7 @@
         <v>44845</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39474,7 +39474,7 @@
         <v>44847</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39531,7 +39531,7 @@
         <v>44851</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39593,7 +39593,7 @@
         <v>44851</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39655,7 +39655,7 @@
         <v>44851</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39717,7 +39717,7 @@
         <v>44851</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39779,7 +39779,7 @@
         <v>44855</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39841,7 +39841,7 @@
         <v>44860</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39903,7 +39903,7 @@
         <v>44862</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39965,7 +39965,7 @@
         <v>44862</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40027,7 +40027,7 @@
         <v>44866</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40089,7 +40089,7 @@
         <v>44866</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40151,7 +40151,7 @@
         <v>44866</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40213,7 +40213,7 @@
         <v>44866</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40270,7 +40270,7 @@
         <v>44868</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40327,7 +40327,7 @@
         <v>44872</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40384,7 +40384,7 @@
         <v>44873</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40441,7 +40441,7 @@
         <v>44873</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40498,7 +40498,7 @@
         <v>44873</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40555,7 +40555,7 @@
         <v>44874</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40612,7 +40612,7 @@
         <v>44874</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40669,7 +40669,7 @@
         <v>44875</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40726,7 +40726,7 @@
         <v>44875</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40783,7 +40783,7 @@
         <v>44879</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40845,7 +40845,7 @@
         <v>44882</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40902,7 +40902,7 @@
         <v>44883</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40964,7 +40964,7 @@
         <v>44883</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41026,7 +41026,7 @@
         <v>44887</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41083,7 +41083,7 @@
         <v>44889</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41140,7 +41140,7 @@
         <v>44890</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41197,7 +41197,7 @@
         <v>44891</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41254,7 +41254,7 @@
         <v>44893</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41311,7 +41311,7 @@
         <v>44897</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41368,7 +41368,7 @@
         <v>44903</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41425,7 +41425,7 @@
         <v>44907</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41487,7 +41487,7 @@
         <v>44907</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41544,7 +41544,7 @@
         <v>44909</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41606,7 +41606,7 @@
         <v>44909</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41688,7 +41688,7 @@
         <v>44909</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41745,7 +41745,7 @@
         <v>44909</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41802,7 +41802,7 @@
         <v>44910</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41859,7 +41859,7 @@
         <v>44911</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41916,7 +41916,7 @@
         <v>44911</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41973,7 +41973,7 @@
         <v>44911</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42030,7 +42030,7 @@
         <v>44911</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42087,7 +42087,7 @@
         <v>44914</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42144,7 +42144,7 @@
         <v>44914</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42201,7 +42201,7 @@
         <v>44914</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42258,7 +42258,7 @@
         <v>44916</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42315,7 +42315,7 @@
         <v>44916</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42372,7 +42372,7 @@
         <v>44922</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42429,7 +42429,7 @@
         <v>44928</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42486,7 +42486,7 @@
         <v>44929</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42543,7 +42543,7 @@
         <v>44929</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42600,7 +42600,7 @@
         <v>44930</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42657,7 +42657,7 @@
         <v>44930</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42714,7 +42714,7 @@
         <v>44930</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42771,7 +42771,7 @@
         <v>44930</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42828,7 +42828,7 @@
         <v>44931</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42890,7 +42890,7 @@
         <v>44939</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42947,7 +42947,7 @@
         <v>44939</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43004,7 +43004,7 @@
         <v>44944</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43061,7 +43061,7 @@
         <v>44944</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43118,7 +43118,7 @@
         <v>44945</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43175,7 +43175,7 @@
         <v>44949</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43232,7 +43232,7 @@
         <v>44950</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43289,7 +43289,7 @@
         <v>44950</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43346,7 +43346,7 @@
         <v>44953</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43403,7 +43403,7 @@
         <v>44956</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43460,7 +43460,7 @@
         <v>44960</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43517,7 +43517,7 @@
         <v>44964</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43574,7 +43574,7 @@
         <v>44964</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43631,7 +43631,7 @@
         <v>44964</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43688,7 +43688,7 @@
         <v>44964</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43745,7 +43745,7 @@
         <v>44964</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43802,7 +43802,7 @@
         <v>44964</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43859,7 +43859,7 @@
         <v>44964</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43916,7 +43916,7 @@
         <v>44966</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43973,7 +43973,7 @@
         <v>44967</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44030,7 +44030,7 @@
         <v>44967</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44087,7 +44087,7 @@
         <v>44967</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44144,7 +44144,7 @@
         <v>44967</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44201,7 +44201,7 @@
         <v>44967</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44258,7 +44258,7 @@
         <v>44970</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44315,7 +44315,7 @@
         <v>44970</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44372,7 +44372,7 @@
         <v>44973</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44429,7 +44429,7 @@
         <v>44977</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44486,7 +44486,7 @@
         <v>44977</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44543,7 +44543,7 @@
         <v>44982</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44600,7 +44600,7 @@
         <v>44991</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -44657,7 +44657,7 @@
         <v>44997</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44714,7 +44714,7 @@
         <v>45002</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44771,7 +44771,7 @@
         <v>45002</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44828,7 +44828,7 @@
         <v>45002</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44885,7 +44885,7 @@
         <v>45019</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44942,7 +44942,7 @@
         <v>45019</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44999,7 +44999,7 @@
         <v>45019</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45056,7 +45056,7 @@
         <v>45021</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45113,7 +45113,7 @@
         <v>45027</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45170,7 +45170,7 @@
         <v>45033</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45227,7 +45227,7 @@
         <v>45040</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45289,7 +45289,7 @@
         <v>45042</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45346,7 +45346,7 @@
         <v>45058</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45403,7 +45403,7 @@
         <v>45062</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45465,7 +45465,7 @@
         <v>45063</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45522,7 +45522,7 @@
         <v>45070</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45579,7 +45579,7 @@
         <v>45071</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45636,7 +45636,7 @@
         <v>45071</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45693,7 +45693,7 @@
         <v>45071</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45750,7 +45750,7 @@
         <v>45071</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45807,7 +45807,7 @@
         <v>45071</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45864,7 +45864,7 @@
         <v>45071</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45921,7 +45921,7 @@
         <v>45072</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -45978,7 +45978,7 @@
         <v>45072</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46035,7 +46035,7 @@
         <v>45072</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46097,7 +46097,7 @@
         <v>45075</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46154,7 +46154,7 @@
         <v>45075</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46211,7 +46211,7 @@
         <v>45077</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46268,7 +46268,7 @@
         <v>45079</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46325,7 +46325,7 @@
         <v>45084</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46382,7 +46382,7 @@
         <v>45085</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46439,7 +46439,7 @@
         <v>45085</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46496,7 +46496,7 @@
         <v>45090</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46553,7 +46553,7 @@
         <v>45090</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46610,7 +46610,7 @@
         <v>45090</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46667,7 +46667,7 @@
         <v>45092</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46729,7 +46729,7 @@
         <v>45092</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46786,7 +46786,7 @@
         <v>45093</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46848,7 +46848,7 @@
         <v>45093</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46910,7 +46910,7 @@
         <v>45096</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46967,7 +46967,7 @@
         <v>45096</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47029,7 +47029,7 @@
         <v>45096</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47091,7 +47091,7 @@
         <v>45097</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47148,7 +47148,7 @@
         <v>45097</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47210,7 +47210,7 @@
         <v>45097</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47272,7 +47272,7 @@
         <v>45098</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47329,7 +47329,7 @@
         <v>45098</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47386,7 +47386,7 @@
         <v>45099</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47448,7 +47448,7 @@
         <v>45103</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -47505,7 +47505,7 @@
         <v>45103</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47562,7 +47562,7 @@
         <v>45104</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -47619,7 +47619,7 @@
         <v>45105</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -47676,7 +47676,7 @@
         <v>45105</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -47733,7 +47733,7 @@
         <v>45106</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47790,7 +47790,7 @@
         <v>45107</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -47847,7 +47847,7 @@
         <v>45107</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -47904,7 +47904,7 @@
         <v>45107</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -47961,7 +47961,7 @@
         <v>45111</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -48023,7 +48023,7 @@
         <v>45111</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48080,7 +48080,7 @@
         <v>45112</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -48137,7 +48137,7 @@
         <v>45112</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -48199,7 +48199,7 @@
         <v>45112</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48261,7 +48261,7 @@
         <v>45112</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48318,7 +48318,7 @@
         <v>45114</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48375,7 +48375,7 @@
         <v>45114</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48432,7 +48432,7 @@
         <v>45119</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -48489,7 +48489,7 @@
         <v>45120</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -48551,7 +48551,7 @@
         <v>45124</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -48613,7 +48613,7 @@
         <v>45124</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -48670,7 +48670,7 @@
         <v>45131</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -48732,7 +48732,7 @@
         <v>45131</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48794,7 +48794,7 @@
         <v>45132</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -48851,7 +48851,7 @@
         <v>45132</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -48908,7 +48908,7 @@
         <v>45138</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -48970,7 +48970,7 @@
         <v>45138</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -49032,7 +49032,7 @@
         <v>45139</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -49089,7 +49089,7 @@
         <v>45139</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -49146,7 +49146,7 @@
         <v>45140</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -49203,7 +49203,7 @@
         <v>45145</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49265,7 +49265,7 @@
         <v>45148</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -49322,7 +49322,7 @@
         <v>45152</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49379,7 +49379,7 @@
         <v>45152</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49441,7 +49441,7 @@
         <v>45152</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -49503,7 +49503,7 @@
         <v>45154</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -49560,7 +49560,7 @@
         <v>45155</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -49617,7 +49617,7 @@
         <v>45159</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -49679,7 +49679,7 @@
         <v>45159</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -49736,7 +49736,7 @@
         <v>45160</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -49798,7 +49798,7 @@
         <v>45160</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -49860,7 +49860,7 @@
         <v>45161</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -49917,7 +49917,7 @@
         <v>45161</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -49979,7 +49979,7 @@
         <v>45166</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -50036,7 +50036,7 @@
         <v>45167</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -50093,7 +50093,7 @@
         <v>45168</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -50150,7 +50150,7 @@
         <v>45168</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -50207,7 +50207,7 @@
         <v>45168</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -50264,7 +50264,7 @@
         <v>45173</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -50321,7 +50321,7 @@
         <v>45173</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -50378,7 +50378,7 @@
         <v>45173</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -50435,7 +50435,7 @@
         <v>45174</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -50492,7 +50492,7 @@
         <v>45175</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -50554,7 +50554,7 @@
         <v>45175</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -50616,7 +50616,7 @@
         <v>45176</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -50678,7 +50678,7 @@
         <v>45176</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -50740,7 +50740,7 @@
         <v>45176</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -50802,7 +50802,7 @@
         <v>45176</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -50864,7 +50864,7 @@
         <v>45176</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -50921,7 +50921,7 @@
         <v>45176</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -50978,7 +50978,7 @@
         <v>45176</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -51035,7 +51035,7 @@
         <v>45180</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -51097,7 +51097,7 @@
         <v>45180</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -51159,7 +51159,7 @@
         <v>45181</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -51216,7 +51216,7 @@
         <v>45181</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -51273,7 +51273,7 @@
         <v>45181</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -51330,7 +51330,7 @@
         <v>45181</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -51387,7 +51387,7 @@
         <v>45182</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -51444,7 +51444,7 @@
         <v>45182</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -51501,7 +51501,7 @@
         <v>45182</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -51558,7 +51558,7 @@
         <v>45183</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -51615,7 +51615,7 @@
         <v>45183</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -51672,7 +51672,7 @@
         <v>45183</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -51729,7 +51729,7 @@
         <v>45187</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -51786,7 +51786,7 @@
         <v>45187</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -51848,7 +51848,7 @@
         <v>45188</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -51905,7 +51905,7 @@
         <v>45188</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -51962,7 +51962,7 @@
         <v>45188</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -52019,7 +52019,7 @@
         <v>45188</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -52076,7 +52076,7 @@
         <v>45190</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -52133,7 +52133,7 @@
         <v>45190</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -52190,7 +52190,7 @@
         <v>45194</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -52247,7 +52247,7 @@
         <v>45194</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -52304,7 +52304,7 @@
         <v>45194</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -52361,7 +52361,7 @@
         <v>45194</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -52418,7 +52418,7 @@
         <v>45194</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -52475,7 +52475,7 @@
         <v>45194</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -52537,7 +52537,7 @@
         <v>45194</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -52594,7 +52594,7 @@
         <v>45194</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -52651,7 +52651,7 @@
         <v>45194</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -52713,7 +52713,7 @@
         <v>45194</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -52775,7 +52775,7 @@
         <v>45195</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -52832,7 +52832,7 @@
         <v>45198</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -52889,7 +52889,7 @@
         <v>45198</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -52946,7 +52946,7 @@
         <v>45201</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -53003,7 +53003,7 @@
         <v>45201</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -53060,7 +53060,7 @@
         <v>45201</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -53117,7 +53117,7 @@
         <v>45201</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -53174,7 +53174,7 @@
         <v>45202</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -53231,7 +53231,7 @@
         <v>45203</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -53288,7 +53288,7 @@
         <v>45203</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -53345,7 +53345,7 @@
         <v>45204</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -53402,7 +53402,7 @@
         <v>45204</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -53459,7 +53459,7 @@
         <v>45204</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -53516,7 +53516,7 @@
         <v>45204</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -53578,7 +53578,7 @@
         <v>45204</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -53635,7 +53635,7 @@
         <v>45205</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -53697,7 +53697,7 @@
         <v>45208</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -53754,7 +53754,7 @@
         <v>45209</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -53816,7 +53816,7 @@
         <v>45209</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -53878,7 +53878,7 @@
         <v>45210</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -53935,7 +53935,7 @@
         <v>45210</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -53992,7 +53992,7 @@
         <v>45210</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -54049,7 +54049,7 @@
         <v>45211</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -54106,7 +54106,7 @@
         <v>45211</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -54168,7 +54168,7 @@
         <v>45215</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -54225,7 +54225,7 @@
         <v>45215</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -54282,7 +54282,7 @@
         <v>45216</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -54339,7 +54339,7 @@
         <v>45217</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -54396,7 +54396,7 @@
         <v>45217</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -54453,7 +54453,7 @@
         <v>45217</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -54510,7 +54510,7 @@
         <v>45217</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -54567,7 +54567,7 @@
         <v>45222</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -54629,7 +54629,7 @@
         <v>45222</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -54686,7 +54686,7 @@
         <v>45222</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -54743,7 +54743,7 @@
         <v>45223</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -54805,7 +54805,7 @@
         <v>45223</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -54862,7 +54862,7 @@
         <v>45225</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -54924,7 +54924,7 @@
         <v>45225</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -54981,7 +54981,7 @@
         <v>45225</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -55043,7 +55043,7 @@
         <v>45225</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -55100,7 +55100,7 @@
         <v>45225</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -55157,7 +55157,7 @@
         <v>45225</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -55214,7 +55214,7 @@
         <v>45225</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -55271,7 +55271,7 @@
         <v>45225</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -55328,7 +55328,7 @@
         <v>45225</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -55385,7 +55385,7 @@
         <v>45226</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -55442,7 +55442,7 @@
         <v>45229</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -55499,7 +55499,7 @@
         <v>45229</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -55556,7 +55556,7 @@
         <v>45229</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -55613,7 +55613,7 @@
         <v>45229</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -55670,7 +55670,7 @@
         <v>45229</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -55727,7 +55727,7 @@
         <v>45230</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -55784,7 +55784,7 @@
         <v>45230</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -55841,7 +55841,7 @@
         <v>45230</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -55898,7 +55898,7 @@
         <v>45230</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -55955,7 +55955,7 @@
         <v>45230</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -56012,7 +56012,7 @@
         <v>45231</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -56069,7 +56069,7 @@
         <v>45231</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -56126,7 +56126,7 @@
         <v>45231</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -56183,7 +56183,7 @@
         <v>45231</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -56240,7 +56240,7 @@
         <v>45231</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -56297,7 +56297,7 @@
         <v>45231</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -56354,7 +56354,7 @@
         <v>45231</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -56411,7 +56411,7 @@
         <v>45232</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -56473,7 +56473,7 @@
         <v>45232</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -56530,7 +56530,7 @@
         <v>45232</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -56587,7 +56587,7 @@
         <v>45232</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -56644,7 +56644,7 @@
         <v>45233</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -56706,7 +56706,7 @@
         <v>45236</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -56763,7 +56763,7 @@
         <v>45236</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -56820,7 +56820,7 @@
         <v>45236</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -56877,7 +56877,7 @@
         <v>45237</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -56934,7 +56934,7 @@
         <v>45237</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -56996,7 +56996,7 @@
         <v>45239</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -57053,7 +57053,7 @@
         <v>45239</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -57110,7 +57110,7 @@
         <v>45240</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -57172,7 +57172,7 @@
         <v>45243</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -57229,7 +57229,7 @@
         <v>45243</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -57286,7 +57286,7 @@
         <v>45243</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -57343,7 +57343,7 @@
         <v>45243</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -57400,7 +57400,7 @@
         <v>45243</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -57457,7 +57457,7 @@
         <v>45243</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -57514,7 +57514,7 @@
         <v>45244</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -57571,7 +57571,7 @@
         <v>45244</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -57633,7 +57633,7 @@
         <v>45244</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -57695,7 +57695,7 @@
         <v>45244</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -57752,7 +57752,7 @@
         <v>45244</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -57809,7 +57809,7 @@
         <v>45244</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -57871,7 +57871,7 @@
         <v>45244</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -57928,7 +57928,7 @@
         <v>45245</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -57985,7 +57985,7 @@
         <v>45245</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -58042,7 +58042,7 @@
         <v>45245</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -58099,7 +58099,7 @@
         <v>45245</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -58156,7 +58156,7 @@
         <v>45245</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -58218,7 +58218,7 @@
         <v>45245</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -58275,7 +58275,7 @@
         <v>45245</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -58332,7 +58332,7 @@
         <v>45247</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -58389,7 +58389,7 @@
         <v>45247</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -58446,7 +58446,7 @@
         <v>45248</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -58503,7 +58503,7 @@
         <v>45250</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -58560,7 +58560,7 @@
         <v>45250</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -58617,7 +58617,7 @@
         <v>45251</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -58674,7 +58674,7 @@
         <v>45251</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -58731,7 +58731,7 @@
         <v>45251</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -58788,7 +58788,7 @@
         <v>45252</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -58845,7 +58845,7 @@
         <v>45253</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -58907,7 +58907,7 @@
         <v>45253</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -58964,7 +58964,7 @@
         <v>45253</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -59026,7 +59026,7 @@
         <v>45253</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -59083,7 +59083,7 @@
         <v>45253</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -59145,7 +59145,7 @@
         <v>45253</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -59207,7 +59207,7 @@
         <v>45253</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -59264,7 +59264,7 @@
         <v>45257</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -59321,7 +59321,7 @@
         <v>45258</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -59378,7 +59378,7 @@
         <v>45259</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -59435,7 +59435,7 @@
         <v>45260</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -59492,7 +59492,7 @@
         <v>45261</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -59549,7 +59549,7 @@
         <v>45261</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -59606,7 +59606,7 @@
         <v>45264</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -59663,7 +59663,7 @@
         <v>45264</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -59720,7 +59720,7 @@
         <v>45264</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -59777,7 +59777,7 @@
         <v>45264</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -59834,7 +59834,7 @@
         <v>45264</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -59891,7 +59891,7 @@
         <v>45264</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -59948,7 +59948,7 @@
         <v>45265</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -60005,7 +60005,7 @@
         <v>45265</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -60062,7 +60062,7 @@
         <v>45265</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -60119,7 +60119,7 @@
         <v>45266</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -60176,7 +60176,7 @@
         <v>45266</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -60233,7 +60233,7 @@
         <v>45266</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -60290,7 +60290,7 @@
         <v>45266</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -60352,7 +60352,7 @@
         <v>45267</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -60409,7 +60409,7 @@
         <v>45267</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -60466,7 +60466,7 @@
         <v>45267</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -60523,7 +60523,7 @@
         <v>45267</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -60580,7 +60580,7 @@
         <v>45267</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -60637,7 +60637,7 @@
         <v>45268</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -60694,7 +60694,7 @@
         <v>45271</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -60751,7 +60751,7 @@
         <v>45273</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -60808,7 +60808,7 @@
         <v>45273</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -60865,7 +60865,7 @@
         <v>45275</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -60922,7 +60922,7 @@
         <v>45279</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -60979,7 +60979,7 @@
         <v>45279</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -61036,7 +61036,7 @@
         <v>45279</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -61093,7 +61093,7 @@
         <v>45281</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -61150,7 +61150,7 @@
         <v>45281</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -61212,7 +61212,7 @@
         <v>45282</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -61269,7 +61269,7 @@
         <v>45287</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -61331,7 +61331,7 @@
         <v>45297</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -61393,7 +61393,7 @@
         <v>45299</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -61450,7 +61450,7 @@
         <v>45300</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -61507,7 +61507,7 @@
         <v>45300</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -61564,7 +61564,7 @@
         <v>45302</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -61621,7 +61621,7 @@
         <v>45302</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -61678,7 +61678,7 @@
         <v>45303</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -61735,7 +61735,7 @@
         <v>45306</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -61792,7 +61792,7 @@
         <v>45306</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -61849,7 +61849,7 @@
         <v>45307</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -61906,7 +61906,7 @@
         <v>45307</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -61963,7 +61963,7 @@
         <v>45307</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -62020,7 +62020,7 @@
         <v>45307</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -62077,7 +62077,7 @@
         <v>45307</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -62134,7 +62134,7 @@
         <v>45310</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -62191,7 +62191,7 @@
         <v>45310</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -62248,7 +62248,7 @@
         <v>45310</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -62305,7 +62305,7 @@
         <v>45310</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -62362,7 +62362,7 @@
         <v>45310</v>
       </c>
       <c r="C1038" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
@@ -62419,7 +62419,7 @@
         <v>45310</v>
       </c>
       <c r="C1039" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
@@ -62476,7 +62476,7 @@
         <v>45310</v>
       </c>
       <c r="C1040" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
@@ -62533,7 +62533,7 @@
         <v>45310</v>
       </c>
       <c r="C1041" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
@@ -62590,7 +62590,7 @@
         <v>45310</v>
       </c>
       <c r="C1042" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
@@ -62647,7 +62647,7 @@
         <v>45313</v>
       </c>
       <c r="C1043" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1043" t="inlineStr">
         <is>
@@ -62704,7 +62704,7 @@
         <v>45314</v>
       </c>
       <c r="C1044" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1044" t="inlineStr">
         <is>
@@ -62761,7 +62761,7 @@
         <v>45314</v>
       </c>
       <c r="C1045" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1045" t="inlineStr">
         <is>
@@ -62818,7 +62818,7 @@
         <v>45314</v>
       </c>
       <c r="C1046" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1046" t="inlineStr">
         <is>
@@ -62875,7 +62875,7 @@
         <v>45316</v>
       </c>
       <c r="C1047" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1047" t="inlineStr">
         <is>
@@ -62932,7 +62932,7 @@
         <v>45317</v>
       </c>
       <c r="C1048" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1048" t="inlineStr">
         <is>
@@ -62982,14 +62982,14 @@
     <row r="1049" ht="15" customHeight="1">
       <c r="A1049" t="inlineStr">
         <is>
-          <t>A 3640-2024</t>
+          <t>A 3686-2024</t>
         </is>
       </c>
       <c r="B1049" s="1" t="n">
         <v>45321</v>
       </c>
       <c r="C1049" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1049" t="inlineStr">
         <is>
@@ -63039,14 +63039,14 @@
     <row r="1050" ht="15" customHeight="1">
       <c r="A1050" t="inlineStr">
         <is>
-          <t>A 3644-2024</t>
+          <t>A 3643-2024</t>
         </is>
       </c>
       <c r="B1050" s="1" t="n">
         <v>45321</v>
       </c>
       <c r="C1050" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1050" t="inlineStr">
         <is>
@@ -63059,7 +63059,7 @@
         </is>
       </c>
       <c r="G1050" t="n">
-        <v>1.5</v>
+        <v>0.2</v>
       </c>
       <c r="H1050" t="n">
         <v>0</v>
@@ -63103,7 +63103,7 @@
         <v>45321</v>
       </c>
       <c r="C1051" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1051" t="inlineStr">
         <is>
@@ -63160,7 +63160,7 @@
         <v>45321</v>
       </c>
       <c r="C1052" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1052" t="inlineStr">
         <is>
@@ -63217,7 +63217,7 @@
         <v>45321</v>
       </c>
       <c r="C1053" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1053" t="inlineStr">
         <is>
@@ -63267,14 +63267,14 @@
     <row r="1054" ht="15" customHeight="1">
       <c r="A1054" t="inlineStr">
         <is>
-          <t>A 3686-2024</t>
+          <t>A 3725-2024</t>
         </is>
       </c>
       <c r="B1054" s="1" t="n">
         <v>45321</v>
       </c>
       <c r="C1054" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1054" t="inlineStr">
         <is>
@@ -63324,14 +63324,14 @@
     <row r="1055" ht="15" customHeight="1">
       <c r="A1055" t="inlineStr">
         <is>
-          <t>A 3643-2024</t>
+          <t>A 3741-2024</t>
         </is>
       </c>
       <c r="B1055" s="1" t="n">
         <v>45321</v>
       </c>
       <c r="C1055" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1055" t="inlineStr">
         <is>
@@ -63344,7 +63344,7 @@
         </is>
       </c>
       <c r="G1055" t="n">
-        <v>0.2</v>
+        <v>1.3</v>
       </c>
       <c r="H1055" t="n">
         <v>0</v>
@@ -63381,14 +63381,14 @@
     <row r="1056" ht="15" customHeight="1">
       <c r="A1056" t="inlineStr">
         <is>
-          <t>A 3725-2024</t>
+          <t>A 3722-2024</t>
         </is>
       </c>
       <c r="B1056" s="1" t="n">
         <v>45321</v>
       </c>
       <c r="C1056" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1056" t="inlineStr">
         <is>
@@ -63401,7 +63401,7 @@
         </is>
       </c>
       <c r="G1056" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="H1056" t="n">
         <v>0</v>
@@ -63438,14 +63438,14 @@
     <row r="1057" ht="15" customHeight="1">
       <c r="A1057" t="inlineStr">
         <is>
-          <t>A 3741-2024</t>
+          <t>A 3738-2024</t>
         </is>
       </c>
       <c r="B1057" s="1" t="n">
         <v>45321</v>
       </c>
       <c r="C1057" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1057" t="inlineStr">
         <is>
@@ -63458,7 +63458,7 @@
         </is>
       </c>
       <c r="G1057" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="H1057" t="n">
         <v>0</v>
@@ -63495,14 +63495,14 @@
     <row r="1058" ht="15" customHeight="1">
       <c r="A1058" t="inlineStr">
         <is>
-          <t>A 3722-2024</t>
+          <t>A 3742-2024</t>
         </is>
       </c>
       <c r="B1058" s="1" t="n">
         <v>45321</v>
       </c>
       <c r="C1058" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1058" t="inlineStr">
         <is>
@@ -63515,7 +63515,7 @@
         </is>
       </c>
       <c r="G1058" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="H1058" t="n">
         <v>0</v>
@@ -63552,14 +63552,14 @@
     <row r="1059" ht="15" customHeight="1">
       <c r="A1059" t="inlineStr">
         <is>
-          <t>A 3738-2024</t>
+          <t>A 3640-2024</t>
         </is>
       </c>
       <c r="B1059" s="1" t="n">
         <v>45321</v>
       </c>
       <c r="C1059" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1059" t="inlineStr">
         <is>
@@ -63572,7 +63572,7 @@
         </is>
       </c>
       <c r="G1059" t="n">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="H1059" t="n">
         <v>0</v>
@@ -63609,14 +63609,14 @@
     <row r="1060" ht="15" customHeight="1">
       <c r="A1060" t="inlineStr">
         <is>
-          <t>A 3742-2024</t>
+          <t>A 3644-2024</t>
         </is>
       </c>
       <c r="B1060" s="1" t="n">
         <v>45321</v>
       </c>
       <c r="C1060" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1060" t="inlineStr">
         <is>
@@ -63629,7 +63629,7 @@
         </is>
       </c>
       <c r="G1060" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="H1060" t="n">
         <v>0</v>
@@ -63673,7 +63673,7 @@
         <v>45322</v>
       </c>
       <c r="C1061" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1061" t="inlineStr">
         <is>
@@ -63730,7 +63730,7 @@
         <v>45324</v>
       </c>
       <c r="C1062" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1062" t="inlineStr">
         <is>
@@ -63787,7 +63787,7 @@
         <v>45329</v>
       </c>
       <c r="C1063" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1063" t="inlineStr">
         <is>
@@ -63844,7 +63844,7 @@
         <v>45329</v>
       </c>
       <c r="C1064" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1064" t="inlineStr">
         <is>
@@ -63894,14 +63894,14 @@
     <row r="1065" ht="15" customHeight="1">
       <c r="A1065" t="inlineStr">
         <is>
-          <t>A 5110-2024</t>
+          <t>A 5124-2024</t>
         </is>
       </c>
       <c r="B1065" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C1065" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1065" t="inlineStr">
         <is>
@@ -63914,7 +63914,7 @@
         </is>
       </c>
       <c r="G1065" t="n">
-        <v>3.3</v>
+        <v>2.6</v>
       </c>
       <c r="H1065" t="n">
         <v>0</v>
@@ -63951,14 +63951,14 @@
     <row r="1066" ht="15" customHeight="1">
       <c r="A1066" t="inlineStr">
         <is>
-          <t>A 5124-2024</t>
+          <t>A 5174-2024</t>
         </is>
       </c>
       <c r="B1066" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C1066" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1066" t="inlineStr">
         <is>
@@ -63971,7 +63971,7 @@
         </is>
       </c>
       <c r="G1066" t="n">
-        <v>2.6</v>
+        <v>1.4</v>
       </c>
       <c r="H1066" t="n">
         <v>0</v>
@@ -64008,14 +64008,14 @@
     <row r="1067" ht="15" customHeight="1">
       <c r="A1067" t="inlineStr">
         <is>
-          <t>A 5156-2024</t>
+          <t>A 5110-2024</t>
         </is>
       </c>
       <c r="B1067" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C1067" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1067" t="inlineStr">
         <is>
@@ -64028,7 +64028,7 @@
         </is>
       </c>
       <c r="G1067" t="n">
-        <v>0.4</v>
+        <v>3.3</v>
       </c>
       <c r="H1067" t="n">
         <v>0</v>
@@ -64065,14 +64065,14 @@
     <row r="1068" ht="15" customHeight="1">
       <c r="A1068" t="inlineStr">
         <is>
-          <t>A 5174-2024</t>
+          <t>A 5122-2024</t>
         </is>
       </c>
       <c r="B1068" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C1068" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1068" t="inlineStr">
         <is>
@@ -64085,7 +64085,7 @@
         </is>
       </c>
       <c r="G1068" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="H1068" t="n">
         <v>0</v>
@@ -64122,14 +64122,14 @@
     <row r="1069" ht="15" customHeight="1">
       <c r="A1069" t="inlineStr">
         <is>
-          <t>A 5122-2024</t>
+          <t>A 5156-2024</t>
         </is>
       </c>
       <c r="B1069" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C1069" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1069" t="inlineStr">
         <is>
@@ -64142,7 +64142,7 @@
         </is>
       </c>
       <c r="G1069" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="H1069" t="n">
         <v>0</v>
@@ -64186,7 +64186,7 @@
         <v>45330</v>
       </c>
       <c r="C1070" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1070" t="inlineStr">
         <is>
@@ -64243,7 +64243,7 @@
         <v>45331</v>
       </c>
       <c r="C1071" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1071" t="inlineStr">
         <is>
@@ -64300,7 +64300,7 @@
         <v>45331</v>
       </c>
       <c r="C1072" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1072" t="inlineStr">
         <is>
@@ -64357,7 +64357,7 @@
         <v>45334</v>
       </c>
       <c r="C1073" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1073" t="inlineStr">
         <is>
@@ -64414,7 +64414,7 @@
         <v>45334</v>
       </c>
       <c r="C1074" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1074" t="inlineStr">
         <is>
@@ -64464,14 +64464,14 @@
     <row r="1075" ht="15" customHeight="1">
       <c r="A1075" t="inlineStr">
         <is>
-          <t>A 6187-2024</t>
+          <t>A 6169-2024</t>
         </is>
       </c>
       <c r="B1075" s="1" t="n">
         <v>45337</v>
       </c>
       <c r="C1075" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1075" t="inlineStr">
         <is>
@@ -64484,7 +64484,7 @@
         </is>
       </c>
       <c r="G1075" t="n">
-        <v>0.8</v>
+        <v>3.3</v>
       </c>
       <c r="H1075" t="n">
         <v>0</v>
@@ -64521,14 +64521,14 @@
     <row r="1076" ht="15" customHeight="1">
       <c r="A1076" t="inlineStr">
         <is>
-          <t>A 6213-2024</t>
+          <t>A 6187-2024</t>
         </is>
       </c>
       <c r="B1076" s="1" t="n">
         <v>45337</v>
       </c>
       <c r="C1076" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1076" t="inlineStr">
         <is>
@@ -64541,7 +64541,7 @@
         </is>
       </c>
       <c r="G1076" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="H1076" t="n">
         <v>0</v>
@@ -64578,14 +64578,14 @@
     <row r="1077" ht="15" customHeight="1">
       <c r="A1077" t="inlineStr">
         <is>
-          <t>A 6169-2024</t>
+          <t>A 6213-2024</t>
         </is>
       </c>
       <c r="B1077" s="1" t="n">
         <v>45337</v>
       </c>
       <c r="C1077" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1077" t="inlineStr">
         <is>
@@ -64598,7 +64598,7 @@
         </is>
       </c>
       <c r="G1077" t="n">
-        <v>3.3</v>
+        <v>0.6</v>
       </c>
       <c r="H1077" t="n">
         <v>0</v>
@@ -64642,7 +64642,7 @@
         <v>45343</v>
       </c>
       <c r="C1078" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1078" t="inlineStr">
         <is>
@@ -64704,7 +64704,7 @@
         <v>45344</v>
       </c>
       <c r="C1079" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1079" t="inlineStr">
         <is>

--- a/Översikt RÄTTVIK.xlsx
+++ b/Översikt RÄTTVIK.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z1084"/>
+  <dimension ref="A1:Z1085"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="26"/>
@@ -569,7 +569,7 @@
         <v>43542</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         <v>44909</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
         <v>43663</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>43619</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>43740</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>44909</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>44874</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
         <v>45147</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>44237</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>44624</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>43634</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>43663</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
         <v>44148</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
         <v>44435</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v>44799</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2008,7 +2008,7 @@
         <v>44909</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2100,7 +2100,7 @@
         <v>44909</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2192,7 +2192,7 @@
         <v>45111</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
         <v>43700</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2370,7 +2370,7 @@
         <v>44496</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2456,7 +2456,7 @@
         <v>45033</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
         <v>45264</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         <v>43440</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2717,7 +2717,7 @@
         <v>43493</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         <v>43623</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2887,7 +2887,7 @@
         <v>43705</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2972,7 +2972,7 @@
         <v>44088</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3057,7 +3057,7 @@
         <v>44361</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3142,7 +3142,7 @@
         <v>44391</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3232,7 +3232,7 @@
         <v>44414</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3322,7 +3322,7 @@
         <v>44470</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3412,7 +3412,7 @@
         <v>44496</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3502,7 +3502,7 @@
         <v>44511</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3587,7 +3587,7 @@
         <v>44568</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3681,7 +3681,7 @@
         <v>44728</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3775,7 +3775,7 @@
         <v>44855</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3865,7 +3865,7 @@
         <v>44894</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         <v>44918</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4045,7 +4045,7 @@
         <v>44986</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4130,7 +4130,7 @@
         <v>45077</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4215,7 +4215,7 @@
         <v>45194</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4300,7 +4300,7 @@
         <v>45194</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4385,7 +4385,7 @@
         <v>45231</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4470,7 +4470,7 @@
         <v>43333</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4527,7 +4527,7 @@
         <v>43348</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4584,7 +4584,7 @@
         <v>43356</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4641,7 +4641,7 @@
         <v>43361</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4698,7 +4698,7 @@
         <v>43362</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4755,7 +4755,7 @@
         <v>43362</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4812,7 +4812,7 @@
         <v>43362</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4869,7 +4869,7 @@
         <v>43362</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4926,7 +4926,7 @@
         <v>43367</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4983,7 +4983,7 @@
         <v>43369</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5040,7 +5040,7 @@
         <v>43373</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         <v>43378</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5154,7 +5154,7 @@
         <v>43381</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5211,7 +5211,7 @@
         <v>43381</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5268,7 +5268,7 @@
         <v>43388</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5325,7 +5325,7 @@
         <v>43388</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5387,7 +5387,7 @@
         <v>43388</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5444,7 +5444,7 @@
         <v>43391</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5501,7 +5501,7 @@
         <v>43398</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5558,7 +5558,7 @@
         <v>43399</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5615,7 +5615,7 @@
         <v>43401</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5672,7 +5672,7 @@
         <v>43405</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5729,7 +5729,7 @@
         <v>43405</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5786,7 +5786,7 @@
         <v>43410</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5843,7 +5843,7 @@
         <v>43410</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5900,7 +5900,7 @@
         <v>43411</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5957,7 +5957,7 @@
         <v>43412</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6014,7 +6014,7 @@
         <v>43416</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6071,7 +6071,7 @@
         <v>43416</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6128,7 +6128,7 @@
         <v>43416</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6185,7 +6185,7 @@
         <v>43419</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6242,7 +6242,7 @@
         <v>43419</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6299,7 +6299,7 @@
         <v>43423</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6361,7 +6361,7 @@
         <v>43423</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6423,7 +6423,7 @@
         <v>43423</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         <v>43424</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6547,7 +6547,7 @@
         <v>43425</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6604,7 +6604,7 @@
         <v>43427</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6666,7 +6666,7 @@
         <v>43428</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6723,7 +6723,7 @@
         <v>43428</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6780,7 +6780,7 @@
         <v>43430</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6837,7 +6837,7 @@
         <v>43430</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6894,7 +6894,7 @@
         <v>43430</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6951,7 +6951,7 @@
         <v>43430</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7008,7 +7008,7 @@
         <v>43431</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7070,7 +7070,7 @@
         <v>43432</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7127,7 +7127,7 @@
         <v>43432</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7184,7 +7184,7 @@
         <v>43434</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7241,7 +7241,7 @@
         <v>43434</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7298,7 +7298,7 @@
         <v>43438</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7355,7 +7355,7 @@
         <v>43441</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7412,7 +7412,7 @@
         <v>43447</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         <v>43448</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7526,7 +7526,7 @@
         <v>43451</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7583,7 +7583,7 @@
         <v>43451</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7640,7 +7640,7 @@
         <v>43451</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7697,7 +7697,7 @@
         <v>43452</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7754,7 +7754,7 @@
         <v>43454</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7816,7 +7816,7 @@
         <v>43454</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7878,7 +7878,7 @@
         <v>43454</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7940,7 +7940,7 @@
         <v>43455</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7997,7 +7997,7 @@
         <v>43461</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8054,7 +8054,7 @@
         <v>43471</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8111,7 +8111,7 @@
         <v>43472</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8168,7 +8168,7 @@
         <v>43472</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8230,7 +8230,7 @@
         <v>43473</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8287,7 +8287,7 @@
         <v>43475</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8344,7 +8344,7 @@
         <v>43481</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8401,7 +8401,7 @@
         <v>43490</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8458,7 +8458,7 @@
         <v>43495</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8515,7 +8515,7 @@
         <v>43499</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8572,7 +8572,7 @@
         <v>43500</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8634,7 +8634,7 @@
         <v>43511</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8691,7 +8691,7 @@
         <v>43511</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8748,7 +8748,7 @@
         <v>43514</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8805,7 +8805,7 @@
         <v>43517</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8862,7 +8862,7 @@
         <v>43524</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8919,7 +8919,7 @@
         <v>43546</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8976,7 +8976,7 @@
         <v>43553</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9038,7 +9038,7 @@
         <v>43553</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9095,7 +9095,7 @@
         <v>43554</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9152,7 +9152,7 @@
         <v>43556</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9209,7 +9209,7 @@
         <v>43559</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9271,7 +9271,7 @@
         <v>43564</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9328,7 +9328,7 @@
         <v>43566</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9385,7 +9385,7 @@
         <v>43570</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9447,7 +9447,7 @@
         <v>43570</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9509,7 +9509,7 @@
         <v>43570</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9566,7 +9566,7 @@
         <v>43580</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9623,7 +9623,7 @@
         <v>43584</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9680,7 +9680,7 @@
         <v>43585</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9737,7 +9737,7 @@
         <v>43587</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9794,7 +9794,7 @@
         <v>43592</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9851,7 +9851,7 @@
         <v>43592</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9908,7 +9908,7 @@
         <v>43592</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9965,7 +9965,7 @@
         <v>43599</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10022,7 +10022,7 @@
         <v>43609</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10079,7 +10079,7 @@
         <v>43612</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10136,7 +10136,7 @@
         <v>43612</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10193,7 +10193,7 @@
         <v>43612</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10250,7 +10250,7 @@
         <v>43612</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10307,7 +10307,7 @@
         <v>43616</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10364,7 +10364,7 @@
         <v>43619</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10426,7 +10426,7 @@
         <v>43621</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10483,7 +10483,7 @@
         <v>43623</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10540,7 +10540,7 @@
         <v>43628</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10602,7 +10602,7 @@
         <v>43628</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10664,7 +10664,7 @@
         <v>43629</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10721,7 +10721,7 @@
         <v>43630</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10778,7 +10778,7 @@
         <v>43633</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10835,7 +10835,7 @@
         <v>43633</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10892,7 +10892,7 @@
         <v>43641</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10949,7 +10949,7 @@
         <v>43643</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11011,7 +11011,7 @@
         <v>43643</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11073,7 +11073,7 @@
         <v>43647</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11135,7 +11135,7 @@
         <v>43651</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11192,7 +11192,7 @@
         <v>43651</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11249,7 +11249,7 @@
         <v>43656</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11306,7 +11306,7 @@
         <v>43657</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11363,7 +11363,7 @@
         <v>43662</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11420,7 +11420,7 @@
         <v>43662</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11477,7 +11477,7 @@
         <v>43663</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11559,7 +11559,7 @@
         <v>43663</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11621,7 +11621,7 @@
         <v>43663</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11683,7 +11683,7 @@
         <v>43663</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11745,7 +11745,7 @@
         <v>43682</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11802,7 +11802,7 @@
         <v>43686</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11864,7 +11864,7 @@
         <v>43686</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11921,7 +11921,7 @@
         <v>43689</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11983,7 +11983,7 @@
         <v>43690</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12040,7 +12040,7 @@
         <v>43697</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12097,7 +12097,7 @@
         <v>43700</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12154,7 +12154,7 @@
         <v>43705</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12211,7 +12211,7 @@
         <v>43711</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12273,7 +12273,7 @@
         <v>43712</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12330,7 +12330,7 @@
         <v>43713</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12387,7 +12387,7 @@
         <v>43714</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12444,7 +12444,7 @@
         <v>43714</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12501,7 +12501,7 @@
         <v>43717</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12558,7 +12558,7 @@
         <v>43718</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12615,7 +12615,7 @@
         <v>43720</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12672,7 +12672,7 @@
         <v>43724</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12729,7 +12729,7 @@
         <v>43726</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12786,7 +12786,7 @@
         <v>43727</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12843,7 +12843,7 @@
         <v>43727</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12900,7 +12900,7 @@
         <v>43727</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12957,7 +12957,7 @@
         <v>43732</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13014,7 +13014,7 @@
         <v>43734</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13076,7 +13076,7 @@
         <v>43734</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13133,7 +13133,7 @@
         <v>43734</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13190,7 +13190,7 @@
         <v>43735</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13252,7 +13252,7 @@
         <v>43735</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13309,7 +13309,7 @@
         <v>43740</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13371,7 +13371,7 @@
         <v>43740</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13428,7 +13428,7 @@
         <v>43740</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13485,7 +13485,7 @@
         <v>43740</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13542,7 +13542,7 @@
         <v>43742</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13604,7 +13604,7 @@
         <v>43742</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13661,7 +13661,7 @@
         <v>43747</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13718,7 +13718,7 @@
         <v>43758</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13775,7 +13775,7 @@
         <v>43761</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13832,7 +13832,7 @@
         <v>43766</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13889,7 +13889,7 @@
         <v>43767</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13951,7 +13951,7 @@
         <v>43769</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14013,7 +14013,7 @@
         <v>43770</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14070,7 +14070,7 @@
         <v>43770</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14127,7 +14127,7 @@
         <v>43773</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14184,7 +14184,7 @@
         <v>43775</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14241,7 +14241,7 @@
         <v>43776</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14298,7 +14298,7 @@
         <v>43776</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14355,7 +14355,7 @@
         <v>43776</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14412,7 +14412,7 @@
         <v>43776</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14469,7 +14469,7 @@
         <v>43780</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14531,7 +14531,7 @@
         <v>43780</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14588,7 +14588,7 @@
         <v>43780</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14645,7 +14645,7 @@
         <v>43780</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14702,7 +14702,7 @@
         <v>43783</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14764,7 +14764,7 @@
         <v>43784</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14821,7 +14821,7 @@
         <v>43786</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14878,7 +14878,7 @@
         <v>43797</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14935,7 +14935,7 @@
         <v>43804</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14997,7 +14997,7 @@
         <v>43805</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15054,7 +15054,7 @@
         <v>43805</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15111,7 +15111,7 @@
         <v>43812</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15168,7 +15168,7 @@
         <v>43812</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15225,7 +15225,7 @@
         <v>43815</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15282,7 +15282,7 @@
         <v>43815</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15339,7 +15339,7 @@
         <v>43829</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15396,7 +15396,7 @@
         <v>43833</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15453,7 +15453,7 @@
         <v>43837</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15510,7 +15510,7 @@
         <v>43839</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15567,7 +15567,7 @@
         <v>43840</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15624,7 +15624,7 @@
         <v>43843</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15681,7 +15681,7 @@
         <v>43845</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15743,7 +15743,7 @@
         <v>43850</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15800,7 +15800,7 @@
         <v>43854</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15862,7 +15862,7 @@
         <v>43857</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15919,7 +15919,7 @@
         <v>43857</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15981,7 +15981,7 @@
         <v>43857</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16038,7 +16038,7 @@
         <v>43864</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16095,7 +16095,7 @@
         <v>43864</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16157,7 +16157,7 @@
         <v>43864</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16219,7 +16219,7 @@
         <v>43867</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16281,7 +16281,7 @@
         <v>43871</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16338,7 +16338,7 @@
         <v>43872</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16400,7 +16400,7 @@
         <v>43873</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16457,7 +16457,7 @@
         <v>43873</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16514,7 +16514,7 @@
         <v>43873</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16571,7 +16571,7 @@
         <v>43874</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16628,7 +16628,7 @@
         <v>43878</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16685,7 +16685,7 @@
         <v>43879</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16747,7 +16747,7 @@
         <v>43880</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16804,7 +16804,7 @@
         <v>43894</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16861,7 +16861,7 @@
         <v>43894</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16918,7 +16918,7 @@
         <v>43902</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16975,7 +16975,7 @@
         <v>43917</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17032,7 +17032,7 @@
         <v>43917</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17094,7 +17094,7 @@
         <v>43920</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17156,7 +17156,7 @@
         <v>43920</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17218,7 +17218,7 @@
         <v>43921</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17280,7 +17280,7 @@
         <v>43922</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17342,7 +17342,7 @@
         <v>43922</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17404,7 +17404,7 @@
         <v>43924</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17461,7 +17461,7 @@
         <v>43924</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17518,7 +17518,7 @@
         <v>43927</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17575,7 +17575,7 @@
         <v>43927</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17632,7 +17632,7 @@
         <v>43928</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17689,7 +17689,7 @@
         <v>43928</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17746,7 +17746,7 @@
         <v>43930</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17808,7 +17808,7 @@
         <v>43933</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17870,7 +17870,7 @@
         <v>43933</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17932,7 +17932,7 @@
         <v>43935</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17989,7 +17989,7 @@
         <v>43937</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18051,7 +18051,7 @@
         <v>43941</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18108,7 +18108,7 @@
         <v>43941</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18165,7 +18165,7 @@
         <v>43948</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18222,7 +18222,7 @@
         <v>43949</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18284,7 +18284,7 @@
         <v>43949</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18346,7 +18346,7 @@
         <v>43949</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18408,7 +18408,7 @@
         <v>43949</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18470,7 +18470,7 @@
         <v>43950</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18527,7 +18527,7 @@
         <v>43951</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18589,7 +18589,7 @@
         <v>43959</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18651,7 +18651,7 @@
         <v>43959</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18713,7 +18713,7 @@
         <v>43959</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18775,7 +18775,7 @@
         <v>43959</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18832,7 +18832,7 @@
         <v>43969</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18894,7 +18894,7 @@
         <v>43970</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18951,7 +18951,7 @@
         <v>43973</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19008,7 +19008,7 @@
         <v>43985</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19065,7 +19065,7 @@
         <v>43990</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19122,7 +19122,7 @@
         <v>43991</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19184,7 +19184,7 @@
         <v>43991</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19246,7 +19246,7 @@
         <v>43991</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19308,7 +19308,7 @@
         <v>43991</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19370,7 +19370,7 @@
         <v>43991</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19432,7 +19432,7 @@
         <v>44005</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19494,7 +19494,7 @@
         <v>44033</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19551,7 +19551,7 @@
         <v>44039</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19608,7 +19608,7 @@
         <v>44048</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19665,7 +19665,7 @@
         <v>44049</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19722,7 +19722,7 @@
         <v>44053</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19779,7 +19779,7 @@
         <v>44053</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19836,7 +19836,7 @@
         <v>44053</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19893,7 +19893,7 @@
         <v>44054</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19955,7 +19955,7 @@
         <v>44054</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20012,7 +20012,7 @@
         <v>44054</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20069,7 +20069,7 @@
         <v>44055</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20131,7 +20131,7 @@
         <v>44055</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20193,7 +20193,7 @@
         <v>44074</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20250,7 +20250,7 @@
         <v>44074</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20307,7 +20307,7 @@
         <v>44077</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20364,7 +20364,7 @@
         <v>44078</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20426,7 +20426,7 @@
         <v>44078</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20488,7 +20488,7 @@
         <v>44082</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20545,7 +20545,7 @@
         <v>44084</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20607,7 +20607,7 @@
         <v>44089</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20664,7 +20664,7 @@
         <v>44091</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20721,7 +20721,7 @@
         <v>44095</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20778,7 +20778,7 @@
         <v>44097</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20835,7 +20835,7 @@
         <v>44102</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20892,7 +20892,7 @@
         <v>44104</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20949,7 +20949,7 @@
         <v>44105</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21006,7 +21006,7 @@
         <v>44109</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21063,7 +21063,7 @@
         <v>44109</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21125,7 +21125,7 @@
         <v>44110</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21182,7 +21182,7 @@
         <v>44117</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21244,7 +21244,7 @@
         <v>44126</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21306,7 +21306,7 @@
         <v>44126</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21368,7 +21368,7 @@
         <v>44126</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21430,7 +21430,7 @@
         <v>44126</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21492,7 +21492,7 @@
         <v>44126</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21554,7 +21554,7 @@
         <v>44130</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21611,7 +21611,7 @@
         <v>44130</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21668,7 +21668,7 @@
         <v>44130</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21725,7 +21725,7 @@
         <v>44130</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21782,7 +21782,7 @@
         <v>44131</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21839,7 +21839,7 @@
         <v>44133</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21901,7 +21901,7 @@
         <v>44137</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21958,7 +21958,7 @@
         <v>44139</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22015,7 +22015,7 @@
         <v>44139</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22072,7 +22072,7 @@
         <v>44141</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22129,7 +22129,7 @@
         <v>44145</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22186,7 +22186,7 @@
         <v>44145</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22243,7 +22243,7 @@
         <v>44151</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22300,7 +22300,7 @@
         <v>44151</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22357,7 +22357,7 @@
         <v>44153</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22414,7 +22414,7 @@
         <v>44159</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22471,7 +22471,7 @@
         <v>44159</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22528,7 +22528,7 @@
         <v>44159</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22585,7 +22585,7 @@
         <v>44159</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22642,7 +22642,7 @@
         <v>44160</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22699,7 +22699,7 @@
         <v>44160</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22756,7 +22756,7 @@
         <v>44160</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22813,7 +22813,7 @@
         <v>44161</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22870,7 +22870,7 @@
         <v>44162</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22927,7 +22927,7 @@
         <v>44173</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22984,7 +22984,7 @@
         <v>44175</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23041,7 +23041,7 @@
         <v>44175</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23098,7 +23098,7 @@
         <v>44179</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23155,7 +23155,7 @@
         <v>44179</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23212,7 +23212,7 @@
         <v>44180</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23269,7 +23269,7 @@
         <v>44185</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23326,7 +23326,7 @@
         <v>44186</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23383,7 +23383,7 @@
         <v>44186</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23440,7 +23440,7 @@
         <v>44194</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23497,7 +23497,7 @@
         <v>44195</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23554,7 +23554,7 @@
         <v>44214</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23611,7 +23611,7 @@
         <v>44214</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23668,7 +23668,7 @@
         <v>44217</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23725,7 +23725,7 @@
         <v>44217</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23782,7 +23782,7 @@
         <v>44228</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23839,7 +23839,7 @@
         <v>44228</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23896,7 +23896,7 @@
         <v>44238</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23953,7 +23953,7 @@
         <v>44242</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24010,7 +24010,7 @@
         <v>44242</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24067,7 +24067,7 @@
         <v>44271</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24124,7 +24124,7 @@
         <v>44273</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24181,7 +24181,7 @@
         <v>44280</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24238,7 +24238,7 @@
         <v>44281</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24295,7 +24295,7 @@
         <v>44284</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24352,7 +24352,7 @@
         <v>44284</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24409,7 +24409,7 @@
         <v>44300</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24466,7 +24466,7 @@
         <v>44300</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24523,7 +24523,7 @@
         <v>44300</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24580,7 +24580,7 @@
         <v>44305</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24637,7 +24637,7 @@
         <v>44306</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24694,7 +24694,7 @@
         <v>44307</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24751,7 +24751,7 @@
         <v>44322</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24813,7 +24813,7 @@
         <v>44326</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24870,7 +24870,7 @@
         <v>44326</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24927,7 +24927,7 @@
         <v>44326</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24984,7 +24984,7 @@
         <v>44326</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25041,7 +25041,7 @@
         <v>44330</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25098,7 +25098,7 @@
         <v>44335</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25155,7 +25155,7 @@
         <v>44336</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25217,7 +25217,7 @@
         <v>44340</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25274,7 +25274,7 @@
         <v>44342</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25336,7 +25336,7 @@
         <v>44347</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25393,7 +25393,7 @@
         <v>44347</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25450,7 +25450,7 @@
         <v>44348</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25507,7 +25507,7 @@
         <v>44348</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25564,7 +25564,7 @@
         <v>44349</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25621,7 +25621,7 @@
         <v>44349</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25678,7 +25678,7 @@
         <v>44350</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25735,7 +25735,7 @@
         <v>44351</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25792,7 +25792,7 @@
         <v>44351</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25849,7 +25849,7 @@
         <v>44363</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25906,7 +25906,7 @@
         <v>44377</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25968,7 +25968,7 @@
         <v>44377</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26025,7 +26025,7 @@
         <v>44377</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26082,7 +26082,7 @@
         <v>44377</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26139,7 +26139,7 @@
         <v>44377</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26201,7 +26201,7 @@
         <v>44386</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26263,7 +26263,7 @@
         <v>44386</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26325,7 +26325,7 @@
         <v>44391</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26387,7 +26387,7 @@
         <v>44391</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26449,7 +26449,7 @@
         <v>44399</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26506,7 +26506,7 @@
         <v>44400</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26563,7 +26563,7 @@
         <v>44403</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26620,7 +26620,7 @@
         <v>44408</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26682,7 +26682,7 @@
         <v>44409</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26744,7 +26744,7 @@
         <v>44414</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26806,7 +26806,7 @@
         <v>44414</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26868,7 +26868,7 @@
         <v>44414</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26930,7 +26930,7 @@
         <v>44418</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26987,7 +26987,7 @@
         <v>44420</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27044,7 +27044,7 @@
         <v>44421</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27101,7 +27101,7 @@
         <v>44421</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27163,7 +27163,7 @@
         <v>44424</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27225,7 +27225,7 @@
         <v>44424</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27282,7 +27282,7 @@
         <v>44432</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27344,7 +27344,7 @@
         <v>44435</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27401,7 +27401,7 @@
         <v>44441</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27458,7 +27458,7 @@
         <v>44441</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27520,7 +27520,7 @@
         <v>44449</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27582,7 +27582,7 @@
         <v>44451</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27644,7 +27644,7 @@
         <v>44451</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27706,7 +27706,7 @@
         <v>44454</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27763,7 +27763,7 @@
         <v>44459</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27825,7 +27825,7 @@
         <v>44459</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27887,7 +27887,7 @@
         <v>44459</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27949,7 +27949,7 @@
         <v>44459</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28011,7 +28011,7 @@
         <v>44459</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28073,7 +28073,7 @@
         <v>44459</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28135,7 +28135,7 @@
         <v>44460</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28192,7 +28192,7 @@
         <v>44460</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28249,7 +28249,7 @@
         <v>44461</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28306,7 +28306,7 @@
         <v>44463</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28368,7 +28368,7 @@
         <v>44467</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28430,7 +28430,7 @@
         <v>44469</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28492,7 +28492,7 @@
         <v>44469</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28554,7 +28554,7 @@
         <v>44469</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28616,7 +28616,7 @@
         <v>44469</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28678,7 +28678,7 @@
         <v>44470</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28740,7 +28740,7 @@
         <v>44470</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28797,7 +28797,7 @@
         <v>44470</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28859,7 +28859,7 @@
         <v>44473</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28916,7 +28916,7 @@
         <v>44474</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28973,7 +28973,7 @@
         <v>44475</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29030,7 +29030,7 @@
         <v>44475</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29087,7 +29087,7 @@
         <v>44477</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29144,7 +29144,7 @@
         <v>44477</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29201,7 +29201,7 @@
         <v>44477</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29258,7 +29258,7 @@
         <v>44479</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29320,7 +29320,7 @@
         <v>44484</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29382,7 +29382,7 @@
         <v>44484</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29444,7 +29444,7 @@
         <v>44488</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29501,7 +29501,7 @@
         <v>44489</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29563,7 +29563,7 @@
         <v>44495</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29625,7 +29625,7 @@
         <v>44495</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29687,7 +29687,7 @@
         <v>44495</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29749,7 +29749,7 @@
         <v>44495</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29811,7 +29811,7 @@
         <v>44495</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29873,7 +29873,7 @@
         <v>44495</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29935,7 +29935,7 @@
         <v>44495</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29997,7 +29997,7 @@
         <v>44496</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30054,7 +30054,7 @@
         <v>44498</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30111,7 +30111,7 @@
         <v>44509</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30173,7 +30173,7 @@
         <v>44511</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30230,7 +30230,7 @@
         <v>44512</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30287,7 +30287,7 @@
         <v>44515</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30344,7 +30344,7 @@
         <v>44517</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30401,7 +30401,7 @@
         <v>44519</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30458,7 +30458,7 @@
         <v>44519</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30515,7 +30515,7 @@
         <v>44523</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30577,7 +30577,7 @@
         <v>44524</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30634,7 +30634,7 @@
         <v>44529</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30696,7 +30696,7 @@
         <v>44529</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30753,7 +30753,7 @@
         <v>44529</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30810,7 +30810,7 @@
         <v>44529</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30867,7 +30867,7 @@
         <v>44529</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30924,7 +30924,7 @@
         <v>44533</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30981,7 +30981,7 @@
         <v>44536</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31038,7 +31038,7 @@
         <v>44537</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31095,7 +31095,7 @@
         <v>44537</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31152,7 +31152,7 @@
         <v>44537</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31209,7 +31209,7 @@
         <v>44541</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31266,7 +31266,7 @@
         <v>44544</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31323,7 +31323,7 @@
         <v>44544</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31380,7 +31380,7 @@
         <v>44545</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31437,7 +31437,7 @@
         <v>44551</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31494,7 +31494,7 @@
         <v>44551</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31551,7 +31551,7 @@
         <v>44552</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31608,7 +31608,7 @@
         <v>44556</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31665,7 +31665,7 @@
         <v>44559</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31722,7 +31722,7 @@
         <v>44562</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31779,7 +31779,7 @@
         <v>44565</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31841,7 +31841,7 @@
         <v>44565</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31903,7 +31903,7 @@
         <v>44565</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31965,7 +31965,7 @@
         <v>44571</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32022,7 +32022,7 @@
         <v>44571</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32079,7 +32079,7 @@
         <v>44572</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32136,7 +32136,7 @@
         <v>44573</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32193,7 +32193,7 @@
         <v>44578</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32250,7 +32250,7 @@
         <v>44579</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32307,7 +32307,7 @@
         <v>44600</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32364,7 +32364,7 @@
         <v>44602</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32421,7 +32421,7 @@
         <v>44610</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32483,7 +32483,7 @@
         <v>44620</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32540,7 +32540,7 @@
         <v>44621</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32597,7 +32597,7 @@
         <v>44627</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32654,7 +32654,7 @@
         <v>44637</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32711,7 +32711,7 @@
         <v>44638</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32768,7 +32768,7 @@
         <v>44638</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32825,7 +32825,7 @@
         <v>44638</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32882,7 +32882,7 @@
         <v>44641</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32939,7 +32939,7 @@
         <v>44644</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32996,7 +32996,7 @@
         <v>44651</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33053,7 +33053,7 @@
         <v>44651</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33110,7 +33110,7 @@
         <v>44655</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33167,7 +33167,7 @@
         <v>44679</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33224,7 +33224,7 @@
         <v>44679</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33281,7 +33281,7 @@
         <v>44679</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33338,7 +33338,7 @@
         <v>44680</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33395,7 +33395,7 @@
         <v>44683</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33452,7 +33452,7 @@
         <v>44684</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33509,7 +33509,7 @@
         <v>44686</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33566,7 +33566,7 @@
         <v>44692</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33623,7 +33623,7 @@
         <v>44700</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33680,7 +33680,7 @@
         <v>44701</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33737,7 +33737,7 @@
         <v>44715</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33794,7 +33794,7 @@
         <v>44719</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33851,7 +33851,7 @@
         <v>44722</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33908,7 +33908,7 @@
         <v>44727</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33965,7 +33965,7 @@
         <v>44727</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34022,7 +34022,7 @@
         <v>44728</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34084,7 +34084,7 @@
         <v>44728</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34146,7 +34146,7 @@
         <v>44729</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34208,7 +34208,7 @@
         <v>44732</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34265,7 +34265,7 @@
         <v>44733</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34322,7 +34322,7 @@
         <v>44736</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34379,7 +34379,7 @@
         <v>44740</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34436,7 +34436,7 @@
         <v>44742</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34493,7 +34493,7 @@
         <v>44743</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34555,7 +34555,7 @@
         <v>44746</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34612,7 +34612,7 @@
         <v>44746</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34669,7 +34669,7 @@
         <v>44747</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34731,7 +34731,7 @@
         <v>44747</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34788,7 +34788,7 @@
         <v>44747</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34850,7 +34850,7 @@
         <v>44747</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34907,7 +34907,7 @@
         <v>44748</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34964,7 +34964,7 @@
         <v>44749</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35026,7 +35026,7 @@
         <v>44749</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35088,7 +35088,7 @@
         <v>44749</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35145,7 +35145,7 @@
         <v>44762</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35202,7 +35202,7 @@
         <v>44762</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35259,7 +35259,7 @@
         <v>44762</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35316,7 +35316,7 @@
         <v>44763</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35373,7 +35373,7 @@
         <v>44763</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35435,7 +35435,7 @@
         <v>44774</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35497,7 +35497,7 @@
         <v>44775</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35554,7 +35554,7 @@
         <v>44775</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35611,7 +35611,7 @@
         <v>44775</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35668,7 +35668,7 @@
         <v>44783</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35725,7 +35725,7 @@
         <v>44785</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35787,7 +35787,7 @@
         <v>44789</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35844,7 +35844,7 @@
         <v>44789</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35906,7 +35906,7 @@
         <v>44790</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35963,7 +35963,7 @@
         <v>44790</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36020,7 +36020,7 @@
         <v>44791</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36077,7 +36077,7 @@
         <v>44791</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36134,7 +36134,7 @@
         <v>44792</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36196,7 +36196,7 @@
         <v>44792</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36258,7 +36258,7 @@
         <v>44792</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36320,7 +36320,7 @@
         <v>44792</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36382,7 +36382,7 @@
         <v>44792</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36444,7 +36444,7 @@
         <v>44795</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36501,7 +36501,7 @@
         <v>44795</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36558,7 +36558,7 @@
         <v>44795</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36615,7 +36615,7 @@
         <v>44796</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36672,7 +36672,7 @@
         <v>44797</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36729,7 +36729,7 @@
         <v>44798</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36786,7 +36786,7 @@
         <v>44798</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36843,7 +36843,7 @@
         <v>44799</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36905,7 +36905,7 @@
         <v>44799</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36967,7 +36967,7 @@
         <v>44799</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37029,7 +37029,7 @@
         <v>44799</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37091,7 +37091,7 @@
         <v>44803</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37148,7 +37148,7 @@
         <v>44803</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37205,7 +37205,7 @@
         <v>44804</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37262,7 +37262,7 @@
         <v>44804</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37319,7 +37319,7 @@
         <v>44806</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37401,7 +37401,7 @@
         <v>44806</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37458,7 +37458,7 @@
         <v>44806</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37515,7 +37515,7 @@
         <v>44806</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37572,7 +37572,7 @@
         <v>44806</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37629,7 +37629,7 @@
         <v>44806</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37686,7 +37686,7 @@
         <v>44807</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37743,7 +37743,7 @@
         <v>44813</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37805,7 +37805,7 @@
         <v>44817</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37867,7 +37867,7 @@
         <v>44817</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37929,7 +37929,7 @@
         <v>44818</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37986,7 +37986,7 @@
         <v>44818</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38043,7 +38043,7 @@
         <v>44818</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38100,7 +38100,7 @@
         <v>44818</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38157,7 +38157,7 @@
         <v>44818</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38214,7 +38214,7 @@
         <v>44819</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38271,7 +38271,7 @@
         <v>44819</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38333,7 +38333,7 @@
         <v>44819</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38390,7 +38390,7 @@
         <v>44820</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38452,7 +38452,7 @@
         <v>44823</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38509,7 +38509,7 @@
         <v>44824</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38566,7 +38566,7 @@
         <v>44826</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38623,7 +38623,7 @@
         <v>44827</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38685,7 +38685,7 @@
         <v>44833</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38742,7 +38742,7 @@
         <v>44834</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38799,7 +38799,7 @@
         <v>44834</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38856,7 +38856,7 @@
         <v>44837</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38913,7 +38913,7 @@
         <v>44838</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38975,7 +38975,7 @@
         <v>44839</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39037,7 +39037,7 @@
         <v>44839</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39094,7 +39094,7 @@
         <v>44839</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39156,7 +39156,7 @@
         <v>44840</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39213,7 +39213,7 @@
         <v>44841</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39270,7 +39270,7 @@
         <v>44841</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39332,7 +39332,7 @@
         <v>44841</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39389,7 +39389,7 @@
         <v>44841</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39446,7 +39446,7 @@
         <v>44845</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39508,7 +39508,7 @@
         <v>44845</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39570,7 +39570,7 @@
         <v>44847</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39627,7 +39627,7 @@
         <v>44851</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39689,7 +39689,7 @@
         <v>44851</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39751,7 +39751,7 @@
         <v>44851</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39813,7 +39813,7 @@
         <v>44851</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39875,7 +39875,7 @@
         <v>44855</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39937,7 +39937,7 @@
         <v>44860</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39999,7 +39999,7 @@
         <v>44862</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40061,7 +40061,7 @@
         <v>44862</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40123,7 +40123,7 @@
         <v>44866</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40185,7 +40185,7 @@
         <v>44866</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40247,7 +40247,7 @@
         <v>44866</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40309,7 +40309,7 @@
         <v>44866</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40366,7 +40366,7 @@
         <v>44868</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40423,7 +40423,7 @@
         <v>44872</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40480,7 +40480,7 @@
         <v>44873</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40537,7 +40537,7 @@
         <v>44873</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40594,7 +40594,7 @@
         <v>44873</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40651,7 +40651,7 @@
         <v>44874</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40708,7 +40708,7 @@
         <v>44874</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40765,7 +40765,7 @@
         <v>44875</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40822,7 +40822,7 @@
         <v>44875</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40879,7 +40879,7 @@
         <v>44879</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40941,7 +40941,7 @@
         <v>44882</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40998,7 +40998,7 @@
         <v>44883</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41060,7 +41060,7 @@
         <v>44883</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41122,7 +41122,7 @@
         <v>44887</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41179,7 +41179,7 @@
         <v>44889</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41236,7 +41236,7 @@
         <v>44890</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41293,7 +41293,7 @@
         <v>44891</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41350,7 +41350,7 @@
         <v>44893</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41407,7 +41407,7 @@
         <v>44897</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41464,7 +41464,7 @@
         <v>44903</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41521,7 +41521,7 @@
         <v>44907</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41583,7 +41583,7 @@
         <v>44907</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41640,7 +41640,7 @@
         <v>44909</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41702,7 +41702,7 @@
         <v>44909</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41784,7 +41784,7 @@
         <v>44909</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41841,7 +41841,7 @@
         <v>44909</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41898,7 +41898,7 @@
         <v>44910</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41955,7 +41955,7 @@
         <v>44911</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42012,7 +42012,7 @@
         <v>44911</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42069,7 +42069,7 @@
         <v>44911</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42126,7 +42126,7 @@
         <v>44911</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42183,7 +42183,7 @@
         <v>44914</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42240,7 +42240,7 @@
         <v>44914</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42297,7 +42297,7 @@
         <v>44914</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42354,7 +42354,7 @@
         <v>44916</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42411,7 +42411,7 @@
         <v>44916</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42468,7 +42468,7 @@
         <v>44922</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42525,7 +42525,7 @@
         <v>44928</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42582,7 +42582,7 @@
         <v>44929</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42639,7 +42639,7 @@
         <v>44929</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42696,7 +42696,7 @@
         <v>44930</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42753,7 +42753,7 @@
         <v>44930</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42810,7 +42810,7 @@
         <v>44930</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42867,7 +42867,7 @@
         <v>44930</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42924,7 +42924,7 @@
         <v>44931</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42986,7 +42986,7 @@
         <v>44939</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43043,7 +43043,7 @@
         <v>44939</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43100,7 +43100,7 @@
         <v>44944</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43157,7 +43157,7 @@
         <v>44944</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43214,7 +43214,7 @@
         <v>44945</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43271,7 +43271,7 @@
         <v>44949</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43328,7 +43328,7 @@
         <v>44950</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43385,7 +43385,7 @@
         <v>44950</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43442,7 +43442,7 @@
         <v>44953</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43499,7 +43499,7 @@
         <v>44956</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43556,7 +43556,7 @@
         <v>44960</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43613,7 +43613,7 @@
         <v>44964</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43670,7 +43670,7 @@
         <v>44964</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43727,7 +43727,7 @@
         <v>44964</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43784,7 +43784,7 @@
         <v>44964</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43841,7 +43841,7 @@
         <v>44964</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43898,7 +43898,7 @@
         <v>44964</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43955,7 +43955,7 @@
         <v>44964</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44012,7 +44012,7 @@
         <v>44966</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44069,7 +44069,7 @@
         <v>44967</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44126,7 +44126,7 @@
         <v>44967</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44183,7 +44183,7 @@
         <v>44967</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44240,7 +44240,7 @@
         <v>44967</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44297,7 +44297,7 @@
         <v>44967</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44354,7 +44354,7 @@
         <v>44970</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44411,7 +44411,7 @@
         <v>44970</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44468,7 +44468,7 @@
         <v>44973</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44525,7 +44525,7 @@
         <v>44977</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44582,7 +44582,7 @@
         <v>44977</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44639,7 +44639,7 @@
         <v>44982</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -44696,7 +44696,7 @@
         <v>44991</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44753,7 +44753,7 @@
         <v>44997</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44810,7 +44810,7 @@
         <v>45002</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44867,7 +44867,7 @@
         <v>45002</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44924,7 +44924,7 @@
         <v>45002</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44981,7 +44981,7 @@
         <v>45019</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45038,7 +45038,7 @@
         <v>45019</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45095,7 +45095,7 @@
         <v>45019</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45152,7 +45152,7 @@
         <v>45021</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45209,7 +45209,7 @@
         <v>45027</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45266,7 +45266,7 @@
         <v>45033</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45323,7 +45323,7 @@
         <v>45040</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45385,7 +45385,7 @@
         <v>45042</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45442,7 +45442,7 @@
         <v>45058</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45499,7 +45499,7 @@
         <v>45062</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45561,7 +45561,7 @@
         <v>45063</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45618,7 +45618,7 @@
         <v>45070</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45675,7 +45675,7 @@
         <v>45071</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45732,7 +45732,7 @@
         <v>45071</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45789,7 +45789,7 @@
         <v>45071</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45846,7 +45846,7 @@
         <v>45071</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45903,7 +45903,7 @@
         <v>45071</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45960,7 +45960,7 @@
         <v>45071</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46017,7 +46017,7 @@
         <v>45072</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46074,7 +46074,7 @@
         <v>45072</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46131,7 +46131,7 @@
         <v>45072</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46193,7 +46193,7 @@
         <v>45075</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46250,7 +46250,7 @@
         <v>45075</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46307,7 +46307,7 @@
         <v>45077</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46364,7 +46364,7 @@
         <v>45079</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46421,7 +46421,7 @@
         <v>45084</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46478,7 +46478,7 @@
         <v>45085</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46535,7 +46535,7 @@
         <v>45085</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46592,7 +46592,7 @@
         <v>45090</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46649,7 +46649,7 @@
         <v>45090</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46706,7 +46706,7 @@
         <v>45090</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46763,7 +46763,7 @@
         <v>45092</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46825,7 +46825,7 @@
         <v>45092</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46882,7 +46882,7 @@
         <v>45093</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46944,7 +46944,7 @@
         <v>45093</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47006,7 +47006,7 @@
         <v>45096</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47063,7 +47063,7 @@
         <v>45096</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47125,7 +47125,7 @@
         <v>45096</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47187,7 +47187,7 @@
         <v>45097</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47244,7 +47244,7 @@
         <v>45097</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47306,7 +47306,7 @@
         <v>45097</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47368,7 +47368,7 @@
         <v>45098</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47425,7 +47425,7 @@
         <v>45098</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47482,7 +47482,7 @@
         <v>45099</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -47544,7 +47544,7 @@
         <v>45103</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47601,7 +47601,7 @@
         <v>45103</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -47658,7 +47658,7 @@
         <v>45104</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -47715,7 +47715,7 @@
         <v>45105</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -47772,7 +47772,7 @@
         <v>45105</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47829,7 +47829,7 @@
         <v>45106</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -47886,7 +47886,7 @@
         <v>45107</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -47943,7 +47943,7 @@
         <v>45107</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -48000,7 +48000,7 @@
         <v>45107</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -48057,7 +48057,7 @@
         <v>45111</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48119,7 +48119,7 @@
         <v>45111</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -48176,7 +48176,7 @@
         <v>45112</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -48233,7 +48233,7 @@
         <v>45112</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48295,7 +48295,7 @@
         <v>45112</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48357,7 +48357,7 @@
         <v>45112</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48414,7 +48414,7 @@
         <v>45114</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48471,7 +48471,7 @@
         <v>45114</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -48528,7 +48528,7 @@
         <v>45119</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -48585,7 +48585,7 @@
         <v>45120</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -48647,7 +48647,7 @@
         <v>45124</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -48709,7 +48709,7 @@
         <v>45124</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -48766,7 +48766,7 @@
         <v>45131</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48828,7 +48828,7 @@
         <v>45131</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -48890,7 +48890,7 @@
         <v>45132</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -48947,7 +48947,7 @@
         <v>45132</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -49004,7 +49004,7 @@
         <v>45138</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -49066,7 +49066,7 @@
         <v>45138</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -49128,7 +49128,7 @@
         <v>45139</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -49185,7 +49185,7 @@
         <v>45139</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -49242,7 +49242,7 @@
         <v>45140</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49299,7 +49299,7 @@
         <v>45145</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -49361,7 +49361,7 @@
         <v>45148</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49418,7 +49418,7 @@
         <v>45152</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49475,7 +49475,7 @@
         <v>45152</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -49537,7 +49537,7 @@
         <v>45152</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -49599,7 +49599,7 @@
         <v>45154</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -49656,7 +49656,7 @@
         <v>45155</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -49713,7 +49713,7 @@
         <v>45159</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -49775,7 +49775,7 @@
         <v>45159</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -49832,7 +49832,7 @@
         <v>45160</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -49894,7 +49894,7 @@
         <v>45160</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -49956,7 +49956,7 @@
         <v>45161</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -50013,7 +50013,7 @@
         <v>45161</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -50075,7 +50075,7 @@
         <v>45166</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -50132,7 +50132,7 @@
         <v>45167</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -50189,7 +50189,7 @@
         <v>45168</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -50246,7 +50246,7 @@
         <v>45168</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -50303,7 +50303,7 @@
         <v>45168</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -50360,7 +50360,7 @@
         <v>45173</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -50417,7 +50417,7 @@
         <v>45173</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -50474,7 +50474,7 @@
         <v>45173</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -50531,7 +50531,7 @@
         <v>45174</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -50588,7 +50588,7 @@
         <v>45175</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -50650,7 +50650,7 @@
         <v>45175</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -50712,7 +50712,7 @@
         <v>45176</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -50774,7 +50774,7 @@
         <v>45176</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -50836,7 +50836,7 @@
         <v>45176</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -50898,7 +50898,7 @@
         <v>45176</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -50960,7 +50960,7 @@
         <v>45176</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -51017,7 +51017,7 @@
         <v>45176</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -51074,7 +51074,7 @@
         <v>45176</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -51131,7 +51131,7 @@
         <v>45180</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -51193,7 +51193,7 @@
         <v>45180</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -51255,7 +51255,7 @@
         <v>45181</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -51312,7 +51312,7 @@
         <v>45181</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -51369,7 +51369,7 @@
         <v>45181</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -51426,7 +51426,7 @@
         <v>45181</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -51483,7 +51483,7 @@
         <v>45182</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -51540,7 +51540,7 @@
         <v>45182</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -51597,7 +51597,7 @@
         <v>45182</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -51654,7 +51654,7 @@
         <v>45183</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -51711,7 +51711,7 @@
         <v>45183</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -51768,7 +51768,7 @@
         <v>45183</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -51825,7 +51825,7 @@
         <v>45187</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -51882,7 +51882,7 @@
         <v>45187</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -51944,7 +51944,7 @@
         <v>45188</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -52001,7 +52001,7 @@
         <v>45188</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -52058,7 +52058,7 @@
         <v>45188</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -52115,7 +52115,7 @@
         <v>45188</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -52172,7 +52172,7 @@
         <v>45190</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -52229,7 +52229,7 @@
         <v>45190</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -52286,7 +52286,7 @@
         <v>45194</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -52343,7 +52343,7 @@
         <v>45194</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -52400,7 +52400,7 @@
         <v>45194</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -52457,7 +52457,7 @@
         <v>45194</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -52514,7 +52514,7 @@
         <v>45194</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -52571,7 +52571,7 @@
         <v>45194</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -52633,7 +52633,7 @@
         <v>45194</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -52690,7 +52690,7 @@
         <v>45194</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -52747,7 +52747,7 @@
         <v>45194</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -52809,7 +52809,7 @@
         <v>45194</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -52871,7 +52871,7 @@
         <v>45195</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -52928,7 +52928,7 @@
         <v>45198</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -52985,7 +52985,7 @@
         <v>45198</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -53042,7 +53042,7 @@
         <v>45201</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -53099,7 +53099,7 @@
         <v>45201</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -53156,7 +53156,7 @@
         <v>45201</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -53213,7 +53213,7 @@
         <v>45201</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -53270,7 +53270,7 @@
         <v>45202</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -53327,7 +53327,7 @@
         <v>45203</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -53384,7 +53384,7 @@
         <v>45203</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -53441,7 +53441,7 @@
         <v>45204</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -53498,7 +53498,7 @@
         <v>45204</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -53555,7 +53555,7 @@
         <v>45204</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -53612,7 +53612,7 @@
         <v>45204</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -53674,7 +53674,7 @@
         <v>45204</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -53731,7 +53731,7 @@
         <v>45205</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -53793,7 +53793,7 @@
         <v>45208</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -53850,7 +53850,7 @@
         <v>45209</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -53912,7 +53912,7 @@
         <v>45209</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -53974,7 +53974,7 @@
         <v>45210</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -54031,7 +54031,7 @@
         <v>45210</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -54088,7 +54088,7 @@
         <v>45210</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -54145,7 +54145,7 @@
         <v>45211</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -54202,7 +54202,7 @@
         <v>45211</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -54264,7 +54264,7 @@
         <v>45215</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -54321,7 +54321,7 @@
         <v>45215</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -54378,7 +54378,7 @@
         <v>45216</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -54435,7 +54435,7 @@
         <v>45217</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -54492,7 +54492,7 @@
         <v>45217</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -54549,7 +54549,7 @@
         <v>45217</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -54606,7 +54606,7 @@
         <v>45217</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -54663,7 +54663,7 @@
         <v>45222</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -54725,7 +54725,7 @@
         <v>45222</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -54782,7 +54782,7 @@
         <v>45222</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -54839,7 +54839,7 @@
         <v>45223</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -54901,7 +54901,7 @@
         <v>45223</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -54958,7 +54958,7 @@
         <v>45225</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -55020,7 +55020,7 @@
         <v>45225</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -55077,7 +55077,7 @@
         <v>45225</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -55139,7 +55139,7 @@
         <v>45225</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -55196,7 +55196,7 @@
         <v>45225</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -55253,7 +55253,7 @@
         <v>45225</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -55310,7 +55310,7 @@
         <v>45225</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -55367,7 +55367,7 @@
         <v>45225</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -55424,7 +55424,7 @@
         <v>45225</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -55481,7 +55481,7 @@
         <v>45226</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -55538,7 +55538,7 @@
         <v>45229</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -55595,7 +55595,7 @@
         <v>45229</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -55652,7 +55652,7 @@
         <v>45229</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -55709,7 +55709,7 @@
         <v>45229</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -55766,7 +55766,7 @@
         <v>45229</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -55823,7 +55823,7 @@
         <v>45230</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -55880,7 +55880,7 @@
         <v>45230</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -55937,7 +55937,7 @@
         <v>45230</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -55994,7 +55994,7 @@
         <v>45230</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -56051,7 +56051,7 @@
         <v>45230</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -56108,7 +56108,7 @@
         <v>45231</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -56165,7 +56165,7 @@
         <v>45231</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -56222,7 +56222,7 @@
         <v>45231</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -56279,7 +56279,7 @@
         <v>45231</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -56336,7 +56336,7 @@
         <v>45231</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -56393,7 +56393,7 @@
         <v>45231</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -56450,7 +56450,7 @@
         <v>45231</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -56507,7 +56507,7 @@
         <v>45232</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -56569,7 +56569,7 @@
         <v>45232</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -56626,7 +56626,7 @@
         <v>45232</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -56683,7 +56683,7 @@
         <v>45232</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -56740,7 +56740,7 @@
         <v>45233</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -56802,7 +56802,7 @@
         <v>45236</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -56859,7 +56859,7 @@
         <v>45236</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -56916,7 +56916,7 @@
         <v>45236</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -56973,7 +56973,7 @@
         <v>45237</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -57030,7 +57030,7 @@
         <v>45237</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -57092,7 +57092,7 @@
         <v>45239</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -57149,7 +57149,7 @@
         <v>45239</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -57206,7 +57206,7 @@
         <v>45240</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -57268,7 +57268,7 @@
         <v>45243</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -57325,7 +57325,7 @@
         <v>45243</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -57382,7 +57382,7 @@
         <v>45243</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -57439,7 +57439,7 @@
         <v>45243</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -57496,7 +57496,7 @@
         <v>45243</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -57553,7 +57553,7 @@
         <v>45243</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -57610,7 +57610,7 @@
         <v>45244</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -57667,7 +57667,7 @@
         <v>45244</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -57729,7 +57729,7 @@
         <v>45244</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -57791,7 +57791,7 @@
         <v>45244</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -57848,7 +57848,7 @@
         <v>45244</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -57905,7 +57905,7 @@
         <v>45244</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -57967,7 +57967,7 @@
         <v>45244</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -58024,7 +58024,7 @@
         <v>45245</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -58081,7 +58081,7 @@
         <v>45245</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -58138,7 +58138,7 @@
         <v>45245</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -58195,7 +58195,7 @@
         <v>45245</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -58252,7 +58252,7 @@
         <v>45245</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -58314,7 +58314,7 @@
         <v>45245</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -58371,7 +58371,7 @@
         <v>45245</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -58428,7 +58428,7 @@
         <v>45247</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -58485,7 +58485,7 @@
         <v>45247</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -58542,7 +58542,7 @@
         <v>45248</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -58599,7 +58599,7 @@
         <v>45250</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -58656,7 +58656,7 @@
         <v>45250</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -58713,7 +58713,7 @@
         <v>45251</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -58770,7 +58770,7 @@
         <v>45251</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -58827,7 +58827,7 @@
         <v>45251</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -58884,7 +58884,7 @@
         <v>45252</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -58941,7 +58941,7 @@
         <v>45253</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -59003,7 +59003,7 @@
         <v>45253</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -59060,7 +59060,7 @@
         <v>45253</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -59122,7 +59122,7 @@
         <v>45253</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -59179,7 +59179,7 @@
         <v>45253</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -59241,7 +59241,7 @@
         <v>45253</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -59303,7 +59303,7 @@
         <v>45253</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -59360,7 +59360,7 @@
         <v>45257</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -59417,7 +59417,7 @@
         <v>45258</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -59474,7 +59474,7 @@
         <v>45259</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -59531,7 +59531,7 @@
         <v>45260</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -59588,7 +59588,7 @@
         <v>45261</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -59645,7 +59645,7 @@
         <v>45261</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -59702,7 +59702,7 @@
         <v>45264</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -59759,7 +59759,7 @@
         <v>45264</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -59816,7 +59816,7 @@
         <v>45264</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -59873,7 +59873,7 @@
         <v>45264</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -59930,7 +59930,7 @@
         <v>45264</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -59987,7 +59987,7 @@
         <v>45265</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -60044,7 +60044,7 @@
         <v>45265</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -60101,7 +60101,7 @@
         <v>45265</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -60158,7 +60158,7 @@
         <v>45266</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -60215,7 +60215,7 @@
         <v>45266</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -60272,7 +60272,7 @@
         <v>45266</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -60329,7 +60329,7 @@
         <v>45266</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -60391,7 +60391,7 @@
         <v>45267</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -60448,7 +60448,7 @@
         <v>45267</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -60505,7 +60505,7 @@
         <v>45267</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -60562,7 +60562,7 @@
         <v>45267</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -60619,7 +60619,7 @@
         <v>45267</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -60676,7 +60676,7 @@
         <v>45268</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -60733,7 +60733,7 @@
         <v>45271</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -60790,7 +60790,7 @@
         <v>45273</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -60847,7 +60847,7 @@
         <v>45273</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -60904,7 +60904,7 @@
         <v>45275</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -60961,7 +60961,7 @@
         <v>45279</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -61018,7 +61018,7 @@
         <v>45279</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -61075,7 +61075,7 @@
         <v>45279</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -61132,7 +61132,7 @@
         <v>45281</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -61189,7 +61189,7 @@
         <v>45281</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -61251,7 +61251,7 @@
         <v>45282</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -61308,7 +61308,7 @@
         <v>45287</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -61370,7 +61370,7 @@
         <v>45297</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -61432,7 +61432,7 @@
         <v>45299</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -61489,7 +61489,7 @@
         <v>45300</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -61546,7 +61546,7 @@
         <v>45300</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -61603,7 +61603,7 @@
         <v>45302</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -61660,7 +61660,7 @@
         <v>45302</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -61717,7 +61717,7 @@
         <v>45303</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -61774,7 +61774,7 @@
         <v>45306</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -61831,7 +61831,7 @@
         <v>45306</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -61888,7 +61888,7 @@
         <v>45307</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -61945,7 +61945,7 @@
         <v>45307</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -62002,7 +62002,7 @@
         <v>45307</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -62059,7 +62059,7 @@
         <v>45307</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -62116,7 +62116,7 @@
         <v>45307</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -62173,7 +62173,7 @@
         <v>45310</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -62230,7 +62230,7 @@
         <v>45310</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -62287,7 +62287,7 @@
         <v>45310</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -62344,7 +62344,7 @@
         <v>45310</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -62401,7 +62401,7 @@
         <v>45310</v>
       </c>
       <c r="C1038" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
@@ -62458,7 +62458,7 @@
         <v>45310</v>
       </c>
       <c r="C1039" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
@@ -62515,7 +62515,7 @@
         <v>45310</v>
       </c>
       <c r="C1040" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
@@ -62572,7 +62572,7 @@
         <v>45310</v>
       </c>
       <c r="C1041" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
@@ -62629,7 +62629,7 @@
         <v>45310</v>
       </c>
       <c r="C1042" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
@@ -62686,7 +62686,7 @@
         <v>45313</v>
       </c>
       <c r="C1043" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D1043" t="inlineStr">
         <is>
@@ -62743,7 +62743,7 @@
         <v>45314</v>
       </c>
       <c r="C1044" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D1044" t="inlineStr">
         <is>
@@ -62800,7 +62800,7 @@
         <v>45314</v>
       </c>
       <c r="C1045" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D1045" t="inlineStr">
         <is>
@@ -62857,7 +62857,7 @@
         <v>45314</v>
       </c>
       <c r="C1046" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D1046" t="inlineStr">
         <is>
@@ -62914,7 +62914,7 @@
         <v>45316</v>
       </c>
       <c r="C1047" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D1047" t="inlineStr">
         <is>
@@ -62971,7 +62971,7 @@
         <v>45317</v>
       </c>
       <c r="C1048" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D1048" t="inlineStr">
         <is>
@@ -63028,7 +63028,7 @@
         <v>45321</v>
       </c>
       <c r="C1049" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D1049" t="inlineStr">
         <is>
@@ -63085,7 +63085,7 @@
         <v>45321</v>
       </c>
       <c r="C1050" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D1050" t="inlineStr">
         <is>
@@ -63142,7 +63142,7 @@
         <v>45321</v>
       </c>
       <c r="C1051" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D1051" t="inlineStr">
         <is>
@@ -63199,7 +63199,7 @@
         <v>45321</v>
       </c>
       <c r="C1052" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D1052" t="inlineStr">
         <is>
@@ -63256,7 +63256,7 @@
         <v>45321</v>
       </c>
       <c r="C1053" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D1053" t="inlineStr">
         <is>
@@ -63313,7 +63313,7 @@
         <v>45321</v>
       </c>
       <c r="C1054" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D1054" t="inlineStr">
         <is>
@@ -63370,7 +63370,7 @@
         <v>45321</v>
       </c>
       <c r="C1055" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D1055" t="inlineStr">
         <is>
@@ -63427,7 +63427,7 @@
         <v>45321</v>
       </c>
       <c r="C1056" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D1056" t="inlineStr">
         <is>
@@ -63484,7 +63484,7 @@
         <v>45321</v>
       </c>
       <c r="C1057" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D1057" t="inlineStr">
         <is>
@@ -63541,7 +63541,7 @@
         <v>45321</v>
       </c>
       <c r="C1058" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D1058" t="inlineStr">
         <is>
@@ -63598,7 +63598,7 @@
         <v>45321</v>
       </c>
       <c r="C1059" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D1059" t="inlineStr">
         <is>
@@ -63655,7 +63655,7 @@
         <v>45321</v>
       </c>
       <c r="C1060" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D1060" t="inlineStr">
         <is>
@@ -63712,7 +63712,7 @@
         <v>45322</v>
       </c>
       <c r="C1061" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D1061" t="inlineStr">
         <is>
@@ -63769,7 +63769,7 @@
         <v>45324</v>
       </c>
       <c r="C1062" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D1062" t="inlineStr">
         <is>
@@ -63826,7 +63826,7 @@
         <v>45329</v>
       </c>
       <c r="C1063" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D1063" t="inlineStr">
         <is>
@@ -63883,7 +63883,7 @@
         <v>45329</v>
       </c>
       <c r="C1064" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D1064" t="inlineStr">
         <is>
@@ -63933,14 +63933,14 @@
     <row r="1065" ht="15" customHeight="1">
       <c r="A1065" t="inlineStr">
         <is>
-          <t>A 5124-2024</t>
+          <t>A 5174-2024</t>
         </is>
       </c>
       <c r="B1065" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C1065" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D1065" t="inlineStr">
         <is>
@@ -63953,7 +63953,7 @@
         </is>
       </c>
       <c r="G1065" t="n">
-        <v>2.6</v>
+        <v>1.4</v>
       </c>
       <c r="H1065" t="n">
         <v>0</v>
@@ -63990,14 +63990,14 @@
     <row r="1066" ht="15" customHeight="1">
       <c r="A1066" t="inlineStr">
         <is>
-          <t>A 5189-2024</t>
+          <t>A 5156-2024</t>
         </is>
       </c>
       <c r="B1066" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C1066" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D1066" t="inlineStr">
         <is>
@@ -64010,7 +64010,7 @@
         </is>
       </c>
       <c r="G1066" t="n">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
       <c r="H1066" t="n">
         <v>0</v>
@@ -64054,7 +64054,7 @@
         <v>45330</v>
       </c>
       <c r="C1067" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D1067" t="inlineStr">
         <is>
@@ -64111,7 +64111,7 @@
         <v>45330</v>
       </c>
       <c r="C1068" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D1068" t="inlineStr">
         <is>
@@ -64161,14 +64161,14 @@
     <row r="1069" ht="15" customHeight="1">
       <c r="A1069" t="inlineStr">
         <is>
-          <t>A 5156-2024</t>
+          <t>A 5124-2024</t>
         </is>
       </c>
       <c r="B1069" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C1069" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D1069" t="inlineStr">
         <is>
@@ -64181,7 +64181,7 @@
         </is>
       </c>
       <c r="G1069" t="n">
-        <v>0.4</v>
+        <v>2.6</v>
       </c>
       <c r="H1069" t="n">
         <v>0</v>
@@ -64218,14 +64218,14 @@
     <row r="1070" ht="15" customHeight="1">
       <c r="A1070" t="inlineStr">
         <is>
-          <t>A 5174-2024</t>
+          <t>A 5189-2024</t>
         </is>
       </c>
       <c r="B1070" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C1070" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D1070" t="inlineStr">
         <is>
@@ -64238,7 +64238,7 @@
         </is>
       </c>
       <c r="G1070" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="H1070" t="n">
         <v>0</v>
@@ -64282,7 +64282,7 @@
         <v>45331</v>
       </c>
       <c r="C1071" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D1071" t="inlineStr">
         <is>
@@ -64339,7 +64339,7 @@
         <v>45331</v>
       </c>
       <c r="C1072" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D1072" t="inlineStr">
         <is>
@@ -64396,7 +64396,7 @@
         <v>45334</v>
       </c>
       <c r="C1073" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D1073" t="inlineStr">
         <is>
@@ -64453,7 +64453,7 @@
         <v>45334</v>
       </c>
       <c r="C1074" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D1074" t="inlineStr">
         <is>
@@ -64503,14 +64503,14 @@
     <row r="1075" ht="15" customHeight="1">
       <c r="A1075" t="inlineStr">
         <is>
-          <t>A 6213-2024</t>
+          <t>A 6169-2024</t>
         </is>
       </c>
       <c r="B1075" s="1" t="n">
         <v>45337</v>
       </c>
       <c r="C1075" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D1075" t="inlineStr">
         <is>
@@ -64523,7 +64523,7 @@
         </is>
       </c>
       <c r="G1075" t="n">
-        <v>0.6</v>
+        <v>3.3</v>
       </c>
       <c r="H1075" t="n">
         <v>0</v>
@@ -64560,14 +64560,14 @@
     <row r="1076" ht="15" customHeight="1">
       <c r="A1076" t="inlineStr">
         <is>
-          <t>A 6169-2024</t>
+          <t>A 6187-2024</t>
         </is>
       </c>
       <c r="B1076" s="1" t="n">
         <v>45337</v>
       </c>
       <c r="C1076" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D1076" t="inlineStr">
         <is>
@@ -64580,7 +64580,7 @@
         </is>
       </c>
       <c r="G1076" t="n">
-        <v>3.3</v>
+        <v>0.8</v>
       </c>
       <c r="H1076" t="n">
         <v>0</v>
@@ -64617,14 +64617,14 @@
     <row r="1077" ht="15" customHeight="1">
       <c r="A1077" t="inlineStr">
         <is>
-          <t>A 6187-2024</t>
+          <t>A 6213-2024</t>
         </is>
       </c>
       <c r="B1077" s="1" t="n">
         <v>45337</v>
       </c>
       <c r="C1077" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D1077" t="inlineStr">
         <is>
@@ -64637,7 +64637,7 @@
         </is>
       </c>
       <c r="G1077" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="H1077" t="n">
         <v>0</v>
@@ -64681,7 +64681,7 @@
         <v>45343</v>
       </c>
       <c r="C1078" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D1078" t="inlineStr">
         <is>
@@ -64736,14 +64736,14 @@
     <row r="1079" ht="15" customHeight="1">
       <c r="A1079" t="inlineStr">
         <is>
-          <t>A 7146-2024</t>
+          <t>A 7140-2024</t>
         </is>
       </c>
       <c r="B1079" s="1" t="n">
         <v>45344</v>
       </c>
       <c r="C1079" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D1079" t="inlineStr">
         <is>
@@ -64756,7 +64756,7 @@
         </is>
       </c>
       <c r="G1079" t="n">
-        <v>0.4</v>
+        <v>5.9</v>
       </c>
       <c r="H1079" t="n">
         <v>0</v>
@@ -64793,14 +64793,14 @@
     <row r="1080" ht="15" customHeight="1">
       <c r="A1080" t="inlineStr">
         <is>
-          <t>A 7140-2024</t>
+          <t>A 7146-2024</t>
         </is>
       </c>
       <c r="B1080" s="1" t="n">
         <v>45344</v>
       </c>
       <c r="C1080" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D1080" t="inlineStr">
         <is>
@@ -64813,7 +64813,7 @@
         </is>
       </c>
       <c r="G1080" t="n">
-        <v>5.9</v>
+        <v>0.4</v>
       </c>
       <c r="H1080" t="n">
         <v>0</v>
@@ -64857,7 +64857,7 @@
         <v>45349</v>
       </c>
       <c r="C1081" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D1081" t="inlineStr">
         <is>
@@ -64914,7 +64914,7 @@
         <v>45350</v>
       </c>
       <c r="C1082" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D1082" t="inlineStr">
         <is>
@@ -64971,7 +64971,7 @@
         <v>45351</v>
       </c>
       <c r="C1083" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D1083" t="inlineStr">
         <is>
@@ -65018,7 +65018,7 @@
       </c>
       <c r="R1083" s="2" t="inlineStr"/>
     </row>
-    <row r="1084">
+    <row r="1084" ht="15" customHeight="1">
       <c r="A1084" t="inlineStr">
         <is>
           <t>A 8127-2024</t>
@@ -65028,7 +65028,7 @@
         <v>45351</v>
       </c>
       <c r="C1084" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D1084" t="inlineStr">
         <is>
@@ -65074,6 +65074,63 @@
         <v>0</v>
       </c>
       <c r="R1084" s="2" t="inlineStr"/>
+    </row>
+    <row r="1085">
+      <c r="A1085" t="inlineStr">
+        <is>
+          <t>A 8381-2024</t>
+        </is>
+      </c>
+      <c r="B1085" s="1" t="n">
+        <v>45352</v>
+      </c>
+      <c r="C1085" s="1" t="n">
+        <v>45353</v>
+      </c>
+      <c r="D1085" t="inlineStr">
+        <is>
+          <t>DALARNAS LÄN</t>
+        </is>
+      </c>
+      <c r="E1085" t="inlineStr">
+        <is>
+          <t>RÄTTVIK</t>
+        </is>
+      </c>
+      <c r="G1085" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H1085" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1085" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1085" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1085" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1085" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1085" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1085" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1085" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1085" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1085" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1085" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt RÄTTVIK.xlsx
+++ b/Översikt RÄTTVIK.xlsx
@@ -569,7 +569,7 @@
         <v>43542</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         <v>44909</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
         <v>43663</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>43619</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>43740</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>44909</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>44874</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
         <v>45147</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>44237</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>44624</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>43634</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>43663</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
         <v>44148</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
         <v>44435</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v>44799</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2008,7 +2008,7 @@
         <v>44909</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2100,7 +2100,7 @@
         <v>44909</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2192,7 +2192,7 @@
         <v>45111</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
         <v>43700</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2370,7 +2370,7 @@
         <v>44496</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2456,7 +2456,7 @@
         <v>45033</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
         <v>45264</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         <v>43440</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2717,7 +2717,7 @@
         <v>43493</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         <v>43623</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2887,7 +2887,7 @@
         <v>43705</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2972,7 +2972,7 @@
         <v>44088</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3057,7 +3057,7 @@
         <v>44110</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3142,7 +3142,7 @@
         <v>44361</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3227,7 +3227,7 @@
         <v>44391</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3317,7 +3317,7 @@
         <v>44414</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3407,7 +3407,7 @@
         <v>44470</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3497,7 +3497,7 @@
         <v>44496</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3587,7 +3587,7 @@
         <v>44511</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3672,7 +3672,7 @@
         <v>44568</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3766,7 +3766,7 @@
         <v>44728</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3860,7 +3860,7 @@
         <v>44855</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3950,7 +3950,7 @@
         <v>44894</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4040,7 +4040,7 @@
         <v>44918</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4130,7 +4130,7 @@
         <v>44986</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4215,7 +4215,7 @@
         <v>45077</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4300,7 +4300,7 @@
         <v>45194</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4385,7 +4385,7 @@
         <v>45194</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4470,7 +4470,7 @@
         <v>45231</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4555,7 +4555,7 @@
         <v>43333</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4612,7 +4612,7 @@
         <v>43348</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4669,7 +4669,7 @@
         <v>43356</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4726,7 +4726,7 @@
         <v>43361</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4783,7 +4783,7 @@
         <v>43362</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4840,7 +4840,7 @@
         <v>43362</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4897,7 +4897,7 @@
         <v>43362</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4954,7 +4954,7 @@
         <v>43362</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5011,7 +5011,7 @@
         <v>43367</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5068,7 +5068,7 @@
         <v>43369</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5125,7 +5125,7 @@
         <v>43373</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5182,7 +5182,7 @@
         <v>43378</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5239,7 +5239,7 @@
         <v>43381</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5296,7 +5296,7 @@
         <v>43381</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5353,7 +5353,7 @@
         <v>43388</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5410,7 +5410,7 @@
         <v>43388</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5472,7 +5472,7 @@
         <v>43388</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5529,7 +5529,7 @@
         <v>43391</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5586,7 +5586,7 @@
         <v>43398</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5643,7 +5643,7 @@
         <v>43399</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5700,7 +5700,7 @@
         <v>43401</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5757,7 +5757,7 @@
         <v>43405</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5814,7 +5814,7 @@
         <v>43405</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5871,7 +5871,7 @@
         <v>43410</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5928,7 +5928,7 @@
         <v>43410</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5985,7 +5985,7 @@
         <v>43411</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6042,7 +6042,7 @@
         <v>43412</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6099,7 +6099,7 @@
         <v>43416</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6156,7 +6156,7 @@
         <v>43416</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6213,7 +6213,7 @@
         <v>43416</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6270,7 +6270,7 @@
         <v>43419</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         <v>43419</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6384,7 +6384,7 @@
         <v>43423</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6446,7 +6446,7 @@
         <v>43423</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6508,7 +6508,7 @@
         <v>43423</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6570,7 +6570,7 @@
         <v>43424</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6632,7 +6632,7 @@
         <v>43425</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6689,7 +6689,7 @@
         <v>43427</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6751,7 +6751,7 @@
         <v>43428</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6808,7 +6808,7 @@
         <v>43428</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6865,7 +6865,7 @@
         <v>43430</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6922,7 +6922,7 @@
         <v>43430</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6979,7 +6979,7 @@
         <v>43430</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7036,7 +7036,7 @@
         <v>43430</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7093,7 +7093,7 @@
         <v>43431</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7155,7 +7155,7 @@
         <v>43432</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7212,7 +7212,7 @@
         <v>43432</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7269,7 +7269,7 @@
         <v>43434</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7326,7 +7326,7 @@
         <v>43434</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7383,7 +7383,7 @@
         <v>43438</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7440,7 +7440,7 @@
         <v>43441</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7497,7 +7497,7 @@
         <v>43447</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
         <v>43448</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7611,7 +7611,7 @@
         <v>43451</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7668,7 +7668,7 @@
         <v>43451</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7725,7 +7725,7 @@
         <v>43451</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7782,7 +7782,7 @@
         <v>43452</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7839,7 +7839,7 @@
         <v>43454</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7901,7 +7901,7 @@
         <v>43454</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7963,7 +7963,7 @@
         <v>43454</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8025,7 +8025,7 @@
         <v>43455</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8082,7 +8082,7 @@
         <v>43461</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8139,7 +8139,7 @@
         <v>43471</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8196,7 +8196,7 @@
         <v>43472</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8253,7 +8253,7 @@
         <v>43472</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8315,7 +8315,7 @@
         <v>43473</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8372,7 +8372,7 @@
         <v>43475</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8429,7 +8429,7 @@
         <v>43481</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8486,7 +8486,7 @@
         <v>43490</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8543,7 +8543,7 @@
         <v>43495</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8600,7 +8600,7 @@
         <v>43499</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8657,7 +8657,7 @@
         <v>43500</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8719,7 +8719,7 @@
         <v>43511</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8776,7 +8776,7 @@
         <v>43511</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8833,7 +8833,7 @@
         <v>43514</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8890,7 +8890,7 @@
         <v>43517</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8947,7 +8947,7 @@
         <v>43524</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9004,7 +9004,7 @@
         <v>43546</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9061,7 +9061,7 @@
         <v>43553</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9123,7 +9123,7 @@
         <v>43553</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9180,7 +9180,7 @@
         <v>43554</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9237,7 +9237,7 @@
         <v>43556</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9294,7 +9294,7 @@
         <v>43559</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9356,7 +9356,7 @@
         <v>43564</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9413,7 +9413,7 @@
         <v>43566</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9470,7 +9470,7 @@
         <v>43570</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9532,7 +9532,7 @@
         <v>43570</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9594,7 +9594,7 @@
         <v>43570</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9651,7 +9651,7 @@
         <v>43580</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9708,7 +9708,7 @@
         <v>43584</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9765,7 +9765,7 @@
         <v>43585</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9822,7 +9822,7 @@
         <v>43587</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9879,7 +9879,7 @@
         <v>43592</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9936,7 +9936,7 @@
         <v>43592</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9993,7 +9993,7 @@
         <v>43592</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10050,7 +10050,7 @@
         <v>43599</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10107,7 +10107,7 @@
         <v>43609</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10164,7 +10164,7 @@
         <v>43612</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10221,7 +10221,7 @@
         <v>43612</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10278,7 +10278,7 @@
         <v>43612</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10335,7 +10335,7 @@
         <v>43612</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10392,7 +10392,7 @@
         <v>43616</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10449,7 +10449,7 @@
         <v>43619</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10511,7 +10511,7 @@
         <v>43621</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10568,7 +10568,7 @@
         <v>43623</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10625,7 +10625,7 @@
         <v>43628</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10687,7 +10687,7 @@
         <v>43628</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10749,7 +10749,7 @@
         <v>43629</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10806,7 +10806,7 @@
         <v>43630</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10863,7 +10863,7 @@
         <v>43633</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10920,7 +10920,7 @@
         <v>43633</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10977,7 +10977,7 @@
         <v>43641</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11034,7 +11034,7 @@
         <v>43643</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11096,7 +11096,7 @@
         <v>43643</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11158,7 +11158,7 @@
         <v>43647</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11220,7 +11220,7 @@
         <v>43651</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11277,7 +11277,7 @@
         <v>43651</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11334,7 +11334,7 @@
         <v>43656</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11391,7 +11391,7 @@
         <v>43657</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11448,7 +11448,7 @@
         <v>43662</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11505,7 +11505,7 @@
         <v>43662</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11562,7 +11562,7 @@
         <v>43663</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11644,7 +11644,7 @@
         <v>43663</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11706,7 +11706,7 @@
         <v>43663</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11768,7 +11768,7 @@
         <v>43663</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11830,7 +11830,7 @@
         <v>43682</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11887,7 +11887,7 @@
         <v>43686</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11949,7 +11949,7 @@
         <v>43686</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12006,7 +12006,7 @@
         <v>43689</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12068,7 +12068,7 @@
         <v>43690</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12125,7 +12125,7 @@
         <v>43697</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12182,7 +12182,7 @@
         <v>43700</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12239,7 +12239,7 @@
         <v>43705</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12296,7 +12296,7 @@
         <v>43711</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12358,7 +12358,7 @@
         <v>43712</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12415,7 +12415,7 @@
         <v>43713</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12472,7 +12472,7 @@
         <v>43714</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12529,7 +12529,7 @@
         <v>43714</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12586,7 +12586,7 @@
         <v>43717</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12643,7 +12643,7 @@
         <v>43718</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12700,7 +12700,7 @@
         <v>43720</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12757,7 +12757,7 @@
         <v>43724</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12814,7 +12814,7 @@
         <v>43726</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12871,7 +12871,7 @@
         <v>43727</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12928,7 +12928,7 @@
         <v>43727</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12985,7 +12985,7 @@
         <v>43727</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13042,7 +13042,7 @@
         <v>43732</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13099,7 +13099,7 @@
         <v>43734</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13161,7 +13161,7 @@
         <v>43734</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13218,7 +13218,7 @@
         <v>43734</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13275,7 +13275,7 @@
         <v>43735</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13337,7 +13337,7 @@
         <v>43735</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13394,7 +13394,7 @@
         <v>43740</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13456,7 +13456,7 @@
         <v>43740</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13513,7 +13513,7 @@
         <v>43740</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13570,7 +13570,7 @@
         <v>43740</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13627,7 +13627,7 @@
         <v>43742</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13689,7 +13689,7 @@
         <v>43742</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13746,7 +13746,7 @@
         <v>43747</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13803,7 +13803,7 @@
         <v>43758</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13860,7 +13860,7 @@
         <v>43761</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13917,7 +13917,7 @@
         <v>43766</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13974,7 +13974,7 @@
         <v>43767</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14036,7 +14036,7 @@
         <v>43769</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14098,7 +14098,7 @@
         <v>43770</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14155,7 +14155,7 @@
         <v>43770</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14212,7 +14212,7 @@
         <v>43773</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14269,7 +14269,7 @@
         <v>43775</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14326,7 +14326,7 @@
         <v>43776</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14383,7 +14383,7 @@
         <v>43776</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14440,7 +14440,7 @@
         <v>43776</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14497,7 +14497,7 @@
         <v>43776</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14554,7 +14554,7 @@
         <v>43780</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14616,7 +14616,7 @@
         <v>43780</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14673,7 +14673,7 @@
         <v>43780</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14730,7 +14730,7 @@
         <v>43780</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14787,7 +14787,7 @@
         <v>43783</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14849,7 +14849,7 @@
         <v>43784</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14906,7 +14906,7 @@
         <v>43786</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14963,7 +14963,7 @@
         <v>43797</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15020,7 +15020,7 @@
         <v>43804</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15082,7 +15082,7 @@
         <v>43805</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15139,7 +15139,7 @@
         <v>43805</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15196,7 +15196,7 @@
         <v>43812</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15253,7 +15253,7 @@
         <v>43812</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15310,7 +15310,7 @@
         <v>43815</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15367,7 +15367,7 @@
         <v>43815</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15424,7 +15424,7 @@
         <v>43829</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15481,7 +15481,7 @@
         <v>43833</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15538,7 +15538,7 @@
         <v>43837</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15595,7 +15595,7 @@
         <v>43839</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15652,7 +15652,7 @@
         <v>43840</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15709,7 +15709,7 @@
         <v>43843</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15766,7 +15766,7 @@
         <v>43845</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15828,7 +15828,7 @@
         <v>43850</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15885,7 +15885,7 @@
         <v>43854</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15947,7 +15947,7 @@
         <v>43857</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16004,7 +16004,7 @@
         <v>43857</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16066,7 +16066,7 @@
         <v>43857</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16123,7 +16123,7 @@
         <v>43864</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16180,7 +16180,7 @@
         <v>43864</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16242,7 +16242,7 @@
         <v>43864</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16304,7 +16304,7 @@
         <v>43867</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16366,7 +16366,7 @@
         <v>43871</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16423,7 +16423,7 @@
         <v>43872</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16485,7 +16485,7 @@
         <v>43873</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16542,7 +16542,7 @@
         <v>43873</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16599,7 +16599,7 @@
         <v>43873</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16656,7 +16656,7 @@
         <v>43874</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16713,7 +16713,7 @@
         <v>43878</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16770,7 +16770,7 @@
         <v>43879</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16832,7 +16832,7 @@
         <v>43880</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16889,7 +16889,7 @@
         <v>43894</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16946,7 +16946,7 @@
         <v>43894</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17003,7 +17003,7 @@
         <v>43902</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17060,7 +17060,7 @@
         <v>43917</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17117,7 +17117,7 @@
         <v>43917</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17179,7 +17179,7 @@
         <v>43920</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17241,7 +17241,7 @@
         <v>43920</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17303,7 +17303,7 @@
         <v>43921</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17365,7 +17365,7 @@
         <v>43922</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17427,7 +17427,7 @@
         <v>43922</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17489,7 +17489,7 @@
         <v>43924</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17546,7 +17546,7 @@
         <v>43924</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17603,7 +17603,7 @@
         <v>43927</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17660,7 +17660,7 @@
         <v>43927</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17717,7 +17717,7 @@
         <v>43928</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17774,7 +17774,7 @@
         <v>43928</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17831,7 +17831,7 @@
         <v>43930</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17893,7 +17893,7 @@
         <v>43933</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17955,7 +17955,7 @@
         <v>43933</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18017,7 +18017,7 @@
         <v>43935</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18074,7 +18074,7 @@
         <v>43937</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18136,7 +18136,7 @@
         <v>43941</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18193,7 +18193,7 @@
         <v>43941</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18250,7 +18250,7 @@
         <v>43948</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18307,7 +18307,7 @@
         <v>43949</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18369,7 +18369,7 @@
         <v>43949</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18431,7 +18431,7 @@
         <v>43949</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18493,7 +18493,7 @@
         <v>43949</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18555,7 +18555,7 @@
         <v>43950</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18612,7 +18612,7 @@
         <v>43951</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18674,7 +18674,7 @@
         <v>43959</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18736,7 +18736,7 @@
         <v>43959</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18798,7 +18798,7 @@
         <v>43959</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18860,7 +18860,7 @@
         <v>43959</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18917,7 +18917,7 @@
         <v>43969</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18979,7 +18979,7 @@
         <v>43970</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19036,7 +19036,7 @@
         <v>43973</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19093,7 +19093,7 @@
         <v>43985</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19150,7 +19150,7 @@
         <v>43990</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19207,7 +19207,7 @@
         <v>43991</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19269,7 +19269,7 @@
         <v>43991</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19331,7 +19331,7 @@
         <v>43991</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19393,7 +19393,7 @@
         <v>43991</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19455,7 +19455,7 @@
         <v>43991</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19517,7 +19517,7 @@
         <v>44005</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19579,7 +19579,7 @@
         <v>44033</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19636,7 +19636,7 @@
         <v>44039</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19693,7 +19693,7 @@
         <v>44048</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19750,7 +19750,7 @@
         <v>44049</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19807,7 +19807,7 @@
         <v>44053</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19864,7 +19864,7 @@
         <v>44053</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19921,7 +19921,7 @@
         <v>44053</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19978,7 +19978,7 @@
         <v>44054</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20040,7 +20040,7 @@
         <v>44054</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20097,7 +20097,7 @@
         <v>44054</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20154,7 +20154,7 @@
         <v>44055</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20216,7 +20216,7 @@
         <v>44055</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20278,7 +20278,7 @@
         <v>44074</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20335,7 +20335,7 @@
         <v>44074</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20392,7 +20392,7 @@
         <v>44077</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20449,7 +20449,7 @@
         <v>44078</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20511,7 +20511,7 @@
         <v>44078</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20573,7 +20573,7 @@
         <v>44082</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20630,7 +20630,7 @@
         <v>44084</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20692,7 +20692,7 @@
         <v>44089</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20749,7 +20749,7 @@
         <v>44091</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20806,7 +20806,7 @@
         <v>44095</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20863,7 +20863,7 @@
         <v>44097</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20920,7 +20920,7 @@
         <v>44102</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20977,7 +20977,7 @@
         <v>44104</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21034,7 +21034,7 @@
         <v>44105</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21091,7 +21091,7 @@
         <v>44109</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21148,7 +21148,7 @@
         <v>44109</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21210,7 +21210,7 @@
         <v>44117</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21272,7 +21272,7 @@
         <v>44126</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21334,7 +21334,7 @@
         <v>44126</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21396,7 +21396,7 @@
         <v>44126</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21458,7 +21458,7 @@
         <v>44126</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21520,7 +21520,7 @@
         <v>44126</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21582,7 +21582,7 @@
         <v>44130</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21639,7 +21639,7 @@
         <v>44130</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21696,7 +21696,7 @@
         <v>44130</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21753,7 +21753,7 @@
         <v>44130</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21810,7 +21810,7 @@
         <v>44131</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21867,7 +21867,7 @@
         <v>44133</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21929,7 +21929,7 @@
         <v>44137</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21986,7 +21986,7 @@
         <v>44139</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22043,7 +22043,7 @@
         <v>44139</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22100,7 +22100,7 @@
         <v>44141</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22157,7 +22157,7 @@
         <v>44145</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22214,7 +22214,7 @@
         <v>44145</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22271,7 +22271,7 @@
         <v>44151</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22328,7 +22328,7 @@
         <v>44151</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22385,7 +22385,7 @@
         <v>44153</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22442,7 +22442,7 @@
         <v>44159</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22499,7 +22499,7 @@
         <v>44159</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22556,7 +22556,7 @@
         <v>44159</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22613,7 +22613,7 @@
         <v>44159</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22670,7 +22670,7 @@
         <v>44160</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22727,7 +22727,7 @@
         <v>44160</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22784,7 +22784,7 @@
         <v>44160</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22841,7 +22841,7 @@
         <v>44161</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22898,7 +22898,7 @@
         <v>44162</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22955,7 +22955,7 @@
         <v>44173</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23012,7 +23012,7 @@
         <v>44175</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23069,7 +23069,7 @@
         <v>44175</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23126,7 +23126,7 @@
         <v>44179</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23183,7 +23183,7 @@
         <v>44179</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23240,7 +23240,7 @@
         <v>44180</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23297,7 +23297,7 @@
         <v>44185</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23354,7 +23354,7 @@
         <v>44186</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23411,7 +23411,7 @@
         <v>44186</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23468,7 +23468,7 @@
         <v>44194</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23525,7 +23525,7 @@
         <v>44195</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23582,7 +23582,7 @@
         <v>44214</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23639,7 +23639,7 @@
         <v>44214</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23696,7 +23696,7 @@
         <v>44217</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23753,7 +23753,7 @@
         <v>44217</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23810,7 +23810,7 @@
         <v>44228</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23867,7 +23867,7 @@
         <v>44228</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23924,7 +23924,7 @@
         <v>44238</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23981,7 +23981,7 @@
         <v>44242</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24038,7 +24038,7 @@
         <v>44242</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24095,7 +24095,7 @@
         <v>44271</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24152,7 +24152,7 @@
         <v>44273</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24209,7 +24209,7 @@
         <v>44280</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24266,7 +24266,7 @@
         <v>44281</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24323,7 +24323,7 @@
         <v>44284</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24380,7 +24380,7 @@
         <v>44284</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24437,7 +24437,7 @@
         <v>44300</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24494,7 +24494,7 @@
         <v>44300</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24551,7 +24551,7 @@
         <v>44300</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24608,7 +24608,7 @@
         <v>44305</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24665,7 +24665,7 @@
         <v>44306</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24722,7 +24722,7 @@
         <v>44307</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24779,7 +24779,7 @@
         <v>44322</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24841,7 +24841,7 @@
         <v>44326</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24898,7 +24898,7 @@
         <v>44326</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24955,7 +24955,7 @@
         <v>44326</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25012,7 +25012,7 @@
         <v>44326</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25069,7 +25069,7 @@
         <v>44330</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25126,7 +25126,7 @@
         <v>44335</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25183,7 +25183,7 @@
         <v>44336</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25245,7 +25245,7 @@
         <v>44340</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25302,7 +25302,7 @@
         <v>44342</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25364,7 +25364,7 @@
         <v>44347</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25421,7 +25421,7 @@
         <v>44347</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25478,7 +25478,7 @@
         <v>44348</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25535,7 +25535,7 @@
         <v>44348</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25592,7 +25592,7 @@
         <v>44349</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25649,7 +25649,7 @@
         <v>44349</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25706,7 +25706,7 @@
         <v>44350</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25763,7 +25763,7 @@
         <v>44351</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25820,7 +25820,7 @@
         <v>44351</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25877,7 +25877,7 @@
         <v>44363</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25934,7 +25934,7 @@
         <v>44377</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25996,7 +25996,7 @@
         <v>44377</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26053,7 +26053,7 @@
         <v>44377</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26110,7 +26110,7 @@
         <v>44377</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26167,7 +26167,7 @@
         <v>44377</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26229,7 +26229,7 @@
         <v>44386</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26291,7 +26291,7 @@
         <v>44386</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26353,7 +26353,7 @@
         <v>44391</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26415,7 +26415,7 @@
         <v>44391</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26477,7 +26477,7 @@
         <v>44399</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26534,7 +26534,7 @@
         <v>44400</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26591,7 +26591,7 @@
         <v>44403</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26648,7 +26648,7 @@
         <v>44408</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26710,7 +26710,7 @@
         <v>44409</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26772,7 +26772,7 @@
         <v>44414</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26834,7 +26834,7 @@
         <v>44414</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26896,7 +26896,7 @@
         <v>44414</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26958,7 +26958,7 @@
         <v>44418</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27015,7 +27015,7 @@
         <v>44420</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27072,7 +27072,7 @@
         <v>44421</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27129,7 +27129,7 @@
         <v>44421</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27191,7 +27191,7 @@
         <v>44424</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27253,7 +27253,7 @@
         <v>44424</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27310,7 +27310,7 @@
         <v>44432</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27372,7 +27372,7 @@
         <v>44435</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27429,7 +27429,7 @@
         <v>44441</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27486,7 +27486,7 @@
         <v>44441</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27548,7 +27548,7 @@
         <v>44449</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27610,7 +27610,7 @@
         <v>44451</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27672,7 +27672,7 @@
         <v>44451</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27734,7 +27734,7 @@
         <v>44454</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27791,7 +27791,7 @@
         <v>44459</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27853,7 +27853,7 @@
         <v>44459</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27915,7 +27915,7 @@
         <v>44459</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27977,7 +27977,7 @@
         <v>44459</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28039,7 +28039,7 @@
         <v>44459</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28101,7 +28101,7 @@
         <v>44459</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28163,7 +28163,7 @@
         <v>44460</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28220,7 +28220,7 @@
         <v>44460</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28277,7 +28277,7 @@
         <v>44461</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28334,7 +28334,7 @@
         <v>44463</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28396,7 +28396,7 @@
         <v>44467</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28458,7 +28458,7 @@
         <v>44469</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28520,7 +28520,7 @@
         <v>44469</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28582,7 +28582,7 @@
         <v>44469</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28644,7 +28644,7 @@
         <v>44469</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28706,7 +28706,7 @@
         <v>44470</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28768,7 +28768,7 @@
         <v>44470</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28825,7 +28825,7 @@
         <v>44470</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28887,7 +28887,7 @@
         <v>44473</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28944,7 +28944,7 @@
         <v>44474</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29001,7 +29001,7 @@
         <v>44475</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29058,7 +29058,7 @@
         <v>44475</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29115,7 +29115,7 @@
         <v>44477</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29172,7 +29172,7 @@
         <v>44477</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29229,7 +29229,7 @@
         <v>44477</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29286,7 +29286,7 @@
         <v>44479</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29348,7 +29348,7 @@
         <v>44484</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29410,7 +29410,7 @@
         <v>44484</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29472,7 +29472,7 @@
         <v>44488</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29529,7 +29529,7 @@
         <v>44489</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29591,7 +29591,7 @@
         <v>44495</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29653,7 +29653,7 @@
         <v>44495</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29715,7 +29715,7 @@
         <v>44495</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29777,7 +29777,7 @@
         <v>44495</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29839,7 +29839,7 @@
         <v>44495</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29901,7 +29901,7 @@
         <v>44495</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29963,7 +29963,7 @@
         <v>44495</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30025,7 +30025,7 @@
         <v>44496</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30082,7 +30082,7 @@
         <v>44498</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30139,7 +30139,7 @@
         <v>44509</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30201,7 +30201,7 @@
         <v>44511</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30258,7 +30258,7 @@
         <v>44512</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30315,7 +30315,7 @@
         <v>44515</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30372,7 +30372,7 @@
         <v>44517</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30429,7 +30429,7 @@
         <v>44519</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30486,7 +30486,7 @@
         <v>44519</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30543,7 +30543,7 @@
         <v>44523</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30605,7 +30605,7 @@
         <v>44524</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30662,7 +30662,7 @@
         <v>44529</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30724,7 +30724,7 @@
         <v>44529</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30781,7 +30781,7 @@
         <v>44529</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30838,7 +30838,7 @@
         <v>44529</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30895,7 +30895,7 @@
         <v>44529</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30952,7 +30952,7 @@
         <v>44533</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31009,7 +31009,7 @@
         <v>44536</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31066,7 +31066,7 @@
         <v>44537</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31123,7 +31123,7 @@
         <v>44537</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31180,7 +31180,7 @@
         <v>44537</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31237,7 +31237,7 @@
         <v>44541</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31294,7 +31294,7 @@
         <v>44544</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31351,7 +31351,7 @@
         <v>44544</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31408,7 +31408,7 @@
         <v>44545</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31465,7 +31465,7 @@
         <v>44551</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31522,7 +31522,7 @@
         <v>44551</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31579,7 +31579,7 @@
         <v>44552</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31636,7 +31636,7 @@
         <v>44556</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31693,7 +31693,7 @@
         <v>44559</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31750,7 +31750,7 @@
         <v>44562</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31807,7 +31807,7 @@
         <v>44565</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31869,7 +31869,7 @@
         <v>44565</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31931,7 +31931,7 @@
         <v>44565</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31993,7 +31993,7 @@
         <v>44571</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32050,7 +32050,7 @@
         <v>44571</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32107,7 +32107,7 @@
         <v>44572</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32164,7 +32164,7 @@
         <v>44573</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32221,7 +32221,7 @@
         <v>44578</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32278,7 +32278,7 @@
         <v>44579</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32335,7 +32335,7 @@
         <v>44600</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32392,7 +32392,7 @@
         <v>44602</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32449,7 +32449,7 @@
         <v>44610</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32511,7 +32511,7 @@
         <v>44620</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32568,7 +32568,7 @@
         <v>44621</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32625,7 +32625,7 @@
         <v>44627</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32682,7 +32682,7 @@
         <v>44637</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32739,7 +32739,7 @@
         <v>44638</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32796,7 +32796,7 @@
         <v>44638</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32853,7 +32853,7 @@
         <v>44638</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32910,7 +32910,7 @@
         <v>44641</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32967,7 +32967,7 @@
         <v>44644</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33024,7 +33024,7 @@
         <v>44651</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33081,7 +33081,7 @@
         <v>44651</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33138,7 +33138,7 @@
         <v>44655</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33195,7 +33195,7 @@
         <v>44679</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33252,7 +33252,7 @@
         <v>44679</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33309,7 +33309,7 @@
         <v>44679</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33366,7 +33366,7 @@
         <v>44680</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33423,7 +33423,7 @@
         <v>44683</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33480,7 +33480,7 @@
         <v>44684</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33537,7 +33537,7 @@
         <v>44686</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33594,7 +33594,7 @@
         <v>44692</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33651,7 +33651,7 @@
         <v>44700</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33708,7 +33708,7 @@
         <v>44701</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33765,7 +33765,7 @@
         <v>44715</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33822,7 +33822,7 @@
         <v>44719</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33879,7 +33879,7 @@
         <v>44722</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33936,7 +33936,7 @@
         <v>44727</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33993,7 +33993,7 @@
         <v>44727</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34050,7 +34050,7 @@
         <v>44728</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34112,7 +34112,7 @@
         <v>44728</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34174,7 +34174,7 @@
         <v>44729</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34236,7 +34236,7 @@
         <v>44732</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34293,7 +34293,7 @@
         <v>44733</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34350,7 +34350,7 @@
         <v>44736</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34407,7 +34407,7 @@
         <v>44740</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34464,7 +34464,7 @@
         <v>44742</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34521,7 +34521,7 @@
         <v>44743</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34583,7 +34583,7 @@
         <v>44746</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34640,7 +34640,7 @@
         <v>44746</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34697,7 +34697,7 @@
         <v>44747</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34759,7 +34759,7 @@
         <v>44747</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34816,7 +34816,7 @@
         <v>44747</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34878,7 +34878,7 @@
         <v>44747</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34935,7 +34935,7 @@
         <v>44748</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34992,7 +34992,7 @@
         <v>44749</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35054,7 +35054,7 @@
         <v>44749</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35116,7 +35116,7 @@
         <v>44749</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35173,7 +35173,7 @@
         <v>44762</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35230,7 +35230,7 @@
         <v>44762</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35287,7 +35287,7 @@
         <v>44762</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35344,7 +35344,7 @@
         <v>44763</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35401,7 +35401,7 @@
         <v>44763</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35463,7 +35463,7 @@
         <v>44774</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35525,7 +35525,7 @@
         <v>44775</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35582,7 +35582,7 @@
         <v>44775</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35639,7 +35639,7 @@
         <v>44775</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35696,7 +35696,7 @@
         <v>44783</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35753,7 +35753,7 @@
         <v>44785</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35815,7 +35815,7 @@
         <v>44789</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35872,7 +35872,7 @@
         <v>44789</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35934,7 +35934,7 @@
         <v>44790</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35991,7 +35991,7 @@
         <v>44790</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36048,7 +36048,7 @@
         <v>44791</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36105,7 +36105,7 @@
         <v>44791</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36162,7 +36162,7 @@
         <v>44792</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36224,7 +36224,7 @@
         <v>44792</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36286,7 +36286,7 @@
         <v>44792</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36348,7 +36348,7 @@
         <v>44792</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36410,7 +36410,7 @@
         <v>44792</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36472,7 +36472,7 @@
         <v>44795</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36529,7 +36529,7 @@
         <v>44795</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36586,7 +36586,7 @@
         <v>44795</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36643,7 +36643,7 @@
         <v>44796</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36700,7 +36700,7 @@
         <v>44797</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36757,7 +36757,7 @@
         <v>44798</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36814,7 +36814,7 @@
         <v>44798</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36871,7 +36871,7 @@
         <v>44799</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36933,7 +36933,7 @@
         <v>44799</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36995,7 +36995,7 @@
         <v>44799</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37057,7 +37057,7 @@
         <v>44799</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37119,7 +37119,7 @@
         <v>44803</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37176,7 +37176,7 @@
         <v>44803</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37233,7 +37233,7 @@
         <v>44804</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37290,7 +37290,7 @@
         <v>44804</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37347,7 +37347,7 @@
         <v>44806</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37429,7 +37429,7 @@
         <v>44806</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37486,7 +37486,7 @@
         <v>44806</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37543,7 +37543,7 @@
         <v>44806</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37600,7 +37600,7 @@
         <v>44806</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37657,7 +37657,7 @@
         <v>44806</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37714,7 +37714,7 @@
         <v>44807</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37771,7 +37771,7 @@
         <v>44813</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37833,7 +37833,7 @@
         <v>44817</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37895,7 +37895,7 @@
         <v>44817</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37957,7 +37957,7 @@
         <v>44818</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38014,7 +38014,7 @@
         <v>44818</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38071,7 +38071,7 @@
         <v>44818</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38128,7 +38128,7 @@
         <v>44818</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38185,7 +38185,7 @@
         <v>44818</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38242,7 +38242,7 @@
         <v>44819</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38299,7 +38299,7 @@
         <v>44819</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38361,7 +38361,7 @@
         <v>44819</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38418,7 +38418,7 @@
         <v>44820</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38480,7 +38480,7 @@
         <v>44823</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38537,7 +38537,7 @@
         <v>44824</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38594,7 +38594,7 @@
         <v>44826</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38651,7 +38651,7 @@
         <v>44827</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38713,7 +38713,7 @@
         <v>44833</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38770,7 +38770,7 @@
         <v>44834</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38827,7 +38827,7 @@
         <v>44834</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38884,7 +38884,7 @@
         <v>44837</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38941,7 +38941,7 @@
         <v>44838</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39003,7 +39003,7 @@
         <v>44839</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39065,7 +39065,7 @@
         <v>44839</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39122,7 +39122,7 @@
         <v>44839</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39184,7 +39184,7 @@
         <v>44840</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39241,7 +39241,7 @@
         <v>44841</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39298,7 +39298,7 @@
         <v>44841</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39360,7 +39360,7 @@
         <v>44841</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39417,7 +39417,7 @@
         <v>44841</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39474,7 +39474,7 @@
         <v>44845</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39536,7 +39536,7 @@
         <v>44845</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39598,7 +39598,7 @@
         <v>44847</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39655,7 +39655,7 @@
         <v>44851</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39717,7 +39717,7 @@
         <v>44851</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39779,7 +39779,7 @@
         <v>44851</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39841,7 +39841,7 @@
         <v>44851</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39903,7 +39903,7 @@
         <v>44855</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39965,7 +39965,7 @@
         <v>44860</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40027,7 +40027,7 @@
         <v>44862</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40089,7 +40089,7 @@
         <v>44862</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40151,7 +40151,7 @@
         <v>44866</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40213,7 +40213,7 @@
         <v>44866</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40275,7 +40275,7 @@
         <v>44866</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40337,7 +40337,7 @@
         <v>44866</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40394,7 +40394,7 @@
         <v>44868</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40451,7 +40451,7 @@
         <v>44872</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40508,7 +40508,7 @@
         <v>44873</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40565,7 +40565,7 @@
         <v>44873</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40622,7 +40622,7 @@
         <v>44873</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40679,7 +40679,7 @@
         <v>44874</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40736,7 +40736,7 @@
         <v>44874</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40793,7 +40793,7 @@
         <v>44875</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40850,7 +40850,7 @@
         <v>44875</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40907,7 +40907,7 @@
         <v>44879</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40969,7 +40969,7 @@
         <v>44882</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41026,7 +41026,7 @@
         <v>44883</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41088,7 +41088,7 @@
         <v>44883</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41150,7 +41150,7 @@
         <v>44887</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41207,7 +41207,7 @@
         <v>44889</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41264,7 +41264,7 @@
         <v>44890</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41321,7 +41321,7 @@
         <v>44891</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41378,7 +41378,7 @@
         <v>44893</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41435,7 +41435,7 @@
         <v>44897</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41492,7 +41492,7 @@
         <v>44903</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41549,7 +41549,7 @@
         <v>44907</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41611,7 +41611,7 @@
         <v>44907</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41668,7 +41668,7 @@
         <v>44909</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41730,7 +41730,7 @@
         <v>44909</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41812,7 +41812,7 @@
         <v>44909</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41869,7 +41869,7 @@
         <v>44909</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41926,7 +41926,7 @@
         <v>44910</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41983,7 +41983,7 @@
         <v>44911</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42040,7 +42040,7 @@
         <v>44911</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42097,7 +42097,7 @@
         <v>44911</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42154,7 +42154,7 @@
         <v>44911</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42211,7 +42211,7 @@
         <v>44914</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42268,7 +42268,7 @@
         <v>44914</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42325,7 +42325,7 @@
         <v>44914</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42382,7 +42382,7 @@
         <v>44916</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42439,7 +42439,7 @@
         <v>44916</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42496,7 +42496,7 @@
         <v>44922</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42553,7 +42553,7 @@
         <v>44928</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42610,7 +42610,7 @@
         <v>44929</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42667,7 +42667,7 @@
         <v>44929</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42724,7 +42724,7 @@
         <v>44930</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42781,7 +42781,7 @@
         <v>44930</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42838,7 +42838,7 @@
         <v>44930</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42895,7 +42895,7 @@
         <v>44930</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42952,7 +42952,7 @@
         <v>44931</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43014,7 +43014,7 @@
         <v>44939</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43071,7 +43071,7 @@
         <v>44939</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43128,7 +43128,7 @@
         <v>44944</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43185,7 +43185,7 @@
         <v>44944</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43242,7 +43242,7 @@
         <v>44945</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43299,7 +43299,7 @@
         <v>44949</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43356,7 +43356,7 @@
         <v>44950</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43413,7 +43413,7 @@
         <v>44950</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43470,7 +43470,7 @@
         <v>44953</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43527,7 +43527,7 @@
         <v>44956</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43584,7 +43584,7 @@
         <v>44960</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43641,7 +43641,7 @@
         <v>44964</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43698,7 +43698,7 @@
         <v>44964</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43755,7 +43755,7 @@
         <v>44964</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43812,7 +43812,7 @@
         <v>44964</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43869,7 +43869,7 @@
         <v>44964</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43926,7 +43926,7 @@
         <v>44964</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43983,7 +43983,7 @@
         <v>44964</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44040,7 +44040,7 @@
         <v>44966</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44097,7 +44097,7 @@
         <v>44967</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44154,7 +44154,7 @@
         <v>44967</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44211,7 +44211,7 @@
         <v>44967</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44268,7 +44268,7 @@
         <v>44967</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44325,7 +44325,7 @@
         <v>44967</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44382,7 +44382,7 @@
         <v>44970</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44439,7 +44439,7 @@
         <v>44970</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44496,7 +44496,7 @@
         <v>44973</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44553,7 +44553,7 @@
         <v>44977</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44610,7 +44610,7 @@
         <v>44977</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44667,7 +44667,7 @@
         <v>44982</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -44724,7 +44724,7 @@
         <v>44991</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44781,7 +44781,7 @@
         <v>44997</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44838,7 +44838,7 @@
         <v>45002</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44895,7 +44895,7 @@
         <v>45002</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44952,7 +44952,7 @@
         <v>45002</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45009,7 +45009,7 @@
         <v>45019</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45066,7 +45066,7 @@
         <v>45019</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45123,7 +45123,7 @@
         <v>45019</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45180,7 +45180,7 @@
         <v>45021</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45237,7 +45237,7 @@
         <v>45027</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45294,7 +45294,7 @@
         <v>45033</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45351,7 +45351,7 @@
         <v>45040</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45413,7 +45413,7 @@
         <v>45042</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45470,7 +45470,7 @@
         <v>45058</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45527,7 +45527,7 @@
         <v>45062</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45589,7 +45589,7 @@
         <v>45063</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45646,7 +45646,7 @@
         <v>45070</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45703,7 +45703,7 @@
         <v>45071</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45760,7 +45760,7 @@
         <v>45071</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45817,7 +45817,7 @@
         <v>45071</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45874,7 +45874,7 @@
         <v>45071</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45931,7 +45931,7 @@
         <v>45071</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45988,7 +45988,7 @@
         <v>45071</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46045,7 +46045,7 @@
         <v>45072</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46102,7 +46102,7 @@
         <v>45072</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46159,7 +46159,7 @@
         <v>45072</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46221,7 +46221,7 @@
         <v>45075</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46278,7 +46278,7 @@
         <v>45075</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46335,7 +46335,7 @@
         <v>45077</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46392,7 +46392,7 @@
         <v>45079</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46449,7 +46449,7 @@
         <v>45084</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46506,7 +46506,7 @@
         <v>45085</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46563,7 +46563,7 @@
         <v>45085</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46620,7 +46620,7 @@
         <v>45090</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46677,7 +46677,7 @@
         <v>45090</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46734,7 +46734,7 @@
         <v>45090</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46791,7 +46791,7 @@
         <v>45092</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46853,7 +46853,7 @@
         <v>45092</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46910,7 +46910,7 @@
         <v>45093</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46972,7 +46972,7 @@
         <v>45093</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47034,7 +47034,7 @@
         <v>45096</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47091,7 +47091,7 @@
         <v>45096</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47153,7 +47153,7 @@
         <v>45096</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47215,7 +47215,7 @@
         <v>45097</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47272,7 +47272,7 @@
         <v>45097</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47334,7 +47334,7 @@
         <v>45097</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47396,7 +47396,7 @@
         <v>45098</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47453,7 +47453,7 @@
         <v>45098</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47510,7 +47510,7 @@
         <v>45099</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -47572,7 +47572,7 @@
         <v>45103</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47629,7 +47629,7 @@
         <v>45103</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -47686,7 +47686,7 @@
         <v>45104</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -47743,7 +47743,7 @@
         <v>45105</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -47800,7 +47800,7 @@
         <v>45105</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47857,7 +47857,7 @@
         <v>45106</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -47914,7 +47914,7 @@
         <v>45107</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -47971,7 +47971,7 @@
         <v>45107</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -48028,7 +48028,7 @@
         <v>45107</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -48085,7 +48085,7 @@
         <v>45111</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48147,7 +48147,7 @@
         <v>45111</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -48204,7 +48204,7 @@
         <v>45112</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -48261,7 +48261,7 @@
         <v>45112</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48323,7 +48323,7 @@
         <v>45112</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48385,7 +48385,7 @@
         <v>45112</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48442,7 +48442,7 @@
         <v>45114</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48499,7 +48499,7 @@
         <v>45114</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -48556,7 +48556,7 @@
         <v>45119</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -48613,7 +48613,7 @@
         <v>45120</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -48675,7 +48675,7 @@
         <v>45124</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -48737,7 +48737,7 @@
         <v>45124</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -48794,7 +48794,7 @@
         <v>45131</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48856,7 +48856,7 @@
         <v>45131</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -48918,7 +48918,7 @@
         <v>45132</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -48975,7 +48975,7 @@
         <v>45132</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -49032,7 +49032,7 @@
         <v>45138</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -49094,7 +49094,7 @@
         <v>45138</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -49156,7 +49156,7 @@
         <v>45139</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -49213,7 +49213,7 @@
         <v>45139</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -49270,7 +49270,7 @@
         <v>45140</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49327,7 +49327,7 @@
         <v>45145</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -49389,7 +49389,7 @@
         <v>45148</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49446,7 +49446,7 @@
         <v>45152</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49503,7 +49503,7 @@
         <v>45152</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -49565,7 +49565,7 @@
         <v>45152</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -49627,7 +49627,7 @@
         <v>45154</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -49684,7 +49684,7 @@
         <v>45155</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -49741,7 +49741,7 @@
         <v>45159</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -49803,7 +49803,7 @@
         <v>45159</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -49860,7 +49860,7 @@
         <v>45160</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -49922,7 +49922,7 @@
         <v>45160</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -49984,7 +49984,7 @@
         <v>45161</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -50041,7 +50041,7 @@
         <v>45161</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -50103,7 +50103,7 @@
         <v>45166</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -50160,7 +50160,7 @@
         <v>45167</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -50217,7 +50217,7 @@
         <v>45168</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -50274,7 +50274,7 @@
         <v>45168</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -50331,7 +50331,7 @@
         <v>45168</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -50388,7 +50388,7 @@
         <v>45173</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -50445,7 +50445,7 @@
         <v>45173</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -50502,7 +50502,7 @@
         <v>45173</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -50559,7 +50559,7 @@
         <v>45174</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -50616,7 +50616,7 @@
         <v>45175</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -50678,7 +50678,7 @@
         <v>45175</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -50740,7 +50740,7 @@
         <v>45176</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -50802,7 +50802,7 @@
         <v>45176</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -50864,7 +50864,7 @@
         <v>45176</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -50926,7 +50926,7 @@
         <v>45176</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -50988,7 +50988,7 @@
         <v>45176</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -51045,7 +51045,7 @@
         <v>45176</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -51102,7 +51102,7 @@
         <v>45176</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -51159,7 +51159,7 @@
         <v>45180</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -51221,7 +51221,7 @@
         <v>45180</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -51283,7 +51283,7 @@
         <v>45181</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -51340,7 +51340,7 @@
         <v>45181</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -51397,7 +51397,7 @@
         <v>45181</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -51454,7 +51454,7 @@
         <v>45181</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -51511,7 +51511,7 @@
         <v>45182</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -51568,7 +51568,7 @@
         <v>45182</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -51625,7 +51625,7 @@
         <v>45182</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -51682,7 +51682,7 @@
         <v>45183</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -51739,7 +51739,7 @@
         <v>45183</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -51796,7 +51796,7 @@
         <v>45183</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -51853,7 +51853,7 @@
         <v>45187</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -51910,7 +51910,7 @@
         <v>45187</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -51972,7 +51972,7 @@
         <v>45188</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -52029,7 +52029,7 @@
         <v>45188</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -52086,7 +52086,7 @@
         <v>45188</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -52143,7 +52143,7 @@
         <v>45188</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -52200,7 +52200,7 @@
         <v>45190</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -52257,7 +52257,7 @@
         <v>45190</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -52314,7 +52314,7 @@
         <v>45194</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -52371,7 +52371,7 @@
         <v>45194</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -52428,7 +52428,7 @@
         <v>45194</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -52485,7 +52485,7 @@
         <v>45194</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -52542,7 +52542,7 @@
         <v>45194</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -52599,7 +52599,7 @@
         <v>45194</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -52661,7 +52661,7 @@
         <v>45194</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -52718,7 +52718,7 @@
         <v>45194</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -52775,7 +52775,7 @@
         <v>45194</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -52837,7 +52837,7 @@
         <v>45194</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -52899,7 +52899,7 @@
         <v>45195</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -52956,7 +52956,7 @@
         <v>45198</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -53013,7 +53013,7 @@
         <v>45198</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -53070,7 +53070,7 @@
         <v>45201</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -53127,7 +53127,7 @@
         <v>45201</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -53184,7 +53184,7 @@
         <v>45201</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -53241,7 +53241,7 @@
         <v>45201</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -53298,7 +53298,7 @@
         <v>45202</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -53355,7 +53355,7 @@
         <v>45203</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -53412,7 +53412,7 @@
         <v>45203</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -53469,7 +53469,7 @@
         <v>45204</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -53526,7 +53526,7 @@
         <v>45204</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -53583,7 +53583,7 @@
         <v>45204</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -53640,7 +53640,7 @@
         <v>45204</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -53702,7 +53702,7 @@
         <v>45204</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -53759,7 +53759,7 @@
         <v>45205</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -53821,7 +53821,7 @@
         <v>45208</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -53878,7 +53878,7 @@
         <v>45209</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -53940,7 +53940,7 @@
         <v>45209</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -54002,7 +54002,7 @@
         <v>45210</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -54059,7 +54059,7 @@
         <v>45210</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -54116,7 +54116,7 @@
         <v>45210</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -54173,7 +54173,7 @@
         <v>45211</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -54230,7 +54230,7 @@
         <v>45211</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -54292,7 +54292,7 @@
         <v>45215</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -54349,7 +54349,7 @@
         <v>45215</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -54406,7 +54406,7 @@
         <v>45216</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -54463,7 +54463,7 @@
         <v>45217</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -54520,7 +54520,7 @@
         <v>45217</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -54577,7 +54577,7 @@
         <v>45217</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -54634,7 +54634,7 @@
         <v>45217</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -54691,7 +54691,7 @@
         <v>45222</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -54753,7 +54753,7 @@
         <v>45222</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -54810,7 +54810,7 @@
         <v>45222</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -54867,7 +54867,7 @@
         <v>45223</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -54929,7 +54929,7 @@
         <v>45223</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -54986,7 +54986,7 @@
         <v>45225</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -55048,7 +55048,7 @@
         <v>45225</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -55105,7 +55105,7 @@
         <v>45225</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -55167,7 +55167,7 @@
         <v>45225</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -55224,7 +55224,7 @@
         <v>45225</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -55281,7 +55281,7 @@
         <v>45225</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -55338,7 +55338,7 @@
         <v>45225</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -55395,7 +55395,7 @@
         <v>45225</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -55452,7 +55452,7 @@
         <v>45225</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -55509,7 +55509,7 @@
         <v>45226</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -55566,7 +55566,7 @@
         <v>45229</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -55623,7 +55623,7 @@
         <v>45229</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -55680,7 +55680,7 @@
         <v>45229</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -55737,7 +55737,7 @@
         <v>45229</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -55794,7 +55794,7 @@
         <v>45229</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -55851,7 +55851,7 @@
         <v>45230</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -55908,7 +55908,7 @@
         <v>45230</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -55965,7 +55965,7 @@
         <v>45230</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -56022,7 +56022,7 @@
         <v>45230</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -56079,7 +56079,7 @@
         <v>45230</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -56136,7 +56136,7 @@
         <v>45231</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -56193,7 +56193,7 @@
         <v>45231</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -56250,7 +56250,7 @@
         <v>45231</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -56307,7 +56307,7 @@
         <v>45231</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -56364,7 +56364,7 @@
         <v>45231</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -56421,7 +56421,7 @@
         <v>45231</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -56478,7 +56478,7 @@
         <v>45231</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -56535,7 +56535,7 @@
         <v>45232</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -56597,7 +56597,7 @@
         <v>45232</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -56654,7 +56654,7 @@
         <v>45232</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -56711,7 +56711,7 @@
         <v>45232</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -56768,7 +56768,7 @@
         <v>45233</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -56830,7 +56830,7 @@
         <v>45236</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -56887,7 +56887,7 @@
         <v>45236</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -56944,7 +56944,7 @@
         <v>45236</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -57001,7 +57001,7 @@
         <v>45237</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -57058,7 +57058,7 @@
         <v>45237</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -57120,7 +57120,7 @@
         <v>45239</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -57177,7 +57177,7 @@
         <v>45239</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -57234,7 +57234,7 @@
         <v>45240</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -57296,7 +57296,7 @@
         <v>45243</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -57353,7 +57353,7 @@
         <v>45243</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -57410,7 +57410,7 @@
         <v>45243</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -57467,7 +57467,7 @@
         <v>45243</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -57524,7 +57524,7 @@
         <v>45243</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -57581,7 +57581,7 @@
         <v>45243</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -57638,7 +57638,7 @@
         <v>45244</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -57695,7 +57695,7 @@
         <v>45244</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -57757,7 +57757,7 @@
         <v>45244</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -57819,7 +57819,7 @@
         <v>45244</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -57876,7 +57876,7 @@
         <v>45244</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -57933,7 +57933,7 @@
         <v>45244</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -57995,7 +57995,7 @@
         <v>45244</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -58052,7 +58052,7 @@
         <v>45245</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -58109,7 +58109,7 @@
         <v>45245</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -58166,7 +58166,7 @@
         <v>45245</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -58223,7 +58223,7 @@
         <v>45245</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -58280,7 +58280,7 @@
         <v>45245</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -58342,7 +58342,7 @@
         <v>45245</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -58399,7 +58399,7 @@
         <v>45245</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -58456,7 +58456,7 @@
         <v>45247</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -58513,7 +58513,7 @@
         <v>45247</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -58570,7 +58570,7 @@
         <v>45248</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -58627,7 +58627,7 @@
         <v>45250</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -58684,7 +58684,7 @@
         <v>45250</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -58741,7 +58741,7 @@
         <v>45251</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -58798,7 +58798,7 @@
         <v>45251</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -58855,7 +58855,7 @@
         <v>45251</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -58912,7 +58912,7 @@
         <v>45252</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -58969,7 +58969,7 @@
         <v>45253</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -59031,7 +59031,7 @@
         <v>45253</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -59088,7 +59088,7 @@
         <v>45253</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -59150,7 +59150,7 @@
         <v>45253</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -59207,7 +59207,7 @@
         <v>45253</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -59269,7 +59269,7 @@
         <v>45253</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -59331,7 +59331,7 @@
         <v>45253</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -59388,7 +59388,7 @@
         <v>45257</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -59445,7 +59445,7 @@
         <v>45258</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -59502,7 +59502,7 @@
         <v>45259</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -59559,7 +59559,7 @@
         <v>45260</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -59616,7 +59616,7 @@
         <v>45261</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -59673,7 +59673,7 @@
         <v>45261</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -59730,7 +59730,7 @@
         <v>45264</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -59787,7 +59787,7 @@
         <v>45264</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -59844,7 +59844,7 @@
         <v>45264</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -59901,7 +59901,7 @@
         <v>45264</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -59958,7 +59958,7 @@
         <v>45264</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -60015,7 +60015,7 @@
         <v>45265</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -60072,7 +60072,7 @@
         <v>45265</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -60129,7 +60129,7 @@
         <v>45265</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -60186,7 +60186,7 @@
         <v>45266</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -60243,7 +60243,7 @@
         <v>45266</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -60300,7 +60300,7 @@
         <v>45266</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -60357,7 +60357,7 @@
         <v>45266</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -60419,7 +60419,7 @@
         <v>45267</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -60476,7 +60476,7 @@
         <v>45267</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -60533,7 +60533,7 @@
         <v>45267</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -60590,7 +60590,7 @@
         <v>45267</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -60647,7 +60647,7 @@
         <v>45267</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -60704,7 +60704,7 @@
         <v>45268</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -60761,7 +60761,7 @@
         <v>45271</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -60818,7 +60818,7 @@
         <v>45273</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -60875,7 +60875,7 @@
         <v>45273</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -60932,7 +60932,7 @@
         <v>45275</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -60989,7 +60989,7 @@
         <v>45279</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -61046,7 +61046,7 @@
         <v>45279</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -61103,7 +61103,7 @@
         <v>45279</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -61160,7 +61160,7 @@
         <v>45281</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -61217,7 +61217,7 @@
         <v>45281</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -61279,7 +61279,7 @@
         <v>45282</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -61336,7 +61336,7 @@
         <v>45287</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -61398,7 +61398,7 @@
         <v>45297</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -61460,7 +61460,7 @@
         <v>45299</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -61517,7 +61517,7 @@
         <v>45300</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -61574,7 +61574,7 @@
         <v>45300</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -61631,7 +61631,7 @@
         <v>45302</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -61688,7 +61688,7 @@
         <v>45302</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -61745,7 +61745,7 @@
         <v>45303</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -61802,7 +61802,7 @@
         <v>45306</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -61859,7 +61859,7 @@
         <v>45306</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -61916,7 +61916,7 @@
         <v>45307</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -61973,7 +61973,7 @@
         <v>45307</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -62030,7 +62030,7 @@
         <v>45307</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -62087,7 +62087,7 @@
         <v>45307</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -62144,7 +62144,7 @@
         <v>45307</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -62201,7 +62201,7 @@
         <v>45310</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -62258,7 +62258,7 @@
         <v>45310</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -62315,7 +62315,7 @@
         <v>45310</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -62372,7 +62372,7 @@
         <v>45310</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -62429,7 +62429,7 @@
         <v>45310</v>
       </c>
       <c r="C1038" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
@@ -62486,7 +62486,7 @@
         <v>45310</v>
       </c>
       <c r="C1039" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
@@ -62543,7 +62543,7 @@
         <v>45310</v>
       </c>
       <c r="C1040" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
@@ -62600,7 +62600,7 @@
         <v>45310</v>
       </c>
       <c r="C1041" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
@@ -62657,7 +62657,7 @@
         <v>45310</v>
       </c>
       <c r="C1042" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
@@ -62714,7 +62714,7 @@
         <v>45313</v>
       </c>
       <c r="C1043" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1043" t="inlineStr">
         <is>
@@ -62771,7 +62771,7 @@
         <v>45314</v>
       </c>
       <c r="C1044" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1044" t="inlineStr">
         <is>
@@ -62828,7 +62828,7 @@
         <v>45314</v>
       </c>
       <c r="C1045" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1045" t="inlineStr">
         <is>
@@ -62885,7 +62885,7 @@
         <v>45314</v>
       </c>
       <c r="C1046" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1046" t="inlineStr">
         <is>
@@ -62942,7 +62942,7 @@
         <v>45316</v>
       </c>
       <c r="C1047" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1047" t="inlineStr">
         <is>
@@ -62999,7 +62999,7 @@
         <v>45317</v>
       </c>
       <c r="C1048" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1048" t="inlineStr">
         <is>
@@ -63056,7 +63056,7 @@
         <v>45321</v>
       </c>
       <c r="C1049" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1049" t="inlineStr">
         <is>
@@ -63113,7 +63113,7 @@
         <v>45321</v>
       </c>
       <c r="C1050" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1050" t="inlineStr">
         <is>
@@ -63170,7 +63170,7 @@
         <v>45321</v>
       </c>
       <c r="C1051" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1051" t="inlineStr">
         <is>
@@ -63227,7 +63227,7 @@
         <v>45321</v>
       </c>
       <c r="C1052" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1052" t="inlineStr">
         <is>
@@ -63284,7 +63284,7 @@
         <v>45321</v>
       </c>
       <c r="C1053" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1053" t="inlineStr">
         <is>
@@ -63341,7 +63341,7 @@
         <v>45321</v>
       </c>
       <c r="C1054" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1054" t="inlineStr">
         <is>
@@ -63398,7 +63398,7 @@
         <v>45321</v>
       </c>
       <c r="C1055" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1055" t="inlineStr">
         <is>
@@ -63455,7 +63455,7 @@
         <v>45321</v>
       </c>
       <c r="C1056" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1056" t="inlineStr">
         <is>
@@ -63512,7 +63512,7 @@
         <v>45321</v>
       </c>
       <c r="C1057" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1057" t="inlineStr">
         <is>
@@ -63569,7 +63569,7 @@
         <v>45321</v>
       </c>
       <c r="C1058" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1058" t="inlineStr">
         <is>
@@ -63626,7 +63626,7 @@
         <v>45321</v>
       </c>
       <c r="C1059" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1059" t="inlineStr">
         <is>
@@ -63683,7 +63683,7 @@
         <v>45321</v>
       </c>
       <c r="C1060" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1060" t="inlineStr">
         <is>
@@ -63740,7 +63740,7 @@
         <v>45322</v>
       </c>
       <c r="C1061" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1061" t="inlineStr">
         <is>
@@ -63797,7 +63797,7 @@
         <v>45324</v>
       </c>
       <c r="C1062" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1062" t="inlineStr">
         <is>
@@ -63854,7 +63854,7 @@
         <v>45329</v>
       </c>
       <c r="C1063" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1063" t="inlineStr">
         <is>
@@ -63911,7 +63911,7 @@
         <v>45329</v>
       </c>
       <c r="C1064" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1064" t="inlineStr">
         <is>
@@ -63961,14 +63961,14 @@
     <row r="1065" ht="15" customHeight="1">
       <c r="A1065" t="inlineStr">
         <is>
-          <t>A 5110-2024</t>
+          <t>A 5174-2024</t>
         </is>
       </c>
       <c r="B1065" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C1065" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1065" t="inlineStr">
         <is>
@@ -63981,7 +63981,7 @@
         </is>
       </c>
       <c r="G1065" t="n">
-        <v>3.3</v>
+        <v>1.4</v>
       </c>
       <c r="H1065" t="n">
         <v>0</v>
@@ -64018,14 +64018,14 @@
     <row r="1066" ht="15" customHeight="1">
       <c r="A1066" t="inlineStr">
         <is>
-          <t>A 5124-2024</t>
+          <t>A 5110-2024</t>
         </is>
       </c>
       <c r="B1066" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C1066" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1066" t="inlineStr">
         <is>
@@ -64038,7 +64038,7 @@
         </is>
       </c>
       <c r="G1066" t="n">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="H1066" t="n">
         <v>0</v>
@@ -64075,14 +64075,14 @@
     <row r="1067" ht="15" customHeight="1">
       <c r="A1067" t="inlineStr">
         <is>
-          <t>A 5122-2024</t>
+          <t>A 5156-2024</t>
         </is>
       </c>
       <c r="B1067" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C1067" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1067" t="inlineStr">
         <is>
@@ -64095,7 +64095,7 @@
         </is>
       </c>
       <c r="G1067" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="H1067" t="n">
         <v>0</v>
@@ -64132,14 +64132,14 @@
     <row r="1068" ht="15" customHeight="1">
       <c r="A1068" t="inlineStr">
         <is>
-          <t>A 5189-2024</t>
+          <t>A 5122-2024</t>
         </is>
       </c>
       <c r="B1068" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C1068" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1068" t="inlineStr">
         <is>
@@ -64152,7 +64152,7 @@
         </is>
       </c>
       <c r="G1068" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="H1068" t="n">
         <v>0</v>
@@ -64189,14 +64189,14 @@
     <row r="1069" ht="15" customHeight="1">
       <c r="A1069" t="inlineStr">
         <is>
-          <t>A 5174-2024</t>
+          <t>A 5124-2024</t>
         </is>
       </c>
       <c r="B1069" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C1069" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1069" t="inlineStr">
         <is>
@@ -64209,7 +64209,7 @@
         </is>
       </c>
       <c r="G1069" t="n">
-        <v>1.4</v>
+        <v>2.6</v>
       </c>
       <c r="H1069" t="n">
         <v>0</v>
@@ -64246,14 +64246,14 @@
     <row r="1070" ht="15" customHeight="1">
       <c r="A1070" t="inlineStr">
         <is>
-          <t>A 5156-2024</t>
+          <t>A 5189-2024</t>
         </is>
       </c>
       <c r="B1070" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C1070" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1070" t="inlineStr">
         <is>
@@ -64266,7 +64266,7 @@
         </is>
       </c>
       <c r="G1070" t="n">
-        <v>0.4</v>
+        <v>1.3</v>
       </c>
       <c r="H1070" t="n">
         <v>0</v>
@@ -64310,7 +64310,7 @@
         <v>45331</v>
       </c>
       <c r="C1071" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1071" t="inlineStr">
         <is>
@@ -64367,7 +64367,7 @@
         <v>45331</v>
       </c>
       <c r="C1072" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1072" t="inlineStr">
         <is>
@@ -64424,7 +64424,7 @@
         <v>45334</v>
       </c>
       <c r="C1073" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1073" t="inlineStr">
         <is>
@@ -64481,7 +64481,7 @@
         <v>45334</v>
       </c>
       <c r="C1074" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1074" t="inlineStr">
         <is>
@@ -64531,14 +64531,14 @@
     <row r="1075" ht="15" customHeight="1">
       <c r="A1075" t="inlineStr">
         <is>
-          <t>A 6213-2024</t>
+          <t>A 6169-2024</t>
         </is>
       </c>
       <c r="B1075" s="1" t="n">
         <v>45337</v>
       </c>
       <c r="C1075" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1075" t="inlineStr">
         <is>
@@ -64551,7 +64551,7 @@
         </is>
       </c>
       <c r="G1075" t="n">
-        <v>0.6</v>
+        <v>3.3</v>
       </c>
       <c r="H1075" t="n">
         <v>0</v>
@@ -64595,7 +64595,7 @@
         <v>45337</v>
       </c>
       <c r="C1076" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1076" t="inlineStr">
         <is>
@@ -64645,14 +64645,14 @@
     <row r="1077" ht="15" customHeight="1">
       <c r="A1077" t="inlineStr">
         <is>
-          <t>A 6169-2024</t>
+          <t>A 6213-2024</t>
         </is>
       </c>
       <c r="B1077" s="1" t="n">
         <v>45337</v>
       </c>
       <c r="C1077" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1077" t="inlineStr">
         <is>
@@ -64665,7 +64665,7 @@
         </is>
       </c>
       <c r="G1077" t="n">
-        <v>3.3</v>
+        <v>0.6</v>
       </c>
       <c r="H1077" t="n">
         <v>0</v>
@@ -64709,7 +64709,7 @@
         <v>45343</v>
       </c>
       <c r="C1078" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1078" t="inlineStr">
         <is>
@@ -64764,14 +64764,14 @@
     <row r="1079" ht="15" customHeight="1">
       <c r="A1079" t="inlineStr">
         <is>
-          <t>A 7146-2024</t>
+          <t>A 7140-2024</t>
         </is>
       </c>
       <c r="B1079" s="1" t="n">
         <v>45344</v>
       </c>
       <c r="C1079" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1079" t="inlineStr">
         <is>
@@ -64784,7 +64784,7 @@
         </is>
       </c>
       <c r="G1079" t="n">
-        <v>0.4</v>
+        <v>5.9</v>
       </c>
       <c r="H1079" t="n">
         <v>0</v>
@@ -64821,14 +64821,14 @@
     <row r="1080" ht="15" customHeight="1">
       <c r="A1080" t="inlineStr">
         <is>
-          <t>A 7140-2024</t>
+          <t>A 7146-2024</t>
         </is>
       </c>
       <c r="B1080" s="1" t="n">
         <v>45344</v>
       </c>
       <c r="C1080" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1080" t="inlineStr">
         <is>
@@ -64841,7 +64841,7 @@
         </is>
       </c>
       <c r="G1080" t="n">
-        <v>5.9</v>
+        <v>0.4</v>
       </c>
       <c r="H1080" t="n">
         <v>0</v>
@@ -64885,7 +64885,7 @@
         <v>45349</v>
       </c>
       <c r="C1081" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1081" t="inlineStr">
         <is>
@@ -64942,7 +64942,7 @@
         <v>45350</v>
       </c>
       <c r="C1082" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1082" t="inlineStr">
         <is>
@@ -64999,7 +64999,7 @@
         <v>45351</v>
       </c>
       <c r="C1083" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1083" t="inlineStr">
         <is>
@@ -65056,7 +65056,7 @@
         <v>45351</v>
       </c>
       <c r="C1084" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1084" t="inlineStr">
         <is>
@@ -65113,7 +65113,7 @@
         <v>45352</v>
       </c>
       <c r="C1085" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1085" t="inlineStr">
         <is>

--- a/Översikt RÄTTVIK.xlsx
+++ b/Översikt RÄTTVIK.xlsx
@@ -569,7 +569,7 @@
         <v>43542</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         <v>44909</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
         <v>43663</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>43619</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>43740</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>44909</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>44874</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
         <v>45147</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>44237</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>44624</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>43634</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>43663</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
         <v>44148</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
         <v>44435</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v>44799</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2008,7 +2008,7 @@
         <v>44909</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2100,7 +2100,7 @@
         <v>44909</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2192,7 +2192,7 @@
         <v>45111</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
         <v>43700</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2370,7 +2370,7 @@
         <v>44496</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2456,7 +2456,7 @@
         <v>45033</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
         <v>45264</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         <v>43440</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2717,7 +2717,7 @@
         <v>43493</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         <v>43623</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2887,7 +2887,7 @@
         <v>43705</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2972,7 +2972,7 @@
         <v>44088</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3057,7 +3057,7 @@
         <v>44110</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3142,7 +3142,7 @@
         <v>44361</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3227,7 +3227,7 @@
         <v>44391</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3317,7 +3317,7 @@
         <v>44414</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3407,7 +3407,7 @@
         <v>44470</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3497,7 +3497,7 @@
         <v>44496</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3587,7 +3587,7 @@
         <v>44511</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3672,7 +3672,7 @@
         <v>44568</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3766,7 +3766,7 @@
         <v>44728</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3860,7 +3860,7 @@
         <v>44855</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3950,7 +3950,7 @@
         <v>44894</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4040,7 +4040,7 @@
         <v>44918</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4130,7 +4130,7 @@
         <v>44986</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4215,7 +4215,7 @@
         <v>45077</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4300,7 +4300,7 @@
         <v>45194</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4385,7 +4385,7 @@
         <v>45194</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4470,7 +4470,7 @@
         <v>45231</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4555,7 +4555,7 @@
         <v>43333</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4612,7 +4612,7 @@
         <v>43348</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4669,7 +4669,7 @@
         <v>43356</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4726,7 +4726,7 @@
         <v>43361</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4783,7 +4783,7 @@
         <v>43362</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4840,7 +4840,7 @@
         <v>43362</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4897,7 +4897,7 @@
         <v>43362</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4954,7 +4954,7 @@
         <v>43362</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5011,7 +5011,7 @@
         <v>43367</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5068,7 +5068,7 @@
         <v>43369</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5125,7 +5125,7 @@
         <v>43373</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5182,7 +5182,7 @@
         <v>43378</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5239,7 +5239,7 @@
         <v>43381</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5296,7 +5296,7 @@
         <v>43381</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5353,7 +5353,7 @@
         <v>43388</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5410,7 +5410,7 @@
         <v>43388</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5472,7 +5472,7 @@
         <v>43388</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5529,7 +5529,7 @@
         <v>43391</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5586,7 +5586,7 @@
         <v>43398</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5643,7 +5643,7 @@
         <v>43399</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5700,7 +5700,7 @@
         <v>43401</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5757,7 +5757,7 @@
         <v>43405</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5814,7 +5814,7 @@
         <v>43405</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5871,7 +5871,7 @@
         <v>43410</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5928,7 +5928,7 @@
         <v>43410</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5985,7 +5985,7 @@
         <v>43411</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6042,7 +6042,7 @@
         <v>43412</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6099,7 +6099,7 @@
         <v>43416</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6156,7 +6156,7 @@
         <v>43416</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6213,7 +6213,7 @@
         <v>43416</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6270,7 +6270,7 @@
         <v>43419</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         <v>43419</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6384,7 +6384,7 @@
         <v>43423</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6446,7 +6446,7 @@
         <v>43423</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6508,7 +6508,7 @@
         <v>43423</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6570,7 +6570,7 @@
         <v>43424</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6632,7 +6632,7 @@
         <v>43425</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6689,7 +6689,7 @@
         <v>43427</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6751,7 +6751,7 @@
         <v>43428</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6808,7 +6808,7 @@
         <v>43428</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6865,7 +6865,7 @@
         <v>43430</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6922,7 +6922,7 @@
         <v>43430</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6979,7 +6979,7 @@
         <v>43430</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7036,7 +7036,7 @@
         <v>43430</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7093,7 +7093,7 @@
         <v>43431</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7155,7 +7155,7 @@
         <v>43432</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7212,7 +7212,7 @@
         <v>43432</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7269,7 +7269,7 @@
         <v>43434</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7326,7 +7326,7 @@
         <v>43434</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7383,7 +7383,7 @@
         <v>43438</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7440,7 +7440,7 @@
         <v>43441</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7497,7 +7497,7 @@
         <v>43447</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
         <v>43448</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7611,7 +7611,7 @@
         <v>43451</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7668,7 +7668,7 @@
         <v>43451</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7725,7 +7725,7 @@
         <v>43451</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7782,7 +7782,7 @@
         <v>43452</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7839,7 +7839,7 @@
         <v>43454</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7901,7 +7901,7 @@
         <v>43454</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7963,7 +7963,7 @@
         <v>43454</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8025,7 +8025,7 @@
         <v>43455</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8082,7 +8082,7 @@
         <v>43461</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8139,7 +8139,7 @@
         <v>43471</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8196,7 +8196,7 @@
         <v>43472</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8253,7 +8253,7 @@
         <v>43472</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8315,7 +8315,7 @@
         <v>43473</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8372,7 +8372,7 @@
         <v>43475</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8429,7 +8429,7 @@
         <v>43481</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8486,7 +8486,7 @@
         <v>43490</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8543,7 +8543,7 @@
         <v>43495</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8600,7 +8600,7 @@
         <v>43499</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8657,7 +8657,7 @@
         <v>43500</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8719,7 +8719,7 @@
         <v>43511</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8776,7 +8776,7 @@
         <v>43511</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8833,7 +8833,7 @@
         <v>43514</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8890,7 +8890,7 @@
         <v>43517</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8947,7 +8947,7 @@
         <v>43524</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9004,7 +9004,7 @@
         <v>43546</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9061,7 +9061,7 @@
         <v>43553</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9123,7 +9123,7 @@
         <v>43553</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9180,7 +9180,7 @@
         <v>43554</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9237,7 +9237,7 @@
         <v>43556</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9294,7 +9294,7 @@
         <v>43559</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9356,7 +9356,7 @@
         <v>43564</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9413,7 +9413,7 @@
         <v>43566</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9470,7 +9470,7 @@
         <v>43570</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9532,7 +9532,7 @@
         <v>43570</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9594,7 +9594,7 @@
         <v>43570</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9651,7 +9651,7 @@
         <v>43580</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9708,7 +9708,7 @@
         <v>43584</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9765,7 +9765,7 @@
         <v>43585</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9822,7 +9822,7 @@
         <v>43587</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9879,7 +9879,7 @@
         <v>43592</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9936,7 +9936,7 @@
         <v>43592</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9993,7 +9993,7 @@
         <v>43592</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10050,7 +10050,7 @@
         <v>43599</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10107,7 +10107,7 @@
         <v>43609</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10164,7 +10164,7 @@
         <v>43612</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10221,7 +10221,7 @@
         <v>43612</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10278,7 +10278,7 @@
         <v>43612</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10335,7 +10335,7 @@
         <v>43612</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10392,7 +10392,7 @@
         <v>43616</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10449,7 +10449,7 @@
         <v>43619</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10511,7 +10511,7 @@
         <v>43621</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10568,7 +10568,7 @@
         <v>43623</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10625,7 +10625,7 @@
         <v>43628</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10687,7 +10687,7 @@
         <v>43628</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10749,7 +10749,7 @@
         <v>43629</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10806,7 +10806,7 @@
         <v>43630</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10863,7 +10863,7 @@
         <v>43633</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10920,7 +10920,7 @@
         <v>43633</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10977,7 +10977,7 @@
         <v>43641</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11034,7 +11034,7 @@
         <v>43643</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11096,7 +11096,7 @@
         <v>43643</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11158,7 +11158,7 @@
         <v>43647</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11220,7 +11220,7 @@
         <v>43651</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11277,7 +11277,7 @@
         <v>43651</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11334,7 +11334,7 @@
         <v>43656</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11391,7 +11391,7 @@
         <v>43657</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11448,7 +11448,7 @@
         <v>43662</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11505,7 +11505,7 @@
         <v>43662</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11562,7 +11562,7 @@
         <v>43663</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11644,7 +11644,7 @@
         <v>43663</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11706,7 +11706,7 @@
         <v>43663</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11768,7 +11768,7 @@
         <v>43663</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11830,7 +11830,7 @@
         <v>43682</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11887,7 +11887,7 @@
         <v>43686</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11949,7 +11949,7 @@
         <v>43686</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12006,7 +12006,7 @@
         <v>43689</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12068,7 +12068,7 @@
         <v>43690</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12125,7 +12125,7 @@
         <v>43697</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12182,7 +12182,7 @@
         <v>43700</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12239,7 +12239,7 @@
         <v>43705</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12296,7 +12296,7 @@
         <v>43711</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12358,7 +12358,7 @@
         <v>43712</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12415,7 +12415,7 @@
         <v>43713</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12472,7 +12472,7 @@
         <v>43714</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12529,7 +12529,7 @@
         <v>43714</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12586,7 +12586,7 @@
         <v>43717</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12643,7 +12643,7 @@
         <v>43718</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12700,7 +12700,7 @@
         <v>43720</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12757,7 +12757,7 @@
         <v>43724</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12814,7 +12814,7 @@
         <v>43726</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12871,7 +12871,7 @@
         <v>43727</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12928,7 +12928,7 @@
         <v>43727</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12985,7 +12985,7 @@
         <v>43727</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13042,7 +13042,7 @@
         <v>43732</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13099,7 +13099,7 @@
         <v>43734</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13161,7 +13161,7 @@
         <v>43734</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13218,7 +13218,7 @@
         <v>43734</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13275,7 +13275,7 @@
         <v>43735</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13337,7 +13337,7 @@
         <v>43735</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13394,7 +13394,7 @@
         <v>43740</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13456,7 +13456,7 @@
         <v>43740</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13513,7 +13513,7 @@
         <v>43740</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13570,7 +13570,7 @@
         <v>43740</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13627,7 +13627,7 @@
         <v>43742</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13689,7 +13689,7 @@
         <v>43742</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13746,7 +13746,7 @@
         <v>43747</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13803,7 +13803,7 @@
         <v>43758</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13860,7 +13860,7 @@
         <v>43761</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13917,7 +13917,7 @@
         <v>43766</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13974,7 +13974,7 @@
         <v>43767</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14036,7 +14036,7 @@
         <v>43769</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14098,7 +14098,7 @@
         <v>43770</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14155,7 +14155,7 @@
         <v>43770</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14212,7 +14212,7 @@
         <v>43773</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14269,7 +14269,7 @@
         <v>43775</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14326,7 +14326,7 @@
         <v>43776</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14383,7 +14383,7 @@
         <v>43776</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14440,7 +14440,7 @@
         <v>43776</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14497,7 +14497,7 @@
         <v>43776</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14554,7 +14554,7 @@
         <v>43780</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14616,7 +14616,7 @@
         <v>43780</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14673,7 +14673,7 @@
         <v>43780</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14730,7 +14730,7 @@
         <v>43780</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14787,7 +14787,7 @@
         <v>43783</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14849,7 +14849,7 @@
         <v>43784</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14906,7 +14906,7 @@
         <v>43786</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14963,7 +14963,7 @@
         <v>43797</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15020,7 +15020,7 @@
         <v>43804</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15082,7 +15082,7 @@
         <v>43805</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15139,7 +15139,7 @@
         <v>43805</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15196,7 +15196,7 @@
         <v>43812</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15253,7 +15253,7 @@
         <v>43812</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15310,7 +15310,7 @@
         <v>43815</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15367,7 +15367,7 @@
         <v>43815</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15424,7 +15424,7 @@
         <v>43829</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15481,7 +15481,7 @@
         <v>43833</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15538,7 +15538,7 @@
         <v>43837</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15595,7 +15595,7 @@
         <v>43839</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15652,7 +15652,7 @@
         <v>43840</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15709,7 +15709,7 @@
         <v>43843</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15766,7 +15766,7 @@
         <v>43845</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15828,7 +15828,7 @@
         <v>43850</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15885,7 +15885,7 @@
         <v>43854</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15947,7 +15947,7 @@
         <v>43857</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16004,7 +16004,7 @@
         <v>43857</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16066,7 +16066,7 @@
         <v>43857</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16123,7 +16123,7 @@
         <v>43864</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16180,7 +16180,7 @@
         <v>43864</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16242,7 +16242,7 @@
         <v>43864</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16304,7 +16304,7 @@
         <v>43867</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16366,7 +16366,7 @@
         <v>43871</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16423,7 +16423,7 @@
         <v>43872</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16485,7 +16485,7 @@
         <v>43873</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16542,7 +16542,7 @@
         <v>43873</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16599,7 +16599,7 @@
         <v>43873</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16656,7 +16656,7 @@
         <v>43874</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16713,7 +16713,7 @@
         <v>43878</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16770,7 +16770,7 @@
         <v>43879</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16832,7 +16832,7 @@
         <v>43880</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16889,7 +16889,7 @@
         <v>43894</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16946,7 +16946,7 @@
         <v>43894</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17003,7 +17003,7 @@
         <v>43902</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17060,7 +17060,7 @@
         <v>43917</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17117,7 +17117,7 @@
         <v>43917</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17179,7 +17179,7 @@
         <v>43920</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17241,7 +17241,7 @@
         <v>43920</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17303,7 +17303,7 @@
         <v>43921</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17365,7 +17365,7 @@
         <v>43922</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17427,7 +17427,7 @@
         <v>43922</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17489,7 +17489,7 @@
         <v>43924</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17546,7 +17546,7 @@
         <v>43924</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17603,7 +17603,7 @@
         <v>43927</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17660,7 +17660,7 @@
         <v>43927</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17717,7 +17717,7 @@
         <v>43928</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17774,7 +17774,7 @@
         <v>43928</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17831,7 +17831,7 @@
         <v>43930</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17893,7 +17893,7 @@
         <v>43933</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17955,7 +17955,7 @@
         <v>43933</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18017,7 +18017,7 @@
         <v>43935</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18074,7 +18074,7 @@
         <v>43937</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18136,7 +18136,7 @@
         <v>43941</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18193,7 +18193,7 @@
         <v>43941</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18250,7 +18250,7 @@
         <v>43948</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18307,7 +18307,7 @@
         <v>43949</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18369,7 +18369,7 @@
         <v>43949</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18431,7 +18431,7 @@
         <v>43949</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18493,7 +18493,7 @@
         <v>43949</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18555,7 +18555,7 @@
         <v>43950</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18612,7 +18612,7 @@
         <v>43951</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18674,7 +18674,7 @@
         <v>43959</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18736,7 +18736,7 @@
         <v>43959</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18798,7 +18798,7 @@
         <v>43959</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18860,7 +18860,7 @@
         <v>43959</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18917,7 +18917,7 @@
         <v>43969</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18979,7 +18979,7 @@
         <v>43970</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19036,7 +19036,7 @@
         <v>43973</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19093,7 +19093,7 @@
         <v>43985</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19150,7 +19150,7 @@
         <v>43990</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19207,7 +19207,7 @@
         <v>43991</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19269,7 +19269,7 @@
         <v>43991</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19331,7 +19331,7 @@
         <v>43991</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19393,7 +19393,7 @@
         <v>43991</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19455,7 +19455,7 @@
         <v>43991</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19517,7 +19517,7 @@
         <v>44005</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19579,7 +19579,7 @@
         <v>44033</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19636,7 +19636,7 @@
         <v>44039</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19693,7 +19693,7 @@
         <v>44048</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19750,7 +19750,7 @@
         <v>44049</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19807,7 +19807,7 @@
         <v>44053</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19864,7 +19864,7 @@
         <v>44053</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19921,7 +19921,7 @@
         <v>44053</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19978,7 +19978,7 @@
         <v>44054</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20040,7 +20040,7 @@
         <v>44054</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20097,7 +20097,7 @@
         <v>44054</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20154,7 +20154,7 @@
         <v>44055</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20216,7 +20216,7 @@
         <v>44055</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20278,7 +20278,7 @@
         <v>44074</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20335,7 +20335,7 @@
         <v>44074</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20392,7 +20392,7 @@
         <v>44077</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20449,7 +20449,7 @@
         <v>44078</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20511,7 +20511,7 @@
         <v>44078</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20573,7 +20573,7 @@
         <v>44082</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20630,7 +20630,7 @@
         <v>44084</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20692,7 +20692,7 @@
         <v>44089</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20749,7 +20749,7 @@
         <v>44091</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20806,7 +20806,7 @@
         <v>44095</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20863,7 +20863,7 @@
         <v>44097</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20920,7 +20920,7 @@
         <v>44102</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20977,7 +20977,7 @@
         <v>44104</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21034,7 +21034,7 @@
         <v>44105</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21091,7 +21091,7 @@
         <v>44109</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21148,7 +21148,7 @@
         <v>44109</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21210,7 +21210,7 @@
         <v>44117</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21272,7 +21272,7 @@
         <v>44126</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21334,7 +21334,7 @@
         <v>44126</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21396,7 +21396,7 @@
         <v>44126</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21458,7 +21458,7 @@
         <v>44126</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21520,7 +21520,7 @@
         <v>44126</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21582,7 +21582,7 @@
         <v>44130</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21639,7 +21639,7 @@
         <v>44130</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21696,7 +21696,7 @@
         <v>44130</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21753,7 +21753,7 @@
         <v>44130</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21810,7 +21810,7 @@
         <v>44131</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21867,7 +21867,7 @@
         <v>44133</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21929,7 +21929,7 @@
         <v>44137</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21986,7 +21986,7 @@
         <v>44139</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22043,7 +22043,7 @@
         <v>44139</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22100,7 +22100,7 @@
         <v>44141</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22157,7 +22157,7 @@
         <v>44145</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22214,7 +22214,7 @@
         <v>44145</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22271,7 +22271,7 @@
         <v>44151</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22328,7 +22328,7 @@
         <v>44151</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22385,7 +22385,7 @@
         <v>44153</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22442,7 +22442,7 @@
         <v>44159</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22499,7 +22499,7 @@
         <v>44159</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22556,7 +22556,7 @@
         <v>44159</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22613,7 +22613,7 @@
         <v>44159</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22670,7 +22670,7 @@
         <v>44160</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22727,7 +22727,7 @@
         <v>44160</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22784,7 +22784,7 @@
         <v>44160</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22841,7 +22841,7 @@
         <v>44161</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22898,7 +22898,7 @@
         <v>44162</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22955,7 +22955,7 @@
         <v>44173</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23012,7 +23012,7 @@
         <v>44175</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23069,7 +23069,7 @@
         <v>44175</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23126,7 +23126,7 @@
         <v>44179</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23183,7 +23183,7 @@
         <v>44179</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23240,7 +23240,7 @@
         <v>44180</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23297,7 +23297,7 @@
         <v>44185</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23354,7 +23354,7 @@
         <v>44186</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23411,7 +23411,7 @@
         <v>44186</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23468,7 +23468,7 @@
         <v>44194</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23525,7 +23525,7 @@
         <v>44195</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23582,7 +23582,7 @@
         <v>44214</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23639,7 +23639,7 @@
         <v>44214</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23696,7 +23696,7 @@
         <v>44217</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23753,7 +23753,7 @@
         <v>44217</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23810,7 +23810,7 @@
         <v>44228</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23867,7 +23867,7 @@
         <v>44228</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23924,7 +23924,7 @@
         <v>44238</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23981,7 +23981,7 @@
         <v>44242</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24038,7 +24038,7 @@
         <v>44242</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24095,7 +24095,7 @@
         <v>44271</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24152,7 +24152,7 @@
         <v>44273</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24209,7 +24209,7 @@
         <v>44280</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24266,7 +24266,7 @@
         <v>44281</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24323,7 +24323,7 @@
         <v>44284</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24380,7 +24380,7 @@
         <v>44284</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24437,7 +24437,7 @@
         <v>44300</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24494,7 +24494,7 @@
         <v>44300</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24551,7 +24551,7 @@
         <v>44300</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24608,7 +24608,7 @@
         <v>44305</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24665,7 +24665,7 @@
         <v>44306</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24722,7 +24722,7 @@
         <v>44307</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24779,7 +24779,7 @@
         <v>44322</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24841,7 +24841,7 @@
         <v>44326</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24898,7 +24898,7 @@
         <v>44326</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24955,7 +24955,7 @@
         <v>44326</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25012,7 +25012,7 @@
         <v>44326</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25069,7 +25069,7 @@
         <v>44330</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25126,7 +25126,7 @@
         <v>44335</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25183,7 +25183,7 @@
         <v>44336</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25245,7 +25245,7 @@
         <v>44340</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25302,7 +25302,7 @@
         <v>44342</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25364,7 +25364,7 @@
         <v>44347</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25421,7 +25421,7 @@
         <v>44347</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25478,7 +25478,7 @@
         <v>44348</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25535,7 +25535,7 @@
         <v>44348</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25592,7 +25592,7 @@
         <v>44349</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25649,7 +25649,7 @@
         <v>44349</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25706,7 +25706,7 @@
         <v>44350</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25763,7 +25763,7 @@
         <v>44351</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25820,7 +25820,7 @@
         <v>44351</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25877,7 +25877,7 @@
         <v>44363</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25934,7 +25934,7 @@
         <v>44377</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25996,7 +25996,7 @@
         <v>44377</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26053,7 +26053,7 @@
         <v>44377</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26110,7 +26110,7 @@
         <v>44377</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26167,7 +26167,7 @@
         <v>44377</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26229,7 +26229,7 @@
         <v>44386</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26291,7 +26291,7 @@
         <v>44386</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26353,7 +26353,7 @@
         <v>44391</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26415,7 +26415,7 @@
         <v>44391</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26477,7 +26477,7 @@
         <v>44399</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26534,7 +26534,7 @@
         <v>44400</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26591,7 +26591,7 @@
         <v>44403</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26648,7 +26648,7 @@
         <v>44408</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26710,7 +26710,7 @@
         <v>44409</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26772,7 +26772,7 @@
         <v>44414</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26834,7 +26834,7 @@
         <v>44414</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26896,7 +26896,7 @@
         <v>44414</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26958,7 +26958,7 @@
         <v>44418</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27015,7 +27015,7 @@
         <v>44420</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27072,7 +27072,7 @@
         <v>44421</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27129,7 +27129,7 @@
         <v>44421</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27191,7 +27191,7 @@
         <v>44424</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27253,7 +27253,7 @@
         <v>44424</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27310,7 +27310,7 @@
         <v>44432</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27372,7 +27372,7 @@
         <v>44435</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27429,7 +27429,7 @@
         <v>44441</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27486,7 +27486,7 @@
         <v>44441</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27548,7 +27548,7 @@
         <v>44449</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27610,7 +27610,7 @@
         <v>44451</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27672,7 +27672,7 @@
         <v>44451</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27734,7 +27734,7 @@
         <v>44454</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27791,7 +27791,7 @@
         <v>44459</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27853,7 +27853,7 @@
         <v>44459</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27915,7 +27915,7 @@
         <v>44459</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27977,7 +27977,7 @@
         <v>44459</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28039,7 +28039,7 @@
         <v>44459</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28101,7 +28101,7 @@
         <v>44459</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28163,7 +28163,7 @@
         <v>44460</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28220,7 +28220,7 @@
         <v>44460</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28277,7 +28277,7 @@
         <v>44461</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28334,7 +28334,7 @@
         <v>44463</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28396,7 +28396,7 @@
         <v>44467</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28458,7 +28458,7 @@
         <v>44469</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28520,7 +28520,7 @@
         <v>44469</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28582,7 +28582,7 @@
         <v>44469</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28644,7 +28644,7 @@
         <v>44469</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28706,7 +28706,7 @@
         <v>44470</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28768,7 +28768,7 @@
         <v>44470</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28825,7 +28825,7 @@
         <v>44470</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28887,7 +28887,7 @@
         <v>44473</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28944,7 +28944,7 @@
         <v>44474</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29001,7 +29001,7 @@
         <v>44475</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29058,7 +29058,7 @@
         <v>44475</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29115,7 +29115,7 @@
         <v>44477</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29172,7 +29172,7 @@
         <v>44477</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29229,7 +29229,7 @@
         <v>44477</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29286,7 +29286,7 @@
         <v>44479</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29348,7 +29348,7 @@
         <v>44484</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29410,7 +29410,7 @@
         <v>44484</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29472,7 +29472,7 @@
         <v>44488</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29529,7 +29529,7 @@
         <v>44489</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29591,7 +29591,7 @@
         <v>44495</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29653,7 +29653,7 @@
         <v>44495</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29715,7 +29715,7 @@
         <v>44495</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29777,7 +29777,7 @@
         <v>44495</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29839,7 +29839,7 @@
         <v>44495</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29901,7 +29901,7 @@
         <v>44495</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29963,7 +29963,7 @@
         <v>44495</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30025,7 +30025,7 @@
         <v>44496</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30082,7 +30082,7 @@
         <v>44498</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30139,7 +30139,7 @@
         <v>44509</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30201,7 +30201,7 @@
         <v>44511</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30258,7 +30258,7 @@
         <v>44512</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30315,7 +30315,7 @@
         <v>44515</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30372,7 +30372,7 @@
         <v>44517</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30429,7 +30429,7 @@
         <v>44519</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30486,7 +30486,7 @@
         <v>44519</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30543,7 +30543,7 @@
         <v>44523</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30605,7 +30605,7 @@
         <v>44524</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30662,7 +30662,7 @@
         <v>44529</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30724,7 +30724,7 @@
         <v>44529</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30781,7 +30781,7 @@
         <v>44529</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30838,7 +30838,7 @@
         <v>44529</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30895,7 +30895,7 @@
         <v>44529</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30952,7 +30952,7 @@
         <v>44533</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31009,7 +31009,7 @@
         <v>44536</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31066,7 +31066,7 @@
         <v>44537</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31123,7 +31123,7 @@
         <v>44537</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31180,7 +31180,7 @@
         <v>44537</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31237,7 +31237,7 @@
         <v>44541</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31294,7 +31294,7 @@
         <v>44544</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31351,7 +31351,7 @@
         <v>44544</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31408,7 +31408,7 @@
         <v>44545</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31465,7 +31465,7 @@
         <v>44551</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31522,7 +31522,7 @@
         <v>44551</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31579,7 +31579,7 @@
         <v>44552</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31636,7 +31636,7 @@
         <v>44556</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31693,7 +31693,7 @@
         <v>44559</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31750,7 +31750,7 @@
         <v>44562</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31807,7 +31807,7 @@
         <v>44565</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31869,7 +31869,7 @@
         <v>44565</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31931,7 +31931,7 @@
         <v>44565</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31993,7 +31993,7 @@
         <v>44571</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32050,7 +32050,7 @@
         <v>44571</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32107,7 +32107,7 @@
         <v>44572</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32164,7 +32164,7 @@
         <v>44573</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32221,7 +32221,7 @@
         <v>44578</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32278,7 +32278,7 @@
         <v>44579</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32335,7 +32335,7 @@
         <v>44600</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32392,7 +32392,7 @@
         <v>44602</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32449,7 +32449,7 @@
         <v>44610</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32511,7 +32511,7 @@
         <v>44620</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32568,7 +32568,7 @@
         <v>44621</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32625,7 +32625,7 @@
         <v>44627</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32682,7 +32682,7 @@
         <v>44637</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32739,7 +32739,7 @@
         <v>44638</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32796,7 +32796,7 @@
         <v>44638</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32853,7 +32853,7 @@
         <v>44638</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32910,7 +32910,7 @@
         <v>44641</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32967,7 +32967,7 @@
         <v>44644</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33024,7 +33024,7 @@
         <v>44651</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33081,7 +33081,7 @@
         <v>44651</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33138,7 +33138,7 @@
         <v>44655</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33195,7 +33195,7 @@
         <v>44679</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33252,7 +33252,7 @@
         <v>44679</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33309,7 +33309,7 @@
         <v>44679</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33366,7 +33366,7 @@
         <v>44680</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33423,7 +33423,7 @@
         <v>44683</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33480,7 +33480,7 @@
         <v>44684</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33537,7 +33537,7 @@
         <v>44686</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33594,7 +33594,7 @@
         <v>44692</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33651,7 +33651,7 @@
         <v>44700</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33708,7 +33708,7 @@
         <v>44701</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33765,7 +33765,7 @@
         <v>44715</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33822,7 +33822,7 @@
         <v>44719</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33879,7 +33879,7 @@
         <v>44722</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33936,7 +33936,7 @@
         <v>44727</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33993,7 +33993,7 @@
         <v>44727</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34050,7 +34050,7 @@
         <v>44728</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34112,7 +34112,7 @@
         <v>44728</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34174,7 +34174,7 @@
         <v>44729</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34236,7 +34236,7 @@
         <v>44732</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34293,7 +34293,7 @@
         <v>44733</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34350,7 +34350,7 @@
         <v>44736</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34407,7 +34407,7 @@
         <v>44740</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34464,7 +34464,7 @@
         <v>44742</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34521,7 +34521,7 @@
         <v>44743</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34583,7 +34583,7 @@
         <v>44746</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34640,7 +34640,7 @@
         <v>44746</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34697,7 +34697,7 @@
         <v>44747</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34759,7 +34759,7 @@
         <v>44747</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34816,7 +34816,7 @@
         <v>44747</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34878,7 +34878,7 @@
         <v>44747</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34935,7 +34935,7 @@
         <v>44748</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34992,7 +34992,7 @@
         <v>44749</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35054,7 +35054,7 @@
         <v>44749</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35116,7 +35116,7 @@
         <v>44749</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35173,7 +35173,7 @@
         <v>44762</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35230,7 +35230,7 @@
         <v>44762</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35287,7 +35287,7 @@
         <v>44762</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35344,7 +35344,7 @@
         <v>44763</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35401,7 +35401,7 @@
         <v>44763</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35463,7 +35463,7 @@
         <v>44774</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35525,7 +35525,7 @@
         <v>44775</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35582,7 +35582,7 @@
         <v>44775</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35639,7 +35639,7 @@
         <v>44775</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35696,7 +35696,7 @@
         <v>44783</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35753,7 +35753,7 @@
         <v>44785</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35815,7 +35815,7 @@
         <v>44789</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35872,7 +35872,7 @@
         <v>44789</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35934,7 +35934,7 @@
         <v>44790</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35991,7 +35991,7 @@
         <v>44790</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36048,7 +36048,7 @@
         <v>44791</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36105,7 +36105,7 @@
         <v>44791</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36162,7 +36162,7 @@
         <v>44792</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36224,7 +36224,7 @@
         <v>44792</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36286,7 +36286,7 @@
         <v>44792</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36348,7 +36348,7 @@
         <v>44792</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36410,7 +36410,7 @@
         <v>44792</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36472,7 +36472,7 @@
         <v>44795</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36529,7 +36529,7 @@
         <v>44795</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36586,7 +36586,7 @@
         <v>44795</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36643,7 +36643,7 @@
         <v>44796</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36700,7 +36700,7 @@
         <v>44797</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36757,7 +36757,7 @@
         <v>44798</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36814,7 +36814,7 @@
         <v>44798</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36871,7 +36871,7 @@
         <v>44799</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36933,7 +36933,7 @@
         <v>44799</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36995,7 +36995,7 @@
         <v>44799</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37057,7 +37057,7 @@
         <v>44799</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37119,7 +37119,7 @@
         <v>44803</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37176,7 +37176,7 @@
         <v>44803</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37233,7 +37233,7 @@
         <v>44804</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37290,7 +37290,7 @@
         <v>44804</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37347,7 +37347,7 @@
         <v>44806</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37429,7 +37429,7 @@
         <v>44806</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37486,7 +37486,7 @@
         <v>44806</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37543,7 +37543,7 @@
         <v>44806</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37600,7 +37600,7 @@
         <v>44806</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37657,7 +37657,7 @@
         <v>44806</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37714,7 +37714,7 @@
         <v>44807</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37771,7 +37771,7 @@
         <v>44813</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37833,7 +37833,7 @@
         <v>44817</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37895,7 +37895,7 @@
         <v>44817</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37957,7 +37957,7 @@
         <v>44818</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38014,7 +38014,7 @@
         <v>44818</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38071,7 +38071,7 @@
         <v>44818</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38128,7 +38128,7 @@
         <v>44818</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38185,7 +38185,7 @@
         <v>44818</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38242,7 +38242,7 @@
         <v>44819</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38299,7 +38299,7 @@
         <v>44819</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38361,7 +38361,7 @@
         <v>44819</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38418,7 +38418,7 @@
         <v>44820</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38480,7 +38480,7 @@
         <v>44823</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38537,7 +38537,7 @@
         <v>44824</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38594,7 +38594,7 @@
         <v>44826</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38651,7 +38651,7 @@
         <v>44827</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38713,7 +38713,7 @@
         <v>44833</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38770,7 +38770,7 @@
         <v>44834</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38827,7 +38827,7 @@
         <v>44834</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38884,7 +38884,7 @@
         <v>44837</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38941,7 +38941,7 @@
         <v>44838</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39003,7 +39003,7 @@
         <v>44839</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39065,7 +39065,7 @@
         <v>44839</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39122,7 +39122,7 @@
         <v>44839</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39184,7 +39184,7 @@
         <v>44840</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39241,7 +39241,7 @@
         <v>44841</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39298,7 +39298,7 @@
         <v>44841</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39360,7 +39360,7 @@
         <v>44841</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39417,7 +39417,7 @@
         <v>44841</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39474,7 +39474,7 @@
         <v>44845</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39536,7 +39536,7 @@
         <v>44845</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39598,7 +39598,7 @@
         <v>44847</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39655,7 +39655,7 @@
         <v>44851</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39717,7 +39717,7 @@
         <v>44851</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39779,7 +39779,7 @@
         <v>44851</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39841,7 +39841,7 @@
         <v>44851</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39903,7 +39903,7 @@
         <v>44855</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39965,7 +39965,7 @@
         <v>44860</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40027,7 +40027,7 @@
         <v>44862</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40089,7 +40089,7 @@
         <v>44862</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40151,7 +40151,7 @@
         <v>44866</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40213,7 +40213,7 @@
         <v>44866</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40275,7 +40275,7 @@
         <v>44866</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40337,7 +40337,7 @@
         <v>44866</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40394,7 +40394,7 @@
         <v>44868</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40451,7 +40451,7 @@
         <v>44872</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40508,7 +40508,7 @@
         <v>44873</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40565,7 +40565,7 @@
         <v>44873</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40622,7 +40622,7 @@
         <v>44873</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40679,7 +40679,7 @@
         <v>44874</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40736,7 +40736,7 @@
         <v>44874</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40793,7 +40793,7 @@
         <v>44875</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40850,7 +40850,7 @@
         <v>44875</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40907,7 +40907,7 @@
         <v>44879</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40969,7 +40969,7 @@
         <v>44882</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41026,7 +41026,7 @@
         <v>44883</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41088,7 +41088,7 @@
         <v>44883</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41150,7 +41150,7 @@
         <v>44887</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41207,7 +41207,7 @@
         <v>44889</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41264,7 +41264,7 @@
         <v>44890</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41321,7 +41321,7 @@
         <v>44891</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41378,7 +41378,7 @@
         <v>44893</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41435,7 +41435,7 @@
         <v>44897</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41492,7 +41492,7 @@
         <v>44903</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41549,7 +41549,7 @@
         <v>44907</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41611,7 +41611,7 @@
         <v>44907</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41668,7 +41668,7 @@
         <v>44909</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41730,7 +41730,7 @@
         <v>44909</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41812,7 +41812,7 @@
         <v>44909</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41869,7 +41869,7 @@
         <v>44909</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41926,7 +41926,7 @@
         <v>44910</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41983,7 +41983,7 @@
         <v>44911</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42040,7 +42040,7 @@
         <v>44911</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42097,7 +42097,7 @@
         <v>44911</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42154,7 +42154,7 @@
         <v>44911</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42211,7 +42211,7 @@
         <v>44914</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42268,7 +42268,7 @@
         <v>44914</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42325,7 +42325,7 @@
         <v>44914</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42382,7 +42382,7 @@
         <v>44916</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42439,7 +42439,7 @@
         <v>44916</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42496,7 +42496,7 @@
         <v>44922</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42553,7 +42553,7 @@
         <v>44928</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42610,7 +42610,7 @@
         <v>44929</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42667,7 +42667,7 @@
         <v>44929</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42724,7 +42724,7 @@
         <v>44930</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42781,7 +42781,7 @@
         <v>44930</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42838,7 +42838,7 @@
         <v>44930</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42895,7 +42895,7 @@
         <v>44930</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42952,7 +42952,7 @@
         <v>44931</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43014,7 +43014,7 @@
         <v>44939</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43071,7 +43071,7 @@
         <v>44939</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43128,7 +43128,7 @@
         <v>44944</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43185,7 +43185,7 @@
         <v>44944</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43242,7 +43242,7 @@
         <v>44945</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43299,7 +43299,7 @@
         <v>44949</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43356,7 +43356,7 @@
         <v>44950</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43413,7 +43413,7 @@
         <v>44950</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43470,7 +43470,7 @@
         <v>44953</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43527,7 +43527,7 @@
         <v>44956</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43584,7 +43584,7 @@
         <v>44960</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43641,7 +43641,7 @@
         <v>44964</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43698,7 +43698,7 @@
         <v>44964</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43755,7 +43755,7 @@
         <v>44964</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43812,7 +43812,7 @@
         <v>44964</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43869,7 +43869,7 @@
         <v>44964</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43926,7 +43926,7 @@
         <v>44964</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43983,7 +43983,7 @@
         <v>44964</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44040,7 +44040,7 @@
         <v>44966</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44097,7 +44097,7 @@
         <v>44967</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44154,7 +44154,7 @@
         <v>44967</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44211,7 +44211,7 @@
         <v>44967</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44268,7 +44268,7 @@
         <v>44967</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44325,7 +44325,7 @@
         <v>44967</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44382,7 +44382,7 @@
         <v>44970</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44439,7 +44439,7 @@
         <v>44970</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44496,7 +44496,7 @@
         <v>44973</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44553,7 +44553,7 @@
         <v>44977</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44610,7 +44610,7 @@
         <v>44977</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44667,7 +44667,7 @@
         <v>44982</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -44724,7 +44724,7 @@
         <v>44991</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44781,7 +44781,7 @@
         <v>44997</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44838,7 +44838,7 @@
         <v>45002</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44895,7 +44895,7 @@
         <v>45002</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44952,7 +44952,7 @@
         <v>45002</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45009,7 +45009,7 @@
         <v>45019</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45066,7 +45066,7 @@
         <v>45019</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45123,7 +45123,7 @@
         <v>45019</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45180,7 +45180,7 @@
         <v>45021</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45237,7 +45237,7 @@
         <v>45027</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45294,7 +45294,7 @@
         <v>45033</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45351,7 +45351,7 @@
         <v>45040</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45413,7 +45413,7 @@
         <v>45042</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45470,7 +45470,7 @@
         <v>45058</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45527,7 +45527,7 @@
         <v>45062</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45589,7 +45589,7 @@
         <v>45063</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45646,7 +45646,7 @@
         <v>45070</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45703,7 +45703,7 @@
         <v>45071</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45760,7 +45760,7 @@
         <v>45071</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45817,7 +45817,7 @@
         <v>45071</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45874,7 +45874,7 @@
         <v>45071</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45931,7 +45931,7 @@
         <v>45071</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45988,7 +45988,7 @@
         <v>45071</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46045,7 +46045,7 @@
         <v>45072</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46102,7 +46102,7 @@
         <v>45072</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46159,7 +46159,7 @@
         <v>45072</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46221,7 +46221,7 @@
         <v>45075</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46278,7 +46278,7 @@
         <v>45075</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46335,7 +46335,7 @@
         <v>45077</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46392,7 +46392,7 @@
         <v>45079</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46449,7 +46449,7 @@
         <v>45084</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46506,7 +46506,7 @@
         <v>45085</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46563,7 +46563,7 @@
         <v>45085</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46620,7 +46620,7 @@
         <v>45090</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46677,7 +46677,7 @@
         <v>45090</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46734,7 +46734,7 @@
         <v>45090</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46791,7 +46791,7 @@
         <v>45092</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46853,7 +46853,7 @@
         <v>45092</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46910,7 +46910,7 @@
         <v>45093</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46972,7 +46972,7 @@
         <v>45093</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47034,7 +47034,7 @@
         <v>45096</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47091,7 +47091,7 @@
         <v>45096</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47153,7 +47153,7 @@
         <v>45096</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47215,7 +47215,7 @@
         <v>45097</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47272,7 +47272,7 @@
         <v>45097</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47334,7 +47334,7 @@
         <v>45097</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47396,7 +47396,7 @@
         <v>45098</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47453,7 +47453,7 @@
         <v>45098</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47510,7 +47510,7 @@
         <v>45099</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -47572,7 +47572,7 @@
         <v>45103</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47629,7 +47629,7 @@
         <v>45103</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -47686,7 +47686,7 @@
         <v>45104</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -47743,7 +47743,7 @@
         <v>45105</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -47800,7 +47800,7 @@
         <v>45105</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47857,7 +47857,7 @@
         <v>45106</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -47914,7 +47914,7 @@
         <v>45107</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -47971,7 +47971,7 @@
         <v>45107</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -48028,7 +48028,7 @@
         <v>45107</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -48085,7 +48085,7 @@
         <v>45111</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48147,7 +48147,7 @@
         <v>45111</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -48204,7 +48204,7 @@
         <v>45112</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -48261,7 +48261,7 @@
         <v>45112</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48323,7 +48323,7 @@
         <v>45112</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48385,7 +48385,7 @@
         <v>45112</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48442,7 +48442,7 @@
         <v>45114</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48499,7 +48499,7 @@
         <v>45114</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -48556,7 +48556,7 @@
         <v>45119</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -48613,7 +48613,7 @@
         <v>45120</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -48675,7 +48675,7 @@
         <v>45124</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -48737,7 +48737,7 @@
         <v>45124</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -48794,7 +48794,7 @@
         <v>45131</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48856,7 +48856,7 @@
         <v>45131</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -48918,7 +48918,7 @@
         <v>45132</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -48975,7 +48975,7 @@
         <v>45132</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -49032,7 +49032,7 @@
         <v>45138</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -49094,7 +49094,7 @@
         <v>45138</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -49156,7 +49156,7 @@
         <v>45139</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -49213,7 +49213,7 @@
         <v>45139</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -49270,7 +49270,7 @@
         <v>45140</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49327,7 +49327,7 @@
         <v>45145</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -49389,7 +49389,7 @@
         <v>45148</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49446,7 +49446,7 @@
         <v>45152</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49503,7 +49503,7 @@
         <v>45152</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -49565,7 +49565,7 @@
         <v>45152</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -49627,7 +49627,7 @@
         <v>45154</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -49684,7 +49684,7 @@
         <v>45155</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -49741,7 +49741,7 @@
         <v>45159</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -49803,7 +49803,7 @@
         <v>45159</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -49860,7 +49860,7 @@
         <v>45160</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -49922,7 +49922,7 @@
         <v>45160</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -49984,7 +49984,7 @@
         <v>45161</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -50041,7 +50041,7 @@
         <v>45161</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -50103,7 +50103,7 @@
         <v>45166</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -50160,7 +50160,7 @@
         <v>45167</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -50217,7 +50217,7 @@
         <v>45168</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -50274,7 +50274,7 @@
         <v>45168</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -50331,7 +50331,7 @@
         <v>45168</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -50388,7 +50388,7 @@
         <v>45173</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -50445,7 +50445,7 @@
         <v>45173</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -50502,7 +50502,7 @@
         <v>45173</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -50559,7 +50559,7 @@
         <v>45174</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -50616,7 +50616,7 @@
         <v>45175</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -50678,7 +50678,7 @@
         <v>45175</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -50740,7 +50740,7 @@
         <v>45176</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -50802,7 +50802,7 @@
         <v>45176</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -50864,7 +50864,7 @@
         <v>45176</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -50926,7 +50926,7 @@
         <v>45176</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -50988,7 +50988,7 @@
         <v>45176</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -51045,7 +51045,7 @@
         <v>45176</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -51102,7 +51102,7 @@
         <v>45176</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -51159,7 +51159,7 @@
         <v>45180</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -51221,7 +51221,7 @@
         <v>45180</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -51283,7 +51283,7 @@
         <v>45181</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -51340,7 +51340,7 @@
         <v>45181</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -51397,7 +51397,7 @@
         <v>45181</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -51454,7 +51454,7 @@
         <v>45181</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -51511,7 +51511,7 @@
         <v>45182</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -51568,7 +51568,7 @@
         <v>45182</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -51625,7 +51625,7 @@
         <v>45182</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -51682,7 +51682,7 @@
         <v>45183</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -51739,7 +51739,7 @@
         <v>45183</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -51796,7 +51796,7 @@
         <v>45183</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -51853,7 +51853,7 @@
         <v>45187</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -51910,7 +51910,7 @@
         <v>45187</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -51972,7 +51972,7 @@
         <v>45188</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -52029,7 +52029,7 @@
         <v>45188</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -52086,7 +52086,7 @@
         <v>45188</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -52143,7 +52143,7 @@
         <v>45188</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -52200,7 +52200,7 @@
         <v>45190</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -52257,7 +52257,7 @@
         <v>45190</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -52314,7 +52314,7 @@
         <v>45194</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -52371,7 +52371,7 @@
         <v>45194</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -52428,7 +52428,7 @@
         <v>45194</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -52485,7 +52485,7 @@
         <v>45194</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -52542,7 +52542,7 @@
         <v>45194</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -52599,7 +52599,7 @@
         <v>45194</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -52661,7 +52661,7 @@
         <v>45194</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -52718,7 +52718,7 @@
         <v>45194</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -52775,7 +52775,7 @@
         <v>45194</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -52837,7 +52837,7 @@
         <v>45194</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -52899,7 +52899,7 @@
         <v>45195</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -52956,7 +52956,7 @@
         <v>45198</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -53013,7 +53013,7 @@
         <v>45198</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -53070,7 +53070,7 @@
         <v>45201</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -53127,7 +53127,7 @@
         <v>45201</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -53184,7 +53184,7 @@
         <v>45201</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -53241,7 +53241,7 @@
         <v>45201</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -53298,7 +53298,7 @@
         <v>45202</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -53355,7 +53355,7 @@
         <v>45203</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -53412,7 +53412,7 @@
         <v>45203</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -53469,7 +53469,7 @@
         <v>45204</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -53526,7 +53526,7 @@
         <v>45204</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -53583,7 +53583,7 @@
         <v>45204</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -53640,7 +53640,7 @@
         <v>45204</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -53702,7 +53702,7 @@
         <v>45204</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -53759,7 +53759,7 @@
         <v>45205</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -53821,7 +53821,7 @@
         <v>45208</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -53878,7 +53878,7 @@
         <v>45209</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -53940,7 +53940,7 @@
         <v>45209</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -54002,7 +54002,7 @@
         <v>45210</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -54059,7 +54059,7 @@
         <v>45210</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -54116,7 +54116,7 @@
         <v>45210</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -54173,7 +54173,7 @@
         <v>45211</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -54230,7 +54230,7 @@
         <v>45211</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -54292,7 +54292,7 @@
         <v>45215</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -54349,7 +54349,7 @@
         <v>45215</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -54406,7 +54406,7 @@
         <v>45216</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -54463,7 +54463,7 @@
         <v>45217</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -54520,7 +54520,7 @@
         <v>45217</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -54577,7 +54577,7 @@
         <v>45217</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -54634,7 +54634,7 @@
         <v>45217</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -54691,7 +54691,7 @@
         <v>45222</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -54753,7 +54753,7 @@
         <v>45222</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -54810,7 +54810,7 @@
         <v>45222</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -54867,7 +54867,7 @@
         <v>45223</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -54929,7 +54929,7 @@
         <v>45223</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -54986,7 +54986,7 @@
         <v>45225</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -55048,7 +55048,7 @@
         <v>45225</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -55105,7 +55105,7 @@
         <v>45225</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -55167,7 +55167,7 @@
         <v>45225</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -55224,7 +55224,7 @@
         <v>45225</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -55281,7 +55281,7 @@
         <v>45225</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -55338,7 +55338,7 @@
         <v>45225</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -55395,7 +55395,7 @@
         <v>45225</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -55452,7 +55452,7 @@
         <v>45225</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -55509,7 +55509,7 @@
         <v>45226</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -55566,7 +55566,7 @@
         <v>45229</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -55623,7 +55623,7 @@
         <v>45229</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -55680,7 +55680,7 @@
         <v>45229</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -55737,7 +55737,7 @@
         <v>45229</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -55794,7 +55794,7 @@
         <v>45229</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -55851,7 +55851,7 @@
         <v>45230</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -55908,7 +55908,7 @@
         <v>45230</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -55965,7 +55965,7 @@
         <v>45230</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -56022,7 +56022,7 @@
         <v>45230</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -56079,7 +56079,7 @@
         <v>45230</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -56136,7 +56136,7 @@
         <v>45231</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -56193,7 +56193,7 @@
         <v>45231</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -56250,7 +56250,7 @@
         <v>45231</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -56307,7 +56307,7 @@
         <v>45231</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -56364,7 +56364,7 @@
         <v>45231</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -56421,7 +56421,7 @@
         <v>45231</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -56478,7 +56478,7 @@
         <v>45231</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -56535,7 +56535,7 @@
         <v>45232</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -56597,7 +56597,7 @@
         <v>45232</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -56654,7 +56654,7 @@
         <v>45232</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -56711,7 +56711,7 @@
         <v>45232</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -56768,7 +56768,7 @@
         <v>45233</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -56830,7 +56830,7 @@
         <v>45236</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -56887,7 +56887,7 @@
         <v>45236</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -56944,7 +56944,7 @@
         <v>45236</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -57001,7 +57001,7 @@
         <v>45237</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -57058,7 +57058,7 @@
         <v>45237</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -57120,7 +57120,7 @@
         <v>45239</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -57177,7 +57177,7 @@
         <v>45239</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -57234,7 +57234,7 @@
         <v>45240</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -57296,7 +57296,7 @@
         <v>45243</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -57353,7 +57353,7 @@
         <v>45243</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -57410,7 +57410,7 @@
         <v>45243</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -57467,7 +57467,7 @@
         <v>45243</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -57524,7 +57524,7 @@
         <v>45243</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -57581,7 +57581,7 @@
         <v>45243</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -57638,7 +57638,7 @@
         <v>45244</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -57695,7 +57695,7 @@
         <v>45244</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -57757,7 +57757,7 @@
         <v>45244</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -57819,7 +57819,7 @@
         <v>45244</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -57876,7 +57876,7 @@
         <v>45244</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -57933,7 +57933,7 @@
         <v>45244</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -57995,7 +57995,7 @@
         <v>45244</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -58052,7 +58052,7 @@
         <v>45245</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -58109,7 +58109,7 @@
         <v>45245</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -58166,7 +58166,7 @@
         <v>45245</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -58223,7 +58223,7 @@
         <v>45245</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -58280,7 +58280,7 @@
         <v>45245</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -58342,7 +58342,7 @@
         <v>45245</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -58399,7 +58399,7 @@
         <v>45245</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -58456,7 +58456,7 @@
         <v>45247</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -58513,7 +58513,7 @@
         <v>45247</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -58570,7 +58570,7 @@
         <v>45248</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -58627,7 +58627,7 @@
         <v>45250</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -58684,7 +58684,7 @@
         <v>45250</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -58741,7 +58741,7 @@
         <v>45251</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -58798,7 +58798,7 @@
         <v>45251</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -58855,7 +58855,7 @@
         <v>45251</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -58912,7 +58912,7 @@
         <v>45252</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -58969,7 +58969,7 @@
         <v>45253</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -59031,7 +59031,7 @@
         <v>45253</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -59088,7 +59088,7 @@
         <v>45253</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -59150,7 +59150,7 @@
         <v>45253</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -59207,7 +59207,7 @@
         <v>45253</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -59269,7 +59269,7 @@
         <v>45253</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -59331,7 +59331,7 @@
         <v>45253</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -59388,7 +59388,7 @@
         <v>45257</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -59445,7 +59445,7 @@
         <v>45258</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -59502,7 +59502,7 @@
         <v>45259</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -59559,7 +59559,7 @@
         <v>45260</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -59616,7 +59616,7 @@
         <v>45261</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -59673,7 +59673,7 @@
         <v>45261</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -59730,7 +59730,7 @@
         <v>45264</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -59787,7 +59787,7 @@
         <v>45264</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -59844,7 +59844,7 @@
         <v>45264</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -59901,7 +59901,7 @@
         <v>45264</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -59958,7 +59958,7 @@
         <v>45264</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -60015,7 +60015,7 @@
         <v>45265</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -60072,7 +60072,7 @@
         <v>45265</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -60129,7 +60129,7 @@
         <v>45265</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -60186,7 +60186,7 @@
         <v>45266</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -60243,7 +60243,7 @@
         <v>45266</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -60300,7 +60300,7 @@
         <v>45266</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -60357,7 +60357,7 @@
         <v>45266</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -60419,7 +60419,7 @@
         <v>45267</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -60476,7 +60476,7 @@
         <v>45267</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -60533,7 +60533,7 @@
         <v>45267</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -60590,7 +60590,7 @@
         <v>45267</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -60647,7 +60647,7 @@
         <v>45267</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -60704,7 +60704,7 @@
         <v>45268</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -60761,7 +60761,7 @@
         <v>45271</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -60818,7 +60818,7 @@
         <v>45273</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -60875,7 +60875,7 @@
         <v>45273</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -60932,7 +60932,7 @@
         <v>45275</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -60989,7 +60989,7 @@
         <v>45279</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -61046,7 +61046,7 @@
         <v>45279</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -61103,7 +61103,7 @@
         <v>45279</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -61160,7 +61160,7 @@
         <v>45281</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -61217,7 +61217,7 @@
         <v>45281</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -61279,7 +61279,7 @@
         <v>45282</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -61336,7 +61336,7 @@
         <v>45287</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -61398,7 +61398,7 @@
         <v>45297</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -61460,7 +61460,7 @@
         <v>45299</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -61517,7 +61517,7 @@
         <v>45300</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -61574,7 +61574,7 @@
         <v>45300</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -61631,7 +61631,7 @@
         <v>45302</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -61688,7 +61688,7 @@
         <v>45302</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -61745,7 +61745,7 @@
         <v>45303</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -61802,7 +61802,7 @@
         <v>45306</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -61859,7 +61859,7 @@
         <v>45306</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -61916,7 +61916,7 @@
         <v>45307</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -61973,7 +61973,7 @@
         <v>45307</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -62030,7 +62030,7 @@
         <v>45307</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -62087,7 +62087,7 @@
         <v>45307</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -62144,7 +62144,7 @@
         <v>45307</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -62201,7 +62201,7 @@
         <v>45310</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -62258,7 +62258,7 @@
         <v>45310</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -62315,7 +62315,7 @@
         <v>45310</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -62372,7 +62372,7 @@
         <v>45310</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -62429,7 +62429,7 @@
         <v>45310</v>
       </c>
       <c r="C1038" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
@@ -62486,7 +62486,7 @@
         <v>45310</v>
       </c>
       <c r="C1039" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
@@ -62543,7 +62543,7 @@
         <v>45310</v>
       </c>
       <c r="C1040" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
@@ -62600,7 +62600,7 @@
         <v>45310</v>
       </c>
       <c r="C1041" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
@@ -62657,7 +62657,7 @@
         <v>45310</v>
       </c>
       <c r="C1042" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
@@ -62714,7 +62714,7 @@
         <v>45313</v>
       </c>
       <c r="C1043" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D1043" t="inlineStr">
         <is>
@@ -62771,7 +62771,7 @@
         <v>45314</v>
       </c>
       <c r="C1044" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D1044" t="inlineStr">
         <is>
@@ -62828,7 +62828,7 @@
         <v>45314</v>
       </c>
       <c r="C1045" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D1045" t="inlineStr">
         <is>
@@ -62885,7 +62885,7 @@
         <v>45314</v>
       </c>
       <c r="C1046" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D1046" t="inlineStr">
         <is>
@@ -62942,7 +62942,7 @@
         <v>45316</v>
       </c>
       <c r="C1047" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D1047" t="inlineStr">
         <is>
@@ -62999,7 +62999,7 @@
         <v>45317</v>
       </c>
       <c r="C1048" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D1048" t="inlineStr">
         <is>
@@ -63056,7 +63056,7 @@
         <v>45321</v>
       </c>
       <c r="C1049" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D1049" t="inlineStr">
         <is>
@@ -63113,7 +63113,7 @@
         <v>45321</v>
       </c>
       <c r="C1050" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D1050" t="inlineStr">
         <is>
@@ -63170,7 +63170,7 @@
         <v>45321</v>
       </c>
       <c r="C1051" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D1051" t="inlineStr">
         <is>
@@ -63227,7 +63227,7 @@
         <v>45321</v>
       </c>
       <c r="C1052" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D1052" t="inlineStr">
         <is>
@@ -63284,7 +63284,7 @@
         <v>45321</v>
       </c>
       <c r="C1053" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D1053" t="inlineStr">
         <is>
@@ -63341,7 +63341,7 @@
         <v>45321</v>
       </c>
       <c r="C1054" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D1054" t="inlineStr">
         <is>
@@ -63398,7 +63398,7 @@
         <v>45321</v>
       </c>
       <c r="C1055" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D1055" t="inlineStr">
         <is>
@@ -63455,7 +63455,7 @@
         <v>45321</v>
       </c>
       <c r="C1056" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D1056" t="inlineStr">
         <is>
@@ -63512,7 +63512,7 @@
         <v>45321</v>
       </c>
       <c r="C1057" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D1057" t="inlineStr">
         <is>
@@ -63569,7 +63569,7 @@
         <v>45321</v>
       </c>
       <c r="C1058" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D1058" t="inlineStr">
         <is>
@@ -63626,7 +63626,7 @@
         <v>45321</v>
       </c>
       <c r="C1059" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D1059" t="inlineStr">
         <is>
@@ -63683,7 +63683,7 @@
         <v>45321</v>
       </c>
       <c r="C1060" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D1060" t="inlineStr">
         <is>
@@ -63740,7 +63740,7 @@
         <v>45322</v>
       </c>
       <c r="C1061" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D1061" t="inlineStr">
         <is>
@@ -63797,7 +63797,7 @@
         <v>45324</v>
       </c>
       <c r="C1062" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D1062" t="inlineStr">
         <is>
@@ -63854,7 +63854,7 @@
         <v>45329</v>
       </c>
       <c r="C1063" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D1063" t="inlineStr">
         <is>
@@ -63911,7 +63911,7 @@
         <v>45329</v>
       </c>
       <c r="C1064" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D1064" t="inlineStr">
         <is>
@@ -63961,14 +63961,14 @@
     <row r="1065" ht="15" customHeight="1">
       <c r="A1065" t="inlineStr">
         <is>
-          <t>A 5174-2024</t>
+          <t>A 5124-2024</t>
         </is>
       </c>
       <c r="B1065" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C1065" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D1065" t="inlineStr">
         <is>
@@ -63981,7 +63981,7 @@
         </is>
       </c>
       <c r="G1065" t="n">
-        <v>1.4</v>
+        <v>2.6</v>
       </c>
       <c r="H1065" t="n">
         <v>0</v>
@@ -64025,7 +64025,7 @@
         <v>45330</v>
       </c>
       <c r="C1066" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D1066" t="inlineStr">
         <is>
@@ -64075,14 +64075,14 @@
     <row r="1067" ht="15" customHeight="1">
       <c r="A1067" t="inlineStr">
         <is>
-          <t>A 5156-2024</t>
+          <t>A 5122-2024</t>
         </is>
       </c>
       <c r="B1067" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C1067" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D1067" t="inlineStr">
         <is>
@@ -64095,7 +64095,7 @@
         </is>
       </c>
       <c r="G1067" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="H1067" t="n">
         <v>0</v>
@@ -64132,14 +64132,14 @@
     <row r="1068" ht="15" customHeight="1">
       <c r="A1068" t="inlineStr">
         <is>
-          <t>A 5122-2024</t>
+          <t>A 5174-2024</t>
         </is>
       </c>
       <c r="B1068" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C1068" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D1068" t="inlineStr">
         <is>
@@ -64152,7 +64152,7 @@
         </is>
       </c>
       <c r="G1068" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="H1068" t="n">
         <v>0</v>
@@ -64189,14 +64189,14 @@
     <row r="1069" ht="15" customHeight="1">
       <c r="A1069" t="inlineStr">
         <is>
-          <t>A 5124-2024</t>
+          <t>A 5189-2024</t>
         </is>
       </c>
       <c r="B1069" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C1069" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D1069" t="inlineStr">
         <is>
@@ -64209,7 +64209,7 @@
         </is>
       </c>
       <c r="G1069" t="n">
-        <v>2.6</v>
+        <v>1.3</v>
       </c>
       <c r="H1069" t="n">
         <v>0</v>
@@ -64246,14 +64246,14 @@
     <row r="1070" ht="15" customHeight="1">
       <c r="A1070" t="inlineStr">
         <is>
-          <t>A 5189-2024</t>
+          <t>A 5156-2024</t>
         </is>
       </c>
       <c r="B1070" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C1070" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D1070" t="inlineStr">
         <is>
@@ -64266,7 +64266,7 @@
         </is>
       </c>
       <c r="G1070" t="n">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
       <c r="H1070" t="n">
         <v>0</v>
@@ -64310,7 +64310,7 @@
         <v>45331</v>
       </c>
       <c r="C1071" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D1071" t="inlineStr">
         <is>
@@ -64367,7 +64367,7 @@
         <v>45331</v>
       </c>
       <c r="C1072" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D1072" t="inlineStr">
         <is>
@@ -64424,7 +64424,7 @@
         <v>45334</v>
       </c>
       <c r="C1073" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D1073" t="inlineStr">
         <is>
@@ -64481,7 +64481,7 @@
         <v>45334</v>
       </c>
       <c r="C1074" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D1074" t="inlineStr">
         <is>
@@ -64538,7 +64538,7 @@
         <v>45337</v>
       </c>
       <c r="C1075" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D1075" t="inlineStr">
         <is>
@@ -64595,7 +64595,7 @@
         <v>45337</v>
       </c>
       <c r="C1076" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D1076" t="inlineStr">
         <is>
@@ -64652,7 +64652,7 @@
         <v>45337</v>
       </c>
       <c r="C1077" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D1077" t="inlineStr">
         <is>
@@ -64709,7 +64709,7 @@
         <v>45343</v>
       </c>
       <c r="C1078" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D1078" t="inlineStr">
         <is>
@@ -64771,7 +64771,7 @@
         <v>45344</v>
       </c>
       <c r="C1079" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D1079" t="inlineStr">
         <is>
@@ -64828,7 +64828,7 @@
         <v>45344</v>
       </c>
       <c r="C1080" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D1080" t="inlineStr">
         <is>
@@ -64885,7 +64885,7 @@
         <v>45349</v>
       </c>
       <c r="C1081" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D1081" t="inlineStr">
         <is>
@@ -64942,7 +64942,7 @@
         <v>45350</v>
       </c>
       <c r="C1082" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D1082" t="inlineStr">
         <is>
@@ -64992,14 +64992,14 @@
     <row r="1083" ht="15" customHeight="1">
       <c r="A1083" t="inlineStr">
         <is>
-          <t>A 8127-2024</t>
+          <t>A 8126-2024</t>
         </is>
       </c>
       <c r="B1083" s="1" t="n">
         <v>45351</v>
       </c>
       <c r="C1083" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D1083" t="inlineStr">
         <is>
@@ -65012,7 +65012,7 @@
         </is>
       </c>
       <c r="G1083" t="n">
-        <v>5.7</v>
+        <v>4.3</v>
       </c>
       <c r="H1083" t="n">
         <v>0</v>
@@ -65049,14 +65049,14 @@
     <row r="1084" ht="15" customHeight="1">
       <c r="A1084" t="inlineStr">
         <is>
-          <t>A 8126-2024</t>
+          <t>A 8127-2024</t>
         </is>
       </c>
       <c r="B1084" s="1" t="n">
         <v>45351</v>
       </c>
       <c r="C1084" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D1084" t="inlineStr">
         <is>
@@ -65069,7 +65069,7 @@
         </is>
       </c>
       <c r="G1084" t="n">
-        <v>4.3</v>
+        <v>5.7</v>
       </c>
       <c r="H1084" t="n">
         <v>0</v>
@@ -65113,7 +65113,7 @@
         <v>45352</v>
       </c>
       <c r="C1085" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D1085" t="inlineStr">
         <is>

--- a/Översikt RÄTTVIK.xlsx
+++ b/Översikt RÄTTVIK.xlsx
@@ -569,7 +569,7 @@
         <v>43542</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         <v>44909</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
         <v>43663</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>43619</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>43740</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>44909</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>44874</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
         <v>45147</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>44237</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>44624</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>43634</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>43663</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
         <v>44148</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
         <v>44435</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v>44799</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2008,7 +2008,7 @@
         <v>44909</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2100,7 +2100,7 @@
         <v>44909</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2192,7 +2192,7 @@
         <v>45111</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
         <v>43700</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2370,7 +2370,7 @@
         <v>44496</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2456,7 +2456,7 @@
         <v>45033</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
         <v>45264</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         <v>43440</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2717,7 +2717,7 @@
         <v>43493</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         <v>43623</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2887,7 +2887,7 @@
         <v>43705</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2972,7 +2972,7 @@
         <v>44088</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3057,7 +3057,7 @@
         <v>44110</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3142,7 +3142,7 @@
         <v>44361</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3227,7 +3227,7 @@
         <v>44391</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3317,7 +3317,7 @@
         <v>44414</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3407,7 +3407,7 @@
         <v>44470</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3497,7 +3497,7 @@
         <v>44496</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3587,7 +3587,7 @@
         <v>44511</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3672,7 +3672,7 @@
         <v>44568</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3766,7 +3766,7 @@
         <v>44728</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3860,7 +3860,7 @@
         <v>44855</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3950,7 +3950,7 @@
         <v>44894</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4040,7 +4040,7 @@
         <v>44918</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4130,7 +4130,7 @@
         <v>44986</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4215,7 +4215,7 @@
         <v>45077</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4300,7 +4300,7 @@
         <v>45194</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4385,7 +4385,7 @@
         <v>45194</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4470,7 +4470,7 @@
         <v>45231</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4555,7 +4555,7 @@
         <v>43333</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4612,7 +4612,7 @@
         <v>43348</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4669,7 +4669,7 @@
         <v>43356</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4726,7 +4726,7 @@
         <v>43361</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4783,7 +4783,7 @@
         <v>43362</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4840,7 +4840,7 @@
         <v>43362</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4897,7 +4897,7 @@
         <v>43362</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4954,7 +4954,7 @@
         <v>43362</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5011,7 +5011,7 @@
         <v>43367</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5068,7 +5068,7 @@
         <v>43369</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5125,7 +5125,7 @@
         <v>43373</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5182,7 +5182,7 @@
         <v>43378</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5239,7 +5239,7 @@
         <v>43381</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5296,7 +5296,7 @@
         <v>43381</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5353,7 +5353,7 @@
         <v>43388</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5410,7 +5410,7 @@
         <v>43388</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5472,7 +5472,7 @@
         <v>43388</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5529,7 +5529,7 @@
         <v>43391</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5586,7 +5586,7 @@
         <v>43398</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5643,7 +5643,7 @@
         <v>43399</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5700,7 +5700,7 @@
         <v>43401</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5757,7 +5757,7 @@
         <v>43405</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5814,7 +5814,7 @@
         <v>43405</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5871,7 +5871,7 @@
         <v>43410</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5928,7 +5928,7 @@
         <v>43410</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5985,7 +5985,7 @@
         <v>43411</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6042,7 +6042,7 @@
         <v>43412</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6099,7 +6099,7 @@
         <v>43416</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6156,7 +6156,7 @@
         <v>43416</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6213,7 +6213,7 @@
         <v>43416</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6270,7 +6270,7 @@
         <v>43419</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         <v>43419</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6384,7 +6384,7 @@
         <v>43423</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6446,7 +6446,7 @@
         <v>43423</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6508,7 +6508,7 @@
         <v>43423</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6570,7 +6570,7 @@
         <v>43424</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6632,7 +6632,7 @@
         <v>43425</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6689,7 +6689,7 @@
         <v>43427</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6751,7 +6751,7 @@
         <v>43428</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6808,7 +6808,7 @@
         <v>43428</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6865,7 +6865,7 @@
         <v>43430</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6922,7 +6922,7 @@
         <v>43430</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6979,7 +6979,7 @@
         <v>43430</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7036,7 +7036,7 @@
         <v>43430</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7093,7 +7093,7 @@
         <v>43431</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7155,7 +7155,7 @@
         <v>43432</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7212,7 +7212,7 @@
         <v>43432</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7269,7 +7269,7 @@
         <v>43434</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7326,7 +7326,7 @@
         <v>43434</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7383,7 +7383,7 @@
         <v>43438</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7440,7 +7440,7 @@
         <v>43441</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7497,7 +7497,7 @@
         <v>43447</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
         <v>43448</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7611,7 +7611,7 @@
         <v>43451</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7668,7 +7668,7 @@
         <v>43451</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7725,7 +7725,7 @@
         <v>43451</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7782,7 +7782,7 @@
         <v>43452</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7839,7 +7839,7 @@
         <v>43454</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7901,7 +7901,7 @@
         <v>43454</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7963,7 +7963,7 @@
         <v>43454</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8025,7 +8025,7 @@
         <v>43455</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8082,7 +8082,7 @@
         <v>43461</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8139,7 +8139,7 @@
         <v>43471</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8196,7 +8196,7 @@
         <v>43472</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8253,7 +8253,7 @@
         <v>43472</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8315,7 +8315,7 @@
         <v>43473</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8372,7 +8372,7 @@
         <v>43475</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8429,7 +8429,7 @@
         <v>43481</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8486,7 +8486,7 @@
         <v>43490</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8543,7 +8543,7 @@
         <v>43495</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8600,7 +8600,7 @@
         <v>43499</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8657,7 +8657,7 @@
         <v>43500</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8719,7 +8719,7 @@
         <v>43511</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8776,7 +8776,7 @@
         <v>43511</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8833,7 +8833,7 @@
         <v>43514</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8890,7 +8890,7 @@
         <v>43517</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8947,7 +8947,7 @@
         <v>43524</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9004,7 +9004,7 @@
         <v>43546</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9061,7 +9061,7 @@
         <v>43553</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9123,7 +9123,7 @@
         <v>43553</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9180,7 +9180,7 @@
         <v>43554</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9237,7 +9237,7 @@
         <v>43556</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9294,7 +9294,7 @@
         <v>43559</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9356,7 +9356,7 @@
         <v>43564</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9413,7 +9413,7 @@
         <v>43566</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9470,7 +9470,7 @@
         <v>43570</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9532,7 +9532,7 @@
         <v>43570</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9594,7 +9594,7 @@
         <v>43570</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9651,7 +9651,7 @@
         <v>43580</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9708,7 +9708,7 @@
         <v>43584</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9765,7 +9765,7 @@
         <v>43585</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9822,7 +9822,7 @@
         <v>43587</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9879,7 +9879,7 @@
         <v>43592</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9936,7 +9936,7 @@
         <v>43592</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9993,7 +9993,7 @@
         <v>43592</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10050,7 +10050,7 @@
         <v>43599</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10107,7 +10107,7 @@
         <v>43609</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10164,7 +10164,7 @@
         <v>43612</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10221,7 +10221,7 @@
         <v>43612</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10278,7 +10278,7 @@
         <v>43612</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10335,7 +10335,7 @@
         <v>43612</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10392,7 +10392,7 @@
         <v>43616</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10449,7 +10449,7 @@
         <v>43619</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10511,7 +10511,7 @@
         <v>43621</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10568,7 +10568,7 @@
         <v>43623</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10625,7 +10625,7 @@
         <v>43628</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10687,7 +10687,7 @@
         <v>43628</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10749,7 +10749,7 @@
         <v>43629</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10806,7 +10806,7 @@
         <v>43630</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10863,7 +10863,7 @@
         <v>43633</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10920,7 +10920,7 @@
         <v>43633</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10977,7 +10977,7 @@
         <v>43641</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11034,7 +11034,7 @@
         <v>43643</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11096,7 +11096,7 @@
         <v>43643</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11158,7 +11158,7 @@
         <v>43647</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11220,7 +11220,7 @@
         <v>43651</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11277,7 +11277,7 @@
         <v>43651</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11334,7 +11334,7 @@
         <v>43656</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11391,7 +11391,7 @@
         <v>43657</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11448,7 +11448,7 @@
         <v>43662</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11505,7 +11505,7 @@
         <v>43662</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11562,7 +11562,7 @@
         <v>43663</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11644,7 +11644,7 @@
         <v>43663</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11706,7 +11706,7 @@
         <v>43663</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11768,7 +11768,7 @@
         <v>43663</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11830,7 +11830,7 @@
         <v>43682</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11887,7 +11887,7 @@
         <v>43686</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11949,7 +11949,7 @@
         <v>43686</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12006,7 +12006,7 @@
         <v>43689</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12068,7 +12068,7 @@
         <v>43690</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12125,7 +12125,7 @@
         <v>43697</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12182,7 +12182,7 @@
         <v>43700</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12239,7 +12239,7 @@
         <v>43705</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12296,7 +12296,7 @@
         <v>43711</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12358,7 +12358,7 @@
         <v>43712</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12415,7 +12415,7 @@
         <v>43713</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12472,7 +12472,7 @@
         <v>43714</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12529,7 +12529,7 @@
         <v>43714</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12586,7 +12586,7 @@
         <v>43717</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12643,7 +12643,7 @@
         <v>43718</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12700,7 +12700,7 @@
         <v>43720</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12757,7 +12757,7 @@
         <v>43724</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12814,7 +12814,7 @@
         <v>43726</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12871,7 +12871,7 @@
         <v>43727</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12928,7 +12928,7 @@
         <v>43727</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12985,7 +12985,7 @@
         <v>43727</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13042,7 +13042,7 @@
         <v>43732</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13099,7 +13099,7 @@
         <v>43734</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13161,7 +13161,7 @@
         <v>43734</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13218,7 +13218,7 @@
         <v>43734</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13275,7 +13275,7 @@
         <v>43735</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13337,7 +13337,7 @@
         <v>43735</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13394,7 +13394,7 @@
         <v>43740</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13456,7 +13456,7 @@
         <v>43740</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13513,7 +13513,7 @@
         <v>43740</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13570,7 +13570,7 @@
         <v>43740</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13627,7 +13627,7 @@
         <v>43742</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13689,7 +13689,7 @@
         <v>43742</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13746,7 +13746,7 @@
         <v>43747</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13803,7 +13803,7 @@
         <v>43758</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13860,7 +13860,7 @@
         <v>43761</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13917,7 +13917,7 @@
         <v>43766</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13974,7 +13974,7 @@
         <v>43767</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14036,7 +14036,7 @@
         <v>43769</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14098,7 +14098,7 @@
         <v>43770</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14155,7 +14155,7 @@
         <v>43770</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14212,7 +14212,7 @@
         <v>43773</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14269,7 +14269,7 @@
         <v>43775</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14326,7 +14326,7 @@
         <v>43776</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14383,7 +14383,7 @@
         <v>43776</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14440,7 +14440,7 @@
         <v>43776</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14497,7 +14497,7 @@
         <v>43776</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14554,7 +14554,7 @@
         <v>43780</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14616,7 +14616,7 @@
         <v>43780</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14673,7 +14673,7 @@
         <v>43780</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14730,7 +14730,7 @@
         <v>43780</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14787,7 +14787,7 @@
         <v>43783</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14849,7 +14849,7 @@
         <v>43784</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14906,7 +14906,7 @@
         <v>43786</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14963,7 +14963,7 @@
         <v>43797</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15020,7 +15020,7 @@
         <v>43804</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15082,7 +15082,7 @@
         <v>43805</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15139,7 +15139,7 @@
         <v>43805</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15196,7 +15196,7 @@
         <v>43812</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15253,7 +15253,7 @@
         <v>43812</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15310,7 +15310,7 @@
         <v>43815</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15367,7 +15367,7 @@
         <v>43815</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15424,7 +15424,7 @@
         <v>43829</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15481,7 +15481,7 @@
         <v>43833</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15538,7 +15538,7 @@
         <v>43837</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15595,7 +15595,7 @@
         <v>43839</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15652,7 +15652,7 @@
         <v>43840</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15709,7 +15709,7 @@
         <v>43843</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15766,7 +15766,7 @@
         <v>43845</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15828,7 +15828,7 @@
         <v>43850</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15885,7 +15885,7 @@
         <v>43854</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15947,7 +15947,7 @@
         <v>43857</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16004,7 +16004,7 @@
         <v>43857</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16066,7 +16066,7 @@
         <v>43857</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16123,7 +16123,7 @@
         <v>43864</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16180,7 +16180,7 @@
         <v>43864</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16242,7 +16242,7 @@
         <v>43864</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16304,7 +16304,7 @@
         <v>43867</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16366,7 +16366,7 @@
         <v>43871</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16423,7 +16423,7 @@
         <v>43872</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16485,7 +16485,7 @@
         <v>43873</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16542,7 +16542,7 @@
         <v>43873</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16599,7 +16599,7 @@
         <v>43873</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16656,7 +16656,7 @@
         <v>43874</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16713,7 +16713,7 @@
         <v>43878</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16770,7 +16770,7 @@
         <v>43879</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16832,7 +16832,7 @@
         <v>43880</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16889,7 +16889,7 @@
         <v>43894</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16946,7 +16946,7 @@
         <v>43894</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17003,7 +17003,7 @@
         <v>43902</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17060,7 +17060,7 @@
         <v>43917</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17117,7 +17117,7 @@
         <v>43917</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17179,7 +17179,7 @@
         <v>43920</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17241,7 +17241,7 @@
         <v>43920</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17303,7 +17303,7 @@
         <v>43921</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17365,7 +17365,7 @@
         <v>43922</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17427,7 +17427,7 @@
         <v>43922</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17489,7 +17489,7 @@
         <v>43924</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17546,7 +17546,7 @@
         <v>43924</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17603,7 +17603,7 @@
         <v>43927</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17660,7 +17660,7 @@
         <v>43927</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17717,7 +17717,7 @@
         <v>43928</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17774,7 +17774,7 @@
         <v>43928</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17831,7 +17831,7 @@
         <v>43930</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17893,7 +17893,7 @@
         <v>43933</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17955,7 +17955,7 @@
         <v>43933</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18017,7 +18017,7 @@
         <v>43935</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18074,7 +18074,7 @@
         <v>43937</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18136,7 +18136,7 @@
         <v>43941</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18193,7 +18193,7 @@
         <v>43941</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18250,7 +18250,7 @@
         <v>43948</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18307,7 +18307,7 @@
         <v>43949</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18369,7 +18369,7 @@
         <v>43949</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18431,7 +18431,7 @@
         <v>43949</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18493,7 +18493,7 @@
         <v>43949</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18555,7 +18555,7 @@
         <v>43950</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18612,7 +18612,7 @@
         <v>43951</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18674,7 +18674,7 @@
         <v>43959</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18736,7 +18736,7 @@
         <v>43959</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18798,7 +18798,7 @@
         <v>43959</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18860,7 +18860,7 @@
         <v>43959</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18917,7 +18917,7 @@
         <v>43969</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18979,7 +18979,7 @@
         <v>43970</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19036,7 +19036,7 @@
         <v>43973</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19093,7 +19093,7 @@
         <v>43985</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19150,7 +19150,7 @@
         <v>43990</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19207,7 +19207,7 @@
         <v>43991</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19269,7 +19269,7 @@
         <v>43991</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19331,7 +19331,7 @@
         <v>43991</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19393,7 +19393,7 @@
         <v>43991</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19455,7 +19455,7 @@
         <v>43991</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19517,7 +19517,7 @@
         <v>44005</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19579,7 +19579,7 @@
         <v>44033</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19636,7 +19636,7 @@
         <v>44039</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19693,7 +19693,7 @@
         <v>44048</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19750,7 +19750,7 @@
         <v>44049</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19807,7 +19807,7 @@
         <v>44053</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19864,7 +19864,7 @@
         <v>44053</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19921,7 +19921,7 @@
         <v>44053</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19978,7 +19978,7 @@
         <v>44054</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20040,7 +20040,7 @@
         <v>44054</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20097,7 +20097,7 @@
         <v>44054</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20154,7 +20154,7 @@
         <v>44055</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20216,7 +20216,7 @@
         <v>44055</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20278,7 +20278,7 @@
         <v>44074</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20335,7 +20335,7 @@
         <v>44074</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20392,7 +20392,7 @@
         <v>44077</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20449,7 +20449,7 @@
         <v>44078</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20511,7 +20511,7 @@
         <v>44078</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20573,7 +20573,7 @@
         <v>44082</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20630,7 +20630,7 @@
         <v>44084</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20692,7 +20692,7 @@
         <v>44089</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20749,7 +20749,7 @@
         <v>44091</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20806,7 +20806,7 @@
         <v>44095</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20863,7 +20863,7 @@
         <v>44097</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20920,7 +20920,7 @@
         <v>44102</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20977,7 +20977,7 @@
         <v>44104</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21034,7 +21034,7 @@
         <v>44105</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21091,7 +21091,7 @@
         <v>44109</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21148,7 +21148,7 @@
         <v>44109</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21210,7 +21210,7 @@
         <v>44117</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21272,7 +21272,7 @@
         <v>44126</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21334,7 +21334,7 @@
         <v>44126</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21396,7 +21396,7 @@
         <v>44126</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21458,7 +21458,7 @@
         <v>44126</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21520,7 +21520,7 @@
         <v>44126</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21582,7 +21582,7 @@
         <v>44130</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21639,7 +21639,7 @@
         <v>44130</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21696,7 +21696,7 @@
         <v>44130</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21753,7 +21753,7 @@
         <v>44130</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21810,7 +21810,7 @@
         <v>44131</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21867,7 +21867,7 @@
         <v>44133</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21929,7 +21929,7 @@
         <v>44137</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21986,7 +21986,7 @@
         <v>44139</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22043,7 +22043,7 @@
         <v>44139</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22100,7 +22100,7 @@
         <v>44141</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22157,7 +22157,7 @@
         <v>44145</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22214,7 +22214,7 @@
         <v>44145</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22271,7 +22271,7 @@
         <v>44151</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22328,7 +22328,7 @@
         <v>44151</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22385,7 +22385,7 @@
         <v>44153</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22442,7 +22442,7 @@
         <v>44159</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22499,7 +22499,7 @@
         <v>44159</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22556,7 +22556,7 @@
         <v>44159</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22613,7 +22613,7 @@
         <v>44159</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22670,7 +22670,7 @@
         <v>44160</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22727,7 +22727,7 @@
         <v>44160</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22784,7 +22784,7 @@
         <v>44160</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22841,7 +22841,7 @@
         <v>44161</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22898,7 +22898,7 @@
         <v>44162</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22955,7 +22955,7 @@
         <v>44173</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23012,7 +23012,7 @@
         <v>44175</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23069,7 +23069,7 @@
         <v>44175</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23126,7 +23126,7 @@
         <v>44179</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23183,7 +23183,7 @@
         <v>44179</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23240,7 +23240,7 @@
         <v>44180</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23297,7 +23297,7 @@
         <v>44185</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23354,7 +23354,7 @@
         <v>44186</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23411,7 +23411,7 @@
         <v>44186</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23468,7 +23468,7 @@
         <v>44194</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23525,7 +23525,7 @@
         <v>44195</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23582,7 +23582,7 @@
         <v>44214</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23639,7 +23639,7 @@
         <v>44214</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23696,7 +23696,7 @@
         <v>44217</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23753,7 +23753,7 @@
         <v>44217</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23810,7 +23810,7 @@
         <v>44228</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23867,7 +23867,7 @@
         <v>44228</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23924,7 +23924,7 @@
         <v>44238</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23981,7 +23981,7 @@
         <v>44242</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24038,7 +24038,7 @@
         <v>44242</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24095,7 +24095,7 @@
         <v>44271</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24152,7 +24152,7 @@
         <v>44273</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24209,7 +24209,7 @@
         <v>44280</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24266,7 +24266,7 @@
         <v>44281</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24323,7 +24323,7 @@
         <v>44284</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24380,7 +24380,7 @@
         <v>44284</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24437,7 +24437,7 @@
         <v>44300</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24494,7 +24494,7 @@
         <v>44300</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24551,7 +24551,7 @@
         <v>44300</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24608,7 +24608,7 @@
         <v>44305</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24665,7 +24665,7 @@
         <v>44306</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24722,7 +24722,7 @@
         <v>44307</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24779,7 +24779,7 @@
         <v>44322</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24841,7 +24841,7 @@
         <v>44326</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24898,7 +24898,7 @@
         <v>44326</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24955,7 +24955,7 @@
         <v>44326</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25012,7 +25012,7 @@
         <v>44326</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25069,7 +25069,7 @@
         <v>44330</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25126,7 +25126,7 @@
         <v>44335</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25183,7 +25183,7 @@
         <v>44336</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25245,7 +25245,7 @@
         <v>44340</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25302,7 +25302,7 @@
         <v>44342</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25364,7 +25364,7 @@
         <v>44347</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25421,7 +25421,7 @@
         <v>44347</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25478,7 +25478,7 @@
         <v>44348</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25535,7 +25535,7 @@
         <v>44348</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25592,7 +25592,7 @@
         <v>44349</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25649,7 +25649,7 @@
         <v>44349</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25706,7 +25706,7 @@
         <v>44350</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25763,7 +25763,7 @@
         <v>44351</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25820,7 +25820,7 @@
         <v>44351</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25877,7 +25877,7 @@
         <v>44363</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25934,7 +25934,7 @@
         <v>44377</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25996,7 +25996,7 @@
         <v>44377</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26053,7 +26053,7 @@
         <v>44377</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26110,7 +26110,7 @@
         <v>44377</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26167,7 +26167,7 @@
         <v>44377</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26229,7 +26229,7 @@
         <v>44386</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26291,7 +26291,7 @@
         <v>44386</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26353,7 +26353,7 @@
         <v>44391</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26415,7 +26415,7 @@
         <v>44391</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26477,7 +26477,7 @@
         <v>44399</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26534,7 +26534,7 @@
         <v>44400</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26591,7 +26591,7 @@
         <v>44403</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26648,7 +26648,7 @@
         <v>44408</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26710,7 +26710,7 @@
         <v>44409</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26772,7 +26772,7 @@
         <v>44414</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26834,7 +26834,7 @@
         <v>44414</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26896,7 +26896,7 @@
         <v>44414</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26958,7 +26958,7 @@
         <v>44418</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27015,7 +27015,7 @@
         <v>44420</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27072,7 +27072,7 @@
         <v>44421</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27129,7 +27129,7 @@
         <v>44421</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27191,7 +27191,7 @@
         <v>44424</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27253,7 +27253,7 @@
         <v>44424</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27310,7 +27310,7 @@
         <v>44432</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27372,7 +27372,7 @@
         <v>44435</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27429,7 +27429,7 @@
         <v>44441</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27486,7 +27486,7 @@
         <v>44441</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27548,7 +27548,7 @@
         <v>44449</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27610,7 +27610,7 @@
         <v>44451</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27672,7 +27672,7 @@
         <v>44451</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27734,7 +27734,7 @@
         <v>44454</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27791,7 +27791,7 @@
         <v>44459</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27853,7 +27853,7 @@
         <v>44459</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27915,7 +27915,7 @@
         <v>44459</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27977,7 +27977,7 @@
         <v>44459</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28039,7 +28039,7 @@
         <v>44459</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28101,7 +28101,7 @@
         <v>44459</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28163,7 +28163,7 @@
         <v>44460</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28220,7 +28220,7 @@
         <v>44460</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28277,7 +28277,7 @@
         <v>44461</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28334,7 +28334,7 @@
         <v>44463</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28396,7 +28396,7 @@
         <v>44467</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28458,7 +28458,7 @@
         <v>44469</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28520,7 +28520,7 @@
         <v>44469</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28582,7 +28582,7 @@
         <v>44469</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28644,7 +28644,7 @@
         <v>44469</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28706,7 +28706,7 @@
         <v>44470</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28768,7 +28768,7 @@
         <v>44470</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28825,7 +28825,7 @@
         <v>44470</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28887,7 +28887,7 @@
         <v>44473</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28944,7 +28944,7 @@
         <v>44474</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29001,7 +29001,7 @@
         <v>44475</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29058,7 +29058,7 @@
         <v>44475</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29115,7 +29115,7 @@
         <v>44477</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29172,7 +29172,7 @@
         <v>44477</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29229,7 +29229,7 @@
         <v>44477</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29286,7 +29286,7 @@
         <v>44479</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29348,7 +29348,7 @@
         <v>44484</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29410,7 +29410,7 @@
         <v>44484</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29472,7 +29472,7 @@
         <v>44488</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29529,7 +29529,7 @@
         <v>44489</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29591,7 +29591,7 @@
         <v>44495</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29653,7 +29653,7 @@
         <v>44495</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29715,7 +29715,7 @@
         <v>44495</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29777,7 +29777,7 @@
         <v>44495</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29839,7 +29839,7 @@
         <v>44495</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29901,7 +29901,7 @@
         <v>44495</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29963,7 +29963,7 @@
         <v>44495</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30025,7 +30025,7 @@
         <v>44496</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30082,7 +30082,7 @@
         <v>44498</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30139,7 +30139,7 @@
         <v>44509</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30201,7 +30201,7 @@
         <v>44511</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30258,7 +30258,7 @@
         <v>44512</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30315,7 +30315,7 @@
         <v>44515</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30372,7 +30372,7 @@
         <v>44517</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30429,7 +30429,7 @@
         <v>44519</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30486,7 +30486,7 @@
         <v>44519</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30543,7 +30543,7 @@
         <v>44523</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30605,7 +30605,7 @@
         <v>44524</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30662,7 +30662,7 @@
         <v>44529</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30724,7 +30724,7 @@
         <v>44529</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30781,7 +30781,7 @@
         <v>44529</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30838,7 +30838,7 @@
         <v>44529</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30895,7 +30895,7 @@
         <v>44529</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30952,7 +30952,7 @@
         <v>44533</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31009,7 +31009,7 @@
         <v>44536</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31066,7 +31066,7 @@
         <v>44537</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31123,7 +31123,7 @@
         <v>44537</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31180,7 +31180,7 @@
         <v>44537</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31237,7 +31237,7 @@
         <v>44541</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31294,7 +31294,7 @@
         <v>44544</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31351,7 +31351,7 @@
         <v>44544</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31408,7 +31408,7 @@
         <v>44545</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31465,7 +31465,7 @@
         <v>44551</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31522,7 +31522,7 @@
         <v>44551</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31579,7 +31579,7 @@
         <v>44552</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31636,7 +31636,7 @@
         <v>44556</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31693,7 +31693,7 @@
         <v>44559</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31750,7 +31750,7 @@
         <v>44562</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31807,7 +31807,7 @@
         <v>44565</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31869,7 +31869,7 @@
         <v>44565</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31931,7 +31931,7 @@
         <v>44565</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31993,7 +31993,7 @@
         <v>44571</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32050,7 +32050,7 @@
         <v>44571</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32107,7 +32107,7 @@
         <v>44572</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32164,7 +32164,7 @@
         <v>44573</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32221,7 +32221,7 @@
         <v>44578</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32278,7 +32278,7 @@
         <v>44579</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32335,7 +32335,7 @@
         <v>44600</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32392,7 +32392,7 @@
         <v>44602</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32449,7 +32449,7 @@
         <v>44610</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32511,7 +32511,7 @@
         <v>44620</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32568,7 +32568,7 @@
         <v>44621</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32625,7 +32625,7 @@
         <v>44627</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32682,7 +32682,7 @@
         <v>44637</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32739,7 +32739,7 @@
         <v>44638</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32796,7 +32796,7 @@
         <v>44638</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32853,7 +32853,7 @@
         <v>44638</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32910,7 +32910,7 @@
         <v>44641</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32967,7 +32967,7 @@
         <v>44644</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33024,7 +33024,7 @@
         <v>44651</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33081,7 +33081,7 @@
         <v>44651</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33138,7 +33138,7 @@
         <v>44655</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33195,7 +33195,7 @@
         <v>44679</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33252,7 +33252,7 @@
         <v>44679</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33309,7 +33309,7 @@
         <v>44679</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33366,7 +33366,7 @@
         <v>44680</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33423,7 +33423,7 @@
         <v>44683</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33480,7 +33480,7 @@
         <v>44684</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33537,7 +33537,7 @@
         <v>44686</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33594,7 +33594,7 @@
         <v>44692</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33651,7 +33651,7 @@
         <v>44700</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33708,7 +33708,7 @@
         <v>44701</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33765,7 +33765,7 @@
         <v>44715</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33822,7 +33822,7 @@
         <v>44719</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33879,7 +33879,7 @@
         <v>44722</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33936,7 +33936,7 @@
         <v>44727</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33993,7 +33993,7 @@
         <v>44727</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34050,7 +34050,7 @@
         <v>44728</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34112,7 +34112,7 @@
         <v>44728</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34174,7 +34174,7 @@
         <v>44729</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34236,7 +34236,7 @@
         <v>44732</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34293,7 +34293,7 @@
         <v>44733</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34350,7 +34350,7 @@
         <v>44736</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34407,7 +34407,7 @@
         <v>44740</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34464,7 +34464,7 @@
         <v>44742</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34521,7 +34521,7 @@
         <v>44743</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34583,7 +34583,7 @@
         <v>44746</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34640,7 +34640,7 @@
         <v>44746</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34697,7 +34697,7 @@
         <v>44747</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34759,7 +34759,7 @@
         <v>44747</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34816,7 +34816,7 @@
         <v>44747</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34878,7 +34878,7 @@
         <v>44747</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34935,7 +34935,7 @@
         <v>44748</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34992,7 +34992,7 @@
         <v>44749</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35054,7 +35054,7 @@
         <v>44749</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35116,7 +35116,7 @@
         <v>44749</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35173,7 +35173,7 @@
         <v>44762</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35230,7 +35230,7 @@
         <v>44762</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35287,7 +35287,7 @@
         <v>44762</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35344,7 +35344,7 @@
         <v>44763</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35401,7 +35401,7 @@
         <v>44763</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35463,7 +35463,7 @@
         <v>44774</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35525,7 +35525,7 @@
         <v>44775</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35582,7 +35582,7 @@
         <v>44775</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35639,7 +35639,7 @@
         <v>44775</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35696,7 +35696,7 @@
         <v>44783</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35753,7 +35753,7 @@
         <v>44785</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35815,7 +35815,7 @@
         <v>44789</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35872,7 +35872,7 @@
         <v>44789</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35934,7 +35934,7 @@
         <v>44790</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35991,7 +35991,7 @@
         <v>44790</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36048,7 +36048,7 @@
         <v>44791</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36105,7 +36105,7 @@
         <v>44791</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36162,7 +36162,7 @@
         <v>44792</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36224,7 +36224,7 @@
         <v>44792</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36286,7 +36286,7 @@
         <v>44792</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36348,7 +36348,7 @@
         <v>44792</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36410,7 +36410,7 @@
         <v>44792</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36472,7 +36472,7 @@
         <v>44795</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36529,7 +36529,7 @@
         <v>44795</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36586,7 +36586,7 @@
         <v>44795</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36643,7 +36643,7 @@
         <v>44796</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36700,7 +36700,7 @@
         <v>44797</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36757,7 +36757,7 @@
         <v>44798</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36814,7 +36814,7 @@
         <v>44798</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36871,7 +36871,7 @@
         <v>44799</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36933,7 +36933,7 @@
         <v>44799</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36995,7 +36995,7 @@
         <v>44799</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37057,7 +37057,7 @@
         <v>44799</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37119,7 +37119,7 @@
         <v>44803</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37176,7 +37176,7 @@
         <v>44803</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37233,7 +37233,7 @@
         <v>44804</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37290,7 +37290,7 @@
         <v>44804</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37347,7 +37347,7 @@
         <v>44806</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37429,7 +37429,7 @@
         <v>44806</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37486,7 +37486,7 @@
         <v>44806</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37543,7 +37543,7 @@
         <v>44806</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37600,7 +37600,7 @@
         <v>44806</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37657,7 +37657,7 @@
         <v>44806</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37714,7 +37714,7 @@
         <v>44807</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37771,7 +37771,7 @@
         <v>44813</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37833,7 +37833,7 @@
         <v>44817</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37895,7 +37895,7 @@
         <v>44817</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37957,7 +37957,7 @@
         <v>44818</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38014,7 +38014,7 @@
         <v>44818</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38071,7 +38071,7 @@
         <v>44818</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38128,7 +38128,7 @@
         <v>44818</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38185,7 +38185,7 @@
         <v>44818</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38242,7 +38242,7 @@
         <v>44819</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38299,7 +38299,7 @@
         <v>44819</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38361,7 +38361,7 @@
         <v>44819</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38418,7 +38418,7 @@
         <v>44820</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38480,7 +38480,7 @@
         <v>44823</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38537,7 +38537,7 @@
         <v>44824</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38594,7 +38594,7 @@
         <v>44826</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38651,7 +38651,7 @@
         <v>44827</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38713,7 +38713,7 @@
         <v>44833</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38770,7 +38770,7 @@
         <v>44834</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38827,7 +38827,7 @@
         <v>44834</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38884,7 +38884,7 @@
         <v>44837</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38941,7 +38941,7 @@
         <v>44838</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39003,7 +39003,7 @@
         <v>44839</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39065,7 +39065,7 @@
         <v>44839</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39122,7 +39122,7 @@
         <v>44839</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39184,7 +39184,7 @@
         <v>44840</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39241,7 +39241,7 @@
         <v>44841</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39298,7 +39298,7 @@
         <v>44841</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39360,7 +39360,7 @@
         <v>44841</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39417,7 +39417,7 @@
         <v>44841</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39474,7 +39474,7 @@
         <v>44845</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39536,7 +39536,7 @@
         <v>44845</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39598,7 +39598,7 @@
         <v>44847</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39655,7 +39655,7 @@
         <v>44851</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39717,7 +39717,7 @@
         <v>44851</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39779,7 +39779,7 @@
         <v>44851</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39841,7 +39841,7 @@
         <v>44851</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39903,7 +39903,7 @@
         <v>44855</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39965,7 +39965,7 @@
         <v>44860</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40027,7 +40027,7 @@
         <v>44862</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40089,7 +40089,7 @@
         <v>44862</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40151,7 +40151,7 @@
         <v>44866</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40213,7 +40213,7 @@
         <v>44866</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40275,7 +40275,7 @@
         <v>44866</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40337,7 +40337,7 @@
         <v>44866</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40394,7 +40394,7 @@
         <v>44868</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40451,7 +40451,7 @@
         <v>44872</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40508,7 +40508,7 @@
         <v>44873</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40565,7 +40565,7 @@
         <v>44873</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40622,7 +40622,7 @@
         <v>44873</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40679,7 +40679,7 @@
         <v>44874</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40736,7 +40736,7 @@
         <v>44874</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40793,7 +40793,7 @@
         <v>44875</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40850,7 +40850,7 @@
         <v>44875</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40907,7 +40907,7 @@
         <v>44879</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40969,7 +40969,7 @@
         <v>44882</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41026,7 +41026,7 @@
         <v>44883</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41088,7 +41088,7 @@
         <v>44883</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41150,7 +41150,7 @@
         <v>44887</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41207,7 +41207,7 @@
         <v>44889</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41264,7 +41264,7 @@
         <v>44890</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41321,7 +41321,7 @@
         <v>44891</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41378,7 +41378,7 @@
         <v>44893</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41435,7 +41435,7 @@
         <v>44897</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41492,7 +41492,7 @@
         <v>44903</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41549,7 +41549,7 @@
         <v>44907</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41611,7 +41611,7 @@
         <v>44907</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41668,7 +41668,7 @@
         <v>44909</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41730,7 +41730,7 @@
         <v>44909</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41812,7 +41812,7 @@
         <v>44909</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41869,7 +41869,7 @@
         <v>44909</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41926,7 +41926,7 @@
         <v>44910</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41983,7 +41983,7 @@
         <v>44911</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42040,7 +42040,7 @@
         <v>44911</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42097,7 +42097,7 @@
         <v>44911</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42154,7 +42154,7 @@
         <v>44911</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42211,7 +42211,7 @@
         <v>44914</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42268,7 +42268,7 @@
         <v>44914</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42325,7 +42325,7 @@
         <v>44914</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42382,7 +42382,7 @@
         <v>44916</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42439,7 +42439,7 @@
         <v>44916</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42496,7 +42496,7 @@
         <v>44922</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42553,7 +42553,7 @@
         <v>44928</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42610,7 +42610,7 @@
         <v>44929</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42667,7 +42667,7 @@
         <v>44929</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42724,7 +42724,7 @@
         <v>44930</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42781,7 +42781,7 @@
         <v>44930</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42838,7 +42838,7 @@
         <v>44930</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42895,7 +42895,7 @@
         <v>44930</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42952,7 +42952,7 @@
         <v>44931</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43014,7 +43014,7 @@
         <v>44939</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43071,7 +43071,7 @@
         <v>44939</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43128,7 +43128,7 @@
         <v>44944</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43185,7 +43185,7 @@
         <v>44944</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43242,7 +43242,7 @@
         <v>44945</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43299,7 +43299,7 @@
         <v>44949</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43356,7 +43356,7 @@
         <v>44950</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43413,7 +43413,7 @@
         <v>44950</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43470,7 +43470,7 @@
         <v>44953</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43527,7 +43527,7 @@
         <v>44956</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43584,7 +43584,7 @@
         <v>44960</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43641,7 +43641,7 @@
         <v>44964</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43698,7 +43698,7 @@
         <v>44964</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43755,7 +43755,7 @@
         <v>44964</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43812,7 +43812,7 @@
         <v>44964</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43869,7 +43869,7 @@
         <v>44964</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43926,7 +43926,7 @@
         <v>44964</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43983,7 +43983,7 @@
         <v>44964</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44040,7 +44040,7 @@
         <v>44966</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44097,7 +44097,7 @@
         <v>44967</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44154,7 +44154,7 @@
         <v>44967</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44211,7 +44211,7 @@
         <v>44967</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44268,7 +44268,7 @@
         <v>44967</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44325,7 +44325,7 @@
         <v>44967</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44382,7 +44382,7 @@
         <v>44970</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44439,7 +44439,7 @@
         <v>44970</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44496,7 +44496,7 @@
         <v>44973</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44553,7 +44553,7 @@
         <v>44977</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44610,7 +44610,7 @@
         <v>44977</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44667,7 +44667,7 @@
         <v>44982</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -44724,7 +44724,7 @@
         <v>44991</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44781,7 +44781,7 @@
         <v>44997</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44838,7 +44838,7 @@
         <v>45002</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44895,7 +44895,7 @@
         <v>45002</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44952,7 +44952,7 @@
         <v>45002</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45009,7 +45009,7 @@
         <v>45019</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45066,7 +45066,7 @@
         <v>45019</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45123,7 +45123,7 @@
         <v>45019</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45180,7 +45180,7 @@
         <v>45021</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45237,7 +45237,7 @@
         <v>45027</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45294,7 +45294,7 @@
         <v>45033</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45351,7 +45351,7 @@
         <v>45040</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45413,7 +45413,7 @@
         <v>45042</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45470,7 +45470,7 @@
         <v>45058</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45527,7 +45527,7 @@
         <v>45062</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45589,7 +45589,7 @@
         <v>45063</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45646,7 +45646,7 @@
         <v>45070</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45703,7 +45703,7 @@
         <v>45071</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45760,7 +45760,7 @@
         <v>45071</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45817,7 +45817,7 @@
         <v>45071</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45874,7 +45874,7 @@
         <v>45071</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45931,7 +45931,7 @@
         <v>45071</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45988,7 +45988,7 @@
         <v>45071</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46045,7 +46045,7 @@
         <v>45072</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46102,7 +46102,7 @@
         <v>45072</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46159,7 +46159,7 @@
         <v>45072</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46221,7 +46221,7 @@
         <v>45075</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46278,7 +46278,7 @@
         <v>45075</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46335,7 +46335,7 @@
         <v>45077</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46392,7 +46392,7 @@
         <v>45079</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46449,7 +46449,7 @@
         <v>45084</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46506,7 +46506,7 @@
         <v>45085</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46563,7 +46563,7 @@
         <v>45085</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46620,7 +46620,7 @@
         <v>45090</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46677,7 +46677,7 @@
         <v>45090</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46734,7 +46734,7 @@
         <v>45090</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46791,7 +46791,7 @@
         <v>45092</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46853,7 +46853,7 @@
         <v>45092</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46910,7 +46910,7 @@
         <v>45093</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46972,7 +46972,7 @@
         <v>45093</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47034,7 +47034,7 @@
         <v>45096</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47091,7 +47091,7 @@
         <v>45096</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47153,7 +47153,7 @@
         <v>45096</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47215,7 +47215,7 @@
         <v>45097</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47272,7 +47272,7 @@
         <v>45097</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47334,7 +47334,7 @@
         <v>45097</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47396,7 +47396,7 @@
         <v>45098</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47453,7 +47453,7 @@
         <v>45098</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47510,7 +47510,7 @@
         <v>45099</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -47572,7 +47572,7 @@
         <v>45103</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47629,7 +47629,7 @@
         <v>45103</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -47686,7 +47686,7 @@
         <v>45104</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -47743,7 +47743,7 @@
         <v>45105</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -47800,7 +47800,7 @@
         <v>45105</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47857,7 +47857,7 @@
         <v>45106</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -47914,7 +47914,7 @@
         <v>45107</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -47971,7 +47971,7 @@
         <v>45107</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -48028,7 +48028,7 @@
         <v>45107</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -48085,7 +48085,7 @@
         <v>45111</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48147,7 +48147,7 @@
         <v>45111</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -48204,7 +48204,7 @@
         <v>45112</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -48261,7 +48261,7 @@
         <v>45112</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48323,7 +48323,7 @@
         <v>45112</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48385,7 +48385,7 @@
         <v>45112</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48442,7 +48442,7 @@
         <v>45114</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48499,7 +48499,7 @@
         <v>45114</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -48556,7 +48556,7 @@
         <v>45119</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -48613,7 +48613,7 @@
         <v>45120</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -48675,7 +48675,7 @@
         <v>45124</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -48737,7 +48737,7 @@
         <v>45124</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -48794,7 +48794,7 @@
         <v>45131</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48856,7 +48856,7 @@
         <v>45131</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -48918,7 +48918,7 @@
         <v>45132</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -48975,7 +48975,7 @@
         <v>45132</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -49032,7 +49032,7 @@
         <v>45138</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -49094,7 +49094,7 @@
         <v>45138</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -49156,7 +49156,7 @@
         <v>45139</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -49213,7 +49213,7 @@
         <v>45139</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -49270,7 +49270,7 @@
         <v>45140</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49327,7 +49327,7 @@
         <v>45145</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -49389,7 +49389,7 @@
         <v>45148</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49446,7 +49446,7 @@
         <v>45152</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49503,7 +49503,7 @@
         <v>45152</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -49565,7 +49565,7 @@
         <v>45152</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -49627,7 +49627,7 @@
         <v>45154</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -49684,7 +49684,7 @@
         <v>45155</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -49741,7 +49741,7 @@
         <v>45159</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -49803,7 +49803,7 @@
         <v>45159</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -49860,7 +49860,7 @@
         <v>45160</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -49922,7 +49922,7 @@
         <v>45160</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -49984,7 +49984,7 @@
         <v>45161</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -50041,7 +50041,7 @@
         <v>45161</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -50103,7 +50103,7 @@
         <v>45166</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -50160,7 +50160,7 @@
         <v>45167</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -50217,7 +50217,7 @@
         <v>45168</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -50274,7 +50274,7 @@
         <v>45168</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -50331,7 +50331,7 @@
         <v>45168</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -50388,7 +50388,7 @@
         <v>45173</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -50445,7 +50445,7 @@
         <v>45173</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -50502,7 +50502,7 @@
         <v>45173</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -50559,7 +50559,7 @@
         <v>45174</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -50616,7 +50616,7 @@
         <v>45175</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -50678,7 +50678,7 @@
         <v>45175</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -50740,7 +50740,7 @@
         <v>45176</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -50802,7 +50802,7 @@
         <v>45176</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -50864,7 +50864,7 @@
         <v>45176</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -50926,7 +50926,7 @@
         <v>45176</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -50988,7 +50988,7 @@
         <v>45176</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -51045,7 +51045,7 @@
         <v>45176</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -51102,7 +51102,7 @@
         <v>45176</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -51159,7 +51159,7 @@
         <v>45180</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -51221,7 +51221,7 @@
         <v>45180</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -51283,7 +51283,7 @@
         <v>45181</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -51340,7 +51340,7 @@
         <v>45181</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -51397,7 +51397,7 @@
         <v>45181</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -51454,7 +51454,7 @@
         <v>45181</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -51511,7 +51511,7 @@
         <v>45182</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -51568,7 +51568,7 @@
         <v>45182</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -51625,7 +51625,7 @@
         <v>45182</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -51682,7 +51682,7 @@
         <v>45183</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -51739,7 +51739,7 @@
         <v>45183</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -51796,7 +51796,7 @@
         <v>45183</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -51853,7 +51853,7 @@
         <v>45187</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -51910,7 +51910,7 @@
         <v>45187</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -51972,7 +51972,7 @@
         <v>45188</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -52029,7 +52029,7 @@
         <v>45188</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -52086,7 +52086,7 @@
         <v>45188</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -52143,7 +52143,7 @@
         <v>45188</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -52200,7 +52200,7 @@
         <v>45190</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -52257,7 +52257,7 @@
         <v>45190</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -52314,7 +52314,7 @@
         <v>45194</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -52371,7 +52371,7 @@
         <v>45194</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -52428,7 +52428,7 @@
         <v>45194</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -52485,7 +52485,7 @@
         <v>45194</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -52542,7 +52542,7 @@
         <v>45194</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -52599,7 +52599,7 @@
         <v>45194</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -52661,7 +52661,7 @@
         <v>45194</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -52718,7 +52718,7 @@
         <v>45194</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -52775,7 +52775,7 @@
         <v>45194</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -52837,7 +52837,7 @@
         <v>45194</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -52899,7 +52899,7 @@
         <v>45195</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -52956,7 +52956,7 @@
         <v>45198</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -53013,7 +53013,7 @@
         <v>45198</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -53070,7 +53070,7 @@
         <v>45201</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -53127,7 +53127,7 @@
         <v>45201</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -53184,7 +53184,7 @@
         <v>45201</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -53241,7 +53241,7 @@
         <v>45201</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -53298,7 +53298,7 @@
         <v>45202</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -53355,7 +53355,7 @@
         <v>45203</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -53412,7 +53412,7 @@
         <v>45203</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -53469,7 +53469,7 @@
         <v>45204</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -53526,7 +53526,7 @@
         <v>45204</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -53583,7 +53583,7 @@
         <v>45204</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -53640,7 +53640,7 @@
         <v>45204</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -53702,7 +53702,7 @@
         <v>45204</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -53759,7 +53759,7 @@
         <v>45205</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -53821,7 +53821,7 @@
         <v>45208</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -53878,7 +53878,7 @@
         <v>45209</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -53940,7 +53940,7 @@
         <v>45209</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -54002,7 +54002,7 @@
         <v>45210</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -54059,7 +54059,7 @@
         <v>45210</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -54116,7 +54116,7 @@
         <v>45210</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -54173,7 +54173,7 @@
         <v>45211</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -54230,7 +54230,7 @@
         <v>45211</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -54292,7 +54292,7 @@
         <v>45215</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -54349,7 +54349,7 @@
         <v>45215</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -54406,7 +54406,7 @@
         <v>45216</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -54463,7 +54463,7 @@
         <v>45217</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -54520,7 +54520,7 @@
         <v>45217</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -54577,7 +54577,7 @@
         <v>45217</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -54634,7 +54634,7 @@
         <v>45217</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -54691,7 +54691,7 @@
         <v>45222</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -54753,7 +54753,7 @@
         <v>45222</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -54810,7 +54810,7 @@
         <v>45222</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -54867,7 +54867,7 @@
         <v>45223</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -54929,7 +54929,7 @@
         <v>45223</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -54986,7 +54986,7 @@
         <v>45225</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -55048,7 +55048,7 @@
         <v>45225</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -55105,7 +55105,7 @@
         <v>45225</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -55167,7 +55167,7 @@
         <v>45225</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -55224,7 +55224,7 @@
         <v>45225</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -55281,7 +55281,7 @@
         <v>45225</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -55338,7 +55338,7 @@
         <v>45225</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -55395,7 +55395,7 @@
         <v>45225</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -55452,7 +55452,7 @@
         <v>45225</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -55509,7 +55509,7 @@
         <v>45226</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -55566,7 +55566,7 @@
         <v>45229</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -55623,7 +55623,7 @@
         <v>45229</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -55680,7 +55680,7 @@
         <v>45229</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -55737,7 +55737,7 @@
         <v>45229</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -55794,7 +55794,7 @@
         <v>45229</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -55851,7 +55851,7 @@
         <v>45230</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -55908,7 +55908,7 @@
         <v>45230</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -55965,7 +55965,7 @@
         <v>45230</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -56022,7 +56022,7 @@
         <v>45230</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -56079,7 +56079,7 @@
         <v>45230</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -56136,7 +56136,7 @@
         <v>45231</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -56193,7 +56193,7 @@
         <v>45231</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -56250,7 +56250,7 @@
         <v>45231</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -56307,7 +56307,7 @@
         <v>45231</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -56364,7 +56364,7 @@
         <v>45231</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -56421,7 +56421,7 @@
         <v>45231</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -56478,7 +56478,7 @@
         <v>45231</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -56535,7 +56535,7 @@
         <v>45232</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -56597,7 +56597,7 @@
         <v>45232</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -56654,7 +56654,7 @@
         <v>45232</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -56711,7 +56711,7 @@
         <v>45232</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -56768,7 +56768,7 @@
         <v>45233</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -56830,7 +56830,7 @@
         <v>45236</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -56887,7 +56887,7 @@
         <v>45236</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -56944,7 +56944,7 @@
         <v>45236</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -57001,7 +57001,7 @@
         <v>45237</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -57058,7 +57058,7 @@
         <v>45237</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -57120,7 +57120,7 @@
         <v>45239</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -57177,7 +57177,7 @@
         <v>45239</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -57234,7 +57234,7 @@
         <v>45240</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -57296,7 +57296,7 @@
         <v>45243</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -57353,7 +57353,7 @@
         <v>45243</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -57410,7 +57410,7 @@
         <v>45243</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -57467,7 +57467,7 @@
         <v>45243</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -57524,7 +57524,7 @@
         <v>45243</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -57581,7 +57581,7 @@
         <v>45243</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -57638,7 +57638,7 @@
         <v>45244</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -57695,7 +57695,7 @@
         <v>45244</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -57757,7 +57757,7 @@
         <v>45244</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -57819,7 +57819,7 @@
         <v>45244</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -57876,7 +57876,7 @@
         <v>45244</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -57933,7 +57933,7 @@
         <v>45244</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -57995,7 +57995,7 @@
         <v>45244</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -58052,7 +58052,7 @@
         <v>45245</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -58109,7 +58109,7 @@
         <v>45245</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -58166,7 +58166,7 @@
         <v>45245</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -58223,7 +58223,7 @@
         <v>45245</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -58280,7 +58280,7 @@
         <v>45245</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -58342,7 +58342,7 @@
         <v>45245</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -58399,7 +58399,7 @@
         <v>45245</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -58456,7 +58456,7 @@
         <v>45247</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -58513,7 +58513,7 @@
         <v>45247</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -58570,7 +58570,7 @@
         <v>45248</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -58627,7 +58627,7 @@
         <v>45250</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -58684,7 +58684,7 @@
         <v>45250</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -58741,7 +58741,7 @@
         <v>45251</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -58798,7 +58798,7 @@
         <v>45251</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -58855,7 +58855,7 @@
         <v>45251</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -58912,7 +58912,7 @@
         <v>45252</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -58969,7 +58969,7 @@
         <v>45253</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -59031,7 +59031,7 @@
         <v>45253</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -59088,7 +59088,7 @@
         <v>45253</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -59150,7 +59150,7 @@
         <v>45253</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -59207,7 +59207,7 @@
         <v>45253</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -59269,7 +59269,7 @@
         <v>45253</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -59331,7 +59331,7 @@
         <v>45253</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -59388,7 +59388,7 @@
         <v>45257</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -59445,7 +59445,7 @@
         <v>45258</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -59502,7 +59502,7 @@
         <v>45259</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -59559,7 +59559,7 @@
         <v>45260</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -59616,7 +59616,7 @@
         <v>45261</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -59673,7 +59673,7 @@
         <v>45261</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -59730,7 +59730,7 @@
         <v>45264</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -59787,7 +59787,7 @@
         <v>45264</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -59844,7 +59844,7 @@
         <v>45264</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -59901,7 +59901,7 @@
         <v>45264</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -59958,7 +59958,7 @@
         <v>45264</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -60015,7 +60015,7 @@
         <v>45265</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -60072,7 +60072,7 @@
         <v>45265</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -60129,7 +60129,7 @@
         <v>45265</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -60186,7 +60186,7 @@
         <v>45266</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -60243,7 +60243,7 @@
         <v>45266</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -60300,7 +60300,7 @@
         <v>45266</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -60357,7 +60357,7 @@
         <v>45266</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -60419,7 +60419,7 @@
         <v>45267</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -60476,7 +60476,7 @@
         <v>45267</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -60533,7 +60533,7 @@
         <v>45267</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -60590,7 +60590,7 @@
         <v>45267</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -60647,7 +60647,7 @@
         <v>45267</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -60704,7 +60704,7 @@
         <v>45268</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -60761,7 +60761,7 @@
         <v>45271</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -60818,7 +60818,7 @@
         <v>45273</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -60875,7 +60875,7 @@
         <v>45273</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -60932,7 +60932,7 @@
         <v>45275</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -60989,7 +60989,7 @@
         <v>45279</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -61046,7 +61046,7 @@
         <v>45279</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -61103,7 +61103,7 @@
         <v>45279</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -61160,7 +61160,7 @@
         <v>45281</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -61217,7 +61217,7 @@
         <v>45281</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -61279,7 +61279,7 @@
         <v>45282</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -61336,7 +61336,7 @@
         <v>45287</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -61398,7 +61398,7 @@
         <v>45297</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -61460,7 +61460,7 @@
         <v>45299</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -61517,7 +61517,7 @@
         <v>45300</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -61574,7 +61574,7 @@
         <v>45300</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -61631,7 +61631,7 @@
         <v>45302</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -61688,7 +61688,7 @@
         <v>45302</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -61745,7 +61745,7 @@
         <v>45303</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -61802,7 +61802,7 @@
         <v>45306</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -61859,7 +61859,7 @@
         <v>45306</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -61916,7 +61916,7 @@
         <v>45307</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -61973,7 +61973,7 @@
         <v>45307</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -62030,7 +62030,7 @@
         <v>45307</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -62087,7 +62087,7 @@
         <v>45307</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -62144,7 +62144,7 @@
         <v>45307</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -62201,7 +62201,7 @@
         <v>45310</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -62258,7 +62258,7 @@
         <v>45310</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -62315,7 +62315,7 @@
         <v>45310</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -62372,7 +62372,7 @@
         <v>45310</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -62429,7 +62429,7 @@
         <v>45310</v>
       </c>
       <c r="C1038" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
@@ -62486,7 +62486,7 @@
         <v>45310</v>
       </c>
       <c r="C1039" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
@@ -62543,7 +62543,7 @@
         <v>45310</v>
       </c>
       <c r="C1040" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
@@ -62600,7 +62600,7 @@
         <v>45310</v>
       </c>
       <c r="C1041" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
@@ -62657,7 +62657,7 @@
         <v>45310</v>
       </c>
       <c r="C1042" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
@@ -62714,7 +62714,7 @@
         <v>45313</v>
       </c>
       <c r="C1043" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D1043" t="inlineStr">
         <is>
@@ -62771,7 +62771,7 @@
         <v>45314</v>
       </c>
       <c r="C1044" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D1044" t="inlineStr">
         <is>
@@ -62828,7 +62828,7 @@
         <v>45314</v>
       </c>
       <c r="C1045" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D1045" t="inlineStr">
         <is>
@@ -62885,7 +62885,7 @@
         <v>45314</v>
       </c>
       <c r="C1046" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D1046" t="inlineStr">
         <is>
@@ -62942,7 +62942,7 @@
         <v>45316</v>
       </c>
       <c r="C1047" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D1047" t="inlineStr">
         <is>
@@ -62999,7 +62999,7 @@
         <v>45317</v>
       </c>
       <c r="C1048" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D1048" t="inlineStr">
         <is>
@@ -63056,7 +63056,7 @@
         <v>45321</v>
       </c>
       <c r="C1049" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D1049" t="inlineStr">
         <is>
@@ -63113,7 +63113,7 @@
         <v>45321</v>
       </c>
       <c r="C1050" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D1050" t="inlineStr">
         <is>
@@ -63170,7 +63170,7 @@
         <v>45321</v>
       </c>
       <c r="C1051" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D1051" t="inlineStr">
         <is>
@@ -63227,7 +63227,7 @@
         <v>45321</v>
       </c>
       <c r="C1052" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D1052" t="inlineStr">
         <is>
@@ -63284,7 +63284,7 @@
         <v>45321</v>
       </c>
       <c r="C1053" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D1053" t="inlineStr">
         <is>
@@ -63341,7 +63341,7 @@
         <v>45321</v>
       </c>
       <c r="C1054" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D1054" t="inlineStr">
         <is>
@@ -63398,7 +63398,7 @@
         <v>45321</v>
       </c>
       <c r="C1055" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D1055" t="inlineStr">
         <is>
@@ -63455,7 +63455,7 @@
         <v>45321</v>
       </c>
       <c r="C1056" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D1056" t="inlineStr">
         <is>
@@ -63512,7 +63512,7 @@
         <v>45321</v>
       </c>
       <c r="C1057" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D1057" t="inlineStr">
         <is>
@@ -63569,7 +63569,7 @@
         <v>45321</v>
       </c>
       <c r="C1058" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D1058" t="inlineStr">
         <is>
@@ -63626,7 +63626,7 @@
         <v>45321</v>
       </c>
       <c r="C1059" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D1059" t="inlineStr">
         <is>
@@ -63683,7 +63683,7 @@
         <v>45321</v>
       </c>
       <c r="C1060" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D1060" t="inlineStr">
         <is>
@@ -63740,7 +63740,7 @@
         <v>45322</v>
       </c>
       <c r="C1061" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D1061" t="inlineStr">
         <is>
@@ -63797,7 +63797,7 @@
         <v>45324</v>
       </c>
       <c r="C1062" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D1062" t="inlineStr">
         <is>
@@ -63854,7 +63854,7 @@
         <v>45329</v>
       </c>
       <c r="C1063" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D1063" t="inlineStr">
         <is>
@@ -63911,7 +63911,7 @@
         <v>45329</v>
       </c>
       <c r="C1064" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D1064" t="inlineStr">
         <is>
@@ -63961,14 +63961,14 @@
     <row r="1065" ht="15" customHeight="1">
       <c r="A1065" t="inlineStr">
         <is>
-          <t>A 5124-2024</t>
+          <t>A 5110-2024</t>
         </is>
       </c>
       <c r="B1065" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C1065" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D1065" t="inlineStr">
         <is>
@@ -63981,7 +63981,7 @@
         </is>
       </c>
       <c r="G1065" t="n">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="H1065" t="n">
         <v>0</v>
@@ -64018,14 +64018,14 @@
     <row r="1066" ht="15" customHeight="1">
       <c r="A1066" t="inlineStr">
         <is>
-          <t>A 5110-2024</t>
+          <t>A 5122-2024</t>
         </is>
       </c>
       <c r="B1066" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C1066" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D1066" t="inlineStr">
         <is>
@@ -64038,7 +64038,7 @@
         </is>
       </c>
       <c r="G1066" t="n">
-        <v>3.3</v>
+        <v>0.7</v>
       </c>
       <c r="H1066" t="n">
         <v>0</v>
@@ -64075,14 +64075,14 @@
     <row r="1067" ht="15" customHeight="1">
       <c r="A1067" t="inlineStr">
         <is>
-          <t>A 5122-2024</t>
+          <t>A 5156-2024</t>
         </is>
       </c>
       <c r="B1067" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C1067" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D1067" t="inlineStr">
         <is>
@@ -64095,7 +64095,7 @@
         </is>
       </c>
       <c r="G1067" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="H1067" t="n">
         <v>0</v>
@@ -64139,7 +64139,7 @@
         <v>45330</v>
       </c>
       <c r="C1068" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D1068" t="inlineStr">
         <is>
@@ -64189,14 +64189,14 @@
     <row r="1069" ht="15" customHeight="1">
       <c r="A1069" t="inlineStr">
         <is>
-          <t>A 5189-2024</t>
+          <t>A 5124-2024</t>
         </is>
       </c>
       <c r="B1069" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C1069" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D1069" t="inlineStr">
         <is>
@@ -64209,7 +64209,7 @@
         </is>
       </c>
       <c r="G1069" t="n">
-        <v>1.3</v>
+        <v>2.6</v>
       </c>
       <c r="H1069" t="n">
         <v>0</v>
@@ -64246,14 +64246,14 @@
     <row r="1070" ht="15" customHeight="1">
       <c r="A1070" t="inlineStr">
         <is>
-          <t>A 5156-2024</t>
+          <t>A 5189-2024</t>
         </is>
       </c>
       <c r="B1070" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C1070" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D1070" t="inlineStr">
         <is>
@@ -64266,7 +64266,7 @@
         </is>
       </c>
       <c r="G1070" t="n">
-        <v>0.4</v>
+        <v>1.3</v>
       </c>
       <c r="H1070" t="n">
         <v>0</v>
@@ -64310,7 +64310,7 @@
         <v>45331</v>
       </c>
       <c r="C1071" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D1071" t="inlineStr">
         <is>
@@ -64367,7 +64367,7 @@
         <v>45331</v>
       </c>
       <c r="C1072" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D1072" t="inlineStr">
         <is>
@@ -64424,7 +64424,7 @@
         <v>45334</v>
       </c>
       <c r="C1073" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D1073" t="inlineStr">
         <is>
@@ -64481,7 +64481,7 @@
         <v>45334</v>
       </c>
       <c r="C1074" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D1074" t="inlineStr">
         <is>
@@ -64538,7 +64538,7 @@
         <v>45337</v>
       </c>
       <c r="C1075" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D1075" t="inlineStr">
         <is>
@@ -64588,14 +64588,14 @@
     <row r="1076" ht="15" customHeight="1">
       <c r="A1076" t="inlineStr">
         <is>
-          <t>A 6187-2024</t>
+          <t>A 6213-2024</t>
         </is>
       </c>
       <c r="B1076" s="1" t="n">
         <v>45337</v>
       </c>
       <c r="C1076" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D1076" t="inlineStr">
         <is>
@@ -64608,7 +64608,7 @@
         </is>
       </c>
       <c r="G1076" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="H1076" t="n">
         <v>0</v>
@@ -64645,14 +64645,14 @@
     <row r="1077" ht="15" customHeight="1">
       <c r="A1077" t="inlineStr">
         <is>
-          <t>A 6213-2024</t>
+          <t>A 6187-2024</t>
         </is>
       </c>
       <c r="B1077" s="1" t="n">
         <v>45337</v>
       </c>
       <c r="C1077" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D1077" t="inlineStr">
         <is>
@@ -64665,7 +64665,7 @@
         </is>
       </c>
       <c r="G1077" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="H1077" t="n">
         <v>0</v>
@@ -64709,7 +64709,7 @@
         <v>45343</v>
       </c>
       <c r="C1078" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D1078" t="inlineStr">
         <is>
@@ -64764,14 +64764,14 @@
     <row r="1079" ht="15" customHeight="1">
       <c r="A1079" t="inlineStr">
         <is>
-          <t>A 7140-2024</t>
+          <t>A 7146-2024</t>
         </is>
       </c>
       <c r="B1079" s="1" t="n">
         <v>45344</v>
       </c>
       <c r="C1079" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D1079" t="inlineStr">
         <is>
@@ -64784,7 +64784,7 @@
         </is>
       </c>
       <c r="G1079" t="n">
-        <v>5.9</v>
+        <v>0.4</v>
       </c>
       <c r="H1079" t="n">
         <v>0</v>
@@ -64821,14 +64821,14 @@
     <row r="1080" ht="15" customHeight="1">
       <c r="A1080" t="inlineStr">
         <is>
-          <t>A 7146-2024</t>
+          <t>A 7140-2024</t>
         </is>
       </c>
       <c r="B1080" s="1" t="n">
         <v>45344</v>
       </c>
       <c r="C1080" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D1080" t="inlineStr">
         <is>
@@ -64841,7 +64841,7 @@
         </is>
       </c>
       <c r="G1080" t="n">
-        <v>0.4</v>
+        <v>5.9</v>
       </c>
       <c r="H1080" t="n">
         <v>0</v>
@@ -64885,7 +64885,7 @@
         <v>45349</v>
       </c>
       <c r="C1081" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D1081" t="inlineStr">
         <is>
@@ -64942,7 +64942,7 @@
         <v>45350</v>
       </c>
       <c r="C1082" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D1082" t="inlineStr">
         <is>
@@ -64999,7 +64999,7 @@
         <v>45351</v>
       </c>
       <c r="C1083" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D1083" t="inlineStr">
         <is>
@@ -65056,7 +65056,7 @@
         <v>45351</v>
       </c>
       <c r="C1084" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D1084" t="inlineStr">
         <is>
@@ -65113,7 +65113,7 @@
         <v>45352</v>
       </c>
       <c r="C1085" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="D1085" t="inlineStr">
         <is>

--- a/Översikt RÄTTVIK.xlsx
+++ b/Översikt RÄTTVIK.xlsx
@@ -569,7 +569,7 @@
         <v>43542</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         <v>44909</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
         <v>43663</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>43619</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>43740</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>44909</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>44874</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
         <v>45147</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>44237</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>44624</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>43634</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>43663</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
         <v>44148</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
         <v>44435</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v>44799</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2008,7 +2008,7 @@
         <v>44909</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2100,7 +2100,7 @@
         <v>44909</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2192,7 +2192,7 @@
         <v>45111</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
         <v>43700</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2370,7 +2370,7 @@
         <v>44496</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2456,7 +2456,7 @@
         <v>45033</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
         <v>45264</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         <v>43440</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2717,7 +2717,7 @@
         <v>43493</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         <v>43623</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2887,7 +2887,7 @@
         <v>43705</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2972,7 +2972,7 @@
         <v>44088</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3057,7 +3057,7 @@
         <v>44110</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3142,7 +3142,7 @@
         <v>44361</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3227,7 +3227,7 @@
         <v>44391</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3317,7 +3317,7 @@
         <v>44414</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3407,7 +3407,7 @@
         <v>44470</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3497,7 +3497,7 @@
         <v>44496</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3587,7 +3587,7 @@
         <v>44511</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3672,7 +3672,7 @@
         <v>44568</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3766,7 +3766,7 @@
         <v>44728</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3860,7 +3860,7 @@
         <v>44855</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3950,7 +3950,7 @@
         <v>44894</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4040,7 +4040,7 @@
         <v>44918</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4130,7 +4130,7 @@
         <v>44986</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4215,7 +4215,7 @@
         <v>45077</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4300,7 +4300,7 @@
         <v>45194</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4385,7 +4385,7 @@
         <v>45194</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4470,7 +4470,7 @@
         <v>45231</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4555,7 +4555,7 @@
         <v>43333</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4612,7 +4612,7 @@
         <v>43348</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4669,7 +4669,7 @@
         <v>43356</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4726,7 +4726,7 @@
         <v>43361</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4783,7 +4783,7 @@
         <v>43362</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4840,7 +4840,7 @@
         <v>43362</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4897,7 +4897,7 @@
         <v>43362</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4954,7 +4954,7 @@
         <v>43362</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5011,7 +5011,7 @@
         <v>43367</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5068,7 +5068,7 @@
         <v>43369</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5125,7 +5125,7 @@
         <v>43373</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5182,7 +5182,7 @@
         <v>43378</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5239,7 +5239,7 @@
         <v>43381</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5296,7 +5296,7 @@
         <v>43381</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5353,7 +5353,7 @@
         <v>43388</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5410,7 +5410,7 @@
         <v>43388</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5472,7 +5472,7 @@
         <v>43388</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5529,7 +5529,7 @@
         <v>43391</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5586,7 +5586,7 @@
         <v>43398</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5643,7 +5643,7 @@
         <v>43399</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5700,7 +5700,7 @@
         <v>43401</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5757,7 +5757,7 @@
         <v>43405</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5814,7 +5814,7 @@
         <v>43405</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5871,7 +5871,7 @@
         <v>43410</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5928,7 +5928,7 @@
         <v>43410</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5985,7 +5985,7 @@
         <v>43411</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6042,7 +6042,7 @@
         <v>43412</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6099,7 +6099,7 @@
         <v>43416</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6156,7 +6156,7 @@
         <v>43416</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6213,7 +6213,7 @@
         <v>43416</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6270,7 +6270,7 @@
         <v>43419</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         <v>43419</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6384,7 +6384,7 @@
         <v>43423</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6446,7 +6446,7 @@
         <v>43423</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6508,7 +6508,7 @@
         <v>43423</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6570,7 +6570,7 @@
         <v>43424</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6632,7 +6632,7 @@
         <v>43425</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6689,7 +6689,7 @@
         <v>43427</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6751,7 +6751,7 @@
         <v>43428</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6808,7 +6808,7 @@
         <v>43428</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6865,7 +6865,7 @@
         <v>43430</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6922,7 +6922,7 @@
         <v>43430</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6979,7 +6979,7 @@
         <v>43430</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7036,7 +7036,7 @@
         <v>43430</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7093,7 +7093,7 @@
         <v>43431</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7155,7 +7155,7 @@
         <v>43432</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7212,7 +7212,7 @@
         <v>43432</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7269,7 +7269,7 @@
         <v>43434</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7326,7 +7326,7 @@
         <v>43434</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7383,7 +7383,7 @@
         <v>43438</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7440,7 +7440,7 @@
         <v>43441</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7497,7 +7497,7 @@
         <v>43447</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
         <v>43448</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7611,7 +7611,7 @@
         <v>43451</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7668,7 +7668,7 @@
         <v>43451</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7725,7 +7725,7 @@
         <v>43451</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7782,7 +7782,7 @@
         <v>43452</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7839,7 +7839,7 @@
         <v>43454</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7901,7 +7901,7 @@
         <v>43454</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7963,7 +7963,7 @@
         <v>43454</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8025,7 +8025,7 @@
         <v>43455</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8082,7 +8082,7 @@
         <v>43461</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8139,7 +8139,7 @@
         <v>43471</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8196,7 +8196,7 @@
         <v>43472</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8253,7 +8253,7 @@
         <v>43472</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8315,7 +8315,7 @@
         <v>43473</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8372,7 +8372,7 @@
         <v>43475</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8429,7 +8429,7 @@
         <v>43481</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8486,7 +8486,7 @@
         <v>43490</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8543,7 +8543,7 @@
         <v>43495</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8600,7 +8600,7 @@
         <v>43499</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8657,7 +8657,7 @@
         <v>43500</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8719,7 +8719,7 @@
         <v>43511</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8776,7 +8776,7 @@
         <v>43511</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8833,7 +8833,7 @@
         <v>43514</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8890,7 +8890,7 @@
         <v>43517</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8947,7 +8947,7 @@
         <v>43524</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9004,7 +9004,7 @@
         <v>43546</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9061,7 +9061,7 @@
         <v>43553</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9123,7 +9123,7 @@
         <v>43553</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9180,7 +9180,7 @@
         <v>43554</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9237,7 +9237,7 @@
         <v>43556</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9294,7 +9294,7 @@
         <v>43559</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9356,7 +9356,7 @@
         <v>43564</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9413,7 +9413,7 @@
         <v>43566</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9470,7 +9470,7 @@
         <v>43570</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9532,7 +9532,7 @@
         <v>43570</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9594,7 +9594,7 @@
         <v>43570</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9651,7 +9651,7 @@
         <v>43580</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9708,7 +9708,7 @@
         <v>43584</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9765,7 +9765,7 @@
         <v>43585</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9822,7 +9822,7 @@
         <v>43587</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9879,7 +9879,7 @@
         <v>43592</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9936,7 +9936,7 @@
         <v>43592</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9993,7 +9993,7 @@
         <v>43592</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10050,7 +10050,7 @@
         <v>43599</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10107,7 +10107,7 @@
         <v>43609</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10164,7 +10164,7 @@
         <v>43612</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10221,7 +10221,7 @@
         <v>43612</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10278,7 +10278,7 @@
         <v>43612</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10335,7 +10335,7 @@
         <v>43612</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10392,7 +10392,7 @@
         <v>43616</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10449,7 +10449,7 @@
         <v>43619</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10511,7 +10511,7 @@
         <v>43621</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10568,7 +10568,7 @@
         <v>43623</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10625,7 +10625,7 @@
         <v>43628</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10687,7 +10687,7 @@
         <v>43628</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10749,7 +10749,7 @@
         <v>43629</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10806,7 +10806,7 @@
         <v>43630</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10863,7 +10863,7 @@
         <v>43633</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10920,7 +10920,7 @@
         <v>43633</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10977,7 +10977,7 @@
         <v>43641</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11034,7 +11034,7 @@
         <v>43643</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11096,7 +11096,7 @@
         <v>43643</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11158,7 +11158,7 @@
         <v>43647</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11220,7 +11220,7 @@
         <v>43651</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11277,7 +11277,7 @@
         <v>43651</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11334,7 +11334,7 @@
         <v>43656</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11391,7 +11391,7 @@
         <v>43657</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11448,7 +11448,7 @@
         <v>43662</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11505,7 +11505,7 @@
         <v>43662</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11562,7 +11562,7 @@
         <v>43663</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11644,7 +11644,7 @@
         <v>43663</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11706,7 +11706,7 @@
         <v>43663</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11768,7 +11768,7 @@
         <v>43663</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11830,7 +11830,7 @@
         <v>43682</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11887,7 +11887,7 @@
         <v>43686</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11949,7 +11949,7 @@
         <v>43686</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12006,7 +12006,7 @@
         <v>43689</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12068,7 +12068,7 @@
         <v>43690</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12125,7 +12125,7 @@
         <v>43697</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12182,7 +12182,7 @@
         <v>43700</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12239,7 +12239,7 @@
         <v>43705</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12296,7 +12296,7 @@
         <v>43711</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12358,7 +12358,7 @@
         <v>43712</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12415,7 +12415,7 @@
         <v>43713</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12472,7 +12472,7 @@
         <v>43714</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12529,7 +12529,7 @@
         <v>43714</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12586,7 +12586,7 @@
         <v>43717</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12643,7 +12643,7 @@
         <v>43718</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12700,7 +12700,7 @@
         <v>43720</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12757,7 +12757,7 @@
         <v>43724</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12814,7 +12814,7 @@
         <v>43726</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12871,7 +12871,7 @@
         <v>43727</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12928,7 +12928,7 @@
         <v>43727</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12985,7 +12985,7 @@
         <v>43727</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13042,7 +13042,7 @@
         <v>43732</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13099,7 +13099,7 @@
         <v>43734</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13161,7 +13161,7 @@
         <v>43734</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13218,7 +13218,7 @@
         <v>43734</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13275,7 +13275,7 @@
         <v>43735</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13337,7 +13337,7 @@
         <v>43735</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13394,7 +13394,7 @@
         <v>43740</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13456,7 +13456,7 @@
         <v>43740</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13513,7 +13513,7 @@
         <v>43740</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13570,7 +13570,7 @@
         <v>43740</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13627,7 +13627,7 @@
         <v>43742</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13689,7 +13689,7 @@
         <v>43742</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13746,7 +13746,7 @@
         <v>43747</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13803,7 +13803,7 @@
         <v>43758</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13860,7 +13860,7 @@
         <v>43761</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13917,7 +13917,7 @@
         <v>43766</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13974,7 +13974,7 @@
         <v>43767</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14036,7 +14036,7 @@
         <v>43769</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14098,7 +14098,7 @@
         <v>43770</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14155,7 +14155,7 @@
         <v>43770</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14212,7 +14212,7 @@
         <v>43773</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14269,7 +14269,7 @@
         <v>43775</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14326,7 +14326,7 @@
         <v>43776</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14383,7 +14383,7 @@
         <v>43776</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14440,7 +14440,7 @@
         <v>43776</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14497,7 +14497,7 @@
         <v>43776</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14554,7 +14554,7 @@
         <v>43780</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14616,7 +14616,7 @@
         <v>43780</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14673,7 +14673,7 @@
         <v>43780</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14730,7 +14730,7 @@
         <v>43780</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14787,7 +14787,7 @@
         <v>43783</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14849,7 +14849,7 @@
         <v>43784</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14906,7 +14906,7 @@
         <v>43786</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14963,7 +14963,7 @@
         <v>43797</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15020,7 +15020,7 @@
         <v>43804</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15082,7 +15082,7 @@
         <v>43805</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15139,7 +15139,7 @@
         <v>43805</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15196,7 +15196,7 @@
         <v>43812</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15253,7 +15253,7 @@
         <v>43812</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15310,7 +15310,7 @@
         <v>43815</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15367,7 +15367,7 @@
         <v>43815</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15424,7 +15424,7 @@
         <v>43829</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15481,7 +15481,7 @@
         <v>43833</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15538,7 +15538,7 @@
         <v>43837</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15595,7 +15595,7 @@
         <v>43839</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15652,7 +15652,7 @@
         <v>43840</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15709,7 +15709,7 @@
         <v>43843</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15766,7 +15766,7 @@
         <v>43845</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15828,7 +15828,7 @@
         <v>43850</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15885,7 +15885,7 @@
         <v>43854</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15947,7 +15947,7 @@
         <v>43857</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16004,7 +16004,7 @@
         <v>43857</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16066,7 +16066,7 @@
         <v>43857</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16123,7 +16123,7 @@
         <v>43864</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16180,7 +16180,7 @@
         <v>43864</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16242,7 +16242,7 @@
         <v>43864</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16304,7 +16304,7 @@
         <v>43867</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16366,7 +16366,7 @@
         <v>43871</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16423,7 +16423,7 @@
         <v>43872</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16485,7 +16485,7 @@
         <v>43873</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16542,7 +16542,7 @@
         <v>43873</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16599,7 +16599,7 @@
         <v>43873</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16656,7 +16656,7 @@
         <v>43874</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16713,7 +16713,7 @@
         <v>43878</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16770,7 +16770,7 @@
         <v>43879</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16832,7 +16832,7 @@
         <v>43880</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16889,7 +16889,7 @@
         <v>43894</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16946,7 +16946,7 @@
         <v>43894</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17003,7 +17003,7 @@
         <v>43902</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17060,7 +17060,7 @@
         <v>43917</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17117,7 +17117,7 @@
         <v>43917</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17179,7 +17179,7 @@
         <v>43920</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17241,7 +17241,7 @@
         <v>43920</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17303,7 +17303,7 @@
         <v>43921</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17365,7 +17365,7 @@
         <v>43922</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17427,7 +17427,7 @@
         <v>43922</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17489,7 +17489,7 @@
         <v>43924</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17546,7 +17546,7 @@
         <v>43924</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17603,7 +17603,7 @@
         <v>43927</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17660,7 +17660,7 @@
         <v>43927</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17717,7 +17717,7 @@
         <v>43928</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17774,7 +17774,7 @@
         <v>43928</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17831,7 +17831,7 @@
         <v>43930</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17893,7 +17893,7 @@
         <v>43933</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17955,7 +17955,7 @@
         <v>43933</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18017,7 +18017,7 @@
         <v>43935</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18074,7 +18074,7 @@
         <v>43937</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18136,7 +18136,7 @@
         <v>43941</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18193,7 +18193,7 @@
         <v>43941</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18250,7 +18250,7 @@
         <v>43948</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18307,7 +18307,7 @@
         <v>43949</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18369,7 +18369,7 @@
         <v>43949</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18431,7 +18431,7 @@
         <v>43949</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18493,7 +18493,7 @@
         <v>43949</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18555,7 +18555,7 @@
         <v>43950</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18612,7 +18612,7 @@
         <v>43951</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18674,7 +18674,7 @@
         <v>43959</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18736,7 +18736,7 @@
         <v>43959</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18798,7 +18798,7 @@
         <v>43959</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18860,7 +18860,7 @@
         <v>43959</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18917,7 +18917,7 @@
         <v>43969</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18979,7 +18979,7 @@
         <v>43970</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19036,7 +19036,7 @@
         <v>43973</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19093,7 +19093,7 @@
         <v>43985</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19150,7 +19150,7 @@
         <v>43990</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19207,7 +19207,7 @@
         <v>43991</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19269,7 +19269,7 @@
         <v>43991</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19331,7 +19331,7 @@
         <v>43991</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19393,7 +19393,7 @@
         <v>43991</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19455,7 +19455,7 @@
         <v>43991</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19517,7 +19517,7 @@
         <v>44005</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19579,7 +19579,7 @@
         <v>44033</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19636,7 +19636,7 @@
         <v>44039</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19693,7 +19693,7 @@
         <v>44048</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19750,7 +19750,7 @@
         <v>44049</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19807,7 +19807,7 @@
         <v>44053</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19864,7 +19864,7 @@
         <v>44053</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19921,7 +19921,7 @@
         <v>44053</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19978,7 +19978,7 @@
         <v>44054</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20040,7 +20040,7 @@
         <v>44054</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20097,7 +20097,7 @@
         <v>44054</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20154,7 +20154,7 @@
         <v>44055</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20216,7 +20216,7 @@
         <v>44055</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20278,7 +20278,7 @@
         <v>44074</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20335,7 +20335,7 @@
         <v>44074</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20392,7 +20392,7 @@
         <v>44077</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20449,7 +20449,7 @@
         <v>44078</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20511,7 +20511,7 @@
         <v>44078</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20573,7 +20573,7 @@
         <v>44082</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20630,7 +20630,7 @@
         <v>44084</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20692,7 +20692,7 @@
         <v>44089</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20749,7 +20749,7 @@
         <v>44091</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20806,7 +20806,7 @@
         <v>44095</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20863,7 +20863,7 @@
         <v>44097</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20920,7 +20920,7 @@
         <v>44102</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20977,7 +20977,7 @@
         <v>44104</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21034,7 +21034,7 @@
         <v>44105</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21091,7 +21091,7 @@
         <v>44109</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21148,7 +21148,7 @@
         <v>44109</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21210,7 +21210,7 @@
         <v>44117</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21272,7 +21272,7 @@
         <v>44126</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21334,7 +21334,7 @@
         <v>44126</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21396,7 +21396,7 @@
         <v>44126</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21458,7 +21458,7 @@
         <v>44126</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21520,7 +21520,7 @@
         <v>44126</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21582,7 +21582,7 @@
         <v>44130</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21639,7 +21639,7 @@
         <v>44130</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21696,7 +21696,7 @@
         <v>44130</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21753,7 +21753,7 @@
         <v>44130</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21810,7 +21810,7 @@
         <v>44131</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21867,7 +21867,7 @@
         <v>44133</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21929,7 +21929,7 @@
         <v>44137</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21986,7 +21986,7 @@
         <v>44139</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22043,7 +22043,7 @@
         <v>44139</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22100,7 +22100,7 @@
         <v>44141</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22157,7 +22157,7 @@
         <v>44145</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22214,7 +22214,7 @@
         <v>44145</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22271,7 +22271,7 @@
         <v>44151</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22328,7 +22328,7 @@
         <v>44151</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22385,7 +22385,7 @@
         <v>44153</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22442,7 +22442,7 @@
         <v>44159</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22499,7 +22499,7 @@
         <v>44159</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22556,7 +22556,7 @@
         <v>44159</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22613,7 +22613,7 @@
         <v>44159</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22670,7 +22670,7 @@
         <v>44160</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22727,7 +22727,7 @@
         <v>44160</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22784,7 +22784,7 @@
         <v>44160</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22841,7 +22841,7 @@
         <v>44161</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22898,7 +22898,7 @@
         <v>44162</v>
       </c>
       <c r="C360" s="1" t="